--- a/Catch models/tabela_resumo_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_resumo_dbsra_macarellus.xlsx
@@ -567,25 +567,25 @@
         <v>18</v>
       </c>
       <c r="H2">
-        <v>6849.455107432717</v>
+        <v>6864.782663382054</v>
       </c>
       <c r="I2">
-        <v>6707.813723645583</v>
+        <v>6695.137566716333</v>
       </c>
       <c r="J2">
-        <v>4601.317200229394</v>
+        <v>4606.853645359995</v>
       </c>
       <c r="K2">
-        <v>10020.85397699078</v>
+        <v>10054.02723784558</v>
       </c>
       <c r="L2">
         <v>10000</v>
       </c>
       <c r="M2">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N2">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -611,25 +611,25 @@
         <v>19</v>
       </c>
       <c r="H3">
-        <v>0.3487955925509073</v>
+        <v>0.3500178711997007</v>
       </c>
       <c r="I3">
-        <v>0.3434158889240949</v>
+        <v>0.3455536283331682</v>
       </c>
       <c r="J3">
-        <v>0.189085337350558</v>
+        <v>0.1894694393837437</v>
       </c>
       <c r="K3">
-        <v>0.5355006897943024</v>
+        <v>0.5372988320919654</v>
       </c>
       <c r="L3">
         <v>10000</v>
       </c>
       <c r="M3">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N3">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -655,25 +655,25 @@
         <v>20</v>
       </c>
       <c r="H4">
-        <v>5005.068925155275</v>
+        <v>5004.065627304772</v>
       </c>
       <c r="I4">
-        <v>4791.256890577773</v>
+        <v>4804.10300257983</v>
       </c>
       <c r="J4">
-        <v>1613.559216909883</v>
+        <v>1584.277452277248</v>
       </c>
       <c r="K4">
-        <v>9781.477041393377</v>
+        <v>9660.363408131838</v>
       </c>
       <c r="L4">
         <v>10000</v>
       </c>
       <c r="M4">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N4">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -699,25 +699,25 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>0.2404823477761067</v>
+        <v>0.2420126436835842</v>
       </c>
       <c r="I5">
-        <v>0.254713818552083</v>
+        <v>0.2560344669816944</v>
       </c>
       <c r="J5">
-        <v>0.09418106566408223</v>
+        <v>0.0937919845082175</v>
       </c>
       <c r="K5">
-        <v>0.3272836006421105</v>
+        <v>0.3276056424938081</v>
       </c>
       <c r="L5">
         <v>10000</v>
       </c>
       <c r="M5">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N5">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -743,25 +743,25 @@
         <v>22</v>
       </c>
       <c r="H6">
-        <v>0.476578809680032</v>
+        <v>0.4759148207418335</v>
       </c>
       <c r="I6">
-        <v>0.4549429136446879</v>
+        <v>0.4526666718295683</v>
       </c>
       <c r="J6">
-        <v>0.248769773277916</v>
+        <v>0.2468402398462165</v>
       </c>
       <c r="K6">
-        <v>0.8255375303020994</v>
+        <v>0.8350668773370838</v>
       </c>
       <c r="L6">
         <v>10000</v>
       </c>
       <c r="M6">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N6">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -787,25 +787,25 @@
         <v>23</v>
       </c>
       <c r="H7">
-        <v>0.7765331908110962</v>
+        <v>0.776200173421971</v>
       </c>
       <c r="I7">
-        <v>0.7416366335160298</v>
+        <v>0.7404109689824199</v>
       </c>
       <c r="J7">
-        <v>0.4168593560885644</v>
+        <v>0.4138101245988932</v>
       </c>
       <c r="K7">
-        <v>1.323718632962586</v>
+        <v>1.324934091215543</v>
       </c>
       <c r="L7">
         <v>10000</v>
       </c>
       <c r="M7">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N7">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -831,25 +831,25 @@
         <v>24</v>
       </c>
       <c r="H8">
-        <v>20775.9855003279</v>
+        <v>20701.97744695799</v>
       </c>
       <c r="I8">
-        <v>19858.91158146162</v>
+        <v>20077.65358092204</v>
       </c>
       <c r="J8">
-        <v>11250.74791052855</v>
+        <v>11278.48234676944</v>
       </c>
       <c r="K8">
-        <v>35831.84874171333</v>
+        <v>35178.22963494794</v>
       </c>
       <c r="L8">
         <v>10000</v>
       </c>
       <c r="M8">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N8">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -875,25 +875,25 @@
         <v>25</v>
       </c>
       <c r="H9">
-        <v>0.6139120987237245</v>
+        <v>0.6133454618288503</v>
       </c>
       <c r="I9">
-        <v>0.6118502666578973</v>
+        <v>0.6120233327953369</v>
       </c>
       <c r="J9">
-        <v>0.5041069721398379</v>
+        <v>0.50257514626376</v>
       </c>
       <c r="K9">
-        <v>0.7411662133149802</v>
+        <v>0.738218703464342</v>
       </c>
       <c r="L9">
         <v>10000</v>
       </c>
       <c r="M9">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N9">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -919,25 +919,25 @@
         <v>26</v>
       </c>
       <c r="H10">
-        <v>1865.698139703661</v>
+        <v>1866.548769321672</v>
       </c>
       <c r="I10">
-        <v>1895.655959588663</v>
+        <v>1896.769409607813</v>
       </c>
       <c r="J10">
-        <v>1584.887723995197</v>
+        <v>1581.59097671675</v>
       </c>
       <c r="K10">
-        <v>2045.121300028806</v>
+        <v>2046.507984910551</v>
       </c>
       <c r="L10">
         <v>10000</v>
       </c>
       <c r="M10">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N10">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -963,25 +963,25 @@
         <v>27</v>
       </c>
       <c r="H11">
-        <v>1629.016688583409</v>
+        <v>1633.910153487818</v>
       </c>
       <c r="I11">
-        <v>1594.490971755434</v>
+        <v>1618.02109005795</v>
       </c>
       <c r="J11">
-        <v>473.9642399443254</v>
+        <v>482.5776735500042</v>
       </c>
       <c r="K11">
-        <v>3026.478932155259</v>
+        <v>3008.082986420435</v>
       </c>
       <c r="L11">
         <v>10000</v>
       </c>
       <c r="M11">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N11">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1007,25 +1007,25 @@
         <v>28</v>
       </c>
       <c r="H12">
-        <v>0.2852230466059573</v>
+        <v>0.2849240982826305</v>
       </c>
       <c r="I12">
-        <v>0.2791670881371361</v>
+        <v>0.2786026719856977</v>
       </c>
       <c r="J12">
-        <v>0.1689196835960778</v>
+        <v>0.1684133898079802</v>
       </c>
       <c r="K12">
-        <v>0.4339592469948238</v>
+        <v>0.434880278252423</v>
       </c>
       <c r="L12">
         <v>10000</v>
       </c>
       <c r="M12">
-        <v>3321</v>
+        <v>3352</v>
       </c>
       <c r="N12">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1051,25 +1051,25 @@
         <v>18</v>
       </c>
       <c r="H13">
-        <v>6813.522933105164</v>
+        <v>6810.004782168921</v>
       </c>
       <c r="I13">
-        <v>6643.293018452629</v>
+        <v>6644.418681266994</v>
       </c>
       <c r="J13">
-        <v>4521.602479686891</v>
+        <v>4548.697870615375</v>
       </c>
       <c r="K13">
-        <v>10089.19815753942</v>
+        <v>9942.594601913197</v>
       </c>
       <c r="L13">
         <v>10000</v>
       </c>
       <c r="M13">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N13">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1095,25 +1095,25 @@
         <v>19</v>
       </c>
       <c r="H14">
-        <v>0.3508911123799499</v>
+        <v>0.3498878298745081</v>
       </c>
       <c r="I14">
-        <v>0.3445852957934323</v>
+        <v>0.3442481798992565</v>
       </c>
       <c r="J14">
-        <v>0.1863424177887156</v>
+        <v>0.1826597433780296</v>
       </c>
       <c r="K14">
-        <v>0.5422190627550322</v>
+        <v>0.5434410206698048</v>
       </c>
       <c r="L14">
         <v>10000</v>
       </c>
       <c r="M14">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N14">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1139,25 +1139,25 @@
         <v>20</v>
       </c>
       <c r="H15">
-        <v>4942.935545451925</v>
+        <v>4935.215273932758</v>
       </c>
       <c r="I15">
-        <v>4764.354477634492</v>
+        <v>4723.789944102824</v>
       </c>
       <c r="J15">
-        <v>1593.778761471759</v>
+        <v>1568.467990845754</v>
       </c>
       <c r="K15">
-        <v>9627.236958337264</v>
+        <v>9773.086897225028</v>
       </c>
       <c r="L15">
         <v>10000</v>
       </c>
       <c r="M15">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N15">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1183,25 +1183,25 @@
         <v>21</v>
       </c>
       <c r="H16">
-        <v>0.2401720440174029</v>
+        <v>0.2385155102241681</v>
       </c>
       <c r="I16">
-        <v>0.2534097489875806</v>
+        <v>0.2510763892261053</v>
       </c>
       <c r="J16">
-        <v>0.09747924735669128</v>
+        <v>0.09296012347650381</v>
       </c>
       <c r="K16">
-        <v>0.32620756167678</v>
+        <v>0.3266319475936343</v>
       </c>
       <c r="L16">
         <v>10000</v>
       </c>
       <c r="M16">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N16">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1227,25 +1227,25 @@
         <v>22</v>
       </c>
       <c r="H17">
-        <v>0.48734746245621</v>
+        <v>0.4862537845484727</v>
       </c>
       <c r="I17">
-        <v>0.4625807960305497</v>
+        <v>0.4627097144307064</v>
       </c>
       <c r="J17">
-        <v>0.247710835376579</v>
+        <v>0.2522768460411423</v>
       </c>
       <c r="K17">
-        <v>0.855537668885775</v>
+        <v>0.8450653109883579</v>
       </c>
       <c r="L17">
         <v>10000</v>
       </c>
       <c r="M17">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N17">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1271,25 +1271,25 @@
         <v>23</v>
       </c>
       <c r="H18">
-        <v>0.7721482177051555</v>
+        <v>0.7695858993619877</v>
       </c>
       <c r="I18">
-        <v>0.7382313931256842</v>
+        <v>0.737886095943088</v>
       </c>
       <c r="J18">
-        <v>0.4067785420775948</v>
+        <v>0.4147305695613956</v>
       </c>
       <c r="K18">
-        <v>1.319861068327205</v>
+        <v>1.339398970624536</v>
       </c>
       <c r="L18">
         <v>10000</v>
       </c>
       <c r="M18">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N18">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1315,25 +1315,25 @@
         <v>24</v>
       </c>
       <c r="H19">
-        <v>20526.67480891698</v>
+        <v>20632.0234972507</v>
       </c>
       <c r="I19">
-        <v>19679.77511752963</v>
+        <v>19624.16171936609</v>
       </c>
       <c r="J19">
-        <v>11266.25958977432</v>
+        <v>11240.00494423015</v>
       </c>
       <c r="K19">
-        <v>34954.73626026814</v>
+        <v>35423.21875744113</v>
       </c>
       <c r="L19">
         <v>10000</v>
       </c>
       <c r="M19">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N19">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1359,25 +1359,25 @@
         <v>25</v>
       </c>
       <c r="H20">
-        <v>0.6313114837463997</v>
+        <v>0.6322156806957537</v>
       </c>
       <c r="I20">
-        <v>0.6279910743253023</v>
+        <v>0.628653918270157</v>
       </c>
       <c r="J20">
-        <v>0.5183352930090456</v>
+        <v>0.5178750689677436</v>
       </c>
       <c r="K20">
-        <v>0.7642810427020059</v>
+        <v>0.760187266599088</v>
       </c>
       <c r="L20">
         <v>10000</v>
       </c>
       <c r="M20">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N20">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1403,25 +1403,25 @@
         <v>26</v>
       </c>
       <c r="H21">
-        <v>1870.384801983228</v>
+        <v>1868.604676803568</v>
       </c>
       <c r="I21">
-        <v>1897.920918315109</v>
+        <v>1895.789243182264</v>
       </c>
       <c r="J21">
-        <v>1589.474762156763</v>
+        <v>1591.736666665113</v>
       </c>
       <c r="K21">
-        <v>2048.342537721155</v>
+        <v>2048.019297247105</v>
       </c>
       <c r="L21">
         <v>10000</v>
       </c>
       <c r="M21">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N21">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1447,25 +1447,25 @@
         <v>27</v>
       </c>
       <c r="H22">
-        <v>1625.727689197452</v>
+        <v>1625.303869778853</v>
       </c>
       <c r="I22">
-        <v>1598.820719114139</v>
+        <v>1598.595326187425</v>
       </c>
       <c r="J22">
-        <v>494.8882876113787</v>
+        <v>450.8581167767194</v>
       </c>
       <c r="K22">
-        <v>3021.092984294164</v>
+        <v>3032.428832724088</v>
       </c>
       <c r="L22">
         <v>10000</v>
       </c>
       <c r="M22">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N22">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1491,25 +1491,25 @@
         <v>28</v>
       </c>
       <c r="H23">
-        <v>0.2880648642598442</v>
+        <v>0.2875611020494008</v>
       </c>
       <c r="I23">
-        <v>0.2825604373636862</v>
+        <v>0.2817648784865671</v>
       </c>
       <c r="J23">
-        <v>0.1666595716585018</v>
+        <v>0.1707117754834451</v>
       </c>
       <c r="K23">
-        <v>0.440723920150473</v>
+        <v>0.4392095764726186</v>
       </c>
       <c r="L23">
         <v>10000</v>
       </c>
       <c r="M23">
-        <v>3330</v>
+        <v>3249</v>
       </c>
       <c r="N23">
-        <v>33.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1535,25 +1535,25 @@
         <v>18</v>
       </c>
       <c r="H24">
-        <v>5863.579579346751</v>
+        <v>5893.443591752249</v>
       </c>
       <c r="I24">
-        <v>5706.534597628202</v>
+        <v>5755.381554336515</v>
       </c>
       <c r="J24">
-        <v>4067.493841724739</v>
+        <v>4048.94361802125</v>
       </c>
       <c r="K24">
-        <v>8514.909204922058</v>
+        <v>8390.122811848511</v>
       </c>
       <c r="L24">
         <v>10000</v>
       </c>
       <c r="M24">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N24">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1579,25 +1579,25 @@
         <v>19</v>
       </c>
       <c r="H25">
-        <v>0.3423362997147911</v>
+        <v>0.3396360904608955</v>
       </c>
       <c r="I25">
-        <v>0.3364287450530211</v>
+        <v>0.3342460186669713</v>
       </c>
       <c r="J25">
-        <v>0.1887150063057542</v>
+        <v>0.1841406512216404</v>
       </c>
       <c r="K25">
-        <v>0.5296391060927046</v>
+        <v>0.5278358389432465</v>
       </c>
       <c r="L25">
         <v>10000</v>
       </c>
       <c r="M25">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N25">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1623,25 +1623,25 @@
         <v>20</v>
       </c>
       <c r="H26">
-        <v>4411.0664315771</v>
+        <v>4503.103609244233</v>
       </c>
       <c r="I26">
-        <v>4284.458477131218</v>
+        <v>4389.611713530116</v>
       </c>
       <c r="J26">
-        <v>1542.782134176391</v>
+        <v>1514.118035357716</v>
       </c>
       <c r="K26">
-        <v>8376.93548177965</v>
+        <v>8821.588159531304</v>
       </c>
       <c r="L26">
         <v>10000</v>
       </c>
       <c r="M26">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N26">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1667,25 +1667,25 @@
         <v>21</v>
       </c>
       <c r="H27">
-        <v>0.2433490984229118</v>
+        <v>0.2443333839574841</v>
       </c>
       <c r="I27">
-        <v>0.2572140581860496</v>
+        <v>0.2609450233952527</v>
       </c>
       <c r="J27">
-        <v>0.1003612921012446</v>
+        <v>0.1015341118276341</v>
       </c>
       <c r="K27">
-        <v>0.3267874555873663</v>
+        <v>0.3271664907747484</v>
       </c>
       <c r="L27">
         <v>10000</v>
       </c>
       <c r="M27">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N27">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1711,25 +1711,25 @@
         <v>22</v>
       </c>
       <c r="H28">
-        <v>0.7107112483607291</v>
+        <v>0.7008379134215857</v>
       </c>
       <c r="I28">
-        <v>0.6798558347030788</v>
+        <v>0.6712549827283477</v>
       </c>
       <c r="J28">
-        <v>0.3663376163851911</v>
+        <v>0.369023329329594</v>
       </c>
       <c r="K28">
-        <v>1.225294853445815</v>
+        <v>1.216665995544531</v>
       </c>
       <c r="L28">
         <v>10000</v>
       </c>
       <c r="M28">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N28">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1755,25 +1755,25 @@
         <v>23</v>
       </c>
       <c r="H29">
-        <v>0.7718800453559592</v>
+        <v>0.7632632572216379</v>
       </c>
       <c r="I29">
-        <v>0.7427875791450461</v>
+        <v>0.7333509663462897</v>
       </c>
       <c r="J29">
-        <v>0.4127194285482865</v>
+        <v>0.4109876522697704</v>
       </c>
       <c r="K29">
-        <v>1.298335562438562</v>
+        <v>1.301580717875003</v>
       </c>
       <c r="L29">
         <v>10000</v>
       </c>
       <c r="M29">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N29">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1799,25 +1799,25 @@
         <v>24</v>
       </c>
       <c r="H30">
-        <v>18104.95952624024</v>
+        <v>18408.48450556907</v>
       </c>
       <c r="I30">
-        <v>16655.79314898231</v>
+        <v>16716.84702912801</v>
       </c>
       <c r="J30">
-        <v>11083.28268665326</v>
+        <v>11034.2705663367</v>
       </c>
       <c r="K30">
-        <v>31185.5305684749</v>
+        <v>31303.94091843505</v>
       </c>
       <c r="L30">
         <v>10000</v>
       </c>
       <c r="M30">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N30">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1843,25 +1843,25 @@
         <v>25</v>
       </c>
       <c r="H31">
-        <v>0.9208665139638168</v>
+        <v>0.918742471602786</v>
       </c>
       <c r="I31">
-        <v>0.9206488511629398</v>
+        <v>0.9160666375802393</v>
       </c>
       <c r="J31">
-        <v>0.7506071653135309</v>
+        <v>0.7558949637840644</v>
       </c>
       <c r="K31">
-        <v>1.097572871836381</v>
+        <v>1.102514873452978</v>
       </c>
       <c r="L31">
         <v>10000</v>
       </c>
       <c r="M31">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N31">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1887,25 +1887,25 @@
         <v>26</v>
       </c>
       <c r="H32">
-        <v>1931.606582742181</v>
+        <v>1927.711138870569</v>
       </c>
       <c r="I32">
-        <v>1946.200405594027</v>
+        <v>1942.305860762551</v>
       </c>
       <c r="J32">
-        <v>1675.858914428738</v>
+        <v>1664.402623716546</v>
       </c>
       <c r="K32">
-        <v>2060.561562760204</v>
+        <v>2062.562932055133</v>
       </c>
       <c r="L32">
         <v>10000</v>
       </c>
       <c r="M32">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N32">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -1931,25 +1931,25 @@
         <v>27</v>
       </c>
       <c r="H33">
-        <v>1789.567256320234</v>
+        <v>1804.920074249158</v>
       </c>
       <c r="I33">
-        <v>1781.036992359931</v>
+        <v>1776.326681679121</v>
       </c>
       <c r="J33">
-        <v>534.319791421971</v>
+        <v>546.1093245174292</v>
       </c>
       <c r="K33">
-        <v>3266.867486609402</v>
+        <v>3307.313934893351</v>
       </c>
       <c r="L33">
         <v>10000</v>
       </c>
       <c r="M33">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N33">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -1975,25 +1975,25 @@
         <v>28</v>
       </c>
       <c r="H34">
-        <v>0.3431458833758398</v>
+        <v>0.3401472568754397</v>
       </c>
       <c r="I34">
-        <v>0.3383824178415798</v>
+        <v>0.3368890479134046</v>
       </c>
       <c r="J34">
-        <v>0.2110138840665829</v>
+        <v>0.2117563311614438</v>
       </c>
       <c r="K34">
-        <v>0.496816193924267</v>
+        <v>0.4995335908860587</v>
       </c>
       <c r="L34">
         <v>10000</v>
       </c>
       <c r="M34">
-        <v>2595</v>
+        <v>2763</v>
       </c>
       <c r="N34">
-        <v>26</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2019,25 +2019,25 @@
         <v>18</v>
       </c>
       <c r="H35">
-        <v>7596.191031681353</v>
+        <v>7610.37730785589</v>
       </c>
       <c r="I35">
-        <v>7276.338305937199</v>
+        <v>7291.874021410215</v>
       </c>
       <c r="J35">
-        <v>4724.93517019658</v>
+        <v>4810.942927549529</v>
       </c>
       <c r="K35">
-        <v>12339.47133821973</v>
+        <v>12367.12500384991</v>
       </c>
       <c r="L35">
         <v>10000</v>
       </c>
       <c r="M35">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N35">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2063,25 +2063,25 @@
         <v>19</v>
       </c>
       <c r="H36">
-        <v>0.3834142070725052</v>
+        <v>0.3816238793288186</v>
       </c>
       <c r="I36">
-        <v>0.3835165213272124</v>
+        <v>0.3800931576964695</v>
       </c>
       <c r="J36">
-        <v>0.2122719298751061</v>
+        <v>0.2095698631893219</v>
       </c>
       <c r="K36">
-        <v>0.5622752114196791</v>
+        <v>0.5645934765456592</v>
       </c>
       <c r="L36">
         <v>10000</v>
       </c>
       <c r="M36">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N36">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2107,25 +2107,25 @@
         <v>20</v>
       </c>
       <c r="H37">
-        <v>9782.146366091687</v>
+        <v>9892.582807878995</v>
       </c>
       <c r="I37">
-        <v>8348.158518878146</v>
+        <v>8449.866283028194</v>
       </c>
       <c r="J37">
-        <v>2662.102413586736</v>
+        <v>2551.278747610037</v>
       </c>
       <c r="K37">
-        <v>25754.19129155958</v>
+        <v>25564.45104349557</v>
       </c>
       <c r="L37">
         <v>10000</v>
       </c>
       <c r="M37">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N37">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2151,25 +2151,25 @@
         <v>21</v>
       </c>
       <c r="H38">
-        <v>0.4553242512148477</v>
+        <v>0.4571403694972818</v>
       </c>
       <c r="I38">
-        <v>0.4652662391158234</v>
+        <v>0.4684281231446773</v>
       </c>
       <c r="J38">
-        <v>0.1523294787193955</v>
+        <v>0.1417678231670771</v>
       </c>
       <c r="K38">
-        <v>0.6790259588969405</v>
+        <v>0.6779177612920511</v>
       </c>
       <c r="L38">
         <v>10000</v>
       </c>
       <c r="M38">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N38">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2195,25 +2195,25 @@
         <v>22</v>
       </c>
       <c r="H39">
-        <v>0.4986841984885825</v>
+        <v>0.4977392341847165</v>
       </c>
       <c r="I39">
-        <v>0.4745729783795616</v>
+        <v>0.4762896216718509</v>
       </c>
       <c r="J39">
-        <v>0.2604504242638813</v>
+        <v>0.2589714707227211</v>
       </c>
       <c r="K39">
-        <v>0.8621119412442236</v>
+        <v>0.8536048747852437</v>
       </c>
       <c r="L39">
         <v>10000</v>
       </c>
       <c r="M39">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N39">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2239,25 +2239,25 @@
         <v>23</v>
       </c>
       <c r="H40">
-        <v>0.8097731143249192</v>
+        <v>0.8088842013808689</v>
       </c>
       <c r="I40">
-        <v>0.7761844096901236</v>
+        <v>0.7782626883450782</v>
       </c>
       <c r="J40">
-        <v>0.4397105261298208</v>
+        <v>0.4412308502920272</v>
       </c>
       <c r="K40">
-        <v>1.376315609604323</v>
+        <v>1.356194402609433</v>
       </c>
       <c r="L40">
         <v>10000</v>
       </c>
       <c r="M40">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N40">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2283,25 +2283,25 @@
         <v>24</v>
       </c>
       <c r="H41">
-        <v>21130.70526436588</v>
+        <v>21311.41424419187</v>
       </c>
       <c r="I41">
-        <v>19058.1301670946</v>
+        <v>19360.56796002976</v>
       </c>
       <c r="J41">
-        <v>11146.71166000013</v>
+        <v>11207.81992764562</v>
       </c>
       <c r="K41">
-        <v>43568.09904834286</v>
+        <v>43664.14939934251</v>
       </c>
       <c r="L41">
         <v>10000</v>
       </c>
       <c r="M41">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N41">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2327,25 +2327,25 @@
         <v>25</v>
       </c>
       <c r="H42">
-        <v>0.6158088544606674</v>
+        <v>0.6159442011324295</v>
       </c>
       <c r="I42">
-        <v>0.6123395165303505</v>
+        <v>0.6125153078059598</v>
       </c>
       <c r="J42">
-        <v>0.5039664380202382</v>
+        <v>0.5063136501188865</v>
       </c>
       <c r="K42">
-        <v>0.7417027742936303</v>
+        <v>0.7427853005592198</v>
       </c>
       <c r="L42">
         <v>10000</v>
       </c>
       <c r="M42">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N42">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2371,25 +2371,25 @@
         <v>26</v>
       </c>
       <c r="H43">
-        <v>2133.691289650567</v>
+        <v>2138.898681807297</v>
       </c>
       <c r="I43">
-        <v>2077.837708754065</v>
+        <v>2081.936303982277</v>
       </c>
       <c r="J43">
-        <v>1709.195918783286</v>
+        <v>1694.109791338248</v>
       </c>
       <c r="K43">
-        <v>2913.989529299489</v>
+        <v>2903.196461211689</v>
       </c>
       <c r="L43">
         <v>10000</v>
       </c>
       <c r="M43">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N43">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2415,25 +2415,25 @@
         <v>27</v>
       </c>
       <c r="H44">
-        <v>3157.948069656955</v>
+        <v>3200.841137560309</v>
       </c>
       <c r="I44">
-        <v>2852.325296398908</v>
+        <v>2903.297318862472</v>
       </c>
       <c r="J44">
-        <v>896.8738407218872</v>
+        <v>804.005251216362</v>
       </c>
       <c r="K44">
-        <v>7346.299700012324</v>
+        <v>7462.878096535278</v>
       </c>
       <c r="L44">
         <v>10000</v>
       </c>
       <c r="M44">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N44">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -2459,25 +2459,25 @@
         <v>28</v>
       </c>
       <c r="H45">
-        <v>0.2953866426082584</v>
+        <v>0.2951475547960126</v>
       </c>
       <c r="I45">
-        <v>0.2894183313324635</v>
+        <v>0.2900649390371017</v>
       </c>
       <c r="J45">
-        <v>0.1760906868801255</v>
+        <v>0.1757115992870882</v>
       </c>
       <c r="K45">
-        <v>0.4454813545579986</v>
+        <v>0.4433139150968769</v>
       </c>
       <c r="L45">
         <v>10000</v>
       </c>
       <c r="M45">
-        <v>6524</v>
+        <v>6466</v>
       </c>
       <c r="N45">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -2503,25 +2503,25 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>7488.076983196129</v>
+        <v>7471.973144650821</v>
       </c>
       <c r="I46">
-        <v>7134.612950476636</v>
+        <v>7104.502807630501</v>
       </c>
       <c r="J46">
-        <v>4734.415107704662</v>
+        <v>4735.209224120008</v>
       </c>
       <c r="K46">
-        <v>12207.61671216099</v>
+        <v>12159.7913609249</v>
       </c>
       <c r="L46">
         <v>10000</v>
       </c>
       <c r="M46">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N46">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2547,25 +2547,25 @@
         <v>19</v>
       </c>
       <c r="H47">
-        <v>0.3815255333187115</v>
+        <v>0.3808846895423443</v>
       </c>
       <c r="I47">
-        <v>0.3799523139131331</v>
+        <v>0.3784359257932898</v>
       </c>
       <c r="J47">
-        <v>0.2070204991873224</v>
+        <v>0.2109291149666363</v>
       </c>
       <c r="K47">
-        <v>0.5656898294776737</v>
+        <v>0.560114750166009</v>
       </c>
       <c r="L47">
         <v>10000</v>
       </c>
       <c r="M47">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N47">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2591,25 +2591,25 @@
         <v>20</v>
       </c>
       <c r="H48">
-        <v>9731.234900813197</v>
+        <v>9710.974409125591</v>
       </c>
       <c r="I48">
-        <v>8275.722378282266</v>
+        <v>8282.776117114936</v>
       </c>
       <c r="J48">
-        <v>2573.676642769234</v>
+        <v>2509.100002356193</v>
       </c>
       <c r="K48">
-        <v>25293.63089387016</v>
+        <v>25125.75031127258</v>
       </c>
       <c r="L48">
         <v>10000</v>
       </c>
       <c r="M48">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N48">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2635,25 +2635,25 @@
         <v>21</v>
       </c>
       <c r="H49">
-        <v>0.4562684332367891</v>
+        <v>0.456535700319403</v>
       </c>
       <c r="I49">
-        <v>0.4670319261454605</v>
+        <v>0.4681192171407856</v>
       </c>
       <c r="J49">
-        <v>0.1435329199430643</v>
+        <v>0.1433466142211333</v>
       </c>
       <c r="K49">
-        <v>0.6787289880718174</v>
+        <v>0.6790782539696146</v>
       </c>
       <c r="L49">
         <v>10000</v>
       </c>
       <c r="M49">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N49">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2679,25 +2679,25 @@
         <v>22</v>
       </c>
       <c r="H50">
-        <v>0.513521023695687</v>
+        <v>0.5163828256285241</v>
       </c>
       <c r="I50">
-        <v>0.4920134741848393</v>
+        <v>0.4958710163764282</v>
       </c>
       <c r="J50">
-        <v>0.2659280680945171</v>
+        <v>0.2666530562247153</v>
       </c>
       <c r="K50">
-        <v>0.8925968480867444</v>
+        <v>0.8997273211091852</v>
       </c>
       <c r="L50">
         <v>10000</v>
       </c>
       <c r="M50">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N50">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2723,25 +2723,25 @@
         <v>23</v>
       </c>
       <c r="H51">
-        <v>0.810696437305628</v>
+        <v>0.81417801241344</v>
       </c>
       <c r="I51">
-        <v>0.7766339684770714</v>
+        <v>0.7859388364019604</v>
       </c>
       <c r="J51">
-        <v>0.4342790231382306</v>
+        <v>0.4327437485655343</v>
       </c>
       <c r="K51">
-        <v>1.369749378381815</v>
+        <v>1.376750765621922</v>
       </c>
       <c r="L51">
         <v>10000</v>
       </c>
       <c r="M51">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N51">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -2767,25 +2767,25 @@
         <v>24</v>
       </c>
       <c r="H52">
-        <v>21011.12380037926</v>
+        <v>20960.22856124816</v>
       </c>
       <c r="I52">
-        <v>18795.61844368477</v>
+        <v>18961.09958559078</v>
       </c>
       <c r="J52">
-        <v>11081.19140059409</v>
+        <v>11084.31099893811</v>
       </c>
       <c r="K52">
-        <v>43720.23656513219</v>
+        <v>42998.24188958864</v>
       </c>
       <c r="L52">
         <v>10000</v>
       </c>
       <c r="M52">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N52">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -2811,25 +2811,25 @@
         <v>25</v>
       </c>
       <c r="H53">
-        <v>0.6337587839000074</v>
+        <v>0.6343690860205273</v>
       </c>
       <c r="I53">
-        <v>0.6317153404645474</v>
+        <v>0.6325789302975318</v>
       </c>
       <c r="J53">
-        <v>0.519543724087219</v>
+        <v>0.5195885042736827</v>
       </c>
       <c r="K53">
-        <v>0.7624441002434467</v>
+        <v>0.7636971447794727</v>
       </c>
       <c r="L53">
         <v>10000</v>
       </c>
       <c r="M53">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N53">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -2855,25 +2855,25 @@
         <v>26</v>
       </c>
       <c r="H54">
-        <v>2139.341609295772</v>
+        <v>2140.938614979218</v>
       </c>
       <c r="I54">
-        <v>2082.971811300938</v>
+        <v>2083.956888765144</v>
       </c>
       <c r="J54">
-        <v>1711.165417780517</v>
+        <v>1714.14079801104</v>
       </c>
       <c r="K54">
-        <v>2905.592249837144</v>
+        <v>2910.003287357169</v>
       </c>
       <c r="L54">
         <v>10000</v>
       </c>
       <c r="M54">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N54">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -2899,25 +2899,25 @@
         <v>27</v>
       </c>
       <c r="H55">
-        <v>3200.56110617829</v>
+        <v>3213.03526523518</v>
       </c>
       <c r="I55">
-        <v>2904.727612718654</v>
+        <v>2928.363248394772</v>
       </c>
       <c r="J55">
-        <v>864.5252885401823</v>
+        <v>796.3882447260494</v>
       </c>
       <c r="K55">
-        <v>7361.13089186179</v>
+        <v>7331.542297573339</v>
       </c>
       <c r="L55">
         <v>10000</v>
       </c>
       <c r="M55">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N55">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -2943,25 +2943,25 @@
         <v>28</v>
       </c>
       <c r="H56">
-        <v>0.300160639694199</v>
+        <v>0.3012728332166774</v>
       </c>
       <c r="I56">
-        <v>0.2947149275553222</v>
+        <v>0.2973914157443509</v>
       </c>
       <c r="J56">
-        <v>0.1779379327521391</v>
+        <v>0.1774047444448943</v>
       </c>
       <c r="K56">
-        <v>0.4496862331932985</v>
+        <v>0.4559728546431386</v>
       </c>
       <c r="L56">
         <v>10000</v>
       </c>
       <c r="M56">
-        <v>6561</v>
+        <v>6568</v>
       </c>
       <c r="N56">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -2987,25 +2987,25 @@
         <v>18</v>
       </c>
       <c r="H57">
-        <v>6462.723259853155</v>
+        <v>6436.349498406952</v>
       </c>
       <c r="I57">
-        <v>6191.222876973651</v>
+        <v>6173.073380671945</v>
       </c>
       <c r="J57">
-        <v>4199.264236030725</v>
+        <v>4276.489739668139</v>
       </c>
       <c r="K57">
-        <v>10342.8670017593</v>
+        <v>10272.19746473855</v>
       </c>
       <c r="L57">
         <v>10000</v>
       </c>
       <c r="M57">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N57">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3031,25 +3031,25 @@
         <v>19</v>
       </c>
       <c r="H58">
-        <v>0.373751142854408</v>
+        <v>0.3728488568098515</v>
       </c>
       <c r="I58">
-        <v>0.3718283551065873</v>
+        <v>0.372182908683152</v>
       </c>
       <c r="J58">
-        <v>0.2050030503700054</v>
+        <v>0.2070167414358267</v>
       </c>
       <c r="K58">
-        <v>0.5467715002904362</v>
+        <v>0.5446303872520492</v>
       </c>
       <c r="L58">
         <v>10000</v>
       </c>
       <c r="M58">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N58">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3075,25 +3075,25 @@
         <v>20</v>
       </c>
       <c r="H59">
-        <v>8731.16114454359</v>
+        <v>8679.656497215003</v>
       </c>
       <c r="I59">
-        <v>7508.17167232753</v>
+        <v>7401.277257666648</v>
       </c>
       <c r="J59">
-        <v>2513.367739479682</v>
+        <v>2614.104686008802</v>
       </c>
       <c r="K59">
-        <v>22330.97208355612</v>
+        <v>22000.61929458107</v>
       </c>
       <c r="L59">
         <v>10000</v>
       </c>
       <c r="M59">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N59">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3119,25 +3119,25 @@
         <v>21</v>
       </c>
       <c r="H60">
-        <v>0.4673438025704766</v>
+        <v>0.465143645444754</v>
       </c>
       <c r="I60">
-        <v>0.4854262515177625</v>
+        <v>0.4753267529951326</v>
       </c>
       <c r="J60">
-        <v>0.1596051527741066</v>
+        <v>0.1632419182440077</v>
       </c>
       <c r="K60">
-        <v>0.6780252365929189</v>
+        <v>0.6793660820639099</v>
       </c>
       <c r="L60">
         <v>10000</v>
       </c>
       <c r="M60">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N60">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3163,25 +3163,25 @@
         <v>22</v>
       </c>
       <c r="H61">
-        <v>0.736075424588532</v>
+        <v>0.735607516451122</v>
       </c>
       <c r="I61">
-        <v>0.706363507472324</v>
+        <v>0.7059530250716693</v>
       </c>
       <c r="J61">
-        <v>0.3792084321766492</v>
+        <v>0.3850505380632616</v>
       </c>
       <c r="K61">
-        <v>1.284034338392607</v>
+        <v>1.241679124117743</v>
       </c>
       <c r="L61">
         <v>10000</v>
       </c>
       <c r="M61">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N61">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3207,25 +3207,25 @@
         <v>23</v>
       </c>
       <c r="H62">
-        <v>0.8012040715191907</v>
+        <v>0.7979817741310794</v>
       </c>
       <c r="I62">
-        <v>0.7689549267000372</v>
+        <v>0.7701385229818893</v>
       </c>
       <c r="J62">
-        <v>0.4334650150021025</v>
+        <v>0.4349983433668077</v>
       </c>
       <c r="K62">
-        <v>1.363603486610696</v>
+        <v>1.328408921900517</v>
       </c>
       <c r="L62">
         <v>10000</v>
       </c>
       <c r="M62">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N62">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3251,25 +3251,25 @@
         <v>24</v>
       </c>
       <c r="H63">
-        <v>18412.52125497711</v>
+        <v>18431.21101927727</v>
       </c>
       <c r="I63">
-        <v>16592.08278582328</v>
+        <v>16547.39477357359</v>
       </c>
       <c r="J63">
-        <v>10465.07489886335</v>
+        <v>10585.78423621155</v>
       </c>
       <c r="K63">
-        <v>37541.78832860195</v>
+        <v>38622.49753784318</v>
       </c>
       <c r="L63">
         <v>10000</v>
       </c>
       <c r="M63">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N63">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3295,25 +3295,25 @@
         <v>25</v>
       </c>
       <c r="H64">
-        <v>0.9190708628068092</v>
+        <v>0.9221424945899301</v>
       </c>
       <c r="I64">
-        <v>0.9150791116761297</v>
+        <v>0.9183894661221652</v>
       </c>
       <c r="J64">
-        <v>0.7544121721077754</v>
+        <v>0.7531280865001242</v>
       </c>
       <c r="K64">
-        <v>1.108032907593595</v>
+        <v>1.10630102990419</v>
       </c>
       <c r="L64">
         <v>10000</v>
       </c>
       <c r="M64">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N64">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3339,25 +3339,25 @@
         <v>26</v>
       </c>
       <c r="H65">
-        <v>2179.942642499535</v>
+        <v>2176.489689006682</v>
       </c>
       <c r="I65">
-        <v>2114.19131252125</v>
+        <v>2108.079725610248</v>
       </c>
       <c r="J65">
-        <v>1838.952883979732</v>
+        <v>1833.898119798687</v>
       </c>
       <c r="K65">
-        <v>2913.131816340114</v>
+        <v>2941.97580699658</v>
       </c>
       <c r="L65">
         <v>10000</v>
       </c>
       <c r="M65">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N65">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3383,25 +3383,25 @@
         <v>27</v>
       </c>
       <c r="H66">
-        <v>3456.025108130856</v>
+        <v>3443.177608054431</v>
       </c>
       <c r="I66">
-        <v>3152.832350810549</v>
+        <v>3136.850435255684</v>
       </c>
       <c r="J66">
-        <v>988.76230299093</v>
+        <v>987.9102729839083</v>
       </c>
       <c r="K66">
-        <v>7729.500046188366</v>
+        <v>7914.105861736847</v>
       </c>
       <c r="L66">
         <v>10000</v>
       </c>
       <c r="M66">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N66">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3427,25 +3427,25 @@
         <v>28</v>
       </c>
       <c r="H67">
-        <v>0.3522293261616317</v>
+        <v>0.3521103141597761</v>
       </c>
       <c r="I67">
-        <v>0.3484466508360335</v>
+        <v>0.3485109688369391</v>
       </c>
       <c r="J67">
-        <v>0.2167074815486378</v>
+        <v>0.2196256864228085</v>
       </c>
       <c r="K67">
-        <v>0.5115930269070197</v>
+        <v>0.5013723404474962</v>
       </c>
       <c r="L67">
         <v>10000</v>
       </c>
       <c r="M67">
-        <v>5895</v>
+        <v>6007</v>
       </c>
       <c r="N67">
-        <v>59</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3471,25 +3471,25 @@
         <v>18</v>
       </c>
       <c r="H68">
-        <v>7705.6981549568</v>
+        <v>7715.169701993248</v>
       </c>
       <c r="I68">
-        <v>7346.020723605208</v>
+        <v>7359.874739157044</v>
       </c>
       <c r="J68">
-        <v>4808.225941612609</v>
+        <v>4841.297590600785</v>
       </c>
       <c r="K68">
-        <v>12581.16696132358</v>
+        <v>12736.66890207055</v>
       </c>
       <c r="L68">
         <v>10000</v>
       </c>
       <c r="M68">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N68">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3515,25 +3515,25 @@
         <v>19</v>
       </c>
       <c r="H69">
-        <v>0.3827939007952134</v>
+        <v>0.3826032503288652</v>
       </c>
       <c r="I69">
-        <v>0.3802160810168383</v>
+        <v>0.3790287977255128</v>
       </c>
       <c r="J69">
-        <v>0.2146094623322472</v>
+        <v>0.2153424158123907</v>
       </c>
       <c r="K69">
-        <v>0.5647582023755691</v>
+        <v>0.560738613569841</v>
       </c>
       <c r="L69">
         <v>10000</v>
       </c>
       <c r="M69">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N69">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3559,25 +3559,25 @@
         <v>20</v>
       </c>
       <c r="H70">
-        <v>10490.73216224267</v>
+        <v>10520.19551236402</v>
       </c>
       <c r="I70">
-        <v>8828.989310761595</v>
+        <v>8857.29234003001</v>
       </c>
       <c r="J70">
-        <v>3835.206157579329</v>
+        <v>3855.639047191008</v>
       </c>
       <c r="K70">
-        <v>26725.77464099658</v>
+        <v>26977.24719569887</v>
       </c>
       <c r="L70">
         <v>10000</v>
       </c>
       <c r="M70">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N70">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -3603,25 +3603,25 @@
         <v>21</v>
       </c>
       <c r="H71">
-        <v>0.4794423040430743</v>
+        <v>0.4788330187957447</v>
       </c>
       <c r="I71">
-        <v>0.4830962462197103</v>
+        <v>0.4843871825962639</v>
       </c>
       <c r="J71">
-        <v>0.2298321060877243</v>
+        <v>0.2267707370118735</v>
       </c>
       <c r="K71">
-        <v>0.6895609348206023</v>
+        <v>0.6895221177652946</v>
       </c>
       <c r="L71">
         <v>10000</v>
       </c>
       <c r="M71">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N71">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3647,25 +3647,25 @@
         <v>22</v>
       </c>
       <c r="H72">
-        <v>0.5012157700675669</v>
+        <v>0.5006681779967327</v>
       </c>
       <c r="I72">
-        <v>0.4799700525037823</v>
+        <v>0.4787187156035503</v>
       </c>
       <c r="J72">
-        <v>0.2620230672548911</v>
+        <v>0.2585219112393521</v>
       </c>
       <c r="K72">
-        <v>0.870415665867316</v>
+        <v>0.8575635511035055</v>
       </c>
       <c r="L72">
         <v>10000</v>
       </c>
       <c r="M72">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N72">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3691,25 +3691,25 @@
         <v>23</v>
       </c>
       <c r="H73">
-        <v>0.8136218362608129</v>
+        <v>0.8131628836587167</v>
       </c>
       <c r="I73">
-        <v>0.7835572602543763</v>
+        <v>0.7811139845471053</v>
       </c>
       <c r="J73">
-        <v>0.4374974359924246</v>
+        <v>0.4363175836155863</v>
       </c>
       <c r="K73">
-        <v>1.371855418489539</v>
+        <v>1.370247851240356</v>
       </c>
       <c r="L73">
         <v>10000</v>
       </c>
       <c r="M73">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N73">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -3735,25 +3735,25 @@
         <v>24</v>
       </c>
       <c r="H74">
-        <v>21519.13252031985</v>
+        <v>21570.84923969641</v>
       </c>
       <c r="I74">
-        <v>19405.32369496001</v>
+        <v>19458.27548677994</v>
       </c>
       <c r="J74">
-        <v>11085.01027241925</v>
+        <v>11162.7507940917</v>
       </c>
       <c r="K74">
-        <v>45019.27183820578</v>
+        <v>45038.47267458051</v>
       </c>
       <c r="L74">
         <v>10000</v>
       </c>
       <c r="M74">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N74">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -3779,25 +3779,25 @@
         <v>25</v>
       </c>
       <c r="H75">
-        <v>0.6160408117528471</v>
+        <v>0.6158840750847684</v>
       </c>
       <c r="I75">
-        <v>0.6128061077202349</v>
+        <v>0.6133484564198348</v>
       </c>
       <c r="J75">
-        <v>0.5052083129160437</v>
+        <v>0.5049725650368861</v>
       </c>
       <c r="K75">
-        <v>0.7429996505119395</v>
+        <v>0.7420970629077792</v>
       </c>
       <c r="L75">
         <v>10000</v>
       </c>
       <c r="M75">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N75">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -3823,25 +3823,25 @@
         <v>26</v>
       </c>
       <c r="H76">
-        <v>2171.470882065062</v>
+        <v>2171.591458168994</v>
       </c>
       <c r="I76">
-        <v>2093.38520539401</v>
+        <v>2094.847121605158</v>
       </c>
       <c r="J76">
-        <v>1786.668352377452</v>
+        <v>1784.020288349707</v>
       </c>
       <c r="K76">
-        <v>3006.847419165902</v>
+        <v>2970.442093443431</v>
       </c>
       <c r="L76">
         <v>10000</v>
       </c>
       <c r="M76">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N76">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -3867,25 +3867,25 @@
         <v>27</v>
       </c>
       <c r="H77">
-        <v>3388.951768214753</v>
+        <v>3381.360003304857</v>
       </c>
       <c r="I77">
-        <v>3016.742350660609</v>
+        <v>3013.449006596783</v>
       </c>
       <c r="J77">
-        <v>1365.822681817208</v>
+        <v>1348.267657840906</v>
       </c>
       <c r="K77">
-        <v>7868.426892045998</v>
+        <v>7567.374986538958</v>
       </c>
       <c r="L77">
         <v>10000</v>
       </c>
       <c r="M77">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N77">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -3911,25 +3911,25 @@
         <v>28</v>
       </c>
       <c r="H78">
-        <v>0.2965238924224037</v>
+        <v>0.2963828785680622</v>
       </c>
       <c r="I78">
-        <v>0.2910281650667687</v>
+        <v>0.2912535340850158</v>
       </c>
       <c r="J78">
-        <v>0.1768137350546991</v>
+        <v>0.1750445726580104</v>
       </c>
       <c r="K78">
-        <v>0.4460031357904131</v>
+        <v>0.4447822122824589</v>
       </c>
       <c r="L78">
         <v>10000</v>
       </c>
       <c r="M78">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="N78">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -3955,25 +3955,25 @@
         <v>18</v>
       </c>
       <c r="H79">
-        <v>7556.666663103842</v>
+        <v>7617.610087840506</v>
       </c>
       <c r="I79">
-        <v>7217.141753756294</v>
+        <v>7271.33379097295</v>
       </c>
       <c r="J79">
-        <v>4743.826079211494</v>
+        <v>4731.125541221625</v>
       </c>
       <c r="K79">
-        <v>12292.0225352278</v>
+        <v>12565.94652215587</v>
       </c>
       <c r="L79">
         <v>10000</v>
       </c>
       <c r="M79">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N79">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -3999,25 +3999,25 @@
         <v>19</v>
       </c>
       <c r="H80">
-        <v>0.3840577095575246</v>
+        <v>0.3824581377063543</v>
       </c>
       <c r="I80">
-        <v>0.3808474040799766</v>
+        <v>0.3797055001223172</v>
       </c>
       <c r="J80">
-        <v>0.210832524217247</v>
+        <v>0.2121402933003401</v>
       </c>
       <c r="K80">
-        <v>0.567016236989858</v>
+        <v>0.5637062864446283</v>
       </c>
       <c r="L80">
         <v>10000</v>
       </c>
       <c r="M80">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N80">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4043,25 +4043,25 @@
         <v>20</v>
       </c>
       <c r="H81">
-        <v>10269.0097374975</v>
+        <v>10397.88153553542</v>
       </c>
       <c r="I81">
-        <v>8715.773566651578</v>
+        <v>8717.78116326226</v>
       </c>
       <c r="J81">
-        <v>3770.827082484838</v>
+        <v>3796.847807991375</v>
       </c>
       <c r="K81">
-        <v>25922.12893753109</v>
+        <v>26103.57190613434</v>
       </c>
       <c r="L81">
         <v>10000</v>
       </c>
       <c r="M81">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N81">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4087,25 +4087,25 @@
         <v>21</v>
       </c>
       <c r="H82">
-        <v>0.4804464685753226</v>
+        <v>0.4805033717306983</v>
       </c>
       <c r="I82">
-        <v>0.4854964665913174</v>
+        <v>0.4865272503340775</v>
       </c>
       <c r="J82">
-        <v>0.2328541371671391</v>
+        <v>0.2300712185340965</v>
       </c>
       <c r="K82">
-        <v>0.689517656418535</v>
+        <v>0.6896080578592316</v>
       </c>
       <c r="L82">
         <v>10000</v>
       </c>
       <c r="M82">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N82">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4131,25 +4131,25 @@
         <v>22</v>
       </c>
       <c r="H83">
-        <v>0.5182145692666246</v>
+        <v>0.5152658720829023</v>
       </c>
       <c r="I83">
-        <v>0.4959489184618466</v>
+        <v>0.4904270606959902</v>
       </c>
       <c r="J83">
-        <v>0.2711063060643814</v>
+        <v>0.2663622945319104</v>
       </c>
       <c r="K83">
-        <v>0.9007432211596753</v>
+        <v>0.8941246793839006</v>
       </c>
       <c r="L83">
         <v>10000</v>
       </c>
       <c r="M83">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N83">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4175,25 +4175,25 @@
         <v>23</v>
       </c>
       <c r="H84">
-        <v>0.8178851462502938</v>
+        <v>0.8130786630421242</v>
       </c>
       <c r="I84">
-        <v>0.7870838437152919</v>
+        <v>0.7772142481864536</v>
       </c>
       <c r="J84">
-        <v>0.4460327687474542</v>
+        <v>0.4342778196604707</v>
       </c>
       <c r="K84">
-        <v>1.379685507385966</v>
+        <v>1.381369701953175</v>
       </c>
       <c r="L84">
         <v>10000</v>
       </c>
       <c r="M84">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N84">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4219,25 +4219,25 @@
         <v>24</v>
       </c>
       <c r="H85">
-        <v>21050.76579393161</v>
+        <v>21286.22747955771</v>
       </c>
       <c r="I85">
-        <v>18935.09051377299</v>
+        <v>19105.73358884299</v>
       </c>
       <c r="J85">
-        <v>11091.09549892215</v>
+        <v>11090.44167276637</v>
       </c>
       <c r="K85">
-        <v>43787.88705808375</v>
+        <v>44146.47668851305</v>
       </c>
       <c r="L85">
         <v>10000</v>
       </c>
       <c r="M85">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N85">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4263,25 +4263,25 @@
         <v>25</v>
       </c>
       <c r="H86">
-        <v>0.6337985234484438</v>
+        <v>0.6339380196559078</v>
       </c>
       <c r="I86">
-        <v>0.6304420836239141</v>
+        <v>0.6312466190914762</v>
       </c>
       <c r="J86">
-        <v>0.5196884268460543</v>
+        <v>0.5177515395725819</v>
       </c>
       <c r="K86">
-        <v>0.7630195792459122</v>
+        <v>0.7620679967176439</v>
       </c>
       <c r="L86">
         <v>10000</v>
       </c>
       <c r="M86">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N86">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4307,25 +4307,25 @@
         <v>26</v>
       </c>
       <c r="H87">
-        <v>2172.718612680434</v>
+        <v>2173.571118993758</v>
       </c>
       <c r="I87">
-        <v>2097.797487060447</v>
+        <v>2097.498961788019</v>
       </c>
       <c r="J87">
-        <v>1793.262480501199</v>
+        <v>1790.030987130527</v>
       </c>
       <c r="K87">
-        <v>2955.003137131763</v>
+        <v>2965.937018363914</v>
       </c>
       <c r="L87">
         <v>10000</v>
       </c>
       <c r="M87">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N87">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -4351,25 +4351,25 @@
         <v>27</v>
       </c>
       <c r="H88">
-        <v>3388.452807433172</v>
+        <v>3396.33622959534</v>
       </c>
       <c r="I88">
-        <v>3013.525588024148</v>
+        <v>3019.826513019449</v>
       </c>
       <c r="J88">
-        <v>1347.826757665926</v>
+        <v>1365.377988906558</v>
       </c>
       <c r="K88">
-        <v>7570.72549420125</v>
+        <v>7710.647386843626</v>
       </c>
       <c r="L88">
         <v>10000</v>
       </c>
       <c r="M88">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N88">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -4395,25 +4395,25 @@
         <v>28</v>
       </c>
       <c r="H89">
-        <v>0.3022559448522538</v>
+        <v>0.3007374132275055</v>
       </c>
       <c r="I89">
-        <v>0.2974151539110378</v>
+        <v>0.2948696270392088</v>
       </c>
       <c r="J89">
-        <v>0.1811197994156034</v>
+        <v>0.1777379653533954</v>
       </c>
       <c r="K89">
-        <v>0.4543874331319378</v>
+        <v>0.4526079208495183</v>
       </c>
       <c r="L89">
         <v>10000</v>
       </c>
       <c r="M89">
-        <v>8030</v>
+        <v>7987</v>
       </c>
       <c r="N89">
-        <v>80.3</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -4439,25 +4439,25 @@
         <v>18</v>
       </c>
       <c r="H90">
-        <v>6487.062569795208</v>
+        <v>6498.548964701636</v>
       </c>
       <c r="I90">
-        <v>6182.405346125499</v>
+        <v>6223.451592648782</v>
       </c>
       <c r="J90">
-        <v>4219.758791927816</v>
+        <v>4227.385222546532</v>
       </c>
       <c r="K90">
-        <v>10483.5517680958</v>
+        <v>10416.40008954754</v>
       </c>
       <c r="L90">
         <v>10000</v>
       </c>
       <c r="M90">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N90">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -4483,25 +4483,25 @@
         <v>19</v>
       </c>
       <c r="H91">
-        <v>0.3751648237549798</v>
+        <v>0.3741239579916703</v>
       </c>
       <c r="I91">
-        <v>0.3740603504312809</v>
+        <v>0.3748199439411724</v>
       </c>
       <c r="J91">
-        <v>0.2104017026912521</v>
+        <v>0.2065424819799263</v>
       </c>
       <c r="K91">
-        <v>0.5453558524560664</v>
+        <v>0.5434578308834137</v>
       </c>
       <c r="L91">
         <v>10000</v>
       </c>
       <c r="M91">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N91">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4527,25 +4527,25 @@
         <v>20</v>
       </c>
       <c r="H92">
-        <v>9109.364837948058</v>
+        <v>9139.338084304343</v>
       </c>
       <c r="I92">
-        <v>7726.353318998183</v>
+        <v>7747.056093273128</v>
       </c>
       <c r="J92">
-        <v>3550.954643749309</v>
+        <v>3530.996891841321</v>
       </c>
       <c r="K92">
-        <v>23111.7690252599</v>
+        <v>23604.96227052747</v>
       </c>
       <c r="L92">
         <v>10000</v>
       </c>
       <c r="M92">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N92">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -4571,25 +4571,25 @@
         <v>21</v>
       </c>
       <c r="H93">
-        <v>0.4863056490370918</v>
+        <v>0.4843580251896784</v>
       </c>
       <c r="I93">
-        <v>0.4918984448688283</v>
+        <v>0.4933085021232647</v>
       </c>
       <c r="J93">
-        <v>0.2341381319334571</v>
+        <v>0.2359000867389185</v>
       </c>
       <c r="K93">
-        <v>0.6896903406550619</v>
+        <v>0.6882625668387893</v>
       </c>
       <c r="L93">
         <v>10000</v>
       </c>
       <c r="M93">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N93">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -4615,25 +4615,25 @@
         <v>22</v>
       </c>
       <c r="H94">
-        <v>0.7437191142404856</v>
+        <v>0.7400635353075505</v>
       </c>
       <c r="I94">
-        <v>0.7092658537801741</v>
+        <v>0.7055672980949361</v>
       </c>
       <c r="J94">
-        <v>0.3884215205052283</v>
+        <v>0.3864020530102387</v>
       </c>
       <c r="K94">
-        <v>1.30422104562733</v>
+        <v>1.285570522311478</v>
       </c>
       <c r="L94">
         <v>10000</v>
       </c>
       <c r="M94">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N94">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -4659,25 +4659,25 @@
         <v>23</v>
       </c>
       <c r="H95">
-        <v>0.8079839506372097</v>
+        <v>0.8042013755708591</v>
       </c>
       <c r="I95">
-        <v>0.7752072200692537</v>
+        <v>0.7732155459830605</v>
       </c>
       <c r="J95">
-        <v>0.4390798502545189</v>
+        <v>0.4325244122623396</v>
       </c>
       <c r="K95">
-        <v>1.378690360349429</v>
+        <v>1.37090111900191</v>
       </c>
       <c r="L95">
         <v>10000</v>
       </c>
       <c r="M95">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N95">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -4703,25 +4703,25 @@
         <v>24</v>
       </c>
       <c r="H96">
-        <v>18470.07448115326</v>
+        <v>18572.69912285846</v>
       </c>
       <c r="I96">
-        <v>16449.66487245703</v>
+        <v>16552.40455176227</v>
       </c>
       <c r="J96">
-        <v>10444.06932223393</v>
+        <v>10535.15812768512</v>
       </c>
       <c r="K96">
-        <v>38442.47330986265</v>
+        <v>39256.83420739126</v>
       </c>
       <c r="L96">
         <v>10000</v>
       </c>
       <c r="M96">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N96">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -4747,25 +4747,25 @@
         <v>25</v>
       </c>
       <c r="H97">
-        <v>0.9207341867336396</v>
+        <v>0.9208490936732033</v>
       </c>
       <c r="I97">
-        <v>0.9163863980785907</v>
+        <v>0.9167558037678601</v>
       </c>
       <c r="J97">
-        <v>0.7543321526971583</v>
+        <v>0.7519384803574555</v>
       </c>
       <c r="K97">
-        <v>1.107824340046832</v>
+        <v>1.107346183402293</v>
       </c>
       <c r="L97">
         <v>10000</v>
       </c>
       <c r="M97">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N97">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -4791,25 +4791,25 @@
         <v>26</v>
       </c>
       <c r="H98">
-        <v>2203.618956750225</v>
+        <v>2203.754984029485</v>
       </c>
       <c r="I98">
-        <v>2122.234724895137</v>
+        <v>2120.447583356405</v>
       </c>
       <c r="J98">
-        <v>1879.695365093291</v>
+        <v>1880.603185148313</v>
       </c>
       <c r="K98">
-        <v>2964.388921447633</v>
+        <v>2994.916968518872</v>
       </c>
       <c r="L98">
         <v>10000</v>
       </c>
       <c r="M98">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N98">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -4835,25 +4835,25 @@
         <v>27</v>
       </c>
       <c r="H99">
-        <v>3610.719221019309</v>
+        <v>3618.261864144526</v>
       </c>
       <c r="I99">
-        <v>3249.191442192596</v>
+        <v>3248.66434571618</v>
       </c>
       <c r="J99">
-        <v>1491.716858640211</v>
+        <v>1480.10888308018</v>
       </c>
       <c r="K99">
-        <v>8030.234852442319</v>
+        <v>8230.320688207174</v>
       </c>
       <c r="L99">
         <v>10000</v>
       </c>
       <c r="M99">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N99">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -4879,25 +4879,25 @@
         <v>28</v>
       </c>
       <c r="H100">
-        <v>0.3547257586453204</v>
+        <v>0.3536315988344439</v>
       </c>
       <c r="I100">
-        <v>0.350813218271891</v>
+        <v>0.3486095351567502</v>
       </c>
       <c r="J100">
-        <v>0.220678676882628</v>
+        <v>0.2198309488658072</v>
       </c>
       <c r="K100">
-        <v>0.5149250844861584</v>
+        <v>0.5114058892738599</v>
       </c>
       <c r="L100">
         <v>10000</v>
       </c>
       <c r="M100">
-        <v>7460</v>
+        <v>7486</v>
       </c>
       <c r="N100">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -4923,25 +4923,25 @@
         <v>18</v>
       </c>
       <c r="H101">
-        <v>9068.471105228286</v>
+        <v>9169.107566441893</v>
       </c>
       <c r="I101">
-        <v>7973.506200988253</v>
+        <v>8010.659636974604</v>
       </c>
       <c r="J101">
-        <v>4940.746387948636</v>
+        <v>4907.440297844495</v>
       </c>
       <c r="K101">
-        <v>20333.42587271679</v>
+        <v>20379.36084326561</v>
       </c>
       <c r="L101">
         <v>10000</v>
       </c>
       <c r="M101">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N101">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -4967,25 +4967,25 @@
         <v>19</v>
       </c>
       <c r="H102">
-        <v>0.3902159377642287</v>
+        <v>0.3928999232396022</v>
       </c>
       <c r="I102">
-        <v>0.3905162780861584</v>
+        <v>0.3905753193762926</v>
       </c>
       <c r="J102">
-        <v>0.2170641224822941</v>
+        <v>0.22261823562424</v>
       </c>
       <c r="K102">
-        <v>0.5649899096090754</v>
+        <v>0.5698139926563284</v>
       </c>
       <c r="L102">
         <v>10000</v>
       </c>
       <c r="M102">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N102">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -5011,25 +5011,25 @@
         <v>20</v>
       </c>
       <c r="H103">
-        <v>14788.10515360559</v>
+        <v>14897.80511978525</v>
       </c>
       <c r="I103">
-        <v>11049.05323294209</v>
+        <v>11088.52147933903</v>
       </c>
       <c r="J103">
-        <v>2895.455948998732</v>
+        <v>2937.705065213941</v>
       </c>
       <c r="K103">
-        <v>47549.77160513693</v>
+        <v>46802.65753546935</v>
       </c>
       <c r="L103">
         <v>10000</v>
       </c>
       <c r="M103">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N103">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5055,25 +5055,25 @@
         <v>21</v>
       </c>
       <c r="H104">
-        <v>0.563762993766863</v>
+        <v>0.5671801959568448</v>
       </c>
       <c r="I104">
-        <v>0.5652438729514194</v>
+        <v>0.5715349566038398</v>
       </c>
       <c r="J104">
-        <v>0.1598845552981337</v>
+        <v>0.1647623294583323</v>
       </c>
       <c r="K104">
-        <v>0.9146584876595218</v>
+        <v>0.913348321756162</v>
       </c>
       <c r="L104">
         <v>10000</v>
       </c>
       <c r="M104">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N104">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -5099,25 +5099,25 @@
         <v>22</v>
       </c>
       <c r="H105">
-        <v>0.5107427240794223</v>
+        <v>0.506122787220727</v>
       </c>
       <c r="I105">
-        <v>0.489741477158246</v>
+        <v>0.4850676886973555</v>
       </c>
       <c r="J105">
-        <v>0.2627406849993552</v>
+        <v>0.2643205540980222</v>
       </c>
       <c r="K105">
-        <v>0.8654959968165304</v>
+        <v>0.873526210552742</v>
       </c>
       <c r="L105">
         <v>10000</v>
       </c>
       <c r="M105">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N105">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5143,25 +5143,25 @@
         <v>23</v>
       </c>
       <c r="H106">
-        <v>0.8279948943542004</v>
+        <v>0.8185314056496569</v>
       </c>
       <c r="I106">
-        <v>0.7992117385269049</v>
+        <v>0.7874383399348528</v>
       </c>
       <c r="J106">
-        <v>0.4462315793663839</v>
+        <v>0.439223433543524</v>
       </c>
       <c r="K106">
-        <v>1.37881124395616</v>
+        <v>1.401482433961807</v>
       </c>
       <c r="L106">
         <v>10000</v>
       </c>
       <c r="M106">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N106">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -5187,25 +5187,25 @@
         <v>24</v>
       </c>
       <c r="H107">
-        <v>24475.46525743564</v>
+        <v>24492.9656339118</v>
       </c>
       <c r="I107">
-        <v>21101.16468273813</v>
+        <v>21271.85849147772</v>
       </c>
       <c r="J107">
-        <v>11333.89450993584</v>
+        <v>11370.68548225511</v>
       </c>
       <c r="K107">
-        <v>57140.41772676152</v>
+        <v>55743.24264141143</v>
       </c>
       <c r="L107">
         <v>10000</v>
       </c>
       <c r="M107">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N107">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -5231,25 +5231,25 @@
         <v>25</v>
       </c>
       <c r="H108">
-        <v>0.6170244417733504</v>
+        <v>0.6184485857412246</v>
       </c>
       <c r="I108">
-        <v>0.6143277318123852</v>
+        <v>0.6161448017735023</v>
       </c>
       <c r="J108">
-        <v>0.5080244203030531</v>
+        <v>0.5094914695322755</v>
       </c>
       <c r="K108">
-        <v>0.7422358782108345</v>
+        <v>0.7436723708625687</v>
       </c>
       <c r="L108">
         <v>10000</v>
       </c>
       <c r="M108">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N108">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -5275,25 +5275,25 @@
         <v>26</v>
       </c>
       <c r="H109">
-        <v>2620.848325972349</v>
+        <v>2621.618129462448</v>
       </c>
       <c r="I109">
-        <v>2199.050122474205</v>
+        <v>2201.94916344533</v>
       </c>
       <c r="J109">
-        <v>1725.895684976724</v>
+        <v>1741.858674603995</v>
       </c>
       <c r="K109">
-        <v>5795.505517341859</v>
+        <v>5782.542181908672</v>
       </c>
       <c r="L109">
         <v>10000</v>
       </c>
       <c r="M109">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N109">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -5319,25 +5319,25 @@
         <v>27</v>
       </c>
       <c r="H110">
-        <v>4777.092566831036</v>
+        <v>4747.508633343231</v>
       </c>
       <c r="I110">
-        <v>3698.230024855548</v>
+        <v>3652.684965716137</v>
       </c>
       <c r="J110">
-        <v>910.3487602924494</v>
+        <v>967.8334061763619</v>
       </c>
       <c r="K110">
-        <v>14773.36045844225</v>
+        <v>14448.69672473076</v>
       </c>
       <c r="L110">
         <v>10000</v>
       </c>
       <c r="M110">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N110">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -5363,25 +5363,25 @@
         <v>28</v>
       </c>
       <c r="H111">
-        <v>0.3010745333588589</v>
+        <v>0.2986238529362966</v>
       </c>
       <c r="I111">
-        <v>0.2958770123946877</v>
+        <v>0.2937269643315786</v>
       </c>
       <c r="J111">
-        <v>0.1784005179262901</v>
+        <v>0.178390039117477</v>
       </c>
       <c r="K111">
-        <v>0.4489351867004563</v>
+        <v>0.4532128538887902</v>
       </c>
       <c r="L111">
         <v>10000</v>
       </c>
       <c r="M111">
-        <v>6231</v>
+        <v>6200</v>
       </c>
       <c r="N111">
-        <v>62.3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -5407,22 +5407,22 @@
         <v>18</v>
       </c>
       <c r="H112">
-        <v>9001.288277954416</v>
+        <v>8967.602587134334</v>
       </c>
       <c r="I112">
-        <v>7901.707451654331</v>
+        <v>7848.644165571045</v>
       </c>
       <c r="J112">
-        <v>4848.429507749993</v>
+        <v>4928.365725005853</v>
       </c>
       <c r="K112">
-        <v>20122.84315254542</v>
+        <v>19801.55890352991</v>
       </c>
       <c r="L112">
         <v>10000</v>
       </c>
       <c r="M112">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N112">
         <v>61.6</v>
@@ -5451,22 +5451,22 @@
         <v>19</v>
       </c>
       <c r="H113">
-        <v>0.3919603265406643</v>
+        <v>0.3923489965473158</v>
       </c>
       <c r="I113">
-        <v>0.391374854362325</v>
+        <v>0.3906637220926012</v>
       </c>
       <c r="J113">
-        <v>0.2256312757765322</v>
+        <v>0.220794907539745</v>
       </c>
       <c r="K113">
-        <v>0.5692052310759397</v>
+        <v>0.5645212427262323</v>
       </c>
       <c r="L113">
         <v>10000</v>
       </c>
       <c r="M113">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N113">
         <v>61.6</v>
@@ -5495,22 +5495,22 @@
         <v>20</v>
       </c>
       <c r="H114">
-        <v>14648.37609529606</v>
+        <v>14661.20267125724</v>
       </c>
       <c r="I114">
-        <v>10943.06945846417</v>
+        <v>10935.06751782134</v>
       </c>
       <c r="J114">
-        <v>2962.783496421237</v>
+        <v>2948.187846650611</v>
       </c>
       <c r="K114">
-        <v>45578.42525922767</v>
+        <v>46141.63156329931</v>
       </c>
       <c r="L114">
         <v>10000</v>
       </c>
       <c r="M114">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N114">
         <v>61.6</v>
@@ -5539,22 +5539,22 @@
         <v>21</v>
       </c>
       <c r="H115">
-        <v>0.5669930456828112</v>
+        <v>0.5680735207956922</v>
       </c>
       <c r="I115">
-        <v>0.5681652473829155</v>
+        <v>0.5740633985226012</v>
       </c>
       <c r="J115">
-        <v>0.1712461532159825</v>
+        <v>0.1694769031268535</v>
       </c>
       <c r="K115">
-        <v>0.9081673842285681</v>
+        <v>0.9091257855806415</v>
       </c>
       <c r="L115">
         <v>10000</v>
       </c>
       <c r="M115">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N115">
         <v>61.6</v>
@@ -5583,22 +5583,22 @@
         <v>22</v>
       </c>
       <c r="H116">
-        <v>0.5200740529546546</v>
+        <v>0.5217933556871494</v>
       </c>
       <c r="I116">
-        <v>0.4945215602027372</v>
+        <v>0.4998600691772305</v>
       </c>
       <c r="J116">
-        <v>0.2719887599068793</v>
+        <v>0.27515885143693</v>
       </c>
       <c r="K116">
-        <v>0.8968160106562816</v>
+        <v>0.8956500656515481</v>
       </c>
       <c r="L116">
         <v>10000</v>
       </c>
       <c r="M116">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N116">
         <v>61.6</v>
@@ -5627,22 +5627,22 @@
         <v>23</v>
       </c>
       <c r="H117">
-        <v>0.8193726854212006</v>
+        <v>0.8252772010029509</v>
       </c>
       <c r="I117">
-        <v>0.784987849821919</v>
+        <v>0.7941316226577038</v>
       </c>
       <c r="J117">
-        <v>0.44796443194556</v>
+        <v>0.4505485592025547</v>
       </c>
       <c r="K117">
-        <v>1.3836882934764</v>
+        <v>1.386040573360363</v>
       </c>
       <c r="L117">
         <v>10000</v>
       </c>
       <c r="M117">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N117">
         <v>61.6</v>
@@ -5671,22 +5671,22 @@
         <v>24</v>
       </c>
       <c r="H118">
-        <v>24118.42532259661</v>
+        <v>24092.45536345959</v>
       </c>
       <c r="I118">
-        <v>21058.34814904685</v>
+        <v>20835.86923112183</v>
       </c>
       <c r="J118">
-        <v>11293.44700747491</v>
+        <v>11198.8144137283</v>
       </c>
       <c r="K118">
-        <v>55956.56771399825</v>
+        <v>55647.62153731555</v>
       </c>
       <c r="L118">
         <v>10000</v>
       </c>
       <c r="M118">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N118">
         <v>61.6</v>
@@ -5715,22 +5715,22 @@
         <v>25</v>
       </c>
       <c r="H119">
-        <v>0.6348019892492814</v>
+        <v>0.6327379622230509</v>
       </c>
       <c r="I119">
-        <v>0.6313495757566961</v>
+        <v>0.6306091632636485</v>
       </c>
       <c r="J119">
-        <v>0.5197799434862507</v>
+        <v>0.5185855678068219</v>
       </c>
       <c r="K119">
-        <v>0.7685031261024736</v>
+        <v>0.7603060150615129</v>
       </c>
       <c r="L119">
         <v>10000</v>
       </c>
       <c r="M119">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N119">
         <v>61.6</v>
@@ -5759,22 +5759,22 @@
         <v>26</v>
       </c>
       <c r="H120">
-        <v>2607.712747381227</v>
+        <v>2616.182818123052</v>
       </c>
       <c r="I120">
-        <v>2209.175181394003</v>
+        <v>2207.351582742057</v>
       </c>
       <c r="J120">
-        <v>1766.887565234377</v>
+        <v>1756.900334388553</v>
       </c>
       <c r="K120">
-        <v>5655.529852698668</v>
+        <v>5645.26797344752</v>
       </c>
       <c r="L120">
         <v>10000</v>
       </c>
       <c r="M120">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N120">
         <v>61.6</v>
@@ -5803,22 +5803,22 @@
         <v>27</v>
       </c>
       <c r="H121">
-        <v>4744.818590823418</v>
+        <v>4779.29216172731</v>
       </c>
       <c r="I121">
-        <v>3694.763082735284</v>
+        <v>3700.95177750612</v>
       </c>
       <c r="J121">
-        <v>997.865311152914</v>
+        <v>1021.80718418917</v>
       </c>
       <c r="K121">
-        <v>14519.90482237302</v>
+        <v>14563.69002601231</v>
       </c>
       <c r="L121">
         <v>10000</v>
       </c>
       <c r="M121">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N121">
         <v>61.6</v>
@@ -5847,22 +5847,22 @@
         <v>28</v>
       </c>
       <c r="H122">
-        <v>0.3029515354012442</v>
+        <v>0.3042607602263876</v>
       </c>
       <c r="I122">
-        <v>0.2969264639654289</v>
+        <v>0.2996219106527815</v>
       </c>
       <c r="J122">
-        <v>0.1809353212350348</v>
+        <v>0.1829624481818056</v>
       </c>
       <c r="K122">
-        <v>0.4550111257864933</v>
+        <v>0.4516017297408405</v>
       </c>
       <c r="L122">
         <v>10000</v>
       </c>
       <c r="M122">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N122">
         <v>61.6</v>
@@ -5891,25 +5891,25 @@
         <v>18</v>
       </c>
       <c r="H123">
-        <v>7952.706168528959</v>
+        <v>7898.967953471688</v>
       </c>
       <c r="I123">
-        <v>6853.193833818495</v>
+        <v>6812.558137874756</v>
       </c>
       <c r="J123">
-        <v>4354.630345793124</v>
+        <v>4321.316153168047</v>
       </c>
       <c r="K123">
-        <v>18545.77048352652</v>
+        <v>17984.27807940006</v>
       </c>
       <c r="L123">
         <v>10000</v>
       </c>
       <c r="M123">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N123">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -5935,25 +5935,25 @@
         <v>19</v>
       </c>
       <c r="H124">
-        <v>0.3801145862153005</v>
+        <v>0.3817445968590758</v>
       </c>
       <c r="I124">
-        <v>0.3809447128440631</v>
+        <v>0.3824187969863528</v>
       </c>
       <c r="J124">
-        <v>0.2187542001503314</v>
+        <v>0.2185941276108566</v>
       </c>
       <c r="K124">
-        <v>0.5466305964999081</v>
+        <v>0.5496820762805545</v>
       </c>
       <c r="L124">
         <v>10000</v>
       </c>
       <c r="M124">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N124">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -5979,25 +5979,25 @@
         <v>20</v>
       </c>
       <c r="H125">
-        <v>13837.22838112832</v>
+        <v>13620.84264388482</v>
       </c>
       <c r="I125">
-        <v>9917.417708136212</v>
+        <v>9754.248875077014</v>
       </c>
       <c r="J125">
-        <v>3103.66621043545</v>
+        <v>2861.698737950199</v>
       </c>
       <c r="K125">
-        <v>46919.62976031088</v>
+        <v>45678.47254309546</v>
       </c>
       <c r="L125">
         <v>10000</v>
       </c>
       <c r="M125">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N125">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6023,25 +6023,25 @@
         <v>21</v>
       </c>
       <c r="H126">
-        <v>0.5815074605429423</v>
+        <v>0.5770993268721153</v>
       </c>
       <c r="I126">
-        <v>0.583927186631331</v>
+        <v>0.5824737206507786</v>
       </c>
       <c r="J126">
-        <v>0.1986056399160235</v>
+        <v>0.1839548936073245</v>
       </c>
       <c r="K126">
-        <v>0.9167241860582448</v>
+        <v>0.9158395527761028</v>
       </c>
       <c r="L126">
         <v>10000</v>
       </c>
       <c r="M126">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N126">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6067,25 +6067,25 @@
         <v>22</v>
       </c>
       <c r="H127">
-        <v>0.7438040915415715</v>
+        <v>0.7394640280027127</v>
       </c>
       <c r="I127">
-        <v>0.7120374429336664</v>
+        <v>0.7062905794367522</v>
       </c>
       <c r="J127">
-        <v>0.391778765524626</v>
+        <v>0.3850730835671168</v>
       </c>
       <c r="K127">
-        <v>1.273323368417864</v>
+        <v>1.269959616287478</v>
       </c>
       <c r="L127">
         <v>10000</v>
       </c>
       <c r="M127">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N127">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6111,25 +6111,25 @@
         <v>23</v>
       </c>
       <c r="H128">
-        <v>0.80689127734623</v>
+        <v>0.8031403663694306</v>
       </c>
       <c r="I128">
-        <v>0.7750337883484997</v>
+        <v>0.7684767452037274</v>
       </c>
       <c r="J128">
-        <v>0.4409446166560791</v>
+        <v>0.4354623878450352</v>
       </c>
       <c r="K128">
-        <v>1.353557862991213</v>
+        <v>1.345789775243464</v>
       </c>
       <c r="L128">
         <v>10000</v>
       </c>
       <c r="M128">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N128">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6155,25 +6155,25 @@
         <v>24</v>
       </c>
       <c r="H129">
-        <v>22064.87922940141</v>
+        <v>21901.17519737682</v>
       </c>
       <c r="I129">
-        <v>18211.81588555906</v>
+        <v>18149.70285573606</v>
       </c>
       <c r="J129">
-        <v>10689.68155432423</v>
+        <v>10679.31230198471</v>
       </c>
       <c r="K129">
-        <v>55403.91420172155</v>
+        <v>53809.77568262721</v>
       </c>
       <c r="L129">
         <v>10000</v>
       </c>
       <c r="M129">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N129">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6199,25 +6199,25 @@
         <v>25</v>
       </c>
       <c r="H130">
-        <v>0.9221591124356263</v>
+        <v>0.9213505299937814</v>
       </c>
       <c r="I130">
-        <v>0.9187919853775115</v>
+        <v>0.916480998422894</v>
       </c>
       <c r="J130">
-        <v>0.7537265660008756</v>
+        <v>0.7506054056019242</v>
       </c>
       <c r="K130">
-        <v>1.111521573167173</v>
+        <v>1.11255014728377</v>
       </c>
       <c r="L130">
         <v>10000</v>
       </c>
       <c r="M130">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N130">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6243,25 +6243,25 @@
         <v>26</v>
       </c>
       <c r="H131">
-        <v>2713.497954230626</v>
+        <v>2685.768349827056</v>
       </c>
       <c r="I131">
-        <v>2243.984724273784</v>
+        <v>2239.701479656338</v>
       </c>
       <c r="J131">
-        <v>1880.961587502711</v>
+        <v>1871.028470787551</v>
       </c>
       <c r="K131">
-        <v>6254.143474230006</v>
+        <v>6017.496607009682</v>
       </c>
       <c r="L131">
         <v>10000</v>
       </c>
       <c r="M131">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N131">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6287,25 +6287,25 @@
         <v>27</v>
       </c>
       <c r="H132">
-        <v>5304.519628683608</v>
+        <v>5197.018853470916</v>
       </c>
       <c r="I132">
-        <v>4026.279208407972</v>
+        <v>4020.866723140656</v>
       </c>
       <c r="J132">
-        <v>1302.081186588454</v>
+        <v>1180.740824738343</v>
       </c>
       <c r="K132">
-        <v>16871.83168475158</v>
+        <v>16339.41039939823</v>
       </c>
       <c r="L132">
         <v>10000</v>
       </c>
       <c r="M132">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N132">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -6331,25 +6331,25 @@
         <v>28</v>
       </c>
       <c r="H133">
-        <v>0.3546764023905794</v>
+        <v>0.3533130228149071</v>
       </c>
       <c r="I133">
-        <v>0.3510045917353629</v>
+        <v>0.3487454600719414</v>
       </c>
       <c r="J133">
-        <v>0.2232388098707915</v>
+        <v>0.2184071672345637</v>
       </c>
       <c r="K133">
-        <v>0.5075505563717337</v>
+        <v>0.5065168945833387</v>
       </c>
       <c r="L133">
         <v>10000</v>
       </c>
       <c r="M133">
-        <v>5828</v>
+        <v>5809</v>
       </c>
       <c r="N133">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tabela_resumo_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_resumo_dbsra_macarellus.xlsx
@@ -558,34 +558,34 @@
         <v>17</v>
       </c>
       <c r="E2">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F2">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
       </c>
       <c r="H2">
-        <v>6864.782663382054</v>
+        <v>5253.459291502098</v>
       </c>
       <c r="I2">
-        <v>6695.137566716333</v>
+        <v>5078.724166815064</v>
       </c>
       <c r="J2">
-        <v>4606.853645359995</v>
+        <v>3471.667773084651</v>
       </c>
       <c r="K2">
-        <v>10054.02723784558</v>
+        <v>8044.162701801042</v>
       </c>
       <c r="L2">
         <v>10000</v>
       </c>
       <c r="M2">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N2">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -602,34 +602,34 @@
         <v>17</v>
       </c>
       <c r="E3">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F3">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
       </c>
       <c r="H3">
-        <v>0.3500178711997007</v>
+        <v>0.3045456603608194</v>
       </c>
       <c r="I3">
-        <v>0.3455536283331682</v>
+        <v>0.2990903375499843</v>
       </c>
       <c r="J3">
-        <v>0.1894694393837437</v>
+        <v>0.1440253107332279</v>
       </c>
       <c r="K3">
-        <v>0.5372988320919654</v>
+        <v>0.4716403342396163</v>
       </c>
       <c r="L3">
         <v>10000</v>
       </c>
       <c r="M3">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N3">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -646,34 +646,34 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F4">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
       </c>
       <c r="H4">
-        <v>5004.065627304772</v>
+        <v>2814.452843888446</v>
       </c>
       <c r="I4">
-        <v>4804.10300257983</v>
+        <v>2930.842970582611</v>
       </c>
       <c r="J4">
-        <v>1584.277452277248</v>
+        <v>806.8150548883962</v>
       </c>
       <c r="K4">
-        <v>9660.363408131838</v>
+        <v>4850.59576495418</v>
       </c>
       <c r="L4">
         <v>10000</v>
       </c>
       <c r="M4">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N4">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -690,34 +690,34 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F5">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
       </c>
       <c r="H5">
-        <v>0.2420126436835842</v>
+        <v>0.1578961314649116</v>
       </c>
       <c r="I5">
-        <v>0.2560344669816944</v>
+        <v>0.174433575906368</v>
       </c>
       <c r="J5">
-        <v>0.0937919845082175</v>
+        <v>0.04907304135551505</v>
       </c>
       <c r="K5">
-        <v>0.3276056424938081</v>
+        <v>0.2163282109136386</v>
       </c>
       <c r="L5">
         <v>10000</v>
       </c>
       <c r="M5">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N5">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -734,34 +734,34 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F6">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
       </c>
       <c r="H6">
-        <v>0.4759148207418335</v>
+        <v>0.3754498110844739</v>
       </c>
       <c r="I6">
-        <v>0.4526666718295683</v>
+        <v>0.3536576049050743</v>
       </c>
       <c r="J6">
-        <v>0.2468402398462165</v>
+        <v>0.201130991947004</v>
       </c>
       <c r="K6">
-        <v>0.8350668773370838</v>
+        <v>0.6675251025241087</v>
       </c>
       <c r="L6">
         <v>10000</v>
       </c>
       <c r="M6">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N6">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -778,34 +778,34 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F7">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
       </c>
       <c r="H7">
-        <v>0.776200173421971</v>
+        <v>0.6288011001310631</v>
       </c>
       <c r="I7">
-        <v>0.7404109689824199</v>
+        <v>0.5987074873581009</v>
       </c>
       <c r="J7">
-        <v>0.4138101245988932</v>
+        <v>0.3370526685357719</v>
       </c>
       <c r="K7">
-        <v>1.324934091215543</v>
+        <v>1.041011734520104</v>
       </c>
       <c r="L7">
         <v>10000</v>
       </c>
       <c r="M7">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N7">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -822,34 +822,34 @@
         <v>17</v>
       </c>
       <c r="E8">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F8">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
       </c>
       <c r="H8">
-        <v>20701.97744695799</v>
+        <v>17779.4168140523</v>
       </c>
       <c r="I8">
-        <v>20077.65358092204</v>
+        <v>16472.31610542222</v>
       </c>
       <c r="J8">
-        <v>11278.48234676944</v>
+        <v>11357.66313131566</v>
       </c>
       <c r="K8">
-        <v>35178.22963494794</v>
+        <v>24871.19142983845</v>
       </c>
       <c r="L8">
         <v>10000</v>
       </c>
       <c r="M8">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N8">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -866,34 +866,34 @@
         <v>17</v>
       </c>
       <c r="E9">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F9">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
       </c>
       <c r="H9">
-        <v>0.6133454618288503</v>
+        <v>0.5969522368290827</v>
       </c>
       <c r="I9">
-        <v>0.6120233327953369</v>
+        <v>0.5904252460775544</v>
       </c>
       <c r="J9">
-        <v>0.50257514626376</v>
+        <v>0.5071096910985985</v>
       </c>
       <c r="K9">
-        <v>0.738218703464342</v>
+        <v>0.7204889618208969</v>
       </c>
       <c r="L9">
         <v>10000</v>
       </c>
       <c r="M9">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N9">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -910,34 +910,34 @@
         <v>17</v>
       </c>
       <c r="E10">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F10">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
       </c>
       <c r="H10">
-        <v>1866.548769321672</v>
+        <v>1182.102646647209</v>
       </c>
       <c r="I10">
-        <v>1896.769409607813</v>
+        <v>1218.986938957394</v>
       </c>
       <c r="J10">
-        <v>1581.59097671675</v>
+        <v>917.8743243933513</v>
       </c>
       <c r="K10">
-        <v>2046.507984910551</v>
+        <v>1410.055572900835</v>
       </c>
       <c r="L10">
         <v>10000</v>
       </c>
       <c r="M10">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N10">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -954,34 +954,34 @@
         <v>17</v>
       </c>
       <c r="E11">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F11">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11">
-        <v>1633.910153487818</v>
+        <v>841.1922629053704</v>
       </c>
       <c r="I11">
-        <v>1618.02109005795</v>
+        <v>836.1722768880262</v>
       </c>
       <c r="J11">
-        <v>482.5776735500042</v>
+        <v>218.152154909901</v>
       </c>
       <c r="K11">
-        <v>3008.082986420435</v>
+        <v>1530.198030421081</v>
       </c>
       <c r="L11">
         <v>10000</v>
       </c>
       <c r="M11">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N11">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -998,34 +998,34 @@
         <v>17</v>
       </c>
       <c r="E12">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F12">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
       </c>
       <c r="H12">
-        <v>0.2849240982826305</v>
+        <v>0.2365942542195358</v>
       </c>
       <c r="I12">
-        <v>0.2786026719856977</v>
+        <v>0.2302399169755964</v>
       </c>
       <c r="J12">
-        <v>0.1684133898079802</v>
+        <v>0.1365931494635365</v>
       </c>
       <c r="K12">
-        <v>0.434880278252423</v>
+        <v>0.3687209558772764</v>
       </c>
       <c r="L12">
         <v>10000</v>
       </c>
       <c r="M12">
-        <v>3352</v>
+        <v>139</v>
       </c>
       <c r="N12">
-        <v>33.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1042,34 +1042,34 @@
         <v>31</v>
       </c>
       <c r="E13">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F13">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G13" t="s">
         <v>18</v>
       </c>
       <c r="H13">
-        <v>6810.004782168921</v>
+        <v>5270.145967727135</v>
       </c>
       <c r="I13">
-        <v>6644.418681266994</v>
+        <v>5032.853328972759</v>
       </c>
       <c r="J13">
-        <v>4548.697870615375</v>
+        <v>3628.308202127683</v>
       </c>
       <c r="K13">
-        <v>9942.594601913197</v>
+        <v>8337.329452018885</v>
       </c>
       <c r="L13">
         <v>10000</v>
       </c>
       <c r="M13">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N13">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1086,34 +1086,34 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F14">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G14" t="s">
         <v>19</v>
       </c>
       <c r="H14">
-        <v>0.3498878298745081</v>
+        <v>0.2991201631312089</v>
       </c>
       <c r="I14">
-        <v>0.3442481798992565</v>
+        <v>0.2924569003652332</v>
       </c>
       <c r="J14">
-        <v>0.1826597433780296</v>
+        <v>0.155448293616995</v>
       </c>
       <c r="K14">
-        <v>0.5434410206698048</v>
+        <v>0.509208366729003</v>
       </c>
       <c r="L14">
         <v>10000</v>
       </c>
       <c r="M14">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N14">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1130,34 +1130,34 @@
         <v>31</v>
       </c>
       <c r="E15">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F15">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15">
-        <v>4935.215273932758</v>
+        <v>2938.213059681037</v>
       </c>
       <c r="I15">
-        <v>4723.789944102824</v>
+        <v>2985.754400899681</v>
       </c>
       <c r="J15">
-        <v>1568.467990845754</v>
+        <v>752.6099142171345</v>
       </c>
       <c r="K15">
-        <v>9773.086897225028</v>
+        <v>5017.253372991271</v>
       </c>
       <c r="L15">
         <v>10000</v>
       </c>
       <c r="M15">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N15">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1174,34 +1174,34 @@
         <v>31</v>
       </c>
       <c r="E16">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F16">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G16" t="s">
         <v>21</v>
       </c>
       <c r="H16">
-        <v>0.2385155102241681</v>
+        <v>0.1597882669539218</v>
       </c>
       <c r="I16">
-        <v>0.2510763892261053</v>
+        <v>0.1710619192432797</v>
       </c>
       <c r="J16">
-        <v>0.09296012347650381</v>
+        <v>0.04575244488811785</v>
       </c>
       <c r="K16">
-        <v>0.3266319475936343</v>
+        <v>0.2163045390791595</v>
       </c>
       <c r="L16">
         <v>10000</v>
       </c>
       <c r="M16">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N16">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1218,34 +1218,34 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F17">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G17" t="s">
         <v>22</v>
       </c>
       <c r="H17">
-        <v>0.4862537845484727</v>
+        <v>0.371428882520539</v>
       </c>
       <c r="I17">
-        <v>0.4627097144307064</v>
+        <v>0.3552840168458432</v>
       </c>
       <c r="J17">
-        <v>0.2522768460411423</v>
+        <v>0.2033811769728956</v>
       </c>
       <c r="K17">
-        <v>0.8450653109883579</v>
+        <v>0.6369400047260438</v>
       </c>
       <c r="L17">
         <v>10000</v>
       </c>
       <c r="M17">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N17">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1262,34 +1262,34 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F18">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G18" t="s">
         <v>23</v>
       </c>
       <c r="H18">
-        <v>0.7695858993619877</v>
+        <v>0.6024637152368141</v>
       </c>
       <c r="I18">
-        <v>0.737886095943088</v>
+        <v>0.5720205696677607</v>
       </c>
       <c r="J18">
-        <v>0.4147305695613956</v>
+        <v>0.3355923419414195</v>
       </c>
       <c r="K18">
-        <v>1.339398970624536</v>
+        <v>1.00786490518904</v>
       </c>
       <c r="L18">
         <v>10000</v>
       </c>
       <c r="M18">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N18">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1306,34 +1306,34 @@
         <v>31</v>
       </c>
       <c r="E19">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F19">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G19" t="s">
         <v>24</v>
       </c>
       <c r="H19">
-        <v>20632.0234972507</v>
+        <v>18288.65270180052</v>
       </c>
       <c r="I19">
-        <v>19624.16171936609</v>
+        <v>16475.32974074528</v>
       </c>
       <c r="J19">
-        <v>11240.00494423015</v>
+        <v>15407.81356696678</v>
       </c>
       <c r="K19">
-        <v>35423.21875744113</v>
+        <v>24968.6613437725</v>
       </c>
       <c r="L19">
         <v>10000</v>
       </c>
       <c r="M19">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N19">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1350,34 +1350,34 @@
         <v>31</v>
       </c>
       <c r="E20">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F20">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
       </c>
       <c r="H20">
-        <v>0.6322156806957537</v>
+        <v>0.6184533686771578</v>
       </c>
       <c r="I20">
-        <v>0.628653918270157</v>
+        <v>0.6128775818947233</v>
       </c>
       <c r="J20">
-        <v>0.5178750689677436</v>
+        <v>0.5156585588346636</v>
       </c>
       <c r="K20">
-        <v>0.760187266599088</v>
+        <v>0.73546962025639</v>
       </c>
       <c r="L20">
         <v>10000</v>
       </c>
       <c r="M20">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N20">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1394,34 +1394,34 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F21">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G21" t="s">
         <v>26</v>
       </c>
       <c r="H21">
-        <v>1868.604676803568</v>
+        <v>1167.168057719447</v>
       </c>
       <c r="I21">
-        <v>1895.789243182264</v>
+        <v>1219.736609997561</v>
       </c>
       <c r="J21">
-        <v>1591.736666665113</v>
+        <v>924.295667998769</v>
       </c>
       <c r="K21">
-        <v>2048.019297247105</v>
+        <v>1289.286137042821</v>
       </c>
       <c r="L21">
         <v>10000</v>
       </c>
       <c r="M21">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N21">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1438,34 +1438,34 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F22">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
       </c>
       <c r="H22">
-        <v>1625.303869778853</v>
+        <v>863.9199030514256</v>
       </c>
       <c r="I22">
-        <v>1598.595326187425</v>
+        <v>858.085798910578</v>
       </c>
       <c r="J22">
-        <v>450.8581167767194</v>
+        <v>208.6328685739466</v>
       </c>
       <c r="K22">
-        <v>3032.428832724088</v>
+        <v>1476.218324107248</v>
       </c>
       <c r="L22">
         <v>10000</v>
       </c>
       <c r="M22">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N22">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1482,34 +1482,34 @@
         <v>31</v>
       </c>
       <c r="E23">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F23">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
       </c>
       <c r="H23">
-        <v>0.2875611020494008</v>
+        <v>0.2327514245064237</v>
       </c>
       <c r="I23">
-        <v>0.2817648784865671</v>
+        <v>0.2282594411339312</v>
       </c>
       <c r="J23">
-        <v>0.1707117754834451</v>
+        <v>0.1387754704210908</v>
       </c>
       <c r="K23">
-        <v>0.4392095764726186</v>
+        <v>0.3571369024241726</v>
       </c>
       <c r="L23">
         <v>10000</v>
       </c>
       <c r="M23">
-        <v>3249</v>
+        <v>115</v>
       </c>
       <c r="N23">
-        <v>32.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1526,34 +1526,34 @@
         <v>34</v>
       </c>
       <c r="E24">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F24">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G24" t="s">
         <v>18</v>
       </c>
       <c r="H24">
-        <v>5893.443591752249</v>
+        <v>4448.730475515813</v>
       </c>
       <c r="I24">
-        <v>5755.381554336515</v>
+        <v>4337.012355751161</v>
       </c>
       <c r="J24">
-        <v>4048.94361802125</v>
+        <v>3373.554870253595</v>
       </c>
       <c r="K24">
-        <v>8390.122811848511</v>
+        <v>6152.912879972838</v>
       </c>
       <c r="L24">
         <v>10000</v>
       </c>
       <c r="M24">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N24">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1570,34 +1570,34 @@
         <v>34</v>
       </c>
       <c r="E25">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F25">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G25" t="s">
         <v>19</v>
       </c>
       <c r="H25">
-        <v>0.3396360904608955</v>
+        <v>0.2639304522090719</v>
       </c>
       <c r="I25">
-        <v>0.3342460186669713</v>
+        <v>0.2694238109048769</v>
       </c>
       <c r="J25">
-        <v>0.1841406512216404</v>
+        <v>0.1434030064276269</v>
       </c>
       <c r="K25">
-        <v>0.5278358389432465</v>
+        <v>0.3751782406619254</v>
       </c>
       <c r="L25">
         <v>10000</v>
       </c>
       <c r="M25">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N25">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1614,34 +1614,34 @@
         <v>34</v>
       </c>
       <c r="E26">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F26">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G26" t="s">
         <v>20</v>
       </c>
       <c r="H26">
-        <v>4503.103609244233</v>
+        <v>2996.468554985752</v>
       </c>
       <c r="I26">
-        <v>4389.611713530116</v>
+        <v>3007.107452112871</v>
       </c>
       <c r="J26">
-        <v>1514.118035357716</v>
+        <v>1639.365617405928</v>
       </c>
       <c r="K26">
-        <v>8821.588159531304</v>
+        <v>4571.939199093361</v>
       </c>
       <c r="L26">
         <v>10000</v>
       </c>
       <c r="M26">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N26">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1658,34 +1658,34 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F27">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G27" t="s">
         <v>21</v>
       </c>
       <c r="H27">
-        <v>0.2443333839574841</v>
+        <v>0.1729339019319249</v>
       </c>
       <c r="I27">
-        <v>0.2609450233952527</v>
+        <v>0.1813852985827583</v>
       </c>
       <c r="J27">
-        <v>0.1015341118276341</v>
+        <v>0.09965441008171005</v>
       </c>
       <c r="K27">
-        <v>0.3271664907747484</v>
+        <v>0.2177286425064219</v>
       </c>
       <c r="L27">
         <v>10000</v>
       </c>
       <c r="M27">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N27">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1702,34 +1702,34 @@
         <v>34</v>
       </c>
       <c r="E28">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F28">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G28" t="s">
         <v>22</v>
       </c>
       <c r="H28">
-        <v>0.7008379134215857</v>
+        <v>0.5370866752874162</v>
       </c>
       <c r="I28">
-        <v>0.6712549827283477</v>
+        <v>0.5110296372748272</v>
       </c>
       <c r="J28">
-        <v>0.369023329329594</v>
+        <v>0.333837600347085</v>
       </c>
       <c r="K28">
-        <v>1.216665995544531</v>
+        <v>0.8457945580148432</v>
       </c>
       <c r="L28">
         <v>10000</v>
       </c>
       <c r="M28">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N28">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1746,34 +1746,34 @@
         <v>34</v>
       </c>
       <c r="E29">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F29">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G29" t="s">
         <v>23</v>
       </c>
       <c r="H29">
-        <v>0.7632632572216379</v>
+        <v>0.5923381665306631</v>
       </c>
       <c r="I29">
-        <v>0.7333509663462897</v>
+        <v>0.5820136656237154</v>
       </c>
       <c r="J29">
-        <v>0.4109876522697704</v>
+        <v>0.3809661703789883</v>
       </c>
       <c r="K29">
-        <v>1.301580717875003</v>
+        <v>0.9355853742628736</v>
       </c>
       <c r="L29">
         <v>10000</v>
       </c>
       <c r="M29">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N29">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1790,34 +1790,34 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F30">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G30" t="s">
         <v>24</v>
       </c>
       <c r="H30">
-        <v>18408.48450556907</v>
+        <v>17399.08605933471</v>
       </c>
       <c r="I30">
-        <v>16716.84702912801</v>
+        <v>16482.84017912596</v>
       </c>
       <c r="J30">
-        <v>11034.2705663367</v>
+        <v>11345.08500882819</v>
       </c>
       <c r="K30">
-        <v>31303.94091843505</v>
+        <v>24858.91455894988</v>
       </c>
       <c r="L30">
         <v>10000</v>
       </c>
       <c r="M30">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N30">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1834,34 +1834,34 @@
         <v>34</v>
       </c>
       <c r="E31">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F31">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
       </c>
       <c r="H31">
-        <v>0.918742471602786</v>
+        <v>0.906761597260057</v>
       </c>
       <c r="I31">
-        <v>0.9160666375802393</v>
+        <v>0.8836062987506794</v>
       </c>
       <c r="J31">
-        <v>0.7558949637840644</v>
+        <v>0.7373460101067425</v>
       </c>
       <c r="K31">
-        <v>1.102514873452978</v>
+        <v>1.091478094670771</v>
       </c>
       <c r="L31">
         <v>10000</v>
       </c>
       <c r="M31">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N31">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1878,34 +1878,34 @@
         <v>34</v>
       </c>
       <c r="E32">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F32">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G32" t="s">
         <v>26</v>
       </c>
       <c r="H32">
-        <v>1927.711138870569</v>
+        <v>1209.485407347333</v>
       </c>
       <c r="I32">
-        <v>1942.305860762551</v>
+        <v>1235.430765168215</v>
       </c>
       <c r="J32">
-        <v>1664.402623716546</v>
+        <v>927.4123239372808</v>
       </c>
       <c r="K32">
-        <v>2062.562932055133</v>
+        <v>1415.438084810834</v>
       </c>
       <c r="L32">
         <v>10000</v>
       </c>
       <c r="M32">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N32">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -1922,34 +1922,34 @@
         <v>34</v>
       </c>
       <c r="E33">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F33">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
       </c>
       <c r="H33">
-        <v>1804.920074249158</v>
+        <v>1096.658314596064</v>
       </c>
       <c r="I33">
-        <v>1776.326681679121</v>
+        <v>1063.108043897339</v>
       </c>
       <c r="J33">
-        <v>546.1093245174292</v>
+        <v>489.4366266641941</v>
       </c>
       <c r="K33">
-        <v>3307.313934893351</v>
+        <v>1716.545379218534</v>
       </c>
       <c r="L33">
         <v>10000</v>
       </c>
       <c r="M33">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N33">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -1966,34 +1966,34 @@
         <v>34</v>
       </c>
       <c r="E34">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F34">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
       </c>
       <c r="H34">
-        <v>0.3401472568754397</v>
+        <v>0.280323525182157</v>
       </c>
       <c r="I34">
-        <v>0.3368890479134046</v>
+        <v>0.2753756840774544</v>
       </c>
       <c r="J34">
-        <v>0.2117563311614438</v>
+        <v>0.1961359168539397</v>
       </c>
       <c r="K34">
-        <v>0.4995335908860587</v>
+        <v>0.3945798813732628</v>
       </c>
       <c r="L34">
         <v>10000</v>
       </c>
       <c r="M34">
-        <v>2763</v>
+        <v>54</v>
       </c>
       <c r="N34">
-        <v>27.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2010,34 +2010,34 @@
         <v>17</v>
       </c>
       <c r="E35">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F35">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G35" t="s">
         <v>18</v>
       </c>
       <c r="H35">
-        <v>7610.37730785589</v>
+        <v>5146.301517269711</v>
       </c>
       <c r="I35">
-        <v>7291.874021410215</v>
+        <v>5066.218785750006</v>
       </c>
       <c r="J35">
-        <v>4810.942927549529</v>
+        <v>3412.862153955652</v>
       </c>
       <c r="K35">
-        <v>12367.12500384991</v>
+        <v>7493.510261011851</v>
       </c>
       <c r="L35">
         <v>10000</v>
       </c>
       <c r="M35">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N35">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2054,34 +2054,34 @@
         <v>17</v>
       </c>
       <c r="E36">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F36">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
       </c>
       <c r="H36">
-        <v>0.3816238793288186</v>
+        <v>0.2897970200677478</v>
       </c>
       <c r="I36">
-        <v>0.3800931576964695</v>
+        <v>0.2857125444532465</v>
       </c>
       <c r="J36">
-        <v>0.2095698631893219</v>
+        <v>0.1672926579460295</v>
       </c>
       <c r="K36">
-        <v>0.5645934765456592</v>
+        <v>0.4385402045638412</v>
       </c>
       <c r="L36">
         <v>10000</v>
       </c>
       <c r="M36">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N36">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2098,34 +2098,34 @@
         <v>17</v>
       </c>
       <c r="E37">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F37">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G37" t="s">
         <v>20</v>
       </c>
       <c r="H37">
-        <v>9892.582807878995</v>
+        <v>5553.446994920153</v>
       </c>
       <c r="I37">
-        <v>8449.866283028194</v>
+        <v>5561.718850403601</v>
       </c>
       <c r="J37">
-        <v>2551.278747610037</v>
+        <v>1834.860491623026</v>
       </c>
       <c r="K37">
-        <v>25564.45104349557</v>
+        <v>9073.884305107478</v>
       </c>
       <c r="L37">
         <v>10000</v>
       </c>
       <c r="M37">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N37">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2142,34 +2142,34 @@
         <v>17</v>
       </c>
       <c r="E38">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F38">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G38" t="s">
         <v>21</v>
       </c>
       <c r="H38">
-        <v>0.4571403694972818</v>
+        <v>0.3046776975329215</v>
       </c>
       <c r="I38">
-        <v>0.4684281231446773</v>
+        <v>0.3253303116207721</v>
       </c>
       <c r="J38">
-        <v>0.1417678231670771</v>
+        <v>0.1100741864031718</v>
       </c>
       <c r="K38">
-        <v>0.6779177612920511</v>
+        <v>0.3874360127669505</v>
       </c>
       <c r="L38">
         <v>10000</v>
       </c>
       <c r="M38">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N38">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2186,34 +2186,34 @@
         <v>17</v>
       </c>
       <c r="E39">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F39">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G39" t="s">
         <v>22</v>
       </c>
       <c r="H39">
-        <v>0.4977392341847165</v>
+        <v>0.390495452547848</v>
       </c>
       <c r="I39">
-        <v>0.4762896216718509</v>
+        <v>0.3662321641931228</v>
       </c>
       <c r="J39">
-        <v>0.2589714707227211</v>
+        <v>0.2051869093247297</v>
       </c>
       <c r="K39">
-        <v>0.8536048747852437</v>
+        <v>0.7181311386784262</v>
       </c>
       <c r="L39">
         <v>10000</v>
       </c>
       <c r="M39">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N39">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2230,34 +2230,34 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F40">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G40" t="s">
         <v>23</v>
       </c>
       <c r="H40">
-        <v>0.8088842013808689</v>
+        <v>0.6520792677914767</v>
       </c>
       <c r="I40">
-        <v>0.7782626883450782</v>
+        <v>0.6163230003966962</v>
       </c>
       <c r="J40">
-        <v>0.4412308502920272</v>
+        <v>0.3558090785101568</v>
       </c>
       <c r="K40">
-        <v>1.356194402609433</v>
+        <v>1.159356348806237</v>
       </c>
       <c r="L40">
         <v>10000</v>
       </c>
       <c r="M40">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N40">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2274,34 +2274,34 @@
         <v>17</v>
       </c>
       <c r="E41">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F41">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
       </c>
       <c r="H41">
-        <v>21311.41424419187</v>
+        <v>18313.43531825173</v>
       </c>
       <c r="I41">
-        <v>19360.56796002976</v>
+        <v>16507.43454731859</v>
       </c>
       <c r="J41">
-        <v>11207.81992764562</v>
+        <v>11333.21783274092</v>
       </c>
       <c r="K41">
-        <v>43664.14939934251</v>
+        <v>26364.38208518607</v>
       </c>
       <c r="L41">
         <v>10000</v>
       </c>
       <c r="M41">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N41">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2318,34 +2318,34 @@
         <v>17</v>
       </c>
       <c r="E42">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F42">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
       </c>
       <c r="H42">
-        <v>0.6159442011324295</v>
+        <v>0.5999424218221453</v>
       </c>
       <c r="I42">
-        <v>0.6125153078059598</v>
+        <v>0.5990827412102351</v>
       </c>
       <c r="J42">
-        <v>0.5063136501188865</v>
+        <v>0.4906986597821065</v>
       </c>
       <c r="K42">
-        <v>0.7427853005592198</v>
+        <v>0.7221043264381691</v>
       </c>
       <c r="L42">
         <v>10000</v>
       </c>
       <c r="M42">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N42">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2362,34 +2362,34 @@
         <v>17</v>
       </c>
       <c r="E43">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F43">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G43" t="s">
         <v>26</v>
       </c>
       <c r="H43">
-        <v>2138.898681807297</v>
+        <v>1199.215377736005</v>
       </c>
       <c r="I43">
-        <v>2081.936303982277</v>
+        <v>1230.762347646194</v>
       </c>
       <c r="J43">
-        <v>1694.109791338248</v>
+        <v>955.6205134377254</v>
       </c>
       <c r="K43">
-        <v>2903.196461211689</v>
+        <v>1418.617182715296</v>
       </c>
       <c r="L43">
         <v>10000</v>
       </c>
       <c r="M43">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N43">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2406,34 +2406,34 @@
         <v>17</v>
       </c>
       <c r="E44">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F44">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G44" t="s">
         <v>27</v>
       </c>
       <c r="H44">
-        <v>3200.841137560309</v>
+        <v>1602.338676702599</v>
       </c>
       <c r="I44">
-        <v>2903.297318862472</v>
+        <v>1593.401757251763</v>
       </c>
       <c r="J44">
-        <v>804.005251216362</v>
+        <v>523.6804674227483</v>
       </c>
       <c r="K44">
-        <v>7462.878096535278</v>
+        <v>2729.727700433165</v>
       </c>
       <c r="L44">
         <v>10000</v>
       </c>
       <c r="M44">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N44">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -2450,34 +2450,34 @@
         <v>17</v>
       </c>
       <c r="E45">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F45">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G45" t="s">
         <v>28</v>
       </c>
       <c r="H45">
-        <v>0.2951475547960126</v>
+        <v>0.2442264101990657</v>
       </c>
       <c r="I45">
-        <v>0.2900649390371017</v>
+        <v>0.2357443684425088</v>
       </c>
       <c r="J45">
-        <v>0.1757115992870882</v>
+        <v>0.1430116386691411</v>
       </c>
       <c r="K45">
-        <v>0.4433139150968769</v>
+        <v>0.390779328343116</v>
       </c>
       <c r="L45">
         <v>10000</v>
       </c>
       <c r="M45">
-        <v>6466</v>
+        <v>521</v>
       </c>
       <c r="N45">
-        <v>64.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -2494,34 +2494,34 @@
         <v>31</v>
       </c>
       <c r="E46">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F46">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G46" t="s">
         <v>18</v>
       </c>
       <c r="H46">
-        <v>7471.973144650821</v>
+        <v>5052.184947845846</v>
       </c>
       <c r="I46">
-        <v>7104.502807630501</v>
+        <v>4946.375883096614</v>
       </c>
       <c r="J46">
-        <v>4735.209224120008</v>
+        <v>3191.863213037029</v>
       </c>
       <c r="K46">
-        <v>12159.7913609249</v>
+        <v>7610.226150922945</v>
       </c>
       <c r="L46">
         <v>10000</v>
       </c>
       <c r="M46">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N46">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2538,34 +2538,34 @@
         <v>31</v>
       </c>
       <c r="E47">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F47">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G47" t="s">
         <v>19</v>
       </c>
       <c r="H47">
-        <v>0.3808846895423443</v>
+        <v>0.2865358614509541</v>
       </c>
       <c r="I47">
-        <v>0.3784359257932898</v>
+        <v>0.2839595659720223</v>
       </c>
       <c r="J47">
-        <v>0.2109291149666363</v>
+        <v>0.1519309688202965</v>
       </c>
       <c r="K47">
-        <v>0.560114750166009</v>
+        <v>0.4518422183362643</v>
       </c>
       <c r="L47">
         <v>10000</v>
       </c>
       <c r="M47">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N47">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2582,34 +2582,34 @@
         <v>31</v>
       </c>
       <c r="E48">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F48">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>
       </c>
       <c r="H48">
-        <v>9710.974409125591</v>
+        <v>5481.676065877481</v>
       </c>
       <c r="I48">
-        <v>8282.776117114936</v>
+        <v>5620.222607830538</v>
       </c>
       <c r="J48">
-        <v>2509.100002356193</v>
+        <v>1934.401971010071</v>
       </c>
       <c r="K48">
-        <v>25125.75031127258</v>
+        <v>8918.734440675133</v>
       </c>
       <c r="L48">
         <v>10000</v>
       </c>
       <c r="M48">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N48">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2626,34 +2626,34 @@
         <v>31</v>
       </c>
       <c r="E49">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F49">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G49" t="s">
         <v>21</v>
       </c>
       <c r="H49">
-        <v>0.456535700319403</v>
+        <v>0.3019381923795668</v>
       </c>
       <c r="I49">
-        <v>0.4681192171407856</v>
+        <v>0.3223990489633294</v>
       </c>
       <c r="J49">
-        <v>0.1433466142211333</v>
+        <v>0.1179810717329529</v>
       </c>
       <c r="K49">
-        <v>0.6790782539696146</v>
+        <v>0.3875476745699803</v>
       </c>
       <c r="L49">
         <v>10000</v>
       </c>
       <c r="M49">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N49">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2670,34 +2670,34 @@
         <v>31</v>
       </c>
       <c r="E50">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F50">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G50" t="s">
         <v>22</v>
       </c>
       <c r="H50">
-        <v>0.5163828256285241</v>
+        <v>0.4075100073040576</v>
       </c>
       <c r="I50">
-        <v>0.4958710163764282</v>
+        <v>0.383050093915798</v>
       </c>
       <c r="J50">
-        <v>0.2666530562247153</v>
+        <v>0.2164807480727969</v>
       </c>
       <c r="K50">
-        <v>0.8997273211091852</v>
+        <v>0.7499051735644949</v>
       </c>
       <c r="L50">
         <v>10000</v>
       </c>
       <c r="M50">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N50">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2714,34 +2714,34 @@
         <v>31</v>
       </c>
       <c r="E51">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F51">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G51" t="s">
         <v>23</v>
       </c>
       <c r="H51">
-        <v>0.81417801241344</v>
+        <v>0.6554249164012934</v>
       </c>
       <c r="I51">
-        <v>0.7859388364019604</v>
+        <v>0.6273758128275378</v>
       </c>
       <c r="J51">
-        <v>0.4327437485655343</v>
+        <v>0.3630594393735882</v>
       </c>
       <c r="K51">
-        <v>1.376750765621922</v>
+        <v>1.143353312173139</v>
       </c>
       <c r="L51">
         <v>10000</v>
       </c>
       <c r="M51">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N51">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -2758,34 +2758,34 @@
         <v>31</v>
       </c>
       <c r="E52">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F52">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G52" t="s">
         <v>24</v>
       </c>
       <c r="H52">
-        <v>20960.22856124816</v>
+        <v>18137.9830412052</v>
       </c>
       <c r="I52">
-        <v>18961.09958559078</v>
+        <v>16512.40818680304</v>
       </c>
       <c r="J52">
-        <v>11084.31099893811</v>
+        <v>14528.96139976323</v>
       </c>
       <c r="K52">
-        <v>42998.24188958864</v>
+        <v>25701.67687822429</v>
       </c>
       <c r="L52">
         <v>10000</v>
       </c>
       <c r="M52">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N52">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -2802,34 +2802,34 @@
         <v>31</v>
       </c>
       <c r="E53">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F53">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
       </c>
       <c r="H53">
-        <v>0.6343690860205273</v>
+        <v>0.6228009363675154</v>
       </c>
       <c r="I53">
-        <v>0.6325789302975318</v>
+        <v>0.6211527322930713</v>
       </c>
       <c r="J53">
-        <v>0.5195885042736827</v>
+        <v>0.5081665567821957</v>
       </c>
       <c r="K53">
-        <v>0.7636971447794727</v>
+        <v>0.7505440790875054</v>
       </c>
       <c r="L53">
         <v>10000</v>
       </c>
       <c r="M53">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N53">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -2846,34 +2846,34 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F54">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G54" t="s">
         <v>26</v>
       </c>
       <c r="H54">
-        <v>2140.938614979218</v>
+        <v>1206.105141498401</v>
       </c>
       <c r="I54">
-        <v>2083.956888765144</v>
+        <v>1234.048760229664</v>
       </c>
       <c r="J54">
-        <v>1714.14079801104</v>
+        <v>989.2641212387655</v>
       </c>
       <c r="K54">
-        <v>2910.003287357169</v>
+        <v>1356.389961688913</v>
       </c>
       <c r="L54">
         <v>10000</v>
       </c>
       <c r="M54">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N54">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -2890,34 +2890,34 @@
         <v>31</v>
       </c>
       <c r="E55">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F55">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G55" t="s">
         <v>27</v>
       </c>
       <c r="H55">
-        <v>3213.03526523518</v>
+        <v>1625.774057177855</v>
       </c>
       <c r="I55">
-        <v>2928.363248394772</v>
+        <v>1615.088444879076</v>
       </c>
       <c r="J55">
-        <v>796.3882447260494</v>
+        <v>512.2523647441722</v>
       </c>
       <c r="K55">
-        <v>7331.542297573339</v>
+        <v>2876.659227664862</v>
       </c>
       <c r="L55">
         <v>10000</v>
       </c>
       <c r="M55">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N55">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -2934,34 +2934,34 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F56">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G56" t="s">
         <v>28</v>
       </c>
       <c r="H56">
-        <v>0.3012728332166774</v>
+        <v>0.2504930265271847</v>
       </c>
       <c r="I56">
-        <v>0.2973914157443509</v>
+        <v>0.2413216812421217</v>
       </c>
       <c r="J56">
-        <v>0.1774047444448943</v>
+        <v>0.1467868489663078</v>
       </c>
       <c r="K56">
-        <v>0.4559728546431386</v>
+        <v>0.4048721227341551</v>
       </c>
       <c r="L56">
         <v>10000</v>
       </c>
       <c r="M56">
-        <v>6568</v>
+        <v>487</v>
       </c>
       <c r="N56">
-        <v>65.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -2978,34 +2978,34 @@
         <v>34</v>
       </c>
       <c r="E57">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F57">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G57" t="s">
         <v>18</v>
       </c>
       <c r="H57">
-        <v>6436.349498406952</v>
+        <v>4239.536427969095</v>
       </c>
       <c r="I57">
-        <v>6173.073380671945</v>
+        <v>4113.026757946881</v>
       </c>
       <c r="J57">
-        <v>4276.489739668139</v>
+        <v>2833.521148779479</v>
       </c>
       <c r="K57">
-        <v>10272.19746473855</v>
+        <v>6326.019450862614</v>
       </c>
       <c r="L57">
         <v>10000</v>
       </c>
       <c r="M57">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N57">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3022,34 +3022,34 @@
         <v>34</v>
       </c>
       <c r="E58">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F58">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G58" t="s">
         <v>19</v>
       </c>
       <c r="H58">
-        <v>0.3728488568098515</v>
+        <v>0.2610275410869637</v>
       </c>
       <c r="I58">
-        <v>0.372182908683152</v>
+        <v>0.2595910406206136</v>
       </c>
       <c r="J58">
-        <v>0.2070167414358267</v>
+        <v>0.1424876963499118</v>
       </c>
       <c r="K58">
-        <v>0.5446303872520492</v>
+        <v>0.3859712380424704</v>
       </c>
       <c r="L58">
         <v>10000</v>
       </c>
       <c r="M58">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N58">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3066,34 +3066,34 @@
         <v>34</v>
       </c>
       <c r="E59">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F59">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G59" t="s">
         <v>20</v>
       </c>
       <c r="H59">
-        <v>8679.656497215003</v>
+        <v>5317.057347299852</v>
       </c>
       <c r="I59">
-        <v>7401.277257666648</v>
+        <v>5464.780340052647</v>
       </c>
       <c r="J59">
-        <v>2614.104686008802</v>
+        <v>2654.061072645682</v>
       </c>
       <c r="K59">
-        <v>22000.61929458107</v>
+        <v>7683.562480673714</v>
       </c>
       <c r="L59">
         <v>10000</v>
       </c>
       <c r="M59">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N59">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3110,34 +3110,34 @@
         <v>34</v>
       </c>
       <c r="E60">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F60">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G60" t="s">
         <v>21</v>
       </c>
       <c r="H60">
-        <v>0.465143645444754</v>
+        <v>0.3192621617221762</v>
       </c>
       <c r="I60">
-        <v>0.4753267529951326</v>
+        <v>0.3356164157968514</v>
       </c>
       <c r="J60">
-        <v>0.1632419182440077</v>
+        <v>0.1629824194954343</v>
       </c>
       <c r="K60">
-        <v>0.6793660820639099</v>
+        <v>0.3871807171823665</v>
       </c>
       <c r="L60">
         <v>10000</v>
       </c>
       <c r="M60">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N60">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3154,34 +3154,34 @@
         <v>34</v>
       </c>
       <c r="E61">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F61">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G61" t="s">
         <v>22</v>
       </c>
       <c r="H61">
-        <v>0.735607516451122</v>
+        <v>0.6198690378601397</v>
       </c>
       <c r="I61">
-        <v>0.7059530250716693</v>
+        <v>0.5698205200095718</v>
       </c>
       <c r="J61">
-        <v>0.3850505380632616</v>
+        <v>0.3277989715875765</v>
       </c>
       <c r="K61">
-        <v>1.241679124117743</v>
+        <v>1.067432749704201</v>
       </c>
       <c r="L61">
         <v>10000</v>
       </c>
       <c r="M61">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N61">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3198,34 +3198,34 @@
         <v>34</v>
       </c>
       <c r="E62">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F62">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G62" t="s">
         <v>23</v>
       </c>
       <c r="H62">
-        <v>0.7979817741310794</v>
+        <v>0.6784681503862182</v>
       </c>
       <c r="I62">
-        <v>0.7701385229818893</v>
+        <v>0.6457363860020324</v>
       </c>
       <c r="J62">
-        <v>0.4349983433668077</v>
+        <v>0.384295969928253</v>
       </c>
       <c r="K62">
-        <v>1.328408921900517</v>
+        <v>1.141400569676865</v>
       </c>
       <c r="L62">
         <v>10000</v>
       </c>
       <c r="M62">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N62">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3242,34 +3242,34 @@
         <v>34</v>
       </c>
       <c r="E63">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F63">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
       </c>
       <c r="H63">
-        <v>18431.21101927727</v>
+        <v>16740.09901029121</v>
       </c>
       <c r="I63">
-        <v>16547.39477357359</v>
+        <v>16246.21617646637</v>
       </c>
       <c r="J63">
-        <v>10585.78423621155</v>
+        <v>11261.80330664593</v>
       </c>
       <c r="K63">
-        <v>38622.49753784318</v>
+        <v>24230.07024198031</v>
       </c>
       <c r="L63">
         <v>10000</v>
       </c>
       <c r="M63">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N63">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3286,34 +3286,34 @@
         <v>34</v>
       </c>
       <c r="E64">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F64">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
       </c>
       <c r="H64">
-        <v>0.9221424945899301</v>
+        <v>0.9130293668655419</v>
       </c>
       <c r="I64">
-        <v>0.9183894661221652</v>
+        <v>0.9153341824671215</v>
       </c>
       <c r="J64">
-        <v>0.7531280865001242</v>
+        <v>0.76118539346882</v>
       </c>
       <c r="K64">
-        <v>1.10630102990419</v>
+        <v>1.084720397297344</v>
       </c>
       <c r="L64">
         <v>10000</v>
       </c>
       <c r="M64">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N64">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3330,34 +3330,34 @@
         <v>34</v>
       </c>
       <c r="E65">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F65">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G65" t="s">
         <v>26</v>
       </c>
       <c r="H65">
-        <v>2176.489689006682</v>
+        <v>1261.279953660125</v>
       </c>
       <c r="I65">
-        <v>2108.079725610248</v>
+        <v>1264.321932736402</v>
       </c>
       <c r="J65">
-        <v>1833.898119798687</v>
+        <v>1044.136251910876</v>
       </c>
       <c r="K65">
-        <v>2941.97580699658</v>
+        <v>1434.005114283734</v>
       </c>
       <c r="L65">
         <v>10000</v>
       </c>
       <c r="M65">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N65">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3374,34 +3374,34 @@
         <v>34</v>
       </c>
       <c r="E66">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F66">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
       </c>
       <c r="H66">
-        <v>3443.177608054431</v>
+        <v>1996.720476635267</v>
       </c>
       <c r="I66">
-        <v>3136.850435255684</v>
+        <v>1965.073172120964</v>
       </c>
       <c r="J66">
-        <v>987.9102729839083</v>
+        <v>888.1463476487094</v>
       </c>
       <c r="K66">
-        <v>7914.105861736847</v>
+        <v>3218.922060513752</v>
       </c>
       <c r="L66">
         <v>10000</v>
       </c>
       <c r="M66">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N66">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3418,34 +3418,34 @@
         <v>34</v>
       </c>
       <c r="E67">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F67">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G67" t="s">
         <v>28</v>
       </c>
       <c r="H67">
-        <v>0.3521103141597761</v>
+        <v>0.3106900831986164</v>
       </c>
       <c r="I67">
-        <v>0.3485109688369391</v>
+        <v>0.3006977402850573</v>
       </c>
       <c r="J67">
-        <v>0.2196256864228085</v>
+        <v>0.1907744645684429</v>
       </c>
       <c r="K67">
-        <v>0.5013723404474962</v>
+        <v>0.4615611379407625</v>
       </c>
       <c r="L67">
         <v>10000</v>
       </c>
       <c r="M67">
-        <v>6007</v>
+        <v>250</v>
       </c>
       <c r="N67">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3471,25 +3471,25 @@
         <v>18</v>
       </c>
       <c r="H68">
-        <v>7715.169701993248</v>
+        <v>5105.223891190145</v>
       </c>
       <c r="I68">
-        <v>7359.874739157044</v>
+        <v>4984.102439961754</v>
       </c>
       <c r="J68">
-        <v>4841.297590600785</v>
+        <v>3332.133820926106</v>
       </c>
       <c r="K68">
-        <v>12736.66890207055</v>
+        <v>7585.337965032452</v>
       </c>
       <c r="L68">
         <v>10000</v>
       </c>
       <c r="M68">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N68">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3515,25 +3515,25 @@
         <v>19</v>
       </c>
       <c r="H69">
-        <v>0.3826032503288652</v>
+        <v>0.3125771296129386</v>
       </c>
       <c r="I69">
-        <v>0.3790287977255128</v>
+        <v>0.3133686193256984</v>
       </c>
       <c r="J69">
-        <v>0.2153424158123907</v>
+        <v>0.1818918580069056</v>
       </c>
       <c r="K69">
-        <v>0.560738613569841</v>
+        <v>0.435045221275533</v>
       </c>
       <c r="L69">
         <v>10000</v>
       </c>
       <c r="M69">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N69">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3559,25 +3559,25 @@
         <v>20</v>
       </c>
       <c r="H70">
-        <v>10520.19551236402</v>
+        <v>8883.518828287939</v>
       </c>
       <c r="I70">
-        <v>8857.29234003001</v>
+        <v>8236.329153489442</v>
       </c>
       <c r="J70">
-        <v>3855.639047191008</v>
+        <v>4870.885168995792</v>
       </c>
       <c r="K70">
-        <v>26977.24719569887</v>
+        <v>16860.64571226393</v>
       </c>
       <c r="L70">
         <v>10000</v>
       </c>
       <c r="M70">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N70">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -3603,25 +3603,25 @@
         <v>21</v>
       </c>
       <c r="H71">
-        <v>0.4788330187957447</v>
+        <v>0.530192463493086</v>
       </c>
       <c r="I71">
-        <v>0.4843871825962639</v>
+        <v>0.5414814609634093</v>
       </c>
       <c r="J71">
-        <v>0.2267707370118735</v>
+        <v>0.2882376039845221</v>
       </c>
       <c r="K71">
-        <v>0.6895221177652946</v>
+        <v>0.6924004008747366</v>
       </c>
       <c r="L71">
         <v>10000</v>
       </c>
       <c r="M71">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N71">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3647,25 +3647,25 @@
         <v>22</v>
       </c>
       <c r="H72">
-        <v>0.5006681779967327</v>
+        <v>0.4508821456229247</v>
       </c>
       <c r="I72">
-        <v>0.4787187156035503</v>
+        <v>0.4278740336490892</v>
       </c>
       <c r="J72">
-        <v>0.2585219112393521</v>
+        <v>0.2454793704156557</v>
       </c>
       <c r="K72">
-        <v>0.8575635511035055</v>
+        <v>0.7968754208542631</v>
       </c>
       <c r="L72">
         <v>10000</v>
       </c>
       <c r="M72">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N72">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3691,25 +3691,25 @@
         <v>23</v>
       </c>
       <c r="H73">
-        <v>0.8131628836587167</v>
+        <v>0.7365662546274462</v>
       </c>
       <c r="I73">
-        <v>0.7811139845471053</v>
+        <v>0.7015909593702885</v>
       </c>
       <c r="J73">
-        <v>0.4363175836155863</v>
+        <v>0.420060612402411</v>
       </c>
       <c r="K73">
-        <v>1.370247851240356</v>
+        <v>1.262206832746822</v>
       </c>
       <c r="L73">
         <v>10000</v>
       </c>
       <c r="M73">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N73">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -3735,25 +3735,25 @@
         <v>24</v>
       </c>
       <c r="H74">
-        <v>21570.84923969641</v>
+        <v>16817.48451283484</v>
       </c>
       <c r="I74">
-        <v>19458.27548677994</v>
+        <v>15784.43909937974</v>
       </c>
       <c r="J74">
-        <v>11162.7507940917</v>
+        <v>11597.194698218</v>
       </c>
       <c r="K74">
-        <v>45038.47267458051</v>
+        <v>28436.42741691112</v>
       </c>
       <c r="L74">
         <v>10000</v>
       </c>
       <c r="M74">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N74">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -3779,25 +3779,25 @@
         <v>25</v>
       </c>
       <c r="H75">
-        <v>0.6158840750847684</v>
+        <v>0.6121616642579185</v>
       </c>
       <c r="I75">
-        <v>0.6133484564198348</v>
+        <v>0.6100348263891545</v>
       </c>
       <c r="J75">
-        <v>0.5049725650368861</v>
+        <v>0.4994332720295949</v>
       </c>
       <c r="K75">
-        <v>0.7420970629077792</v>
+        <v>0.7390645335487384</v>
       </c>
       <c r="L75">
         <v>10000</v>
       </c>
       <c r="M75">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N75">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -3823,25 +3823,25 @@
         <v>26</v>
       </c>
       <c r="H76">
-        <v>2171.591458168994</v>
+        <v>1329.129666915102</v>
       </c>
       <c r="I76">
-        <v>2094.847121605158</v>
+        <v>1337.504959144467</v>
       </c>
       <c r="J76">
-        <v>1784.020288349707</v>
+        <v>1126.993719520127</v>
       </c>
       <c r="K76">
-        <v>2970.442093443431</v>
+        <v>1489.499044081904</v>
       </c>
       <c r="L76">
         <v>10000</v>
       </c>
       <c r="M76">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N76">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -3867,25 +3867,25 @@
         <v>27</v>
       </c>
       <c r="H77">
-        <v>3381.360003304857</v>
+        <v>2696.859705674707</v>
       </c>
       <c r="I77">
-        <v>3013.449006596783</v>
+        <v>2597.166543111541</v>
       </c>
       <c r="J77">
-        <v>1348.267657840906</v>
+        <v>1342.980940879893</v>
       </c>
       <c r="K77">
-        <v>7567.374986538958</v>
+        <v>4615.687562277196</v>
       </c>
       <c r="L77">
         <v>10000</v>
       </c>
       <c r="M77">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N77">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -3911,25 +3911,25 @@
         <v>28</v>
       </c>
       <c r="H78">
-        <v>0.2963828785680622</v>
+        <v>0.2731282835550133</v>
       </c>
       <c r="I78">
-        <v>0.2912535340850158</v>
+        <v>0.2665929505294257</v>
       </c>
       <c r="J78">
-        <v>0.1750445726580104</v>
+        <v>0.1678303180893879</v>
       </c>
       <c r="K78">
-        <v>0.4447822122824589</v>
+        <v>0.4245669076467379</v>
       </c>
       <c r="L78">
         <v>10000</v>
       </c>
       <c r="M78">
-        <v>8068</v>
+        <v>2960</v>
       </c>
       <c r="N78">
-        <v>80.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -3955,25 +3955,25 @@
         <v>18</v>
       </c>
       <c r="H79">
-        <v>7617.610087840506</v>
+        <v>5087.539162053265</v>
       </c>
       <c r="I79">
-        <v>7271.33379097295</v>
+        <v>4954.650305705647</v>
       </c>
       <c r="J79">
-        <v>4731.125541221625</v>
+        <v>3328.197445588636</v>
       </c>
       <c r="K79">
-        <v>12565.94652215587</v>
+        <v>7643.996834887543</v>
       </c>
       <c r="L79">
         <v>10000</v>
       </c>
       <c r="M79">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N79">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -3999,25 +3999,25 @@
         <v>19</v>
       </c>
       <c r="H80">
-        <v>0.3824581377063543</v>
+        <v>0.3134103156955088</v>
       </c>
       <c r="I80">
-        <v>0.3797055001223172</v>
+        <v>0.3155995818859589</v>
       </c>
       <c r="J80">
-        <v>0.2121402933003401</v>
+        <v>0.1818582520175294</v>
       </c>
       <c r="K80">
-        <v>0.5637062864446283</v>
+        <v>0.4333624867503785</v>
       </c>
       <c r="L80">
         <v>10000</v>
       </c>
       <c r="M80">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N80">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4043,25 +4043,25 @@
         <v>20</v>
       </c>
       <c r="H81">
-        <v>10397.88153553542</v>
+        <v>8887.225900085437</v>
       </c>
       <c r="I81">
-        <v>8717.78116326226</v>
+        <v>8193.967229376578</v>
       </c>
       <c r="J81">
-        <v>3796.847807991375</v>
+        <v>4728.906534426157</v>
       </c>
       <c r="K81">
-        <v>26103.57190613434</v>
+        <v>17325.31342409053</v>
       </c>
       <c r="L81">
         <v>10000</v>
       </c>
       <c r="M81">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N81">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4087,25 +4087,25 @@
         <v>21</v>
       </c>
       <c r="H82">
-        <v>0.4805033717306983</v>
+        <v>0.5318923624887593</v>
       </c>
       <c r="I82">
-        <v>0.4865272503340775</v>
+        <v>0.5433125135276939</v>
       </c>
       <c r="J82">
-        <v>0.2300712185340965</v>
+        <v>0.2857118920255624</v>
       </c>
       <c r="K82">
-        <v>0.6896080578592316</v>
+        <v>0.6917981101302446</v>
       </c>
       <c r="L82">
         <v>10000</v>
       </c>
       <c r="M82">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N82">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4131,25 +4131,25 @@
         <v>22</v>
       </c>
       <c r="H83">
-        <v>0.5152658720829023</v>
+        <v>0.4592762933288834</v>
       </c>
       <c r="I83">
-        <v>0.4904270606959902</v>
+        <v>0.4350646892957166</v>
       </c>
       <c r="J83">
-        <v>0.2663622945319104</v>
+        <v>0.2482784724206943</v>
       </c>
       <c r="K83">
-        <v>0.8941246793839006</v>
+        <v>0.7950053978909476</v>
       </c>
       <c r="L83">
         <v>10000</v>
       </c>
       <c r="M83">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N83">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4175,25 +4175,25 @@
         <v>23</v>
       </c>
       <c r="H84">
-        <v>0.8130786630421242</v>
+        <v>0.7300465244002557</v>
       </c>
       <c r="I84">
-        <v>0.7772142481864536</v>
+        <v>0.6964796164652723</v>
       </c>
       <c r="J84">
-        <v>0.4342778196604707</v>
+        <v>0.4079835613381123</v>
       </c>
       <c r="K84">
-        <v>1.381369701953175</v>
+        <v>1.257167163196501</v>
       </c>
       <c r="L84">
         <v>10000</v>
       </c>
       <c r="M84">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N84">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4219,25 +4219,25 @@
         <v>24</v>
       </c>
       <c r="H85">
-        <v>21286.22747955771</v>
+        <v>16747.08460585717</v>
       </c>
       <c r="I85">
-        <v>19105.73358884299</v>
+        <v>15657.07841216248</v>
       </c>
       <c r="J85">
-        <v>11090.44167276637</v>
+        <v>11618.98933259535</v>
       </c>
       <c r="K85">
-        <v>44146.47668851305</v>
+        <v>29009.22446984331</v>
       </c>
       <c r="L85">
         <v>10000</v>
       </c>
       <c r="M85">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N85">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4263,25 +4263,25 @@
         <v>25</v>
       </c>
       <c r="H86">
-        <v>0.6339380196559078</v>
+        <v>0.6293346351132351</v>
       </c>
       <c r="I86">
-        <v>0.6312466190914762</v>
+        <v>0.6261374986006787</v>
       </c>
       <c r="J86">
-        <v>0.5177515395725819</v>
+        <v>0.5180086432551931</v>
       </c>
       <c r="K86">
-        <v>0.7620679967176439</v>
+        <v>0.7568745318085679</v>
       </c>
       <c r="L86">
         <v>10000</v>
       </c>
       <c r="M86">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N86">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4307,25 +4307,25 @@
         <v>26</v>
       </c>
       <c r="H87">
-        <v>2173.571118993758</v>
+        <v>1333.828198679255</v>
       </c>
       <c r="I87">
-        <v>2097.498961788019</v>
+        <v>1341.845049930966</v>
       </c>
       <c r="J87">
-        <v>1790.030987130527</v>
+        <v>1146.180293470113</v>
       </c>
       <c r="K87">
-        <v>2965.937018363914</v>
+        <v>1494.179151500089</v>
       </c>
       <c r="L87">
         <v>10000</v>
       </c>
       <c r="M87">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N87">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -4351,25 +4351,25 @@
         <v>27</v>
       </c>
       <c r="H88">
-        <v>3396.33622959534</v>
+        <v>2714.540960276182</v>
       </c>
       <c r="I88">
-        <v>3019.826513019449</v>
+        <v>2613.904904721776</v>
       </c>
       <c r="J88">
-        <v>1365.377988906558</v>
+        <v>1383.73817843068</v>
       </c>
       <c r="K88">
-        <v>7710.647386843626</v>
+        <v>4802.877496338019</v>
       </c>
       <c r="L88">
         <v>10000</v>
       </c>
       <c r="M88">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N88">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -4395,25 +4395,25 @@
         <v>28</v>
       </c>
       <c r="H89">
-        <v>0.3007374132275055</v>
+        <v>0.2752900105707312</v>
       </c>
       <c r="I89">
-        <v>0.2948696270392088</v>
+        <v>0.2671378937822206</v>
       </c>
       <c r="J89">
-        <v>0.1777379653533954</v>
+        <v>0.1682572223370653</v>
       </c>
       <c r="K89">
-        <v>0.4526079208495183</v>
+        <v>0.4201545467830522</v>
       </c>
       <c r="L89">
         <v>10000</v>
       </c>
       <c r="M89">
-        <v>7987</v>
+        <v>2869</v>
       </c>
       <c r="N89">
-        <v>79.90000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -4439,25 +4439,25 @@
         <v>18</v>
       </c>
       <c r="H90">
-        <v>6498.548964701636</v>
+        <v>4324.514429002568</v>
       </c>
       <c r="I90">
-        <v>6223.451592648782</v>
+        <v>4209.179888794537</v>
       </c>
       <c r="J90">
-        <v>4227.385222546532</v>
+        <v>3011.660859137392</v>
       </c>
       <c r="K90">
-        <v>10416.40008954754</v>
+        <v>6253.85542012724</v>
       </c>
       <c r="L90">
         <v>10000</v>
       </c>
       <c r="M90">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N90">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -4483,25 +4483,25 @@
         <v>19</v>
       </c>
       <c r="H91">
-        <v>0.3741239579916703</v>
+        <v>0.2882569397055366</v>
       </c>
       <c r="I91">
-        <v>0.3748199439411724</v>
+        <v>0.2901579567325177</v>
       </c>
       <c r="J91">
-        <v>0.2065424819799263</v>
+        <v>0.1668297528939139</v>
       </c>
       <c r="K91">
-        <v>0.5434578308834137</v>
+        <v>0.4009647086115574</v>
       </c>
       <c r="L91">
         <v>10000</v>
       </c>
       <c r="M91">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N91">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4527,25 +4527,25 @@
         <v>20</v>
       </c>
       <c r="H92">
-        <v>9139.338084304343</v>
+        <v>8320.381801667561</v>
       </c>
       <c r="I92">
-        <v>7747.056093273128</v>
+        <v>7775.470135186582</v>
       </c>
       <c r="J92">
-        <v>3530.996891841321</v>
+        <v>4505.749071469641</v>
       </c>
       <c r="K92">
-        <v>23604.96227052747</v>
+        <v>15883.74914917328</v>
       </c>
       <c r="L92">
         <v>10000</v>
       </c>
       <c r="M92">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N92">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -4571,25 +4571,25 @@
         <v>21</v>
       </c>
       <c r="H93">
-        <v>0.4843580251896784</v>
+        <v>0.5392885060679456</v>
       </c>
       <c r="I93">
-        <v>0.4933085021232647</v>
+        <v>0.5519127819914973</v>
       </c>
       <c r="J93">
-        <v>0.2359000867389185</v>
+        <v>0.2932303935328783</v>
       </c>
       <c r="K93">
-        <v>0.6882625668387893</v>
+        <v>0.6932691257476057</v>
       </c>
       <c r="L93">
         <v>10000</v>
       </c>
       <c r="M93">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N93">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -4615,25 +4615,25 @@
         <v>22</v>
       </c>
       <c r="H94">
-        <v>0.7400635353075505</v>
+        <v>0.6662093968543099</v>
       </c>
       <c r="I94">
-        <v>0.7055672980949361</v>
+        <v>0.6355112951328425</v>
       </c>
       <c r="J94">
-        <v>0.3864020530102387</v>
+        <v>0.3590534894915375</v>
       </c>
       <c r="K94">
-        <v>1.285570522311478</v>
+        <v>1.128831957808042</v>
       </c>
       <c r="L94">
         <v>10000</v>
       </c>
       <c r="M94">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N94">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -4659,25 +4659,25 @@
         <v>23</v>
       </c>
       <c r="H95">
-        <v>0.8042013755708591</v>
+        <v>0.7278989084407841</v>
       </c>
       <c r="I95">
-        <v>0.7732155459830605</v>
+        <v>0.6963632237269186</v>
       </c>
       <c r="J95">
-        <v>0.4325244122623396</v>
+        <v>0.4077046837622124</v>
       </c>
       <c r="K95">
-        <v>1.37090111900191</v>
+        <v>1.212740790355934</v>
       </c>
       <c r="L95">
         <v>10000</v>
       </c>
       <c r="M95">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N95">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -4703,25 +4703,25 @@
         <v>24</v>
       </c>
       <c r="H96">
-        <v>18572.69912285846</v>
+        <v>15518.25032148387</v>
       </c>
       <c r="I96">
-        <v>16552.40455176227</v>
+        <v>14470.19510293851</v>
       </c>
       <c r="J96">
-        <v>10535.15812768512</v>
+        <v>11095.68874155052</v>
       </c>
       <c r="K96">
-        <v>39256.83420739126</v>
+        <v>26562.31194036832</v>
       </c>
       <c r="L96">
         <v>10000</v>
       </c>
       <c r="M96">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N96">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -4747,25 +4747,25 @@
         <v>25</v>
       </c>
       <c r="H97">
-        <v>0.9208490936732033</v>
+        <v>0.916623230651131</v>
       </c>
       <c r="I97">
-        <v>0.9167558037678601</v>
+        <v>0.9127846380947324</v>
       </c>
       <c r="J97">
-        <v>0.7519384803574555</v>
+        <v>0.7445019215589335</v>
       </c>
       <c r="K97">
-        <v>1.107346183402293</v>
+        <v>1.103797931897162</v>
       </c>
       <c r="L97">
         <v>10000</v>
       </c>
       <c r="M97">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N97">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -4791,25 +4791,25 @@
         <v>26</v>
       </c>
       <c r="H98">
-        <v>2203.754984029485</v>
+        <v>1364.844957536981</v>
       </c>
       <c r="I98">
-        <v>2120.447583356405</v>
+        <v>1374.828057787021</v>
       </c>
       <c r="J98">
-        <v>1880.603185148313</v>
+        <v>1182.429248769567</v>
       </c>
       <c r="K98">
-        <v>2994.916968518872</v>
+        <v>1506.738615495821</v>
       </c>
       <c r="L98">
         <v>10000</v>
       </c>
       <c r="M98">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N98">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -4835,25 +4835,25 @@
         <v>27</v>
       </c>
       <c r="H99">
-        <v>3618.261864144526</v>
+        <v>3078.653335778469</v>
       </c>
       <c r="I99">
-        <v>3248.66434571618</v>
+        <v>2954.494562827202</v>
       </c>
       <c r="J99">
-        <v>1480.10888308018</v>
+        <v>1669.194768476663</v>
       </c>
       <c r="K99">
-        <v>8230.320688207174</v>
+        <v>5063.798310333055</v>
       </c>
       <c r="L99">
         <v>10000</v>
       </c>
       <c r="M99">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N99">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -4879,25 +4879,25 @@
         <v>28</v>
       </c>
       <c r="H100">
-        <v>0.3536315988344439</v>
+        <v>0.3283451278010864</v>
       </c>
       <c r="I100">
-        <v>0.3486095351567502</v>
+        <v>0.3234534582699582</v>
       </c>
       <c r="J100">
-        <v>0.2198309488658072</v>
+        <v>0.2066462411495705</v>
       </c>
       <c r="K100">
-        <v>0.5114058892738599</v>
+        <v>0.4739289933541103</v>
       </c>
       <c r="L100">
         <v>10000</v>
       </c>
       <c r="M100">
-        <v>7486</v>
+        <v>2020</v>
       </c>
       <c r="N100">
-        <v>74.90000000000001</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -4923,25 +4923,25 @@
         <v>18</v>
       </c>
       <c r="H101">
-        <v>9169.107566441893</v>
+        <v>6276.085436859878</v>
       </c>
       <c r="I101">
-        <v>8010.659636974604</v>
+        <v>5435.162477751841</v>
       </c>
       <c r="J101">
-        <v>4907.440297844495</v>
+        <v>3452.583592702533</v>
       </c>
       <c r="K101">
-        <v>20379.36084326561</v>
+        <v>15913.58836446703</v>
       </c>
       <c r="L101">
         <v>10000</v>
       </c>
       <c r="M101">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N101">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -4967,25 +4967,25 @@
         <v>19</v>
       </c>
       <c r="H102">
-        <v>0.3928999232396022</v>
+        <v>0.3217530552686351</v>
       </c>
       <c r="I102">
-        <v>0.3905753193762926</v>
+        <v>0.3232066133233182</v>
       </c>
       <c r="J102">
-        <v>0.22261823562424</v>
+        <v>0.1952099288925556</v>
       </c>
       <c r="K102">
-        <v>0.5698139926563284</v>
+        <v>0.4457199431463122</v>
       </c>
       <c r="L102">
         <v>10000</v>
       </c>
       <c r="M102">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N102">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -5011,25 +5011,25 @@
         <v>20</v>
       </c>
       <c r="H103">
-        <v>14897.80511978525</v>
+        <v>14149.78156234763</v>
       </c>
       <c r="I103">
-        <v>11088.52147933903</v>
+        <v>10675.24020236886</v>
       </c>
       <c r="J103">
-        <v>2937.705065213941</v>
+        <v>4983.514413850215</v>
       </c>
       <c r="K103">
-        <v>46802.65753546935</v>
+        <v>49038.96841776693</v>
       </c>
       <c r="L103">
         <v>10000</v>
       </c>
       <c r="M103">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N103">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5055,25 +5055,25 @@
         <v>21</v>
       </c>
       <c r="H104">
-        <v>0.5671801959568448</v>
+        <v>0.668619600474831</v>
       </c>
       <c r="I104">
-        <v>0.5715349566038398</v>
+        <v>0.670254025343535</v>
       </c>
       <c r="J104">
-        <v>0.1647623294583323</v>
+        <v>0.2900664335421329</v>
       </c>
       <c r="K104">
-        <v>0.913348321756162</v>
+        <v>0.9747325211906257</v>
       </c>
       <c r="L104">
         <v>10000</v>
       </c>
       <c r="M104">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N104">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -5099,25 +5099,25 @@
         <v>22</v>
       </c>
       <c r="H105">
-        <v>0.506122787220727</v>
+        <v>0.4511338152843289</v>
       </c>
       <c r="I105">
-        <v>0.4850676886973555</v>
+        <v>0.4285468478498732</v>
       </c>
       <c r="J105">
-        <v>0.2643205540980222</v>
+        <v>0.2463406563922989</v>
       </c>
       <c r="K105">
-        <v>0.873526210552742</v>
+        <v>0.779705388225941</v>
       </c>
       <c r="L105">
         <v>10000</v>
       </c>
       <c r="M105">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N105">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5143,25 +5143,25 @@
         <v>23</v>
       </c>
       <c r="H106">
-        <v>0.8185314056496569</v>
+        <v>0.7381870022838298</v>
       </c>
       <c r="I106">
-        <v>0.7874383399348528</v>
+        <v>0.7051409363118597</v>
       </c>
       <c r="J106">
-        <v>0.439223433543524</v>
+        <v>0.4120791471856297</v>
       </c>
       <c r="K106">
-        <v>1.401482433961807</v>
+        <v>1.25278156198187</v>
       </c>
       <c r="L106">
         <v>10000</v>
       </c>
       <c r="M106">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N106">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -5187,25 +5187,25 @@
         <v>24</v>
       </c>
       <c r="H107">
-        <v>24492.9656339118</v>
+        <v>20061.52638955965</v>
       </c>
       <c r="I107">
-        <v>21271.85849147772</v>
+        <v>16458.9233927218</v>
       </c>
       <c r="J107">
-        <v>11370.68548225511</v>
+        <v>11780.37992053574</v>
       </c>
       <c r="K107">
-        <v>55743.24264141143</v>
+        <v>54384.00186167066</v>
       </c>
       <c r="L107">
         <v>10000</v>
       </c>
       <c r="M107">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N107">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -5231,25 +5231,25 @@
         <v>25</v>
       </c>
       <c r="H108">
-        <v>0.6184485857412246</v>
+        <v>0.6117019923701807</v>
       </c>
       <c r="I108">
-        <v>0.6161448017735023</v>
+        <v>0.609724155773082</v>
       </c>
       <c r="J108">
-        <v>0.5094914695322755</v>
+        <v>0.5057238512226268</v>
       </c>
       <c r="K108">
-        <v>0.7436723708625687</v>
+        <v>0.7374615834408035</v>
       </c>
       <c r="L108">
         <v>10000</v>
       </c>
       <c r="M108">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N108">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -5275,25 +5275,25 @@
         <v>26</v>
       </c>
       <c r="H109">
-        <v>2621.618129462448</v>
+        <v>1640.13808003679</v>
       </c>
       <c r="I109">
-        <v>2201.94916344533</v>
+        <v>1403.802879020193</v>
       </c>
       <c r="J109">
-        <v>1741.858674603995</v>
+        <v>1166.958912778817</v>
       </c>
       <c r="K109">
-        <v>5782.542181908672</v>
+        <v>4108.145522359886</v>
       </c>
       <c r="L109">
         <v>10000</v>
       </c>
       <c r="M109">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N109">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -5319,25 +5319,25 @@
         <v>27</v>
       </c>
       <c r="H110">
-        <v>4747.508633343231</v>
+        <v>4079.399470740932</v>
       </c>
       <c r="I110">
-        <v>3652.684965716137</v>
+        <v>3222.127809573373</v>
       </c>
       <c r="J110">
-        <v>967.8334061763619</v>
+        <v>1425.367982188336</v>
       </c>
       <c r="K110">
-        <v>14448.69672473076</v>
+        <v>13358.24600439414</v>
       </c>
       <c r="L110">
         <v>10000</v>
       </c>
       <c r="M110">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N110">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -5363,25 +5363,25 @@
         <v>28</v>
       </c>
       <c r="H111">
-        <v>0.2986238529362966</v>
+        <v>0.273470454505516</v>
       </c>
       <c r="I111">
-        <v>0.2937269643315786</v>
+        <v>0.2674820364042256</v>
       </c>
       <c r="J111">
-        <v>0.178390039117477</v>
+        <v>0.1664987432930145</v>
       </c>
       <c r="K111">
-        <v>0.4532128538887902</v>
+        <v>0.4206326229787161</v>
       </c>
       <c r="L111">
         <v>10000</v>
       </c>
       <c r="M111">
-        <v>6200</v>
+        <v>2743</v>
       </c>
       <c r="N111">
-        <v>62</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -5407,25 +5407,25 @@
         <v>18</v>
       </c>
       <c r="H112">
-        <v>8967.602587134334</v>
+        <v>6259.758900724717</v>
       </c>
       <c r="I112">
-        <v>7848.644165571045</v>
+        <v>5307.523982205499</v>
       </c>
       <c r="J112">
-        <v>4928.365725005853</v>
+        <v>3413.638983916297</v>
       </c>
       <c r="K112">
-        <v>19801.55890352991</v>
+        <v>17020.60507728027</v>
       </c>
       <c r="L112">
         <v>10000</v>
       </c>
       <c r="M112">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N112">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -5451,25 +5451,25 @@
         <v>19</v>
       </c>
       <c r="H113">
-        <v>0.3923489965473158</v>
+        <v>0.3190437830546323</v>
       </c>
       <c r="I113">
-        <v>0.3906637220926012</v>
+        <v>0.3211927448859715</v>
       </c>
       <c r="J113">
-        <v>0.220794907539745</v>
+        <v>0.1877956768091836</v>
       </c>
       <c r="K113">
-        <v>0.5645212427262323</v>
+        <v>0.4385633209314888</v>
       </c>
       <c r="L113">
         <v>10000</v>
       </c>
       <c r="M113">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N113">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5495,25 +5495,25 @@
         <v>20</v>
       </c>
       <c r="H114">
-        <v>14661.20267125724</v>
+        <v>14233.29642520092</v>
       </c>
       <c r="I114">
-        <v>10935.06751782134</v>
+        <v>10629.4001269845</v>
       </c>
       <c r="J114">
-        <v>2948.187846650611</v>
+        <v>4800.72070264654</v>
       </c>
       <c r="K114">
-        <v>46141.63156329931</v>
+        <v>52096.47995075984</v>
       </c>
       <c r="L114">
         <v>10000</v>
       </c>
       <c r="M114">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N114">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -5539,25 +5539,25 @@
         <v>21</v>
       </c>
       <c r="H115">
-        <v>0.5680735207956922</v>
+        <v>0.669046390538433</v>
       </c>
       <c r="I115">
-        <v>0.5740633985226012</v>
+        <v>0.6696418406105374</v>
       </c>
       <c r="J115">
-        <v>0.1694769031268535</v>
+        <v>0.2871429635100617</v>
       </c>
       <c r="K115">
-        <v>0.9091257855806415</v>
+        <v>0.9764794172945477</v>
       </c>
       <c r="L115">
         <v>10000</v>
       </c>
       <c r="M115">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N115">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -5583,25 +5583,25 @@
         <v>22</v>
       </c>
       <c r="H116">
-        <v>0.5217933556871494</v>
+        <v>0.4645899645988605</v>
       </c>
       <c r="I116">
-        <v>0.4998600691772305</v>
+        <v>0.4449336120190317</v>
       </c>
       <c r="J116">
-        <v>0.27515885143693</v>
+        <v>0.2459488527580963</v>
       </c>
       <c r="K116">
-        <v>0.8956500656515481</v>
+        <v>0.8000955383829554</v>
       </c>
       <c r="L116">
         <v>10000</v>
       </c>
       <c r="M116">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N116">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -5627,25 +5627,25 @@
         <v>23</v>
       </c>
       <c r="H117">
-        <v>0.8252772010029509</v>
+        <v>0.7386213663120654</v>
       </c>
       <c r="I117">
-        <v>0.7941316226577038</v>
+        <v>0.7069540323113723</v>
       </c>
       <c r="J117">
-        <v>0.4505485592025547</v>
+        <v>0.4102880305877671</v>
       </c>
       <c r="K117">
-        <v>1.386040573360363</v>
+        <v>1.237985311369908</v>
       </c>
       <c r="L117">
         <v>10000</v>
       </c>
       <c r="M117">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N117">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -5671,25 +5671,25 @@
         <v>24</v>
       </c>
       <c r="H118">
-        <v>24092.45536345959</v>
+        <v>20119.96365709514</v>
       </c>
       <c r="I118">
-        <v>20835.86923112183</v>
+        <v>16444.75675033507</v>
       </c>
       <c r="J118">
-        <v>11198.8144137283</v>
+        <v>11803.17808796339</v>
       </c>
       <c r="K118">
-        <v>55647.62153731555</v>
+        <v>56030.13229341226</v>
       </c>
       <c r="L118">
         <v>10000</v>
       </c>
       <c r="M118">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N118">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -5715,25 +5715,25 @@
         <v>25</v>
       </c>
       <c r="H119">
-        <v>0.6327379622230509</v>
+        <v>0.6293114947549534</v>
       </c>
       <c r="I119">
-        <v>0.6306091632636485</v>
+        <v>0.6263543429136408</v>
       </c>
       <c r="J119">
-        <v>0.5185855678068219</v>
+        <v>0.5177959366998385</v>
       </c>
       <c r="K119">
-        <v>0.7603060150615129</v>
+        <v>0.7608716854225089</v>
       </c>
       <c r="L119">
         <v>10000</v>
       </c>
       <c r="M119">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N119">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -5759,25 +5759,25 @@
         <v>26</v>
       </c>
       <c r="H120">
-        <v>2616.182818123052</v>
+        <v>1660.04519449041</v>
       </c>
       <c r="I120">
-        <v>2207.351582742057</v>
+        <v>1405.775491658624</v>
       </c>
       <c r="J120">
-        <v>1756.900334388553</v>
+        <v>1165.384938051262</v>
       </c>
       <c r="K120">
-        <v>5645.26797344752</v>
+        <v>4174.315778247571</v>
       </c>
       <c r="L120">
         <v>10000</v>
       </c>
       <c r="M120">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N120">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -5803,25 +5803,25 @@
         <v>27</v>
       </c>
       <c r="H121">
-        <v>4779.29216172731</v>
+        <v>4162.856426954902</v>
       </c>
       <c r="I121">
-        <v>3700.95177750612</v>
+        <v>3253.728120687998</v>
       </c>
       <c r="J121">
-        <v>1021.80718418917</v>
+        <v>1411.82450485548</v>
       </c>
       <c r="K121">
-        <v>14563.69002601231</v>
+        <v>13817.25374470582</v>
       </c>
       <c r="L121">
         <v>10000</v>
       </c>
       <c r="M121">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N121">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -5847,25 +5847,25 @@
         <v>28</v>
       </c>
       <c r="H122">
-        <v>0.3042607602263876</v>
+        <v>0.2778675672767797</v>
       </c>
       <c r="I122">
-        <v>0.2996219106527815</v>
+        <v>0.272906853062263</v>
       </c>
       <c r="J122">
-        <v>0.1829624481818056</v>
+        <v>0.1667850562736857</v>
       </c>
       <c r="K122">
-        <v>0.4516017297408405</v>
+        <v>0.4218378901542542</v>
       </c>
       <c r="L122">
         <v>10000</v>
       </c>
       <c r="M122">
-        <v>6165</v>
+        <v>2759</v>
       </c>
       <c r="N122">
-        <v>61.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -5891,25 +5891,25 @@
         <v>18</v>
       </c>
       <c r="H123">
-        <v>7898.967953471688</v>
+        <v>5322.325996371825</v>
       </c>
       <c r="I123">
-        <v>6812.558137874756</v>
+        <v>4594.703540882509</v>
       </c>
       <c r="J123">
-        <v>4321.316153168047</v>
+        <v>3065.928626161264</v>
       </c>
       <c r="K123">
-        <v>17984.27807940006</v>
+        <v>13290.1254684769</v>
       </c>
       <c r="L123">
         <v>10000</v>
       </c>
       <c r="M123">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N123">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -5935,25 +5935,25 @@
         <v>19</v>
       </c>
       <c r="H124">
-        <v>0.3817445968590758</v>
+        <v>0.2983752231223951</v>
       </c>
       <c r="I124">
-        <v>0.3824187969863528</v>
+        <v>0.3015104643503322</v>
       </c>
       <c r="J124">
-        <v>0.2185941276108566</v>
+        <v>0.1764311978289097</v>
       </c>
       <c r="K124">
-        <v>0.5496820762805545</v>
+        <v>0.4090104475086185</v>
       </c>
       <c r="L124">
         <v>10000</v>
       </c>
       <c r="M124">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N124">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -5979,25 +5979,25 @@
         <v>20</v>
       </c>
       <c r="H125">
-        <v>13620.84264388482</v>
+        <v>13180.16535997368</v>
       </c>
       <c r="I125">
-        <v>9754.248875077014</v>
+        <v>9974.835770964644</v>
       </c>
       <c r="J125">
-        <v>2861.698737950199</v>
+        <v>5121.983917732026</v>
       </c>
       <c r="K125">
-        <v>45678.47254309546</v>
+        <v>47224.41673215914</v>
       </c>
       <c r="L125">
         <v>10000</v>
       </c>
       <c r="M125">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N125">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6023,25 +6023,25 @@
         <v>21</v>
       </c>
       <c r="H126">
-        <v>0.5770993268721153</v>
+        <v>0.6821819823785248</v>
       </c>
       <c r="I126">
-        <v>0.5824737206507786</v>
+        <v>0.6902303886234111</v>
       </c>
       <c r="J126">
-        <v>0.1839548936073245</v>
+        <v>0.3233765397958505</v>
       </c>
       <c r="K126">
-        <v>0.9158395527761028</v>
+        <v>0.9792700611493604</v>
       </c>
       <c r="L126">
         <v>10000</v>
       </c>
       <c r="M126">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N126">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6067,25 +6067,25 @@
         <v>22</v>
       </c>
       <c r="H127">
-        <v>0.7394640280027127</v>
+        <v>0.6689493855127352</v>
       </c>
       <c r="I127">
-        <v>0.7062905794367522</v>
+        <v>0.6344552388764142</v>
       </c>
       <c r="J127">
-        <v>0.3850730835671168</v>
+        <v>0.3591653029935712</v>
       </c>
       <c r="K127">
-        <v>1.269959616287478</v>
+        <v>1.159188768332651</v>
       </c>
       <c r="L127">
         <v>10000</v>
       </c>
       <c r="M127">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N127">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6111,25 +6111,25 @@
         <v>23</v>
       </c>
       <c r="H128">
-        <v>0.8031403663694306</v>
+        <v>0.7288027979084628</v>
       </c>
       <c r="I128">
-        <v>0.7684767452037274</v>
+        <v>0.6950203056383144</v>
       </c>
       <c r="J128">
-        <v>0.4354623878450352</v>
+        <v>0.3979244771873342</v>
       </c>
       <c r="K128">
-        <v>1.345789775243464</v>
+        <v>1.223278480523335</v>
       </c>
       <c r="L128">
         <v>10000</v>
       </c>
       <c r="M128">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N128">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6155,25 +6155,25 @@
         <v>24</v>
       </c>
       <c r="H129">
-        <v>21901.17519737682</v>
+        <v>18357.19790326466</v>
       </c>
       <c r="I129">
-        <v>18149.70285573606</v>
+        <v>15143.16266900014</v>
       </c>
       <c r="J129">
-        <v>10679.31230198471</v>
+        <v>11189.83388540429</v>
       </c>
       <c r="K129">
-        <v>53809.77568262721</v>
+        <v>50644.23854428908</v>
       </c>
       <c r="L129">
         <v>10000</v>
       </c>
       <c r="M129">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N129">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6199,25 +6199,25 @@
         <v>25</v>
       </c>
       <c r="H130">
-        <v>0.9213505299937814</v>
+        <v>0.9180101713644867</v>
       </c>
       <c r="I130">
-        <v>0.916480998422894</v>
+        <v>0.9146333402846443</v>
       </c>
       <c r="J130">
-        <v>0.7506054056019242</v>
+        <v>0.7545477989565053</v>
       </c>
       <c r="K130">
-        <v>1.11255014728377</v>
+        <v>1.102389140506163</v>
       </c>
       <c r="L130">
         <v>10000</v>
       </c>
       <c r="M130">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N130">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6243,25 +6243,25 @@
         <v>26</v>
       </c>
       <c r="H131">
-        <v>2685.768349827056</v>
+        <v>1684.633443507425</v>
       </c>
       <c r="I131">
-        <v>2239.701479656338</v>
+        <v>1428.855019271932</v>
       </c>
       <c r="J131">
-        <v>1871.028470787551</v>
+        <v>1224.528893382908</v>
       </c>
       <c r="K131">
-        <v>6017.496607009682</v>
+        <v>4118.132057459672</v>
       </c>
       <c r="L131">
         <v>10000</v>
       </c>
       <c r="M131">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N131">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6287,25 +6287,25 @@
         <v>27</v>
       </c>
       <c r="H132">
-        <v>5197.018853470916</v>
+        <v>4612.184999093413</v>
       </c>
       <c r="I132">
-        <v>4020.866723140656</v>
+        <v>3606.503683735635</v>
       </c>
       <c r="J132">
-        <v>1180.740824738343</v>
+        <v>1859.668221201893</v>
       </c>
       <c r="K132">
-        <v>16339.41039939823</v>
+        <v>15544.50708467882</v>
       </c>
       <c r="L132">
         <v>10000</v>
       </c>
       <c r="M132">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N132">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -6331,25 +6331,25 @@
         <v>28</v>
       </c>
       <c r="H133">
-        <v>0.3533130228149071</v>
+        <v>0.3286581083785463</v>
       </c>
       <c r="I133">
-        <v>0.3487454600719414</v>
+        <v>0.3216798242407862</v>
       </c>
       <c r="J133">
-        <v>0.2184071672345637</v>
+        <v>0.2068490167858541</v>
       </c>
       <c r="K133">
-        <v>0.5065168945833387</v>
+        <v>0.4823205430764896</v>
       </c>
       <c r="L133">
         <v>10000</v>
       </c>
       <c r="M133">
-        <v>5809</v>
+        <v>1958</v>
       </c>
       <c r="N133">
-        <v>58.1</v>
+        <v>19.6</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tabela_resumo_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_resumo_dbsra_macarellus.xlsx
@@ -58,7 +58,7 @@
     <t>pct_aceitacao</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Jardim(1981-1994)</t>
+    <t>NN_CMSY_Jardim (1999)</t>
   </si>
   <si>
     <t>NN_CMSY</t>
@@ -103,7 +103,7 @@
     <t>Umsy</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Santos(2005-2018)</t>
+    <t>NN_CMSY_Santos (2018)</t>
   </si>
   <si>
     <t>M_Santos(2005-2018)</t>
@@ -112,7 +112,7 @@
     <t>Santos (2018)</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Vieira(1988-2018)</t>
+    <t>NN_CMSY_Vieira (2019)</t>
   </si>
   <si>
     <t>M_Vieira(1988-2018)</t>
@@ -121,40 +121,40 @@
     <t>Vieira (2019)</t>
   </si>
   <si>
-    <t>zBRT_M_Jardim(1981-1994)</t>
+    <t>zBRT_Jardim (1999)</t>
   </si>
   <si>
     <t>zBRT</t>
   </si>
   <si>
-    <t>zBRT_M_Santos(2005-2018)</t>
+    <t>zBRT_Santos (2018)</t>
   </si>
   <si>
-    <t>zBRT_M_Vieira(1988-2018)</t>
+    <t>zBRT_Vieira (2019)</t>
   </si>
   <si>
-    <t>Target_switch_M_Jardim(1981-1994)</t>
+    <t>Target_switch_Jardim (1999)</t>
   </si>
   <si>
     <t>Target_switch</t>
   </si>
   <si>
-    <t>Target_switch_M_Santos(2005-2018)</t>
+    <t>Target_switch_Santos (2018)</t>
   </si>
   <si>
-    <t>Target_switch_M_Vieira(1988-2018)</t>
+    <t>Target_switch_Vieira (2019)</t>
   </si>
   <si>
-    <t>Uninformative_bk_M_Jardim(1981-1994)</t>
+    <t>Uninformative_bk_Jardim (1999)</t>
   </si>
   <si>
     <t>Uninformative_bk</t>
   </si>
   <si>
-    <t>Uninformative_bk_M_Santos(2005-2018)</t>
+    <t>Uninformative_bk_Santos (2018)</t>
   </si>
   <si>
-    <t>Uninformative_bk_M_Vieira(1988-2018)</t>
+    <t>Uninformative_bk_Vieira (2019)</t>
   </si>
 </sst>
 </file>
@@ -558,34 +558,34 @@
         <v>17</v>
       </c>
       <c r="E2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F2">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
       </c>
       <c r="H2">
-        <v>5253.459291502098</v>
+        <v>7046.986298051394</v>
       </c>
       <c r="I2">
-        <v>5078.724166815064</v>
+        <v>6628.171026839921</v>
       </c>
       <c r="J2">
-        <v>3471.667773084651</v>
+        <v>4756.312189406814</v>
       </c>
       <c r="K2">
-        <v>8044.162701801042</v>
+        <v>10787.43098923945</v>
       </c>
       <c r="L2">
         <v>10000</v>
       </c>
       <c r="M2">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N2">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -602,34 +602,34 @@
         <v>17</v>
       </c>
       <c r="E3">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F3">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
       </c>
       <c r="H3">
-        <v>0.3045456603608194</v>
+        <v>0.3293419698795158</v>
       </c>
       <c r="I3">
-        <v>0.2990903375499843</v>
+        <v>0.3139932815450759</v>
       </c>
       <c r="J3">
-        <v>0.1440253107332279</v>
+        <v>0.1742496815705022</v>
       </c>
       <c r="K3">
-        <v>0.4716403342396163</v>
+        <v>0.5603699449324718</v>
       </c>
       <c r="L3">
         <v>10000</v>
       </c>
       <c r="M3">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N3">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -646,34 +646,34 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F4">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
       </c>
       <c r="H4">
-        <v>2814.452843888446</v>
+        <v>4297.289143370795</v>
       </c>
       <c r="I4">
-        <v>2930.842970582611</v>
+        <v>4060.80727801699</v>
       </c>
       <c r="J4">
-        <v>806.8150548883962</v>
+        <v>1335.293326251064</v>
       </c>
       <c r="K4">
-        <v>4850.59576495418</v>
+        <v>8258.175085056208</v>
       </c>
       <c r="L4">
         <v>10000</v>
       </c>
       <c r="M4">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N4">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -690,34 +690,34 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F5">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
       </c>
       <c r="H5">
-        <v>0.1578961314649116</v>
+        <v>0.186273715977088</v>
       </c>
       <c r="I5">
-        <v>0.174433575906368</v>
+        <v>0.2045312262099458</v>
       </c>
       <c r="J5">
-        <v>0.04907304135551505</v>
+        <v>0.07177731176551452</v>
       </c>
       <c r="K5">
-        <v>0.2163282109136386</v>
+        <v>0.247987475897976</v>
       </c>
       <c r="L5">
         <v>10000</v>
       </c>
       <c r="M5">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N5">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -734,34 +734,34 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F6">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
       </c>
       <c r="H6">
-        <v>0.3754498110844739</v>
+        <v>0.4034342688553139</v>
       </c>
       <c r="I6">
-        <v>0.3536576049050743</v>
+        <v>0.3731647201632613</v>
       </c>
       <c r="J6">
-        <v>0.201130991947004</v>
+        <v>0.1961993826418238</v>
       </c>
       <c r="K6">
-        <v>0.6675251025241087</v>
+        <v>0.6379397675935763</v>
       </c>
       <c r="L6">
         <v>10000</v>
       </c>
       <c r="M6">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N6">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -778,34 +778,34 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F7">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
       </c>
       <c r="H7">
-        <v>0.6288011001310631</v>
+        <v>0.6588742204046329</v>
       </c>
       <c r="I7">
-        <v>0.5987074873581009</v>
+        <v>0.6239379876573132</v>
       </c>
       <c r="J7">
-        <v>0.3370526685357719</v>
+        <v>0.3345148739093901</v>
       </c>
       <c r="K7">
-        <v>1.041011734520104</v>
+        <v>1.044049137565095</v>
       </c>
       <c r="L7">
         <v>10000</v>
       </c>
       <c r="M7">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N7">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -822,34 +822,34 @@
         <v>17</v>
       </c>
       <c r="E8">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F8">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
       </c>
       <c r="H8">
-        <v>17779.4168140523</v>
+        <v>22861.02616526453</v>
       </c>
       <c r="I8">
-        <v>16472.31610542222</v>
+        <v>24573.12589160734</v>
       </c>
       <c r="J8">
-        <v>11357.66313131566</v>
+        <v>11319.62323101314</v>
       </c>
       <c r="K8">
-        <v>24871.19142983845</v>
+        <v>36003.62945699286</v>
       </c>
       <c r="L8">
         <v>10000</v>
       </c>
       <c r="M8">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N8">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -866,34 +866,34 @@
         <v>17</v>
       </c>
       <c r="E9">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F9">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
       </c>
       <c r="H9">
-        <v>0.5969522368290827</v>
+        <v>0.6128133029079534</v>
       </c>
       <c r="I9">
-        <v>0.5904252460775544</v>
+        <v>0.6159454044455225</v>
       </c>
       <c r="J9">
-        <v>0.5071096910985985</v>
+        <v>0.4888520314237196</v>
       </c>
       <c r="K9">
-        <v>0.7204889618208969</v>
+        <v>0.7155380995200575</v>
       </c>
       <c r="L9">
         <v>10000</v>
       </c>
       <c r="M9">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N9">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -910,34 +910,34 @@
         <v>17</v>
       </c>
       <c r="E10">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F10">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
       </c>
       <c r="H10">
-        <v>1182.102646647209</v>
+        <v>1666.753600623704</v>
       </c>
       <c r="I10">
-        <v>1218.986938957394</v>
+        <v>1619.335823732185</v>
       </c>
       <c r="J10">
-        <v>917.8743243933513</v>
+        <v>1223.881424856919</v>
       </c>
       <c r="K10">
-        <v>1410.055572900835</v>
+        <v>2015.997623812133</v>
       </c>
       <c r="L10">
         <v>10000</v>
       </c>
       <c r="M10">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N10">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -954,34 +954,34 @@
         <v>17</v>
       </c>
       <c r="E11">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F11">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
       </c>
       <c r="H11">
-        <v>841.1922629053704</v>
+        <v>1249.65604491451</v>
       </c>
       <c r="I11">
-        <v>836.1722768880262</v>
+        <v>1233.282669721</v>
       </c>
       <c r="J11">
-        <v>218.152154909901</v>
+        <v>345.3504094911675</v>
       </c>
       <c r="K11">
-        <v>1530.198030421081</v>
+        <v>2246.930522855127</v>
       </c>
       <c r="L11">
         <v>10000</v>
       </c>
       <c r="M11">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N11">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -998,34 +998,34 @@
         <v>17</v>
       </c>
       <c r="E12">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F12">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
       </c>
       <c r="H12">
-        <v>0.2365942542195358</v>
+        <v>0.2493028496045075</v>
       </c>
       <c r="I12">
-        <v>0.2302399169755964</v>
+        <v>0.23695019845105</v>
       </c>
       <c r="J12">
-        <v>0.1365931494635365</v>
+        <v>0.1360628274984079</v>
       </c>
       <c r="K12">
-        <v>0.3687209558772764</v>
+        <v>0.3578226376032502</v>
       </c>
       <c r="L12">
         <v>10000</v>
       </c>
       <c r="M12">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1042,34 +1042,34 @@
         <v>31</v>
       </c>
       <c r="E13">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F13">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G13" t="s">
         <v>18</v>
       </c>
       <c r="H13">
-        <v>5270.145967727135</v>
+        <v>6865.306940178486</v>
       </c>
       <c r="I13">
-        <v>5032.853328972759</v>
+        <v>6345.271968265957</v>
       </c>
       <c r="J13">
-        <v>3628.308202127683</v>
+        <v>4775.523950128652</v>
       </c>
       <c r="K13">
-        <v>8337.329452018885</v>
+        <v>10251.49605679527</v>
       </c>
       <c r="L13">
         <v>10000</v>
       </c>
       <c r="M13">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1086,34 +1086,34 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F14">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G14" t="s">
         <v>19</v>
       </c>
       <c r="H14">
-        <v>0.2991201631312089</v>
+        <v>0.3056269570963578</v>
       </c>
       <c r="I14">
-        <v>0.2924569003652332</v>
+        <v>0.3075079160079944</v>
       </c>
       <c r="J14">
-        <v>0.155448293616995</v>
+        <v>0.1252517112101298</v>
       </c>
       <c r="K14">
-        <v>0.509208366729003</v>
+        <v>0.5239381700694707</v>
       </c>
       <c r="L14">
         <v>10000</v>
       </c>
       <c r="M14">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1130,34 +1130,34 @@
         <v>31</v>
       </c>
       <c r="E15">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F15">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15">
-        <v>2938.213059681037</v>
+        <v>4638.443625623486</v>
       </c>
       <c r="I15">
-        <v>2985.754400899681</v>
+        <v>4460.130145876621</v>
       </c>
       <c r="J15">
-        <v>752.6099142171345</v>
+        <v>1624.36232697153</v>
       </c>
       <c r="K15">
-        <v>5017.253372991271</v>
+        <v>8424.497063074587</v>
       </c>
       <c r="L15">
         <v>10000</v>
       </c>
       <c r="M15">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N15">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1174,34 +1174,34 @@
         <v>31</v>
       </c>
       <c r="E16">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F16">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G16" t="s">
         <v>21</v>
       </c>
       <c r="H16">
-        <v>0.1597882669539218</v>
+        <v>0.1904811775897709</v>
       </c>
       <c r="I16">
-        <v>0.1710619192432797</v>
+        <v>0.2013150657442244</v>
       </c>
       <c r="J16">
-        <v>0.04575244488811785</v>
+        <v>0.08569447775812619</v>
       </c>
       <c r="K16">
-        <v>0.2163045390791595</v>
+        <v>0.247102034667326</v>
       </c>
       <c r="L16">
         <v>10000</v>
       </c>
       <c r="M16">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N16">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1218,34 +1218,34 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F17">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G17" t="s">
         <v>22</v>
       </c>
       <c r="H17">
-        <v>0.371428882520539</v>
+        <v>0.4074745124748758</v>
       </c>
       <c r="I17">
-        <v>0.3552840168458432</v>
+        <v>0.3815512135013815</v>
       </c>
       <c r="J17">
-        <v>0.2033811769728956</v>
+        <v>0.20955856046384</v>
       </c>
       <c r="K17">
-        <v>0.6369400047260438</v>
+        <v>0.6545149452300122</v>
       </c>
       <c r="L17">
         <v>10000</v>
       </c>
       <c r="M17">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N17">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1262,34 +1262,34 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F18">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G18" t="s">
         <v>23</v>
       </c>
       <c r="H18">
-        <v>0.6024637152368141</v>
+        <v>0.6485279871268183</v>
       </c>
       <c r="I18">
-        <v>0.5720205696677607</v>
+        <v>0.6376423453553259</v>
       </c>
       <c r="J18">
-        <v>0.3355923419414195</v>
+        <v>0.3362721759919657</v>
       </c>
       <c r="K18">
-        <v>1.00786490518904</v>
+        <v>1.025469484952236</v>
       </c>
       <c r="L18">
         <v>10000</v>
       </c>
       <c r="M18">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N18">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1306,34 +1306,34 @@
         <v>31</v>
       </c>
       <c r="E19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F19">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G19" t="s">
         <v>24</v>
       </c>
       <c r="H19">
-        <v>18288.65270180052</v>
+        <v>24047.99170558515</v>
       </c>
       <c r="I19">
-        <v>16475.32974074528</v>
+        <v>24572.90012472113</v>
       </c>
       <c r="J19">
-        <v>15407.81356696678</v>
+        <v>16401.37881004362</v>
       </c>
       <c r="K19">
-        <v>24968.6613437725</v>
+        <v>39007.27222725579</v>
       </c>
       <c r="L19">
         <v>10000</v>
       </c>
       <c r="M19">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N19">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1350,34 +1350,34 @@
         <v>31</v>
       </c>
       <c r="E20">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F20">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
       </c>
       <c r="H20">
-        <v>0.6184533686771578</v>
+        <v>0.6266195476175922</v>
       </c>
       <c r="I20">
-        <v>0.6128775818947233</v>
+        <v>0.6180446148508905</v>
       </c>
       <c r="J20">
-        <v>0.5156585588346636</v>
+        <v>0.5134445830473854</v>
       </c>
       <c r="K20">
-        <v>0.73546962025639</v>
+        <v>0.7406073907174716</v>
       </c>
       <c r="L20">
         <v>10000</v>
       </c>
       <c r="M20">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N20">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1394,34 +1394,34 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F21">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G21" t="s">
         <v>26</v>
       </c>
       <c r="H21">
-        <v>1167.168057719447</v>
+        <v>1631.746681920773</v>
       </c>
       <c r="I21">
-        <v>1219.736609997561</v>
+        <v>1614.280032106527</v>
       </c>
       <c r="J21">
-        <v>924.295667998769</v>
+        <v>1176.948026002508</v>
       </c>
       <c r="K21">
-        <v>1289.286137042821</v>
+        <v>1879.065718455432</v>
       </c>
       <c r="L21">
         <v>10000</v>
       </c>
       <c r="M21">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N21">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1438,34 +1438,34 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F22">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G22" t="s">
         <v>27</v>
       </c>
       <c r="H22">
-        <v>863.9199030514256</v>
+        <v>1352.765132341309</v>
       </c>
       <c r="I22">
-        <v>858.085798910578</v>
+        <v>1283.874649636698</v>
       </c>
       <c r="J22">
-        <v>208.6328685739466</v>
+        <v>487.9473314400112</v>
       </c>
       <c r="K22">
-        <v>1476.218324107248</v>
+        <v>2430.651756463943</v>
       </c>
       <c r="L22">
         <v>10000</v>
       </c>
       <c r="M22">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N22">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1482,34 +1482,34 @@
         <v>31</v>
       </c>
       <c r="E23">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
       </c>
       <c r="H23">
-        <v>0.2327514245064237</v>
+        <v>0.2497601069255577</v>
       </c>
       <c r="I23">
-        <v>0.2282594411339312</v>
+        <v>0.2379733875269142</v>
       </c>
       <c r="J23">
-        <v>0.1387754704210908</v>
+        <v>0.1418768001706056</v>
       </c>
       <c r="K23">
-        <v>0.3571369024241726</v>
+        <v>0.3654861406470236</v>
       </c>
       <c r="L23">
         <v>10000</v>
       </c>
       <c r="M23">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N23">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1526,34 +1526,34 @@
         <v>34</v>
       </c>
       <c r="E24">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F24">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G24" t="s">
         <v>18</v>
       </c>
       <c r="H24">
-        <v>4448.730475515813</v>
+        <v>5799.113511910413</v>
       </c>
       <c r="I24">
-        <v>4337.012355751161</v>
+        <v>5742.652315896249</v>
       </c>
       <c r="J24">
-        <v>3373.554870253595</v>
+        <v>4485.52616743575</v>
       </c>
       <c r="K24">
-        <v>6152.912879972838</v>
+        <v>7830.813386484137</v>
       </c>
       <c r="L24">
         <v>10000</v>
       </c>
       <c r="M24">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N24">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1570,34 +1570,34 @@
         <v>34</v>
       </c>
       <c r="E25">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F25">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G25" t="s">
         <v>19</v>
       </c>
       <c r="H25">
-        <v>0.2639304522090719</v>
+        <v>0.3008408158590489</v>
       </c>
       <c r="I25">
-        <v>0.2694238109048769</v>
+        <v>0.2843695984357015</v>
       </c>
       <c r="J25">
-        <v>0.1434030064276269</v>
+        <v>0.1232187309603586</v>
       </c>
       <c r="K25">
-        <v>0.3751782406619254</v>
+        <v>0.5748598791971837</v>
       </c>
       <c r="L25">
         <v>10000</v>
       </c>
       <c r="M25">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N25">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1614,34 +1614,34 @@
         <v>34</v>
       </c>
       <c r="E26">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F26">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G26" t="s">
         <v>20</v>
       </c>
       <c r="H26">
-        <v>2996.468554985752</v>
+        <v>4297.696245059041</v>
       </c>
       <c r="I26">
-        <v>3007.107452112871</v>
+        <v>3681.040508429138</v>
       </c>
       <c r="J26">
-        <v>1639.365617405928</v>
+        <v>1238.472826279387</v>
       </c>
       <c r="K26">
-        <v>4571.939199093361</v>
+        <v>9294.794629431568</v>
       </c>
       <c r="L26">
         <v>10000</v>
       </c>
       <c r="M26">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N26">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1658,34 +1658,34 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F27">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G27" t="s">
         <v>21</v>
       </c>
       <c r="H27">
-        <v>0.1729339019319249</v>
+        <v>0.1921345315123242</v>
       </c>
       <c r="I27">
-        <v>0.1813852985827583</v>
+        <v>0.2110487671890631</v>
       </c>
       <c r="J27">
-        <v>0.09965441008171005</v>
+        <v>0.06011302722955814</v>
       </c>
       <c r="K27">
-        <v>0.2177286425064219</v>
+        <v>0.2451069013630588</v>
       </c>
       <c r="L27">
         <v>10000</v>
       </c>
       <c r="M27">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N27">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1702,34 +1702,34 @@
         <v>34</v>
       </c>
       <c r="E28">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F28">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G28" t="s">
         <v>22</v>
       </c>
       <c r="H28">
-        <v>0.5370866752874162</v>
+        <v>0.5827162127850289</v>
       </c>
       <c r="I28">
-        <v>0.5110296372748272</v>
+        <v>0.575111364651208</v>
       </c>
       <c r="J28">
-        <v>0.333837600347085</v>
+        <v>0.3308488423367564</v>
       </c>
       <c r="K28">
-        <v>0.8457945580148432</v>
+        <v>0.9575574001468254</v>
       </c>
       <c r="L28">
         <v>10000</v>
       </c>
       <c r="M28">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N28">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1746,34 +1746,34 @@
         <v>34</v>
       </c>
       <c r="E29">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F29">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G29" t="s">
         <v>23</v>
       </c>
       <c r="H29">
-        <v>0.5923381665306631</v>
+        <v>0.6470445861908306</v>
       </c>
       <c r="I29">
-        <v>0.5820136656237154</v>
+        <v>0.6571126089216035</v>
       </c>
       <c r="J29">
-        <v>0.3809661703789883</v>
+        <v>0.3938553433975715</v>
       </c>
       <c r="K29">
-        <v>0.9355853742628736</v>
+        <v>0.9743386006545144</v>
       </c>
       <c r="L29">
         <v>10000</v>
       </c>
       <c r="M29">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N29">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1790,34 +1790,34 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F30">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G30" t="s">
         <v>24</v>
       </c>
       <c r="H30">
-        <v>17399.08605933471</v>
+        <v>22151.65053710177</v>
       </c>
       <c r="I30">
-        <v>16482.84017912596</v>
+        <v>24340.99857475624</v>
       </c>
       <c r="J30">
-        <v>11345.08500882819</v>
+        <v>11302.49762403837</v>
       </c>
       <c r="K30">
-        <v>24858.91455894988</v>
+        <v>41341.21660804105</v>
       </c>
       <c r="L30">
         <v>10000</v>
       </c>
       <c r="M30">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N30">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1834,34 +1834,34 @@
         <v>34</v>
       </c>
       <c r="E31">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F31">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
       </c>
       <c r="H31">
-        <v>0.906761597260057</v>
+        <v>0.9007072327608807</v>
       </c>
       <c r="I31">
-        <v>0.8836062987506794</v>
+        <v>0.8888320654156797</v>
       </c>
       <c r="J31">
-        <v>0.7373460101067425</v>
+        <v>0.7417128403326928</v>
       </c>
       <c r="K31">
-        <v>1.091478094670771</v>
+        <v>1.07522756130844</v>
       </c>
       <c r="L31">
         <v>10000</v>
       </c>
       <c r="M31">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N31">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1878,34 +1878,34 @@
         <v>34</v>
       </c>
       <c r="E32">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F32">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G32" t="s">
         <v>26</v>
       </c>
       <c r="H32">
-        <v>1209.485407347333</v>
+        <v>1704.049720353024</v>
       </c>
       <c r="I32">
-        <v>1235.430765168215</v>
+        <v>1646.455910822204</v>
       </c>
       <c r="J32">
-        <v>927.4123239372808</v>
+        <v>1189.190416442509</v>
       </c>
       <c r="K32">
-        <v>1415.438084810834</v>
+        <v>2044.880085491651</v>
       </c>
       <c r="L32">
         <v>10000</v>
       </c>
       <c r="M32">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N32">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -1922,34 +1922,34 @@
         <v>34</v>
       </c>
       <c r="E33">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F33">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
       </c>
       <c r="H33">
-        <v>1096.658314596064</v>
+        <v>1516.519632737001</v>
       </c>
       <c r="I33">
-        <v>1063.108043897339</v>
+        <v>1500.77231881485</v>
       </c>
       <c r="J33">
-        <v>489.4366266641941</v>
+        <v>496.3515144364144</v>
       </c>
       <c r="K33">
-        <v>1716.545379218534</v>
+        <v>2608.225528489495</v>
       </c>
       <c r="L33">
         <v>10000</v>
       </c>
       <c r="M33">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N33">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -1966,34 +1966,34 @@
         <v>34</v>
       </c>
       <c r="E34">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F34">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
       </c>
       <c r="H34">
-        <v>0.280323525182157</v>
+        <v>0.2998602400178452</v>
       </c>
       <c r="I34">
-        <v>0.2753756840774544</v>
+        <v>0.3035539052592196</v>
       </c>
       <c r="J34">
-        <v>0.1961359168539397</v>
+        <v>0.1949176850472346</v>
       </c>
       <c r="K34">
-        <v>0.3945798813732628</v>
+        <v>0.4244012976083712</v>
       </c>
       <c r="L34">
         <v>10000</v>
       </c>
       <c r="M34">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="N34">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2013,31 +2013,31 @@
         <v>0.01</v>
       </c>
       <c r="F35">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G35" t="s">
         <v>18</v>
       </c>
       <c r="H35">
-        <v>5146.301517269711</v>
+        <v>6829.874722263886</v>
       </c>
       <c r="I35">
-        <v>5066.218785750006</v>
+        <v>6557.063391813676</v>
       </c>
       <c r="J35">
-        <v>3412.862153955652</v>
+        <v>4692.899546884035</v>
       </c>
       <c r="K35">
-        <v>7493.510261011851</v>
+        <v>10031.26490063599</v>
       </c>
       <c r="L35">
         <v>10000</v>
       </c>
       <c r="M35">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N35">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2057,31 +2057,31 @@
         <v>0.01</v>
       </c>
       <c r="F36">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
       </c>
       <c r="H36">
-        <v>0.2897970200677478</v>
+        <v>0.2999918804874199</v>
       </c>
       <c r="I36">
-        <v>0.2857125444532465</v>
+        <v>0.2887787109303515</v>
       </c>
       <c r="J36">
-        <v>0.1672926579460295</v>
+        <v>0.1708900673198936</v>
       </c>
       <c r="K36">
-        <v>0.4385402045638412</v>
+        <v>0.5332593353747213</v>
       </c>
       <c r="L36">
         <v>10000</v>
       </c>
       <c r="M36">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N36">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2101,31 +2101,31 @@
         <v>0.01</v>
       </c>
       <c r="F37">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G37" t="s">
         <v>20</v>
       </c>
       <c r="H37">
-        <v>5553.446994920153</v>
+        <v>8550.575894286843</v>
       </c>
       <c r="I37">
-        <v>5561.718850403601</v>
+        <v>8876.294238631301</v>
       </c>
       <c r="J37">
-        <v>1834.860491623026</v>
+        <v>3154.397577540963</v>
       </c>
       <c r="K37">
-        <v>9073.884305107478</v>
+        <v>13342.01117736123</v>
       </c>
       <c r="L37">
         <v>10000</v>
       </c>
       <c r="M37">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N37">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2145,31 +2145,31 @@
         <v>0.01</v>
       </c>
       <c r="F38">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G38" t="s">
         <v>21</v>
       </c>
       <c r="H38">
-        <v>0.3046776975329215</v>
+        <v>0.3581535146744402</v>
       </c>
       <c r="I38">
-        <v>0.3253303116207721</v>
+        <v>0.3766801941835974</v>
       </c>
       <c r="J38">
-        <v>0.1100741864031718</v>
+        <v>0.1707980793993921</v>
       </c>
       <c r="K38">
-        <v>0.3874360127669505</v>
+        <v>0.4460334228502941</v>
       </c>
       <c r="L38">
         <v>10000</v>
       </c>
       <c r="M38">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N38">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2189,31 +2189,31 @@
         <v>0.01</v>
       </c>
       <c r="F39">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G39" t="s">
         <v>22</v>
       </c>
       <c r="H39">
-        <v>0.390495452547848</v>
+        <v>0.4195042850546827</v>
       </c>
       <c r="I39">
-        <v>0.3662321641931228</v>
+        <v>0.3982707439503045</v>
       </c>
       <c r="J39">
-        <v>0.2051869093247297</v>
+        <v>0.2262405307731336</v>
       </c>
       <c r="K39">
-        <v>0.7181311386784262</v>
+        <v>0.698220322294747</v>
       </c>
       <c r="L39">
         <v>10000</v>
       </c>
       <c r="M39">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N39">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2233,31 +2233,31 @@
         <v>0.01</v>
       </c>
       <c r="F40">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G40" t="s">
         <v>23</v>
       </c>
       <c r="H40">
-        <v>0.6520792677914767</v>
+        <v>0.6852263261291265</v>
       </c>
       <c r="I40">
-        <v>0.6163230003966962</v>
+        <v>0.6517240731241982</v>
       </c>
       <c r="J40">
-        <v>0.3558090785101568</v>
+        <v>0.3973789822275861</v>
       </c>
       <c r="K40">
-        <v>1.159356348806237</v>
+        <v>1.112370650007429</v>
       </c>
       <c r="L40">
         <v>10000</v>
       </c>
       <c r="M40">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N40">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2277,31 +2277,31 @@
         <v>0.01</v>
       </c>
       <c r="F41">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
       </c>
       <c r="H41">
-        <v>18313.43531825173</v>
+        <v>23903.56667588957</v>
       </c>
       <c r="I41">
-        <v>16507.43454731859</v>
+        <v>23980.92402767145</v>
       </c>
       <c r="J41">
-        <v>11333.21783274092</v>
+        <v>11329.41458737131</v>
       </c>
       <c r="K41">
-        <v>26364.38208518607</v>
+        <v>36499.03581844393</v>
       </c>
       <c r="L41">
         <v>10000</v>
       </c>
       <c r="M41">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N41">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2321,31 +2321,31 @@
         <v>0.01</v>
       </c>
       <c r="F42">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
       </c>
       <c r="H42">
-        <v>0.5999424218221453</v>
+        <v>0.6113203652942724</v>
       </c>
       <c r="I42">
-        <v>0.5990827412102351</v>
+        <v>0.6031142603740018</v>
       </c>
       <c r="J42">
-        <v>0.4906986597821065</v>
+        <v>0.5052200035088713</v>
       </c>
       <c r="K42">
-        <v>0.7221043264381691</v>
+        <v>0.7402059915766219</v>
       </c>
       <c r="L42">
         <v>10000</v>
       </c>
       <c r="M42">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N42">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2365,31 +2365,31 @@
         <v>0.01</v>
       </c>
       <c r="F43">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G43" t="s">
         <v>26</v>
       </c>
       <c r="H43">
-        <v>1199.215377736005</v>
+        <v>1677.61582268252</v>
       </c>
       <c r="I43">
-        <v>1230.762347646194</v>
+        <v>1664.266437260831</v>
       </c>
       <c r="J43">
-        <v>955.6205134377254</v>
+        <v>1372.34336417967</v>
       </c>
       <c r="K43">
-        <v>1418.617182715296</v>
+        <v>2014.485534756329</v>
       </c>
       <c r="L43">
         <v>10000</v>
       </c>
       <c r="M43">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N43">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2409,31 +2409,31 @@
         <v>0.01</v>
       </c>
       <c r="F44">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G44" t="s">
         <v>27</v>
       </c>
       <c r="H44">
-        <v>1602.338676702599</v>
+        <v>2482.782846518696</v>
       </c>
       <c r="I44">
-        <v>1593.401757251763</v>
+        <v>2502.688785162233</v>
       </c>
       <c r="J44">
-        <v>523.6804674227483</v>
+        <v>943.9459368702953</v>
       </c>
       <c r="K44">
-        <v>2729.727700433165</v>
+        <v>3850.455237387946</v>
       </c>
       <c r="L44">
         <v>10000</v>
       </c>
       <c r="M44">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N44">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -2453,31 +2453,31 @@
         <v>0.01</v>
       </c>
       <c r="F45">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G45" t="s">
         <v>28</v>
       </c>
       <c r="H45">
-        <v>0.2442264101990657</v>
+        <v>0.2576311875069281</v>
       </c>
       <c r="I45">
-        <v>0.2357443684425088</v>
+        <v>0.2519159306192667</v>
       </c>
       <c r="J45">
-        <v>0.1430116386691411</v>
+        <v>0.1570964526223744</v>
       </c>
       <c r="K45">
-        <v>0.390779328343116</v>
+        <v>0.3800618554002928</v>
       </c>
       <c r="L45">
         <v>10000</v>
       </c>
       <c r="M45">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="N45">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -2497,31 +2497,31 @@
         <v>0.01</v>
       </c>
       <c r="F46">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G46" t="s">
         <v>18</v>
       </c>
       <c r="H46">
-        <v>5052.184947845846</v>
+        <v>6772.189990635748</v>
       </c>
       <c r="I46">
-        <v>4946.375883096614</v>
+        <v>6478.024679659147</v>
       </c>
       <c r="J46">
-        <v>3191.863213037029</v>
+        <v>4343.337996962162</v>
       </c>
       <c r="K46">
-        <v>7610.226150922945</v>
+        <v>10023.27266720809</v>
       </c>
       <c r="L46">
         <v>10000</v>
       </c>
       <c r="M46">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N46">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2541,31 +2541,31 @@
         <v>0.01</v>
       </c>
       <c r="F47">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G47" t="s">
         <v>19</v>
       </c>
       <c r="H47">
-        <v>0.2865358614509541</v>
+        <v>0.2928079737348597</v>
       </c>
       <c r="I47">
-        <v>0.2839595659720223</v>
+        <v>0.2836306694174814</v>
       </c>
       <c r="J47">
-        <v>0.1519309688202965</v>
+        <v>0.1514791658160154</v>
       </c>
       <c r="K47">
-        <v>0.4518422183362643</v>
+        <v>0.5177518987103785</v>
       </c>
       <c r="L47">
         <v>10000</v>
       </c>
       <c r="M47">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N47">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2585,31 +2585,31 @@
         <v>0.01</v>
       </c>
       <c r="F48">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>
       </c>
       <c r="H48">
-        <v>5481.676065877481</v>
+        <v>8583.774541202845</v>
       </c>
       <c r="I48">
-        <v>5620.222607830538</v>
+        <v>8829.030161250343</v>
       </c>
       <c r="J48">
-        <v>1934.401971010071</v>
+        <v>3052.025427058149</v>
       </c>
       <c r="K48">
-        <v>8918.734440675133</v>
+        <v>14026.50493466572</v>
       </c>
       <c r="L48">
         <v>10000</v>
       </c>
       <c r="M48">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N48">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2629,31 +2629,31 @@
         <v>0.01</v>
       </c>
       <c r="F49">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G49" t="s">
         <v>21</v>
       </c>
       <c r="H49">
-        <v>0.3019381923795668</v>
+        <v>0.3578079123444846</v>
       </c>
       <c r="I49">
-        <v>0.3223990489633294</v>
+        <v>0.3805537550046996</v>
       </c>
       <c r="J49">
-        <v>0.1179810717329529</v>
+        <v>0.1426541511584221</v>
       </c>
       <c r="K49">
-        <v>0.3875476745699803</v>
+        <v>0.447497132478143</v>
       </c>
       <c r="L49">
         <v>10000</v>
       </c>
       <c r="M49">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N49">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2673,31 +2673,31 @@
         <v>0.01</v>
       </c>
       <c r="F50">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G50" t="s">
         <v>22</v>
       </c>
       <c r="H50">
-        <v>0.4075100073040576</v>
+        <v>0.4280311333008788</v>
       </c>
       <c r="I50">
-        <v>0.383050093915798</v>
+        <v>0.4063162792119428</v>
       </c>
       <c r="J50">
-        <v>0.2164807480727969</v>
+        <v>0.2210030097920279</v>
       </c>
       <c r="K50">
-        <v>0.7499051735644949</v>
+        <v>0.7616781302055307</v>
       </c>
       <c r="L50">
         <v>10000</v>
       </c>
       <c r="M50">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N50">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2717,31 +2717,31 @@
         <v>0.01</v>
       </c>
       <c r="F51">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G51" t="s">
         <v>23</v>
       </c>
       <c r="H51">
-        <v>0.6554249164012934</v>
+        <v>0.6788616903775666</v>
       </c>
       <c r="I51">
-        <v>0.6273758128275378</v>
+        <v>0.6429751842076195</v>
       </c>
       <c r="J51">
-        <v>0.3630594393735882</v>
+        <v>0.3559488990495122</v>
       </c>
       <c r="K51">
-        <v>1.143353312173139</v>
+        <v>1.184009480821133</v>
       </c>
       <c r="L51">
         <v>10000</v>
       </c>
       <c r="M51">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N51">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -2761,31 +2761,31 @@
         <v>0.01</v>
       </c>
       <c r="F52">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G52" t="s">
         <v>24</v>
       </c>
       <c r="H52">
-        <v>18137.9830412052</v>
+        <v>24183.51540731907</v>
       </c>
       <c r="I52">
-        <v>16512.40818680304</v>
+        <v>23873.29049108904</v>
       </c>
       <c r="J52">
-        <v>14528.96139976323</v>
+        <v>16217.55415073549</v>
       </c>
       <c r="K52">
-        <v>25701.67687822429</v>
+        <v>37479.60061391628</v>
       </c>
       <c r="L52">
         <v>10000</v>
       </c>
       <c r="M52">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N52">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -2805,31 +2805,31 @@
         <v>0.01</v>
       </c>
       <c r="F53">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
       </c>
       <c r="H53">
-        <v>0.6228009363675154</v>
+        <v>0.6317260282338636</v>
       </c>
       <c r="I53">
-        <v>0.6211527322930713</v>
+        <v>0.631201124480318</v>
       </c>
       <c r="J53">
-        <v>0.5081665567821957</v>
+        <v>0.5125355674905959</v>
       </c>
       <c r="K53">
-        <v>0.7505440790875054</v>
+        <v>0.7552070211468119</v>
       </c>
       <c r="L53">
         <v>10000</v>
       </c>
       <c r="M53">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N53">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -2849,31 +2849,31 @@
         <v>0.01</v>
       </c>
       <c r="F54">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G54" t="s">
         <v>26</v>
       </c>
       <c r="H54">
-        <v>1206.105141498401</v>
+        <v>1667.836457315344</v>
       </c>
       <c r="I54">
-        <v>1234.048760229664</v>
+        <v>1667.193380813786</v>
       </c>
       <c r="J54">
-        <v>989.2641212387655</v>
+        <v>1297.975058933059</v>
       </c>
       <c r="K54">
-        <v>1356.389961688913</v>
+        <v>1891.05669847893</v>
       </c>
       <c r="L54">
         <v>10000</v>
       </c>
       <c r="M54">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N54">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -2893,31 +2893,31 @@
         <v>0.01</v>
       </c>
       <c r="F55">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G55" t="s">
         <v>27</v>
       </c>
       <c r="H55">
-        <v>1625.774057177855</v>
+        <v>2526.343234099279</v>
       </c>
       <c r="I55">
-        <v>1615.088444879076</v>
+        <v>2516.358708766418</v>
       </c>
       <c r="J55">
-        <v>512.2523647441722</v>
+        <v>851.485514826076</v>
       </c>
       <c r="K55">
-        <v>2876.659227664862</v>
+        <v>4294.118728272512</v>
       </c>
       <c r="L55">
         <v>10000</v>
       </c>
       <c r="M55">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N55">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -2937,31 +2937,31 @@
         <v>0.01</v>
       </c>
       <c r="F56">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G56" t="s">
         <v>28</v>
       </c>
       <c r="H56">
-        <v>0.2504930265271847</v>
+        <v>0.2595782913073209</v>
       </c>
       <c r="I56">
-        <v>0.2413216812421217</v>
+        <v>0.2531410958490142</v>
       </c>
       <c r="J56">
-        <v>0.1467868489663078</v>
+        <v>0.1513798224931803</v>
       </c>
       <c r="K56">
-        <v>0.4048721227341551</v>
+        <v>0.4107804590928932</v>
       </c>
       <c r="L56">
         <v>10000</v>
       </c>
       <c r="M56">
-        <v>487</v>
+        <v>609</v>
       </c>
       <c r="N56">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -2981,31 +2981,31 @@
         <v>0.01</v>
       </c>
       <c r="F57">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G57" t="s">
         <v>18</v>
       </c>
       <c r="H57">
-        <v>4239.536427969095</v>
+        <v>5836.077855743641</v>
       </c>
       <c r="I57">
-        <v>4113.026757946881</v>
+        <v>5747.220097170204</v>
       </c>
       <c r="J57">
-        <v>2833.521148779479</v>
+        <v>3897.296950957169</v>
       </c>
       <c r="K57">
-        <v>6326.019450862614</v>
+        <v>8732.437846490244</v>
       </c>
       <c r="L57">
         <v>10000</v>
       </c>
       <c r="M57">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N57">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3025,31 +3025,31 @@
         <v>0.01</v>
       </c>
       <c r="F58">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G58" t="s">
         <v>19</v>
       </c>
       <c r="H58">
-        <v>0.2610275410869637</v>
+        <v>0.2797525240308225</v>
       </c>
       <c r="I58">
-        <v>0.2595910406206136</v>
+        <v>0.2758568907004702</v>
       </c>
       <c r="J58">
-        <v>0.1424876963499118</v>
+        <v>0.1512692182197856</v>
       </c>
       <c r="K58">
-        <v>0.3859712380424704</v>
+        <v>0.5224394754136285</v>
       </c>
       <c r="L58">
         <v>10000</v>
       </c>
       <c r="M58">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N58">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3069,31 +3069,31 @@
         <v>0.01</v>
       </c>
       <c r="F59">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G59" t="s">
         <v>20</v>
       </c>
       <c r="H59">
-        <v>5317.057347299852</v>
+        <v>8064.84023145451</v>
       </c>
       <c r="I59">
-        <v>5464.780340052647</v>
+        <v>8328.007004578694</v>
       </c>
       <c r="J59">
-        <v>2654.061072645682</v>
+        <v>2877.708013267512</v>
       </c>
       <c r="K59">
-        <v>7683.562480673714</v>
+        <v>12666.17599669265</v>
       </c>
       <c r="L59">
         <v>10000</v>
       </c>
       <c r="M59">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N59">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3113,31 +3113,31 @@
         <v>0.01</v>
       </c>
       <c r="F60">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G60" t="s">
         <v>21</v>
       </c>
       <c r="H60">
-        <v>0.3192621617221762</v>
+        <v>0.3659281904200991</v>
       </c>
       <c r="I60">
-        <v>0.3356164157968514</v>
+        <v>0.3879015379872918</v>
       </c>
       <c r="J60">
-        <v>0.1629824194954343</v>
+        <v>0.156099686978556</v>
       </c>
       <c r="K60">
-        <v>0.3871807171823665</v>
+        <v>0.4484844773832642</v>
       </c>
       <c r="L60">
         <v>10000</v>
       </c>
       <c r="M60">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N60">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3157,31 +3157,31 @@
         <v>0.01</v>
       </c>
       <c r="F61">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G61" t="s">
         <v>22</v>
       </c>
       <c r="H61">
-        <v>0.6198690378601397</v>
+        <v>0.6139448270190241</v>
       </c>
       <c r="I61">
-        <v>0.5698205200095718</v>
+        <v>0.5935593385190174</v>
       </c>
       <c r="J61">
-        <v>0.3277989715875765</v>
+        <v>0.3039325283913954</v>
       </c>
       <c r="K61">
-        <v>1.067432749704201</v>
+        <v>1.005064897837944</v>
       </c>
       <c r="L61">
         <v>10000</v>
       </c>
       <c r="M61">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N61">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3201,31 +3201,31 @@
         <v>0.01</v>
       </c>
       <c r="F62">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G62" t="s">
         <v>23</v>
       </c>
       <c r="H62">
-        <v>0.6784681503862182</v>
+        <v>0.6787555490524727</v>
       </c>
       <c r="I62">
-        <v>0.6457363860020324</v>
+        <v>0.6596175442217885</v>
       </c>
       <c r="J62">
-        <v>0.384295969928253</v>
+        <v>0.369500558493571</v>
       </c>
       <c r="K62">
-        <v>1.141400569676865</v>
+        <v>1.108657082176444</v>
       </c>
       <c r="L62">
         <v>10000</v>
       </c>
       <c r="M62">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N62">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3245,31 +3245,31 @@
         <v>0.01</v>
       </c>
       <c r="F63">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
       </c>
       <c r="H63">
-        <v>16740.09901029121</v>
+        <v>22064.07193926913</v>
       </c>
       <c r="I63">
-        <v>16246.21617646637</v>
+        <v>22515.90319898464</v>
       </c>
       <c r="J63">
-        <v>11261.80330664593</v>
+        <v>11317.69673103647</v>
       </c>
       <c r="K63">
-        <v>24230.07024198031</v>
+        <v>34722.03496446583</v>
       </c>
       <c r="L63">
         <v>10000</v>
       </c>
       <c r="M63">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N63">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3289,31 +3289,31 @@
         <v>0.01</v>
       </c>
       <c r="F64">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
       </c>
       <c r="H64">
-        <v>0.9130293668655419</v>
+        <v>0.9051267845384587</v>
       </c>
       <c r="I64">
-        <v>0.9153341824671215</v>
+        <v>0.8998544320063332</v>
       </c>
       <c r="J64">
-        <v>0.76118539346882</v>
+        <v>0.7295617821660523</v>
       </c>
       <c r="K64">
-        <v>1.084720397297344</v>
+        <v>1.088896078952769</v>
       </c>
       <c r="L64">
         <v>10000</v>
       </c>
       <c r="M64">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N64">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3333,31 +3333,31 @@
         <v>0.01</v>
       </c>
       <c r="F65">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G65" t="s">
         <v>26</v>
       </c>
       <c r="H65">
-        <v>1261.279953660125</v>
+        <v>1733.817661094132</v>
       </c>
       <c r="I65">
-        <v>1264.321932736402</v>
+        <v>1718.719879904202</v>
       </c>
       <c r="J65">
-        <v>1044.136251910876</v>
+        <v>1437.087274843967</v>
       </c>
       <c r="K65">
-        <v>1434.005114283734</v>
+        <v>2015.191526504665</v>
       </c>
       <c r="L65">
         <v>10000</v>
       </c>
       <c r="M65">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N65">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3377,31 +3377,31 @@
         <v>0.01</v>
       </c>
       <c r="F66">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
       </c>
       <c r="H66">
-        <v>1996.720476635267</v>
+        <v>2878.840864837459</v>
       </c>
       <c r="I66">
-        <v>1965.073172120964</v>
+        <v>2859.65543774657</v>
       </c>
       <c r="J66">
-        <v>888.1463476487094</v>
+        <v>1082.600800603083</v>
       </c>
       <c r="K66">
-        <v>3218.922060513752</v>
+        <v>4719.498561215662</v>
       </c>
       <c r="L66">
         <v>10000</v>
       </c>
       <c r="M66">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N66">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3421,31 +3421,31 @@
         <v>0.01</v>
       </c>
       <c r="F67">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G67" t="s">
         <v>28</v>
       </c>
       <c r="H67">
-        <v>0.3106900831986164</v>
+        <v>0.3100112560423892</v>
       </c>
       <c r="I67">
-        <v>0.3006977402850573</v>
+        <v>0.3079867941693382</v>
       </c>
       <c r="J67">
-        <v>0.1907744645684429</v>
+        <v>0.1780849106962464</v>
       </c>
       <c r="K67">
-        <v>0.4615611379407625</v>
+        <v>0.4482868419408244</v>
       </c>
       <c r="L67">
         <v>10000</v>
       </c>
       <c r="M67">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="N67">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3462,34 +3462,34 @@
         <v>17</v>
       </c>
       <c r="E68">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F68">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G68" t="s">
         <v>18</v>
       </c>
       <c r="H68">
-        <v>5105.223891190145</v>
+        <v>6776.244562213276</v>
       </c>
       <c r="I68">
-        <v>4984.102439961754</v>
+        <v>6503.398879269822</v>
       </c>
       <c r="J68">
-        <v>3332.133820926106</v>
+        <v>4621.613860117089</v>
       </c>
       <c r="K68">
-        <v>7585.337965032452</v>
+        <v>9897.436523029563</v>
       </c>
       <c r="L68">
         <v>10000</v>
       </c>
       <c r="M68">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N68">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3506,34 +3506,34 @@
         <v>17</v>
       </c>
       <c r="E69">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F69">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G69" t="s">
         <v>19</v>
       </c>
       <c r="H69">
-        <v>0.3125771296129386</v>
+        <v>0.3008354960819474</v>
       </c>
       <c r="I69">
-        <v>0.3133686193256984</v>
+        <v>0.2978155475972033</v>
       </c>
       <c r="J69">
-        <v>0.1818918580069056</v>
+        <v>0.1660862218775367</v>
       </c>
       <c r="K69">
-        <v>0.435045221275533</v>
+        <v>0.4932736851891411</v>
       </c>
       <c r="L69">
         <v>10000</v>
       </c>
       <c r="M69">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N69">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3550,34 +3550,34 @@
         <v>17</v>
       </c>
       <c r="E70">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F70">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G70" t="s">
         <v>20</v>
       </c>
       <c r="H70">
-        <v>8883.518828287939</v>
+        <v>9424.120164127329</v>
       </c>
       <c r="I70">
-        <v>8236.329153489442</v>
+        <v>9366.209850745396</v>
       </c>
       <c r="J70">
-        <v>4870.885168995792</v>
+        <v>3764.64053460894</v>
       </c>
       <c r="K70">
-        <v>16860.64571226393</v>
+        <v>14999.68840535328</v>
       </c>
       <c r="L70">
         <v>10000</v>
       </c>
       <c r="M70">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N70">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -3594,34 +3594,34 @@
         <v>17</v>
       </c>
       <c r="E71">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F71">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G71" t="s">
         <v>21</v>
       </c>
       <c r="H71">
-        <v>0.530192463493086</v>
+        <v>0.4079080343867046</v>
       </c>
       <c r="I71">
-        <v>0.5414814609634093</v>
+        <v>0.4349862293636277</v>
       </c>
       <c r="J71">
-        <v>0.2882376039845221</v>
+        <v>0.1731294827926747</v>
       </c>
       <c r="K71">
-        <v>0.6924004008747366</v>
+        <v>0.4980302509163256</v>
       </c>
       <c r="L71">
         <v>10000</v>
       </c>
       <c r="M71">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N71">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3638,34 +3638,34 @@
         <v>17</v>
       </c>
       <c r="E72">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F72">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G72" t="s">
         <v>22</v>
       </c>
       <c r="H72">
-        <v>0.4508821456229247</v>
+        <v>0.4291481942730555</v>
       </c>
       <c r="I72">
-        <v>0.4278740336490892</v>
+        <v>0.413295656854233</v>
       </c>
       <c r="J72">
-        <v>0.2454793704156557</v>
+        <v>0.2279127288521244</v>
       </c>
       <c r="K72">
-        <v>0.7968754208542631</v>
+        <v>0.6999512291259542</v>
       </c>
       <c r="L72">
         <v>10000</v>
       </c>
       <c r="M72">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N72">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3682,34 +3682,34 @@
         <v>17</v>
       </c>
       <c r="E73">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F73">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G73" t="s">
         <v>23</v>
       </c>
       <c r="H73">
-        <v>0.7365662546274462</v>
+        <v>0.7072265132419536</v>
       </c>
       <c r="I73">
-        <v>0.7015909593702885</v>
+        <v>0.6773271860275104</v>
       </c>
       <c r="J73">
-        <v>0.420060612402411</v>
+        <v>0.3803296850512559</v>
       </c>
       <c r="K73">
-        <v>1.262206832746822</v>
+        <v>1.119063721154705</v>
       </c>
       <c r="L73">
         <v>10000</v>
       </c>
       <c r="M73">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N73">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -3726,34 +3726,34 @@
         <v>17</v>
       </c>
       <c r="E74">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F74">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
       </c>
       <c r="H74">
-        <v>16817.48451283484</v>
+        <v>23346.15658412218</v>
       </c>
       <c r="I74">
-        <v>15784.43909937974</v>
+        <v>23081.87092951552</v>
       </c>
       <c r="J74">
-        <v>11597.194698218</v>
+        <v>16051.65675828712</v>
       </c>
       <c r="K74">
-        <v>28436.42741691112</v>
+        <v>36209.95456438614</v>
       </c>
       <c r="L74">
         <v>10000</v>
       </c>
       <c r="M74">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N74">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -3770,34 +3770,34 @@
         <v>17</v>
       </c>
       <c r="E75">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F75">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G75" t="s">
         <v>25</v>
       </c>
       <c r="H75">
-        <v>0.6121616642579185</v>
+        <v>0.6073382846980566</v>
       </c>
       <c r="I75">
-        <v>0.6100348263891545</v>
+        <v>0.6067320108867457</v>
       </c>
       <c r="J75">
-        <v>0.4994332720295949</v>
+        <v>0.4984386754911733</v>
       </c>
       <c r="K75">
-        <v>0.7390645335487384</v>
+        <v>0.7206693961151469</v>
       </c>
       <c r="L75">
         <v>10000</v>
       </c>
       <c r="M75">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N75">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -3814,34 +3814,34 @@
         <v>17</v>
       </c>
       <c r="E76">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F76">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G76" t="s">
         <v>26</v>
       </c>
       <c r="H76">
-        <v>1329.129666915102</v>
+        <v>1703.546648235164</v>
       </c>
       <c r="I76">
-        <v>1337.504959144467</v>
+        <v>1703.69217956934</v>
       </c>
       <c r="J76">
-        <v>1126.993719520127</v>
+        <v>1372.491761234453</v>
       </c>
       <c r="K76">
-        <v>1489.499044081904</v>
+        <v>1897.51437192714</v>
       </c>
       <c r="L76">
         <v>10000</v>
       </c>
       <c r="M76">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N76">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -3858,34 +3858,34 @@
         <v>17</v>
       </c>
       <c r="E77">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F77">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G77" t="s">
         <v>27</v>
       </c>
       <c r="H77">
-        <v>2696.859705674707</v>
+        <v>2806.783151694705</v>
       </c>
       <c r="I77">
-        <v>2597.166543111541</v>
+        <v>2820.058558751758</v>
       </c>
       <c r="J77">
-        <v>1342.980940879893</v>
+        <v>1061.620412507794</v>
       </c>
       <c r="K77">
-        <v>4615.687562277196</v>
+        <v>4530.514466678316</v>
       </c>
       <c r="L77">
         <v>10000</v>
       </c>
       <c r="M77">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N77">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -3902,34 +3902,34 @@
         <v>17</v>
       </c>
       <c r="E78">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F78">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G78" t="s">
         <v>28</v>
       </c>
       <c r="H78">
-        <v>0.2731282835550133</v>
+        <v>0.2633761018160301</v>
       </c>
       <c r="I78">
-        <v>0.2665929505294257</v>
+        <v>0.2589462884398372</v>
       </c>
       <c r="J78">
-        <v>0.1678303180893879</v>
+        <v>0.155463113349164</v>
       </c>
       <c r="K78">
-        <v>0.4245669076467379</v>
+        <v>0.3850179457043311</v>
       </c>
       <c r="L78">
         <v>10000</v>
       </c>
       <c r="M78">
-        <v>2960</v>
+        <v>983</v>
       </c>
       <c r="N78">
-        <v>29.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -3946,34 +3946,34 @@
         <v>31</v>
       </c>
       <c r="E79">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F79">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G79" t="s">
         <v>18</v>
       </c>
       <c r="H79">
-        <v>5087.539162053265</v>
+        <v>6847.365862761894</v>
       </c>
       <c r="I79">
-        <v>4954.650305705647</v>
+        <v>6561.555892633397</v>
       </c>
       <c r="J79">
-        <v>3328.197445588636</v>
+        <v>4444.174856221061</v>
       </c>
       <c r="K79">
-        <v>7643.996834887543</v>
+        <v>10386.03065899823</v>
       </c>
       <c r="L79">
         <v>10000</v>
       </c>
       <c r="M79">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N79">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -3990,34 +3990,34 @@
         <v>31</v>
       </c>
       <c r="E80">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F80">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G80" t="s">
         <v>19</v>
       </c>
       <c r="H80">
-        <v>0.3134103156955088</v>
+        <v>0.3019475154948902</v>
       </c>
       <c r="I80">
-        <v>0.3155995818859589</v>
+        <v>0.2944775250894013</v>
       </c>
       <c r="J80">
-        <v>0.1818582520175294</v>
+        <v>0.1668434898405195</v>
       </c>
       <c r="K80">
-        <v>0.4333624867503785</v>
+        <v>0.5114294336376854</v>
       </c>
       <c r="L80">
         <v>10000</v>
       </c>
       <c r="M80">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N80">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4034,34 +4034,34 @@
         <v>31</v>
       </c>
       <c r="E81">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F81">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G81" t="s">
         <v>20</v>
       </c>
       <c r="H81">
-        <v>8887.225900085437</v>
+        <v>9503.749492214793</v>
       </c>
       <c r="I81">
-        <v>8193.967229376578</v>
+        <v>9345.148364978415</v>
       </c>
       <c r="J81">
-        <v>4728.906534426157</v>
+        <v>3587.167608464534</v>
       </c>
       <c r="K81">
-        <v>17325.31342409053</v>
+        <v>15853.75739282912</v>
       </c>
       <c r="L81">
         <v>10000</v>
       </c>
       <c r="M81">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N81">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4078,34 +4078,34 @@
         <v>31</v>
       </c>
       <c r="E82">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F82">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G82" t="s">
         <v>21</v>
       </c>
       <c r="H82">
-        <v>0.5318923624887593</v>
+        <v>0.4046420724478278</v>
       </c>
       <c r="I82">
-        <v>0.5433125135276939</v>
+        <v>0.429408594886071</v>
       </c>
       <c r="J82">
-        <v>0.2857118920255624</v>
+        <v>0.1827028946790849</v>
       </c>
       <c r="K82">
-        <v>0.6917981101302446</v>
+        <v>0.4974522160759803</v>
       </c>
       <c r="L82">
         <v>10000</v>
       </c>
       <c r="M82">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N82">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4122,34 +4122,34 @@
         <v>31</v>
       </c>
       <c r="E83">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F83">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G83" t="s">
         <v>22</v>
       </c>
       <c r="H83">
-        <v>0.4592762933288834</v>
+        <v>0.4307803998584295</v>
       </c>
       <c r="I83">
-        <v>0.4350646892957166</v>
+        <v>0.4038011461683063</v>
       </c>
       <c r="J83">
-        <v>0.2482784724206943</v>
+        <v>0.2274867233029389</v>
       </c>
       <c r="K83">
-        <v>0.7950053978909476</v>
+        <v>0.7615272827181386</v>
       </c>
       <c r="L83">
         <v>10000</v>
       </c>
       <c r="M83">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N83">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4166,34 +4166,34 @@
         <v>31</v>
       </c>
       <c r="E84">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F84">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G84" t="s">
         <v>23</v>
       </c>
       <c r="H84">
-        <v>0.7300465244002557</v>
+        <v>0.6900544511333037</v>
       </c>
       <c r="I84">
-        <v>0.6964796164652723</v>
+        <v>0.6540668525571338</v>
       </c>
       <c r="J84">
-        <v>0.4079835613381123</v>
+        <v>0.3628599142824936</v>
       </c>
       <c r="K84">
-        <v>1.257167163196501</v>
+        <v>1.173261808912768</v>
       </c>
       <c r="L84">
         <v>10000</v>
       </c>
       <c r="M84">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N84">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4210,34 +4210,34 @@
         <v>31</v>
       </c>
       <c r="E85">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F85">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G85" t="s">
         <v>24</v>
       </c>
       <c r="H85">
-        <v>16747.08460585717</v>
+        <v>23606.59172204424</v>
       </c>
       <c r="I85">
-        <v>15657.07841216248</v>
+        <v>23489.98197550223</v>
       </c>
       <c r="J85">
-        <v>11618.98933259535</v>
+        <v>15956.7325530036</v>
       </c>
       <c r="K85">
-        <v>29009.22446984331</v>
+        <v>37536.35915463175</v>
       </c>
       <c r="L85">
         <v>10000</v>
       </c>
       <c r="M85">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N85">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4254,34 +4254,34 @@
         <v>31</v>
       </c>
       <c r="E86">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F86">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G86" t="s">
         <v>25</v>
       </c>
       <c r="H86">
-        <v>0.6293346351132351</v>
+        <v>0.6246231059657705</v>
       </c>
       <c r="I86">
-        <v>0.6261374986006787</v>
+        <v>0.6229046909729917</v>
       </c>
       <c r="J86">
-        <v>0.5180086432551931</v>
+        <v>0.5202119775070408</v>
       </c>
       <c r="K86">
-        <v>0.7568745318085679</v>
+        <v>0.7438123191555193</v>
       </c>
       <c r="L86">
         <v>10000</v>
       </c>
       <c r="M86">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N86">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4298,34 +4298,34 @@
         <v>31</v>
       </c>
       <c r="E87">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F87">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G87" t="s">
         <v>26</v>
       </c>
       <c r="H87">
-        <v>1333.828198679255</v>
+        <v>1702.553219208993</v>
       </c>
       <c r="I87">
-        <v>1341.845049930966</v>
+        <v>1689.691650199756</v>
       </c>
       <c r="J87">
-        <v>1146.180293470113</v>
+        <v>1420.416330073579</v>
       </c>
       <c r="K87">
-        <v>1494.179151500089</v>
+        <v>1901.667082821808</v>
       </c>
       <c r="L87">
         <v>10000</v>
       </c>
       <c r="M87">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N87">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -4342,34 +4342,34 @@
         <v>31</v>
       </c>
       <c r="E88">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F88">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G88" t="s">
         <v>27</v>
       </c>
       <c r="H88">
-        <v>2714.540960276182</v>
+        <v>2789.771183386524</v>
       </c>
       <c r="I88">
-        <v>2613.904904721776</v>
+        <v>2782.15528771223</v>
       </c>
       <c r="J88">
-        <v>1383.73817843068</v>
+        <v>1087.340672336203</v>
       </c>
       <c r="K88">
-        <v>4802.877496338019</v>
+        <v>4592.482352121326</v>
       </c>
       <c r="L88">
         <v>10000</v>
       </c>
       <c r="M88">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N88">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -4386,34 +4386,34 @@
         <v>31</v>
       </c>
       <c r="E89">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F89">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G89" t="s">
         <v>28</v>
       </c>
       <c r="H89">
-        <v>0.2752900105707312</v>
+        <v>0.2617721506285441</v>
       </c>
       <c r="I89">
-        <v>0.2671378937822206</v>
+        <v>0.2522673962638359</v>
       </c>
       <c r="J89">
-        <v>0.1682572223370653</v>
+        <v>0.1523018712391045</v>
       </c>
       <c r="K89">
-        <v>0.4201545467830522</v>
+        <v>0.4056182216698112</v>
       </c>
       <c r="L89">
         <v>10000</v>
       </c>
       <c r="M89">
-        <v>2869</v>
+        <v>957</v>
       </c>
       <c r="N89">
-        <v>28.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -4430,34 +4430,34 @@
         <v>34</v>
       </c>
       <c r="E90">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F90">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G90" t="s">
         <v>18</v>
       </c>
       <c r="H90">
-        <v>4324.514429002568</v>
+        <v>5790.257456297879</v>
       </c>
       <c r="I90">
-        <v>4209.179888794537</v>
+        <v>5618.966662518065</v>
       </c>
       <c r="J90">
-        <v>3011.660859137392</v>
+        <v>4123.318657656348</v>
       </c>
       <c r="K90">
-        <v>6253.85542012724</v>
+        <v>8412.961665266292</v>
       </c>
       <c r="L90">
         <v>10000</v>
       </c>
       <c r="M90">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N90">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -4474,34 +4474,34 @@
         <v>34</v>
       </c>
       <c r="E91">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F91">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G91" t="s">
         <v>19</v>
       </c>
       <c r="H91">
-        <v>0.2882569397055366</v>
+        <v>0.2910599242124465</v>
       </c>
       <c r="I91">
-        <v>0.2901579567325177</v>
+        <v>0.2808003466246271</v>
       </c>
       <c r="J91">
-        <v>0.1668297528939139</v>
+        <v>0.1715113949552468</v>
       </c>
       <c r="K91">
-        <v>0.4009647086115574</v>
+        <v>0.4916102161630939</v>
       </c>
       <c r="L91">
         <v>10000</v>
       </c>
       <c r="M91">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N91">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4518,34 +4518,34 @@
         <v>34</v>
       </c>
       <c r="E92">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F92">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G92" t="s">
         <v>20</v>
       </c>
       <c r="H92">
-        <v>8320.381801667561</v>
+        <v>8588.285187367752</v>
       </c>
       <c r="I92">
-        <v>7775.470135186582</v>
+        <v>8753.749967998911</v>
       </c>
       <c r="J92">
-        <v>4505.749071469641</v>
+        <v>3253.031351315968</v>
       </c>
       <c r="K92">
-        <v>15883.74914917328</v>
+        <v>12974.1675378935</v>
       </c>
       <c r="L92">
         <v>10000</v>
       </c>
       <c r="M92">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N92">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -4562,34 +4562,34 @@
         <v>34</v>
       </c>
       <c r="E93">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F93">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G93" t="s">
         <v>21</v>
       </c>
       <c r="H93">
-        <v>0.5392885060679456</v>
+        <v>0.4153690372479473</v>
       </c>
       <c r="I93">
-        <v>0.5519127819914973</v>
+        <v>0.4418078655798539</v>
       </c>
       <c r="J93">
-        <v>0.2932303935328783</v>
+        <v>0.1822191127312429</v>
       </c>
       <c r="K93">
-        <v>0.6932691257476057</v>
+        <v>0.4973522156362331</v>
       </c>
       <c r="L93">
         <v>10000</v>
       </c>
       <c r="M93">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N93">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -4606,34 +4606,34 @@
         <v>34</v>
       </c>
       <c r="E94">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F94">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G94" t="s">
         <v>22</v>
       </c>
       <c r="H94">
-        <v>0.6662093968543099</v>
+        <v>0.6387636289382056</v>
       </c>
       <c r="I94">
-        <v>0.6355112951328425</v>
+        <v>0.6232002816955886</v>
       </c>
       <c r="J94">
-        <v>0.3590534894915375</v>
+        <v>0.3351103631029397</v>
       </c>
       <c r="K94">
-        <v>1.128831957808042</v>
+        <v>1.074048760623468</v>
       </c>
       <c r="L94">
         <v>10000</v>
       </c>
       <c r="M94">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N94">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -4650,34 +4650,34 @@
         <v>34</v>
       </c>
       <c r="E95">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F95">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G95" t="s">
         <v>23</v>
       </c>
       <c r="H95">
-        <v>0.7278989084407841</v>
+        <v>0.6958052768721146</v>
       </c>
       <c r="I95">
-        <v>0.6963632237269186</v>
+        <v>0.6818145546979815</v>
       </c>
       <c r="J95">
-        <v>0.4077046837622124</v>
+        <v>0.3750894915691633</v>
       </c>
       <c r="K95">
-        <v>1.212740790355934</v>
+        <v>1.118718769416768</v>
       </c>
       <c r="L95">
         <v>10000</v>
       </c>
       <c r="M95">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N95">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -4694,34 +4694,34 @@
         <v>34</v>
       </c>
       <c r="E96">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F96">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G96" t="s">
         <v>24</v>
       </c>
       <c r="H96">
-        <v>15518.25032148387</v>
+        <v>20817.34505741964</v>
       </c>
       <c r="I96">
-        <v>14470.19510293851</v>
+        <v>20697.61026447082</v>
       </c>
       <c r="J96">
-        <v>11095.68874155052</v>
+        <v>11327.70904397855</v>
       </c>
       <c r="K96">
-        <v>26562.31194036832</v>
+        <v>32374.22244807966</v>
       </c>
       <c r="L96">
         <v>10000</v>
       </c>
       <c r="M96">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N96">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -4738,34 +4738,34 @@
         <v>34</v>
       </c>
       <c r="E97">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F97">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G97" t="s">
         <v>25</v>
       </c>
       <c r="H97">
-        <v>0.916623230651131</v>
+        <v>0.91759004638219</v>
       </c>
       <c r="I97">
-        <v>0.9127846380947324</v>
+        <v>0.9128779511555655</v>
       </c>
       <c r="J97">
-        <v>0.7445019215589335</v>
+        <v>0.7636358750824277</v>
       </c>
       <c r="K97">
-        <v>1.103797931897162</v>
+        <v>1.120263972412907</v>
       </c>
       <c r="L97">
         <v>10000</v>
       </c>
       <c r="M97">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N97">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -4782,34 +4782,34 @@
         <v>34</v>
       </c>
       <c r="E98">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F98">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G98" t="s">
         <v>26</v>
       </c>
       <c r="H98">
-        <v>1364.844957536981</v>
+        <v>1774.107040278283</v>
       </c>
       <c r="I98">
-        <v>1374.828057787021</v>
+        <v>1779.714733372287</v>
       </c>
       <c r="J98">
-        <v>1182.429248769567</v>
+        <v>1513.226857017925</v>
       </c>
       <c r="K98">
-        <v>1506.738615495821</v>
+        <v>2015.80014922281</v>
       </c>
       <c r="L98">
         <v>10000</v>
       </c>
       <c r="M98">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N98">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -4826,34 +4826,34 @@
         <v>34</v>
       </c>
       <c r="E99">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F99">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G99" t="s">
         <v>27</v>
       </c>
       <c r="H99">
-        <v>3078.653335778469</v>
+        <v>3139.800828491763</v>
       </c>
       <c r="I99">
-        <v>2954.494562827202</v>
+        <v>3176.731407918291</v>
       </c>
       <c r="J99">
-        <v>1669.194768476663</v>
+        <v>1244.404175276711</v>
       </c>
       <c r="K99">
-        <v>5063.798310333055</v>
+        <v>4738.207463839792</v>
       </c>
       <c r="L99">
         <v>10000</v>
       </c>
       <c r="M99">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N99">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -4870,34 +4870,34 @@
         <v>34</v>
       </c>
       <c r="E100">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="F100">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G100" t="s">
         <v>28</v>
       </c>
       <c r="H100">
-        <v>0.3283451278010864</v>
+        <v>0.3181454978978378</v>
       </c>
       <c r="I100">
-        <v>0.3234534582699582</v>
+        <v>0.3181388547589564</v>
       </c>
       <c r="J100">
-        <v>0.2066462411495705</v>
+        <v>0.1950117771885382</v>
       </c>
       <c r="K100">
-        <v>0.4739289933541103</v>
+        <v>0.4538147050650125</v>
       </c>
       <c r="L100">
         <v>10000</v>
       </c>
       <c r="M100">
-        <v>2020</v>
+        <v>634</v>
       </c>
       <c r="N100">
-        <v>20.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -4923,25 +4923,25 @@
         <v>18</v>
       </c>
       <c r="H101">
-        <v>6276.085436859878</v>
+        <v>7916.27830871792</v>
       </c>
       <c r="I101">
-        <v>5435.162477751841</v>
+        <v>7177.206061744403</v>
       </c>
       <c r="J101">
-        <v>3452.583592702533</v>
+        <v>4570.98300436285</v>
       </c>
       <c r="K101">
-        <v>15913.58836446703</v>
+        <v>16835.96701840239</v>
       </c>
       <c r="L101">
         <v>10000</v>
       </c>
       <c r="M101">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N101">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -4967,25 +4967,25 @@
         <v>19</v>
       </c>
       <c r="H102">
-        <v>0.3217530552686351</v>
+        <v>0.3256335880830005</v>
       </c>
       <c r="I102">
-        <v>0.3232066133233182</v>
+        <v>0.324777855820651</v>
       </c>
       <c r="J102">
-        <v>0.1952099288925556</v>
+        <v>0.1935750835295134</v>
       </c>
       <c r="K102">
-        <v>0.4457199431463122</v>
+        <v>0.4726727576113772</v>
       </c>
       <c r="L102">
         <v>10000</v>
       </c>
       <c r="M102">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N102">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -5011,25 +5011,25 @@
         <v>20</v>
       </c>
       <c r="H103">
-        <v>14149.78156234763</v>
+        <v>17585.02682308605</v>
       </c>
       <c r="I103">
-        <v>10675.24020236886</v>
+        <v>14441.35164163577</v>
       </c>
       <c r="J103">
-        <v>4983.514413850215</v>
+        <v>7165.780669183731</v>
       </c>
       <c r="K103">
-        <v>49038.96841776693</v>
+        <v>51647.29425687611</v>
       </c>
       <c r="L103">
         <v>10000</v>
       </c>
       <c r="M103">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N103">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5055,25 +5055,25 @@
         <v>21</v>
       </c>
       <c r="H104">
-        <v>0.668619600474831</v>
+        <v>0.683201780960413</v>
       </c>
       <c r="I104">
-        <v>0.670254025343535</v>
+        <v>0.690027862460305</v>
       </c>
       <c r="J104">
-        <v>0.2900664335421329</v>
+        <v>0.3315769174923187</v>
       </c>
       <c r="K104">
-        <v>0.9747325211906257</v>
+        <v>0.9772457317908091</v>
       </c>
       <c r="L104">
         <v>10000</v>
       </c>
       <c r="M104">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N104">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -5099,25 +5099,25 @@
         <v>22</v>
       </c>
       <c r="H105">
-        <v>0.4511338152843289</v>
+        <v>0.4572107846166508</v>
       </c>
       <c r="I105">
-        <v>0.4285468478498732</v>
+        <v>0.437161486852375</v>
       </c>
       <c r="J105">
-        <v>0.2463406563922989</v>
+        <v>0.2400949828844208</v>
       </c>
       <c r="K105">
-        <v>0.779705388225941</v>
+        <v>0.7840894481659354</v>
       </c>
       <c r="L105">
         <v>10000</v>
       </c>
       <c r="M105">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N105">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5143,25 +5143,25 @@
         <v>23</v>
       </c>
       <c r="H106">
-        <v>0.7381870022838298</v>
+        <v>0.7457937918147646</v>
       </c>
       <c r="I106">
-        <v>0.7051409363118597</v>
+        <v>0.7187859755811506</v>
       </c>
       <c r="J106">
-        <v>0.4120791471856297</v>
+        <v>0.4058883696640245</v>
       </c>
       <c r="K106">
-        <v>1.25278156198187</v>
+        <v>1.238029547773714</v>
       </c>
       <c r="L106">
         <v>10000</v>
       </c>
       <c r="M106">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N106">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -5187,25 +5187,25 @@
         <v>24</v>
       </c>
       <c r="H107">
-        <v>20061.52638955965</v>
+        <v>24996.1823298301</v>
       </c>
       <c r="I107">
-        <v>16458.9233927218</v>
+        <v>22028.20903469654</v>
       </c>
       <c r="J107">
-        <v>11780.37992053574</v>
+        <v>15660.23671072012</v>
       </c>
       <c r="K107">
-        <v>54384.00186167066</v>
+        <v>57352.54573956707</v>
       </c>
       <c r="L107">
         <v>10000</v>
       </c>
       <c r="M107">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N107">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -5231,25 +5231,25 @@
         <v>25</v>
       </c>
       <c r="H108">
-        <v>0.6117019923701807</v>
+        <v>0.6127613700158908</v>
       </c>
       <c r="I108">
-        <v>0.609724155773082</v>
+        <v>0.6102852484264505</v>
       </c>
       <c r="J108">
-        <v>0.5057238512226268</v>
+        <v>0.5022376209929812</v>
       </c>
       <c r="K108">
-        <v>0.7374615834408035</v>
+        <v>0.7391019269038981</v>
       </c>
       <c r="L108">
         <v>10000</v>
       </c>
       <c r="M108">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N108">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -5275,25 +5275,25 @@
         <v>26</v>
       </c>
       <c r="H109">
-        <v>1640.13808003679</v>
+        <v>2082.793261539955</v>
       </c>
       <c r="I109">
-        <v>1403.802879020193</v>
+        <v>1885.944024244911</v>
       </c>
       <c r="J109">
-        <v>1166.958912778817</v>
+        <v>1591.185143711475</v>
       </c>
       <c r="K109">
-        <v>4108.145522359886</v>
+        <v>4371.008299309227</v>
       </c>
       <c r="L109">
         <v>10000</v>
       </c>
       <c r="M109">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N109">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -5319,25 +5319,25 @@
         <v>27</v>
       </c>
       <c r="H110">
-        <v>4079.399470740932</v>
+        <v>5078.05835602465</v>
       </c>
       <c r="I110">
-        <v>3222.127809573373</v>
+        <v>4327.529767267876</v>
       </c>
       <c r="J110">
-        <v>1425.367982188336</v>
+        <v>1995.237488144188</v>
       </c>
       <c r="K110">
-        <v>13358.24600439414</v>
+        <v>13500.5384606472</v>
       </c>
       <c r="L110">
         <v>10000</v>
       </c>
       <c r="M110">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N110">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -5363,25 +5363,25 @@
         <v>28</v>
       </c>
       <c r="H111">
-        <v>0.273470454505516</v>
+        <v>0.2761518196158718</v>
       </c>
       <c r="I111">
-        <v>0.2674820364042256</v>
+        <v>0.2712362749577821</v>
       </c>
       <c r="J111">
-        <v>0.1664987432930145</v>
+        <v>0.1638273753688913</v>
       </c>
       <c r="K111">
-        <v>0.4206326229787161</v>
+        <v>0.4157976769647329</v>
       </c>
       <c r="L111">
         <v>10000</v>
       </c>
       <c r="M111">
-        <v>2743</v>
+        <v>2601</v>
       </c>
       <c r="N111">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -5407,25 +5407,25 @@
         <v>18</v>
       </c>
       <c r="H112">
-        <v>6259.758900724717</v>
+        <v>7707.4646304921</v>
       </c>
       <c r="I112">
-        <v>5307.523982205499</v>
+        <v>7010.13893036634</v>
       </c>
       <c r="J112">
-        <v>3413.638983916297</v>
+        <v>4634.548848217924</v>
       </c>
       <c r="K112">
-        <v>17020.60507728027</v>
+        <v>15735.43980250948</v>
       </c>
       <c r="L112">
         <v>10000</v>
       </c>
       <c r="M112">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N112">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -5451,25 +5451,25 @@
         <v>19</v>
       </c>
       <c r="H113">
-        <v>0.3190437830546323</v>
+        <v>0.3253776203596022</v>
       </c>
       <c r="I113">
-        <v>0.3211927448859715</v>
+        <v>0.3258284038622234</v>
       </c>
       <c r="J113">
-        <v>0.1877956768091836</v>
+        <v>0.1946181793525004</v>
       </c>
       <c r="K113">
-        <v>0.4385633209314888</v>
+        <v>0.4679594895924745</v>
       </c>
       <c r="L113">
         <v>10000</v>
       </c>
       <c r="M113">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N113">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5495,25 +5495,25 @@
         <v>20</v>
       </c>
       <c r="H114">
-        <v>14233.29642520092</v>
+        <v>17059.9705385993</v>
       </c>
       <c r="I114">
-        <v>10629.4001269845</v>
+        <v>14054.20630192981</v>
       </c>
       <c r="J114">
-        <v>4800.72070264654</v>
+        <v>7174.811228422399</v>
       </c>
       <c r="K114">
-        <v>52096.47995075984</v>
+        <v>47515.54756931293</v>
       </c>
       <c r="L114">
         <v>10000</v>
       </c>
       <c r="M114">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N114">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -5539,25 +5539,25 @@
         <v>21</v>
       </c>
       <c r="H115">
-        <v>0.669046390538433</v>
+        <v>0.6806946023630345</v>
       </c>
       <c r="I115">
-        <v>0.6696418406105374</v>
+        <v>0.6848531588456728</v>
       </c>
       <c r="J115">
-        <v>0.2871429635100617</v>
+        <v>0.3169836918979087</v>
       </c>
       <c r="K115">
-        <v>0.9764794172945477</v>
+        <v>0.9770986460179599</v>
       </c>
       <c r="L115">
         <v>10000</v>
       </c>
       <c r="M115">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N115">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -5583,25 +5583,25 @@
         <v>22</v>
       </c>
       <c r="H116">
-        <v>0.4645899645988605</v>
+        <v>0.4703712188802757</v>
       </c>
       <c r="I116">
-        <v>0.4449336120190317</v>
+        <v>0.4520655285363719</v>
       </c>
       <c r="J116">
-        <v>0.2459488527580963</v>
+        <v>0.2541284618742878</v>
       </c>
       <c r="K116">
-        <v>0.8000955383829554</v>
+        <v>0.7851631047242988</v>
       </c>
       <c r="L116">
         <v>10000</v>
       </c>
       <c r="M116">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N116">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -5627,25 +5627,25 @@
         <v>23</v>
       </c>
       <c r="H117">
-        <v>0.7386213663120654</v>
+        <v>0.7491063133589801</v>
       </c>
       <c r="I117">
-        <v>0.7069540323113723</v>
+        <v>0.7233791519649322</v>
       </c>
       <c r="J117">
-        <v>0.4102880305877671</v>
+        <v>0.4185470086432214</v>
       </c>
       <c r="K117">
-        <v>1.237985311369908</v>
+        <v>1.243277726407205</v>
       </c>
       <c r="L117">
         <v>10000</v>
       </c>
       <c r="M117">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N117">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -5671,25 +5671,25 @@
         <v>24</v>
       </c>
       <c r="H118">
-        <v>20119.96365709514</v>
+        <v>24374.90011729125</v>
       </c>
       <c r="I118">
-        <v>16444.75675033507</v>
+        <v>21636.30457727422</v>
       </c>
       <c r="J118">
-        <v>11803.17808796339</v>
+        <v>15603.80064924322</v>
       </c>
       <c r="K118">
-        <v>56030.13229341226</v>
+        <v>53733.58542557591</v>
       </c>
       <c r="L118">
         <v>10000</v>
       </c>
       <c r="M118">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N118">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -5715,25 +5715,25 @@
         <v>25</v>
       </c>
       <c r="H119">
-        <v>0.6293114947549534</v>
+        <v>0.6282838986168311</v>
       </c>
       <c r="I119">
-        <v>0.6263543429136408</v>
+        <v>0.6238525678283064</v>
       </c>
       <c r="J119">
-        <v>0.5177959366998385</v>
+        <v>0.5148318912431213</v>
       </c>
       <c r="K119">
-        <v>0.7608716854225089</v>
+        <v>0.7611831741380765</v>
       </c>
       <c r="L119">
         <v>10000</v>
       </c>
       <c r="M119">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N119">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -5759,25 +5759,25 @@
         <v>26</v>
       </c>
       <c r="H120">
-        <v>1660.04519449041</v>
+        <v>2071.901064368466</v>
       </c>
       <c r="I120">
-        <v>1405.775491658624</v>
+        <v>1885.59195028412</v>
       </c>
       <c r="J120">
-        <v>1165.384938051262</v>
+        <v>1598.615987764362</v>
       </c>
       <c r="K120">
-        <v>4174.315778247571</v>
+        <v>4064.065480070441</v>
       </c>
       <c r="L120">
         <v>10000</v>
       </c>
       <c r="M120">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N120">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -5803,25 +5803,25 @@
         <v>27</v>
       </c>
       <c r="H121">
-        <v>4162.856426954902</v>
+        <v>5046.181104495868</v>
       </c>
       <c r="I121">
-        <v>3253.728120687998</v>
+        <v>4344.915350850498</v>
       </c>
       <c r="J121">
-        <v>1411.82450485548</v>
+        <v>1939.287662133169</v>
       </c>
       <c r="K121">
-        <v>13817.25374470582</v>
+        <v>13895.96267650609</v>
       </c>
       <c r="L121">
         <v>10000</v>
       </c>
       <c r="M121">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N121">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -5847,25 +5847,25 @@
         <v>28</v>
       </c>
       <c r="H122">
-        <v>0.2778675672767797</v>
+        <v>0.2809311849662279</v>
       </c>
       <c r="I122">
-        <v>0.272906853062263</v>
+        <v>0.2760220731431445</v>
       </c>
       <c r="J122">
-        <v>0.1667850562736857</v>
+        <v>0.1699112959845668</v>
       </c>
       <c r="K122">
-        <v>0.4218378901542542</v>
+        <v>0.4192084437424697</v>
       </c>
       <c r="L122">
         <v>10000</v>
       </c>
       <c r="M122">
-        <v>2759</v>
+        <v>2644</v>
       </c>
       <c r="N122">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -5891,25 +5891,25 @@
         <v>18</v>
       </c>
       <c r="H123">
-        <v>5322.325996371825</v>
+        <v>6754.654247055953</v>
       </c>
       <c r="I123">
-        <v>4594.703540882509</v>
+        <v>5991.178135555809</v>
       </c>
       <c r="J123">
-        <v>3065.928626161264</v>
+        <v>4149.273103418855</v>
       </c>
       <c r="K123">
-        <v>13290.1254684769</v>
+        <v>16026.03853325012</v>
       </c>
       <c r="L123">
         <v>10000</v>
       </c>
       <c r="M123">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N123">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -5935,25 +5935,25 @@
         <v>19</v>
       </c>
       <c r="H124">
-        <v>0.2983752231223951</v>
+        <v>0.3054736752821584</v>
       </c>
       <c r="I124">
-        <v>0.3015104643503322</v>
+        <v>0.3062029635508176</v>
       </c>
       <c r="J124">
-        <v>0.1764311978289097</v>
+        <v>0.1819710890571374</v>
       </c>
       <c r="K124">
-        <v>0.4090104475086185</v>
+        <v>0.4237972887743628</v>
       </c>
       <c r="L124">
         <v>10000</v>
       </c>
       <c r="M124">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N124">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -5979,25 +5979,25 @@
         <v>20</v>
       </c>
       <c r="H125">
-        <v>13180.16535997368</v>
+        <v>16241.16509047429</v>
       </c>
       <c r="I125">
-        <v>9974.835770964644</v>
+        <v>13189.56697507538</v>
       </c>
       <c r="J125">
-        <v>5121.983917732026</v>
+        <v>6426.078411049864</v>
       </c>
       <c r="K125">
-        <v>47224.41673215914</v>
+        <v>53872.16555110524</v>
       </c>
       <c r="L125">
         <v>10000</v>
       </c>
       <c r="M125">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N125">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6023,25 +6023,25 @@
         <v>21</v>
       </c>
       <c r="H126">
-        <v>0.6821819823785248</v>
+        <v>0.6880026966595206</v>
       </c>
       <c r="I126">
-        <v>0.6902303886234111</v>
+        <v>0.6909544865108406</v>
       </c>
       <c r="J126">
-        <v>0.3233765397958505</v>
+        <v>0.3291478617148254</v>
       </c>
       <c r="K126">
-        <v>0.9792700611493604</v>
+        <v>0.9766430806003654</v>
       </c>
       <c r="L126">
         <v>10000</v>
       </c>
       <c r="M126">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N126">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6067,25 +6067,25 @@
         <v>22</v>
       </c>
       <c r="H127">
-        <v>0.6689493855127352</v>
+        <v>0.6687148767482751</v>
       </c>
       <c r="I127">
-        <v>0.6344552388764142</v>
+        <v>0.6414108565643502</v>
       </c>
       <c r="J127">
-        <v>0.3591653029935712</v>
+        <v>0.3577606834732284</v>
       </c>
       <c r="K127">
-        <v>1.159188768332651</v>
+        <v>1.111629822469121</v>
       </c>
       <c r="L127">
         <v>10000</v>
       </c>
       <c r="M127">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N127">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6111,25 +6111,25 @@
         <v>23</v>
       </c>
       <c r="H128">
-        <v>0.7288027979084628</v>
+        <v>0.7301469080240576</v>
       </c>
       <c r="I128">
-        <v>0.6950203056383144</v>
+        <v>0.7070154995053128</v>
       </c>
       <c r="J128">
-        <v>0.3979244771873342</v>
+        <v>0.4051375344995057</v>
       </c>
       <c r="K128">
-        <v>1.223278480523335</v>
+        <v>1.192965653848615</v>
       </c>
       <c r="L128">
         <v>10000</v>
       </c>
       <c r="M128">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N128">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6155,25 +6155,25 @@
         <v>24</v>
       </c>
       <c r="H129">
-        <v>18357.19790326466</v>
+        <v>22730.64310743393</v>
       </c>
       <c r="I129">
-        <v>15143.16266900014</v>
+        <v>19492.86309143458</v>
       </c>
       <c r="J129">
-        <v>11189.83388540429</v>
+        <v>14881.07370537047</v>
       </c>
       <c r="K129">
-        <v>50644.23854428908</v>
+        <v>58718.31630508169</v>
       </c>
       <c r="L129">
         <v>10000</v>
       </c>
       <c r="M129">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N129">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6199,25 +6199,25 @@
         <v>25</v>
       </c>
       <c r="H130">
-        <v>0.9180101713644867</v>
+        <v>0.9159778559824597</v>
       </c>
       <c r="I130">
-        <v>0.9146333402846443</v>
+        <v>0.9104772068179458</v>
       </c>
       <c r="J130">
-        <v>0.7545477989565053</v>
+        <v>0.7506372251264619</v>
       </c>
       <c r="K130">
-        <v>1.102389140506163</v>
+        <v>1.108465468098505</v>
       </c>
       <c r="L130">
         <v>10000</v>
       </c>
       <c r="M130">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N130">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6243,25 +6243,25 @@
         <v>26</v>
       </c>
       <c r="H131">
-        <v>1684.633443507425</v>
+        <v>2140.497043516758</v>
       </c>
       <c r="I131">
-        <v>1428.855019271932</v>
+        <v>1907.843899139607</v>
       </c>
       <c r="J131">
-        <v>1224.528893382908</v>
+        <v>1658.326533659113</v>
       </c>
       <c r="K131">
-        <v>4118.132057459672</v>
+        <v>5037.183619841665</v>
       </c>
       <c r="L131">
         <v>10000</v>
       </c>
       <c r="M131">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N131">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6287,25 +6287,25 @@
         <v>27</v>
       </c>
       <c r="H132">
-        <v>4612.184999093413</v>
+        <v>5657.11109314147</v>
       </c>
       <c r="I132">
-        <v>3606.503683735635</v>
+        <v>4734.133743749477</v>
       </c>
       <c r="J132">
-        <v>1859.668221201893</v>
+        <v>2286.551771255532</v>
       </c>
       <c r="K132">
-        <v>15544.50708467882</v>
+        <v>17899.99475987996</v>
       </c>
       <c r="L132">
         <v>10000</v>
       </c>
       <c r="M132">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N132">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -6331,25 +6331,25 @@
         <v>28</v>
       </c>
       <c r="H133">
-        <v>0.3286581083785463</v>
+        <v>0.3293637528482228</v>
       </c>
       <c r="I133">
-        <v>0.3216798242407862</v>
+        <v>0.3267415796110679</v>
       </c>
       <c r="J133">
-        <v>0.2068490167858541</v>
+        <v>0.2052320899187248</v>
       </c>
       <c r="K133">
-        <v>0.4823205430764896</v>
+        <v>0.4713956396189692</v>
       </c>
       <c r="L133">
         <v>10000</v>
       </c>
       <c r="M133">
-        <v>1958</v>
+        <v>1932</v>
       </c>
       <c r="N133">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tabela_resumo_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_resumo_dbsra_macarellus.xlsx
@@ -567,22 +567,22 @@
         <v>18</v>
       </c>
       <c r="H2">
-        <v>7046.986298051394</v>
+        <v>7273.666107631355</v>
       </c>
       <c r="I2">
-        <v>6628.171026839921</v>
+        <v>7026.3594748932</v>
       </c>
       <c r="J2">
-        <v>4756.312189406814</v>
+        <v>5080.472090872069</v>
       </c>
       <c r="K2">
-        <v>10787.43098923945</v>
+        <v>10464.86748319846</v>
       </c>
       <c r="L2">
         <v>10000</v>
       </c>
       <c r="M2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N2">
         <v>1.3</v>
@@ -611,22 +611,22 @@
         <v>19</v>
       </c>
       <c r="H3">
-        <v>0.3293419698795158</v>
+        <v>0.3119947282247122</v>
       </c>
       <c r="I3">
-        <v>0.3139932815450759</v>
+        <v>0.3146381294127724</v>
       </c>
       <c r="J3">
-        <v>0.1742496815705022</v>
+        <v>0.1318318586621171</v>
       </c>
       <c r="K3">
-        <v>0.5603699449324718</v>
+        <v>0.5377221337316416</v>
       </c>
       <c r="L3">
         <v>10000</v>
       </c>
       <c r="M3">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N3">
         <v>1.3</v>
@@ -655,22 +655,22 @@
         <v>20</v>
       </c>
       <c r="H4">
-        <v>4297.289143370795</v>
+        <v>4749.580687244952</v>
       </c>
       <c r="I4">
-        <v>4060.80727801699</v>
+        <v>4480.713838774964</v>
       </c>
       <c r="J4">
-        <v>1335.293326251064</v>
+        <v>1466.189519168164</v>
       </c>
       <c r="K4">
-        <v>8258.175085056208</v>
+        <v>9325.670353131514</v>
       </c>
       <c r="L4">
         <v>10000</v>
       </c>
       <c r="M4">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N4">
         <v>1.3</v>
@@ -699,22 +699,22 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>0.186273715977088</v>
+        <v>0.1845226397745648</v>
       </c>
       <c r="I5">
-        <v>0.2045312262099458</v>
+        <v>0.1979537604596424</v>
       </c>
       <c r="J5">
-        <v>0.07177731176551452</v>
+        <v>0.0695236541062873</v>
       </c>
       <c r="K5">
-        <v>0.247987475897976</v>
+        <v>0.2479766039371336</v>
       </c>
       <c r="L5">
         <v>10000</v>
       </c>
       <c r="M5">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N5">
         <v>1.3</v>
@@ -743,22 +743,22 @@
         <v>22</v>
       </c>
       <c r="H6">
-        <v>0.4034342688553139</v>
+        <v>0.3892729372683353</v>
       </c>
       <c r="I6">
-        <v>0.3731647201632613</v>
+        <v>0.3686333754642635</v>
       </c>
       <c r="J6">
-        <v>0.1961993826418238</v>
+        <v>0.2219792566046727</v>
       </c>
       <c r="K6">
-        <v>0.6379397675935763</v>
+        <v>0.6712396651401078</v>
       </c>
       <c r="L6">
         <v>10000</v>
       </c>
       <c r="M6">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N6">
         <v>1.3</v>
@@ -787,22 +787,22 @@
         <v>23</v>
       </c>
       <c r="H7">
-        <v>0.6588742204046329</v>
+        <v>0.6546665219535609</v>
       </c>
       <c r="I7">
-        <v>0.6239379876573132</v>
+        <v>0.6194483485435378</v>
       </c>
       <c r="J7">
-        <v>0.3345148739093901</v>
+        <v>0.3692640040481108</v>
       </c>
       <c r="K7">
-        <v>1.044049137565095</v>
+        <v>1.105798808863663</v>
       </c>
       <c r="L7">
         <v>10000</v>
       </c>
       <c r="M7">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N7">
         <v>1.3</v>
@@ -831,22 +831,22 @@
         <v>24</v>
       </c>
       <c r="H8">
-        <v>22861.02616526453</v>
+        <v>25681.86796034881</v>
       </c>
       <c r="I8">
-        <v>24573.12589160734</v>
+        <v>24701.46922917609</v>
       </c>
       <c r="J8">
-        <v>11319.62323101314</v>
+        <v>11318.77453298669</v>
       </c>
       <c r="K8">
-        <v>36003.62945699286</v>
+        <v>45531.12794537794</v>
       </c>
       <c r="L8">
         <v>10000</v>
       </c>
       <c r="M8">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N8">
         <v>1.3</v>
@@ -875,22 +875,22 @@
         <v>25</v>
       </c>
       <c r="H9">
-        <v>0.6128133029079534</v>
+        <v>0.598300305133563</v>
       </c>
       <c r="I9">
-        <v>0.6159454044455225</v>
+        <v>0.5972509516880646</v>
       </c>
       <c r="J9">
-        <v>0.4888520314237196</v>
+        <v>0.5034576536017115</v>
       </c>
       <c r="K9">
-        <v>0.7155380995200575</v>
+        <v>0.7251042421365946</v>
       </c>
       <c r="L9">
         <v>10000</v>
       </c>
       <c r="M9">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N9">
         <v>1.3</v>
@@ -919,22 +919,22 @@
         <v>26</v>
       </c>
       <c r="H10">
-        <v>1666.753600623704</v>
+        <v>1701.705992989962</v>
       </c>
       <c r="I10">
-        <v>1619.335823732185</v>
+        <v>1708.684063534089</v>
       </c>
       <c r="J10">
-        <v>1223.881424856919</v>
+        <v>1300.884271090898</v>
       </c>
       <c r="K10">
-        <v>2015.997623812133</v>
+        <v>2028.391810603788</v>
       </c>
       <c r="L10">
         <v>10000</v>
       </c>
       <c r="M10">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N10">
         <v>1.3</v>
@@ -963,22 +963,22 @@
         <v>27</v>
       </c>
       <c r="H11">
-        <v>1249.65604491451</v>
+        <v>1333.560690292407</v>
       </c>
       <c r="I11">
-        <v>1233.282669721</v>
+        <v>1330.049233688347</v>
       </c>
       <c r="J11">
-        <v>345.3504094911675</v>
+        <v>458.6331121427226</v>
       </c>
       <c r="K11">
-        <v>2246.930522855127</v>
+        <v>2476.763984489078</v>
       </c>
       <c r="L11">
         <v>10000</v>
       </c>
       <c r="M11">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N11">
         <v>1.3</v>
@@ -1007,22 +1007,22 @@
         <v>28</v>
       </c>
       <c r="H12">
-        <v>0.2493028496045075</v>
+        <v>0.24418398771015</v>
       </c>
       <c r="I12">
-        <v>0.23695019845105</v>
+        <v>0.2365248299874899</v>
       </c>
       <c r="J12">
-        <v>0.1360628274984079</v>
+        <v>0.1514465089995924</v>
       </c>
       <c r="K12">
-        <v>0.3578226376032502</v>
+        <v>0.3834690123350735</v>
       </c>
       <c r="L12">
         <v>10000</v>
       </c>
       <c r="M12">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N12">
         <v>1.3</v>
@@ -1051,25 +1051,25 @@
         <v>18</v>
       </c>
       <c r="H13">
-        <v>6865.306940178486</v>
+        <v>7117.575373257861</v>
       </c>
       <c r="I13">
-        <v>6345.271968265957</v>
+        <v>6980.198127257525</v>
       </c>
       <c r="J13">
-        <v>4775.523950128652</v>
+        <v>4919.553410659139</v>
       </c>
       <c r="K13">
-        <v>10251.49605679527</v>
+        <v>10065.64295354961</v>
       </c>
       <c r="L13">
         <v>10000</v>
       </c>
       <c r="M13">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N13">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1095,25 +1095,25 @@
         <v>19</v>
       </c>
       <c r="H14">
-        <v>0.3056269570963578</v>
+        <v>0.3044968517622373</v>
       </c>
       <c r="I14">
-        <v>0.3075079160079944</v>
+        <v>0.3029400063669293</v>
       </c>
       <c r="J14">
-        <v>0.1252517112101298</v>
+        <v>0.140769982663112</v>
       </c>
       <c r="K14">
-        <v>0.5239381700694707</v>
+        <v>0.5003905389844165</v>
       </c>
       <c r="L14">
         <v>10000</v>
       </c>
       <c r="M14">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N14">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1139,25 +1139,25 @@
         <v>20</v>
       </c>
       <c r="H15">
-        <v>4638.443625623486</v>
+        <v>4834.663620079497</v>
       </c>
       <c r="I15">
-        <v>4460.130145876621</v>
+        <v>4803.283029003742</v>
       </c>
       <c r="J15">
-        <v>1624.36232697153</v>
+        <v>1016.063355464687</v>
       </c>
       <c r="K15">
-        <v>8424.497063074587</v>
+        <v>9270.451368640779</v>
       </c>
       <c r="L15">
         <v>10000</v>
       </c>
       <c r="M15">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N15">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1183,25 +1183,25 @@
         <v>21</v>
       </c>
       <c r="H16">
-        <v>0.1904811775897709</v>
+        <v>0.1803898799072416</v>
       </c>
       <c r="I16">
-        <v>0.2013150657442244</v>
+        <v>0.1949983102897295</v>
       </c>
       <c r="J16">
-        <v>0.08569447775812619</v>
+        <v>0.05932911460379973</v>
       </c>
       <c r="K16">
-        <v>0.247102034667326</v>
+        <v>0.2460156120247551</v>
       </c>
       <c r="L16">
         <v>10000</v>
       </c>
       <c r="M16">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N16">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1227,25 +1227,25 @@
         <v>22</v>
       </c>
       <c r="H17">
-        <v>0.4074745124748758</v>
+        <v>0.4053111289118926</v>
       </c>
       <c r="I17">
-        <v>0.3815512135013815</v>
+        <v>0.3781808908070914</v>
       </c>
       <c r="J17">
-        <v>0.20955856046384</v>
+        <v>0.2394490845309989</v>
       </c>
       <c r="K17">
-        <v>0.6545149452300122</v>
+        <v>0.7357373641540543</v>
       </c>
       <c r="L17">
         <v>10000</v>
       </c>
       <c r="M17">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N17">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1271,25 +1271,25 @@
         <v>23</v>
       </c>
       <c r="H18">
-        <v>0.6485279871268183</v>
+        <v>0.6475482630354171</v>
       </c>
       <c r="I18">
-        <v>0.6376423453553259</v>
+        <v>0.6156410432614883</v>
       </c>
       <c r="J18">
-        <v>0.3362721759919657</v>
+        <v>0.3819666946753269</v>
       </c>
       <c r="K18">
-        <v>1.025469484952236</v>
+        <v>1.052142800875873</v>
       </c>
       <c r="L18">
         <v>10000</v>
       </c>
       <c r="M18">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N18">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1315,25 +1315,25 @@
         <v>24</v>
       </c>
       <c r="H19">
-        <v>24047.99170558515</v>
+        <v>26015.95084798232</v>
       </c>
       <c r="I19">
-        <v>24572.90012472113</v>
+        <v>24729.53172084751</v>
       </c>
       <c r="J19">
-        <v>16401.37881004362</v>
+        <v>11320.63482707048</v>
       </c>
       <c r="K19">
-        <v>39007.27222725579</v>
+        <v>42657.94260705442</v>
       </c>
       <c r="L19">
         <v>10000</v>
       </c>
       <c r="M19">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N19">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1359,25 +1359,25 @@
         <v>25</v>
       </c>
       <c r="H20">
-        <v>0.6266195476175922</v>
+        <v>0.6265424125618171</v>
       </c>
       <c r="I20">
-        <v>0.6180446148508905</v>
+        <v>0.6210356083734586</v>
       </c>
       <c r="J20">
-        <v>0.5134445830473854</v>
+        <v>0.5177185333806167</v>
       </c>
       <c r="K20">
-        <v>0.7406073907174716</v>
+        <v>0.7421767292018822</v>
       </c>
       <c r="L20">
         <v>10000</v>
       </c>
       <c r="M20">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N20">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1403,25 +1403,25 @@
         <v>26</v>
       </c>
       <c r="H21">
-        <v>1631.746681920773</v>
+        <v>1702.932892203744</v>
       </c>
       <c r="I21">
-        <v>1614.280032106527</v>
+        <v>1709.559722288294</v>
       </c>
       <c r="J21">
-        <v>1176.948026002508</v>
+        <v>1266.247664410434</v>
       </c>
       <c r="K21">
-        <v>1879.065718455432</v>
+        <v>2035.531151567974</v>
       </c>
       <c r="L21">
         <v>10000</v>
       </c>
       <c r="M21">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N21">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1447,25 +1447,25 @@
         <v>27</v>
       </c>
       <c r="H22">
-        <v>1352.765132341309</v>
+        <v>1367.469680623748</v>
       </c>
       <c r="I22">
-        <v>1283.874649636698</v>
+        <v>1374.244076104651</v>
       </c>
       <c r="J22">
-        <v>487.9473314400112</v>
+        <v>270.7906287505036</v>
       </c>
       <c r="K22">
-        <v>2430.651756463943</v>
+        <v>2646.395942719191</v>
       </c>
       <c r="L22">
         <v>10000</v>
       </c>
       <c r="M22">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N22">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1491,25 +1491,25 @@
         <v>28</v>
       </c>
       <c r="H23">
-        <v>0.2497601069255577</v>
+        <v>0.2491603283435361</v>
       </c>
       <c r="I23">
-        <v>0.2379733875269142</v>
+        <v>0.2402257393814853</v>
       </c>
       <c r="J23">
-        <v>0.1418768001706056</v>
+        <v>0.1609117668623209</v>
       </c>
       <c r="K23">
-        <v>0.3654861406470236</v>
+        <v>0.3896740337999982</v>
       </c>
       <c r="L23">
         <v>10000</v>
       </c>
       <c r="M23">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="N23">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1535,25 +1535,25 @@
         <v>18</v>
       </c>
       <c r="H24">
-        <v>5799.113511910413</v>
+        <v>6512.086158442134</v>
       </c>
       <c r="I24">
-        <v>5742.652315896249</v>
+        <v>6164.039669702978</v>
       </c>
       <c r="J24">
-        <v>4485.52616743575</v>
+        <v>4746.408140420475</v>
       </c>
       <c r="K24">
-        <v>7830.813386484137</v>
+        <v>8898.256786303355</v>
       </c>
       <c r="L24">
         <v>10000</v>
       </c>
       <c r="M24">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N24">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1579,25 +1579,25 @@
         <v>19</v>
       </c>
       <c r="H25">
-        <v>0.3008408158590489</v>
+        <v>0.2975337447033494</v>
       </c>
       <c r="I25">
-        <v>0.2843695984357015</v>
+        <v>0.2971029176561058</v>
       </c>
       <c r="J25">
-        <v>0.1232187309603586</v>
+        <v>0.1469359495067342</v>
       </c>
       <c r="K25">
-        <v>0.5748598791971837</v>
+        <v>0.5182878026564417</v>
       </c>
       <c r="L25">
         <v>10000</v>
       </c>
       <c r="M25">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N25">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1623,25 +1623,25 @@
         <v>20</v>
       </c>
       <c r="H26">
-        <v>4297.696245059041</v>
+        <v>4668.26422737368</v>
       </c>
       <c r="I26">
-        <v>3681.040508429138</v>
+        <v>4112.234751968669</v>
       </c>
       <c r="J26">
-        <v>1238.472826279387</v>
+        <v>1278.602955110076</v>
       </c>
       <c r="K26">
-        <v>9294.794629431568</v>
+        <v>9677.52543389353</v>
       </c>
       <c r="L26">
         <v>10000</v>
       </c>
       <c r="M26">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N26">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1667,25 +1667,25 @@
         <v>21</v>
       </c>
       <c r="H27">
-        <v>0.1921345315123242</v>
+        <v>0.1897402161023204</v>
       </c>
       <c r="I27">
-        <v>0.2110487671890631</v>
+        <v>0.2112865384033881</v>
       </c>
       <c r="J27">
-        <v>0.06011302722955814</v>
+        <v>0.07547108679404158</v>
       </c>
       <c r="K27">
-        <v>0.2451069013630588</v>
+        <v>0.2483035144459296</v>
       </c>
       <c r="L27">
         <v>10000</v>
       </c>
       <c r="M27">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N27">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1711,25 +1711,25 @@
         <v>22</v>
       </c>
       <c r="H28">
-        <v>0.5827162127850289</v>
+        <v>0.5285842347904181</v>
       </c>
       <c r="I28">
-        <v>0.575111364651208</v>
+        <v>0.5221024049511337</v>
       </c>
       <c r="J28">
-        <v>0.3308488423367564</v>
+        <v>0.2953486159981975</v>
       </c>
       <c r="K28">
-        <v>0.9575574001468254</v>
+        <v>0.7940221012144453</v>
       </c>
       <c r="L28">
         <v>10000</v>
       </c>
       <c r="M28">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N28">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1755,25 +1755,25 @@
         <v>23</v>
       </c>
       <c r="H29">
-        <v>0.6470445861908306</v>
+        <v>0.5816016237222997</v>
       </c>
       <c r="I29">
-        <v>0.6571126089216035</v>
+        <v>0.5851277809610397</v>
       </c>
       <c r="J29">
-        <v>0.3938553433975715</v>
+        <v>0.3566726315803416</v>
       </c>
       <c r="K29">
-        <v>0.9743386006545144</v>
+        <v>0.895343787464733</v>
       </c>
       <c r="L29">
         <v>10000</v>
       </c>
       <c r="M29">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N29">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1799,25 +1799,25 @@
         <v>24</v>
       </c>
       <c r="H30">
-        <v>22151.65053710177</v>
+        <v>24018.75680803393</v>
       </c>
       <c r="I30">
-        <v>24340.99857475624</v>
+        <v>24650.43125338086</v>
       </c>
       <c r="J30">
-        <v>11302.49762403837</v>
+        <v>11324.28453921776</v>
       </c>
       <c r="K30">
-        <v>41341.21660804105</v>
+        <v>40576.98310429195</v>
       </c>
       <c r="L30">
         <v>10000</v>
       </c>
       <c r="M30">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N30">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1843,25 +1843,25 @@
         <v>25</v>
       </c>
       <c r="H31">
-        <v>0.9007072327608807</v>
+        <v>0.9107387617162999</v>
       </c>
       <c r="I31">
-        <v>0.8888320654156797</v>
+        <v>0.9254387949400841</v>
       </c>
       <c r="J31">
-        <v>0.7417128403326928</v>
+        <v>0.7427471998798394</v>
       </c>
       <c r="K31">
-        <v>1.07522756130844</v>
+        <v>1.084090546942615</v>
       </c>
       <c r="L31">
         <v>10000</v>
       </c>
       <c r="M31">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N31">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1887,25 +1887,25 @@
         <v>26</v>
       </c>
       <c r="H32">
-        <v>1704.049720353024</v>
+        <v>1735.00592365522</v>
       </c>
       <c r="I32">
-        <v>1646.455910822204</v>
+        <v>1723.751843001479</v>
       </c>
       <c r="J32">
-        <v>1189.190416442509</v>
+        <v>1359.403179748416</v>
       </c>
       <c r="K32">
-        <v>2044.880085491651</v>
+        <v>2049.381898989173</v>
       </c>
       <c r="L32">
         <v>10000</v>
       </c>
       <c r="M32">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N32">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -1931,25 +1931,25 @@
         <v>27</v>
       </c>
       <c r="H33">
-        <v>1516.519632737001</v>
+        <v>1497.543592308713</v>
       </c>
       <c r="I33">
-        <v>1500.77231881485</v>
+        <v>1386.293094530655</v>
       </c>
       <c r="J33">
-        <v>496.3515144364144</v>
+        <v>453.4566569774877</v>
       </c>
       <c r="K33">
-        <v>2608.225528489495</v>
+        <v>2812.153045380852</v>
       </c>
       <c r="L33">
         <v>10000</v>
       </c>
       <c r="M33">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N33">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -1975,25 +1975,25 @@
         <v>28</v>
       </c>
       <c r="H34">
-        <v>0.2998602400178452</v>
+        <v>0.2761781552469334</v>
       </c>
       <c r="I34">
-        <v>0.3035539052592196</v>
+        <v>0.2805996522321547</v>
       </c>
       <c r="J34">
-        <v>0.1949176850472346</v>
+        <v>0.1826426090972972</v>
       </c>
       <c r="K34">
-        <v>0.4244012976083712</v>
+        <v>0.3849720448397478</v>
       </c>
       <c r="L34">
         <v>10000</v>
       </c>
       <c r="M34">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="N34">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2019,16 +2019,16 @@
         <v>18</v>
       </c>
       <c r="H35">
-        <v>6829.874722263886</v>
+        <v>7081.212131263737</v>
       </c>
       <c r="I35">
-        <v>6557.063391813676</v>
+        <v>6881.92847806708</v>
       </c>
       <c r="J35">
-        <v>4692.899546884035</v>
+        <v>4613.816550061457</v>
       </c>
       <c r="K35">
-        <v>10031.26490063599</v>
+        <v>10575.43273916402</v>
       </c>
       <c r="L35">
         <v>10000</v>
@@ -2063,16 +2063,16 @@
         <v>19</v>
       </c>
       <c r="H36">
-        <v>0.2999918804874199</v>
+        <v>0.2918722316690675</v>
       </c>
       <c r="I36">
-        <v>0.2887787109303515</v>
+        <v>0.2855832900832965</v>
       </c>
       <c r="J36">
-        <v>0.1708900673198936</v>
+        <v>0.1565662697548788</v>
       </c>
       <c r="K36">
-        <v>0.5332593353747213</v>
+        <v>0.5020585813992111</v>
       </c>
       <c r="L36">
         <v>10000</v>
@@ -2107,16 +2107,16 @@
         <v>20</v>
       </c>
       <c r="H37">
-        <v>8550.575894286843</v>
+        <v>9129.602839068481</v>
       </c>
       <c r="I37">
-        <v>8876.294238631301</v>
+        <v>9247.544026027543</v>
       </c>
       <c r="J37">
-        <v>3154.397577540963</v>
+        <v>2947.941168275791</v>
       </c>
       <c r="K37">
-        <v>13342.01117736123</v>
+        <v>15591.58716289435</v>
       </c>
       <c r="L37">
         <v>10000</v>
@@ -2151,16 +2151,16 @@
         <v>21</v>
       </c>
       <c r="H38">
-        <v>0.3581535146744402</v>
+        <v>0.3590967539825784</v>
       </c>
       <c r="I38">
-        <v>0.3766801941835974</v>
+        <v>0.3841574800444664</v>
       </c>
       <c r="J38">
-        <v>0.1707980793993921</v>
+        <v>0.1541277779640113</v>
       </c>
       <c r="K38">
-        <v>0.4460334228502941</v>
+        <v>0.4472047744608935</v>
       </c>
       <c r="L38">
         <v>10000</v>
@@ -2195,16 +2195,16 @@
         <v>22</v>
       </c>
       <c r="H39">
-        <v>0.4195042850546827</v>
+        <v>0.4205687786056165</v>
       </c>
       <c r="I39">
-        <v>0.3982707439503045</v>
+        <v>0.3965881871939427</v>
       </c>
       <c r="J39">
-        <v>0.2262405307731336</v>
+        <v>0.2247478580509854</v>
       </c>
       <c r="K39">
-        <v>0.698220322294747</v>
+        <v>0.7448312624976202</v>
       </c>
       <c r="L39">
         <v>10000</v>
@@ -2239,16 +2239,16 @@
         <v>23</v>
       </c>
       <c r="H40">
-        <v>0.6852263261291265</v>
+        <v>0.6944016620833188</v>
       </c>
       <c r="I40">
-        <v>0.6517240731241982</v>
+        <v>0.6540911543831536</v>
       </c>
       <c r="J40">
-        <v>0.3973789822275861</v>
+        <v>0.377208510237649</v>
       </c>
       <c r="K40">
-        <v>1.112370650007429</v>
+        <v>1.179903098335789</v>
       </c>
       <c r="L40">
         <v>10000</v>
@@ -2283,16 +2283,16 @@
         <v>24</v>
       </c>
       <c r="H41">
-        <v>23903.56667588957</v>
+        <v>25483.04455053248</v>
       </c>
       <c r="I41">
-        <v>23980.92402767145</v>
+        <v>24405.34008941127</v>
       </c>
       <c r="J41">
-        <v>11329.41458737131</v>
+        <v>12430.1013906666</v>
       </c>
       <c r="K41">
-        <v>36499.03581844393</v>
+        <v>41457.12781724922</v>
       </c>
       <c r="L41">
         <v>10000</v>
@@ -2327,16 +2327,16 @@
         <v>25</v>
       </c>
       <c r="H42">
-        <v>0.6113203652942724</v>
+        <v>0.6051555347426545</v>
       </c>
       <c r="I42">
-        <v>0.6031142603740018</v>
+        <v>0.603725457239373</v>
       </c>
       <c r="J42">
-        <v>0.5052200035088713</v>
+        <v>0.4969413246436898</v>
       </c>
       <c r="K42">
-        <v>0.7402059915766219</v>
+        <v>0.7316611604999959</v>
       </c>
       <c r="L42">
         <v>10000</v>
@@ -2371,16 +2371,16 @@
         <v>26</v>
       </c>
       <c r="H43">
-        <v>1677.61582268252</v>
+        <v>1735.617112732825</v>
       </c>
       <c r="I43">
-        <v>1664.266437260831</v>
+        <v>1733.742440530326</v>
       </c>
       <c r="J43">
-        <v>1372.34336417967</v>
+        <v>1480.171469687042</v>
       </c>
       <c r="K43">
-        <v>2014.485534756329</v>
+        <v>2018.431540066693</v>
       </c>
       <c r="L43">
         <v>10000</v>
@@ -2415,16 +2415,16 @@
         <v>27</v>
       </c>
       <c r="H44">
-        <v>2482.782846518696</v>
+        <v>2656.791149464195</v>
       </c>
       <c r="I44">
-        <v>2502.688785162233</v>
+        <v>2651.937738454573</v>
       </c>
       <c r="J44">
-        <v>943.9459368702953</v>
+        <v>903.8182139176101</v>
       </c>
       <c r="K44">
-        <v>3850.455237387946</v>
+        <v>4505.263207491404</v>
       </c>
       <c r="L44">
         <v>10000</v>
@@ -2459,16 +2459,16 @@
         <v>28</v>
       </c>
       <c r="H45">
-        <v>0.2576311875069281</v>
+        <v>0.2586264569203736</v>
       </c>
       <c r="I45">
-        <v>0.2519159306192667</v>
+        <v>0.2484892464278234</v>
       </c>
       <c r="J45">
-        <v>0.1570964526223744</v>
+        <v>0.1568244249127044</v>
       </c>
       <c r="K45">
-        <v>0.3800618554002928</v>
+        <v>0.4037852476702263</v>
       </c>
       <c r="L45">
         <v>10000</v>
@@ -2503,25 +2503,25 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>6772.189990635748</v>
+        <v>6926.666132871042</v>
       </c>
       <c r="I46">
-        <v>6478.024679659147</v>
+        <v>6560.756856819847</v>
       </c>
       <c r="J46">
-        <v>4343.337996962162</v>
+        <v>4564.326589332573</v>
       </c>
       <c r="K46">
-        <v>10023.27266720809</v>
+        <v>10328.60039198555</v>
       </c>
       <c r="L46">
         <v>10000</v>
       </c>
       <c r="M46">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N46">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2547,25 +2547,25 @@
         <v>19</v>
       </c>
       <c r="H47">
-        <v>0.2928079737348597</v>
+        <v>0.2927458896963153</v>
       </c>
       <c r="I47">
-        <v>0.2836306694174814</v>
+        <v>0.2762184423268856</v>
       </c>
       <c r="J47">
-        <v>0.1514791658160154</v>
+        <v>0.1560728761225079</v>
       </c>
       <c r="K47">
-        <v>0.5177518987103785</v>
+        <v>0.5028952061565849</v>
       </c>
       <c r="L47">
         <v>10000</v>
       </c>
       <c r="M47">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N47">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2591,25 +2591,25 @@
         <v>20</v>
       </c>
       <c r="H48">
-        <v>8583.774541202845</v>
+        <v>8920.498522694472</v>
       </c>
       <c r="I48">
-        <v>8829.030161250343</v>
+        <v>9154.17950053701</v>
       </c>
       <c r="J48">
-        <v>3052.025427058149</v>
+        <v>2998.346453373553</v>
       </c>
       <c r="K48">
-        <v>14026.50493466572</v>
+        <v>15414.70941483396</v>
       </c>
       <c r="L48">
         <v>10000</v>
       </c>
       <c r="M48">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N48">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2635,25 +2635,25 @@
         <v>21</v>
       </c>
       <c r="H49">
-        <v>0.3578079123444846</v>
+        <v>0.3579523924087352</v>
       </c>
       <c r="I49">
-        <v>0.3805537550046996</v>
+        <v>0.3878196927501113</v>
       </c>
       <c r="J49">
-        <v>0.1426541511584221</v>
+        <v>0.1558440648376862</v>
       </c>
       <c r="K49">
-        <v>0.447497132478143</v>
+        <v>0.4479430587203607</v>
       </c>
       <c r="L49">
         <v>10000</v>
       </c>
       <c r="M49">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N49">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2679,25 +2679,25 @@
         <v>22</v>
       </c>
       <c r="H50">
-        <v>0.4280311333008788</v>
+        <v>0.4390098956706909</v>
       </c>
       <c r="I50">
-        <v>0.4063162792119428</v>
+        <v>0.4234682019059178</v>
       </c>
       <c r="J50">
-        <v>0.2210030097920279</v>
+        <v>0.2196095322104563</v>
       </c>
       <c r="K50">
-        <v>0.7616781302055307</v>
+        <v>0.7504235416618262</v>
       </c>
       <c r="L50">
         <v>10000</v>
       </c>
       <c r="M50">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N50">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2723,25 +2723,25 @@
         <v>23</v>
       </c>
       <c r="H51">
-        <v>0.6788616903775666</v>
+        <v>0.701527005434837</v>
       </c>
       <c r="I51">
-        <v>0.6429751842076195</v>
+        <v>0.6850281176506614</v>
       </c>
       <c r="J51">
-        <v>0.3559488990495122</v>
+        <v>0.3516158307778227</v>
       </c>
       <c r="K51">
-        <v>1.184009480821133</v>
+        <v>1.178035138613266</v>
       </c>
       <c r="L51">
         <v>10000</v>
       </c>
       <c r="M51">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N51">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -2767,25 +2767,25 @@
         <v>24</v>
       </c>
       <c r="H52">
-        <v>24183.51540731907</v>
+        <v>24977.52711514215</v>
       </c>
       <c r="I52">
-        <v>23873.29049108904</v>
+        <v>24168.16931097538</v>
       </c>
       <c r="J52">
-        <v>16217.55415073549</v>
+        <v>11337.02672825862</v>
       </c>
       <c r="K52">
-        <v>37479.60061391628</v>
+        <v>41937.09367720256</v>
       </c>
       <c r="L52">
         <v>10000</v>
       </c>
       <c r="M52">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N52">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -2811,25 +2811,25 @@
         <v>25</v>
       </c>
       <c r="H53">
-        <v>0.6317260282338636</v>
+        <v>0.6275646159781559</v>
       </c>
       <c r="I53">
-        <v>0.631201124480318</v>
+        <v>0.6260601043054146</v>
       </c>
       <c r="J53">
-        <v>0.5125355674905959</v>
+        <v>0.5077415087583571</v>
       </c>
       <c r="K53">
-        <v>0.7552070211468119</v>
+        <v>0.7621362892738363</v>
       </c>
       <c r="L53">
         <v>10000</v>
       </c>
       <c r="M53">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N53">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -2855,25 +2855,25 @@
         <v>26</v>
       </c>
       <c r="H54">
-        <v>1667.836457315344</v>
+        <v>1744.390643236002</v>
       </c>
       <c r="I54">
-        <v>1667.193380813786</v>
+        <v>1744.910032740764</v>
       </c>
       <c r="J54">
-        <v>1297.975058933059</v>
+        <v>1431.961778236544</v>
       </c>
       <c r="K54">
-        <v>1891.05669847893</v>
+        <v>2034.32331802209</v>
       </c>
       <c r="L54">
         <v>10000</v>
       </c>
       <c r="M54">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N54">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -2899,25 +2899,25 @@
         <v>27</v>
       </c>
       <c r="H55">
-        <v>2526.343234099279</v>
+        <v>2667.061816488561</v>
       </c>
       <c r="I55">
-        <v>2516.358708766418</v>
+        <v>2681.890846630906</v>
       </c>
       <c r="J55">
-        <v>851.485514826076</v>
+        <v>887.9716235477307</v>
       </c>
       <c r="K55">
-        <v>4294.118728272512</v>
+        <v>4585.157675749039</v>
       </c>
       <c r="L55">
         <v>10000</v>
       </c>
       <c r="M55">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N55">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -2943,25 +2943,25 @@
         <v>28</v>
       </c>
       <c r="H56">
-        <v>0.2595782913073209</v>
+        <v>0.2656034755715275</v>
       </c>
       <c r="I56">
-        <v>0.2531410958490142</v>
+        <v>0.2639603591146208</v>
       </c>
       <c r="J56">
-        <v>0.1513798224931803</v>
+        <v>0.1496525566079671</v>
       </c>
       <c r="K56">
-        <v>0.4107804590928932</v>
+        <v>0.4060961492472046</v>
       </c>
       <c r="L56">
         <v>10000</v>
       </c>
       <c r="M56">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="N56">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -2987,25 +2987,25 @@
         <v>18</v>
       </c>
       <c r="H57">
-        <v>5836.077855743641</v>
+        <v>5979.769062079871</v>
       </c>
       <c r="I57">
-        <v>5747.220097170204</v>
+        <v>5810.070586125463</v>
       </c>
       <c r="J57">
-        <v>3897.296950957169</v>
+        <v>4176.807925909237</v>
       </c>
       <c r="K57">
-        <v>8732.437846490244</v>
+        <v>9286.01903884224</v>
       </c>
       <c r="L57">
         <v>10000</v>
       </c>
       <c r="M57">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N57">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3031,25 +3031,25 @@
         <v>19</v>
       </c>
       <c r="H58">
-        <v>0.2797525240308225</v>
+        <v>0.279552869014069</v>
       </c>
       <c r="I58">
-        <v>0.2758568907004702</v>
+        <v>0.2630976379135611</v>
       </c>
       <c r="J58">
-        <v>0.1512692182197856</v>
+        <v>0.1413682585969316</v>
       </c>
       <c r="K58">
-        <v>0.5224394754136285</v>
+        <v>0.4885716138660823</v>
       </c>
       <c r="L58">
         <v>10000</v>
       </c>
       <c r="M58">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N58">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3075,25 +3075,25 @@
         <v>20</v>
       </c>
       <c r="H59">
-        <v>8064.84023145451</v>
+        <v>8354.179259331933</v>
       </c>
       <c r="I59">
-        <v>8328.007004578694</v>
+        <v>8779.334141336654</v>
       </c>
       <c r="J59">
-        <v>2877.708013267512</v>
+        <v>3014.489872736845</v>
       </c>
       <c r="K59">
-        <v>12666.17599669265</v>
+        <v>13807.31145936405</v>
       </c>
       <c r="L59">
         <v>10000</v>
       </c>
       <c r="M59">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N59">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3119,25 +3119,25 @@
         <v>21</v>
       </c>
       <c r="H60">
-        <v>0.3659281904200991</v>
+        <v>0.3654423104046092</v>
       </c>
       <c r="I60">
-        <v>0.3879015379872918</v>
+        <v>0.3930600305638478</v>
       </c>
       <c r="J60">
-        <v>0.156099686978556</v>
+        <v>0.1404507906790275</v>
       </c>
       <c r="K60">
-        <v>0.4484844773832642</v>
+        <v>0.448250841621816</v>
       </c>
       <c r="L60">
         <v>10000</v>
       </c>
       <c r="M60">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N60">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3163,25 +3163,25 @@
         <v>22</v>
       </c>
       <c r="H61">
-        <v>0.6139448270190241</v>
+        <v>0.624489087555375</v>
       </c>
       <c r="I61">
-        <v>0.5935593385190174</v>
+        <v>0.6079699928886959</v>
       </c>
       <c r="J61">
-        <v>0.3039325283913954</v>
+        <v>0.3172517854593201</v>
       </c>
       <c r="K61">
-        <v>1.005064897837944</v>
+        <v>1.032679081407829</v>
       </c>
       <c r="L61">
         <v>10000</v>
       </c>
       <c r="M61">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N61">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3207,25 +3207,25 @@
         <v>23</v>
       </c>
       <c r="H62">
-        <v>0.6787555490524727</v>
+        <v>0.6815761238161373</v>
       </c>
       <c r="I62">
-        <v>0.6596175442217885</v>
+        <v>0.6624579525148232</v>
       </c>
       <c r="J62">
-        <v>0.369500558493571</v>
+        <v>0.3653038072697088</v>
       </c>
       <c r="K62">
-        <v>1.108657082176444</v>
+        <v>1.098827894049669</v>
       </c>
       <c r="L62">
         <v>10000</v>
       </c>
       <c r="M62">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N62">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3251,25 +3251,25 @@
         <v>24</v>
       </c>
       <c r="H63">
-        <v>22064.07193926913</v>
+        <v>22869.67501442028</v>
       </c>
       <c r="I63">
-        <v>22515.90319898464</v>
+        <v>23330.08264553548</v>
       </c>
       <c r="J63">
-        <v>11317.69673103647</v>
+        <v>11307.85839164636</v>
       </c>
       <c r="K63">
-        <v>34722.03496446583</v>
+        <v>35482.36741946277</v>
       </c>
       <c r="L63">
         <v>10000</v>
       </c>
       <c r="M63">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N63">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3295,25 +3295,25 @@
         <v>25</v>
       </c>
       <c r="H64">
-        <v>0.9051267845384587</v>
+        <v>0.915705671526913</v>
       </c>
       <c r="I64">
-        <v>0.8998544320063332</v>
+        <v>0.9093964438089891</v>
       </c>
       <c r="J64">
-        <v>0.7295617821660523</v>
+        <v>0.756059191718535</v>
       </c>
       <c r="K64">
-        <v>1.088896078952769</v>
+        <v>1.124820281978111</v>
       </c>
       <c r="L64">
         <v>10000</v>
       </c>
       <c r="M64">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N64">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3339,25 +3339,25 @@
         <v>26</v>
       </c>
       <c r="H65">
-        <v>1733.817661094132</v>
+        <v>1789.828020843936</v>
       </c>
       <c r="I65">
-        <v>1718.719879904202</v>
+        <v>1776.07142858124</v>
       </c>
       <c r="J65">
-        <v>1437.087274843967</v>
+        <v>1560.882264480264</v>
       </c>
       <c r="K65">
-        <v>2015.191526504665</v>
+        <v>2036.431411445723</v>
       </c>
       <c r="L65">
         <v>10000</v>
       </c>
       <c r="M65">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N65">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3383,25 +3383,25 @@
         <v>27</v>
       </c>
       <c r="H66">
-        <v>2878.840864837459</v>
+        <v>2990.697749110368</v>
       </c>
       <c r="I66">
-        <v>2859.65543774657</v>
+        <v>2977.546748999448</v>
       </c>
       <c r="J66">
-        <v>1082.600800603083</v>
+        <v>1074.808615500149</v>
       </c>
       <c r="K66">
-        <v>4719.498561215662</v>
+        <v>4786.554537504044</v>
       </c>
       <c r="L66">
         <v>10000</v>
       </c>
       <c r="M66">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N66">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3427,25 +3427,25 @@
         <v>28</v>
       </c>
       <c r="H67">
-        <v>0.3100112560423892</v>
+        <v>0.3126184405210486</v>
       </c>
       <c r="I67">
-        <v>0.3079867941693382</v>
+        <v>0.3132141090443412</v>
       </c>
       <c r="J67">
-        <v>0.1780849106962464</v>
+        <v>0.1864835577424698</v>
       </c>
       <c r="K67">
-        <v>0.4482868419408244</v>
+        <v>0.4470068613906618</v>
       </c>
       <c r="L67">
         <v>10000</v>
       </c>
       <c r="M67">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="N67">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3471,25 +3471,25 @@
         <v>18</v>
       </c>
       <c r="H68">
-        <v>6776.244562213276</v>
+        <v>7076.604302601146</v>
       </c>
       <c r="I68">
-        <v>6503.398879269822</v>
+        <v>6828.313280389134</v>
       </c>
       <c r="J68">
-        <v>4621.613860117089</v>
+        <v>4841.490846866111</v>
       </c>
       <c r="K68">
-        <v>9897.436523029563</v>
+        <v>10608.89470740364</v>
       </c>
       <c r="L68">
         <v>10000</v>
       </c>
       <c r="M68">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N68">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3515,25 +3515,25 @@
         <v>19</v>
       </c>
       <c r="H69">
-        <v>0.3008354960819474</v>
+        <v>0.2994290747573696</v>
       </c>
       <c r="I69">
-        <v>0.2978155475972033</v>
+        <v>0.2939212185213084</v>
       </c>
       <c r="J69">
-        <v>0.1660862218775367</v>
+        <v>0.1625732707919263</v>
       </c>
       <c r="K69">
-        <v>0.4932736851891411</v>
+        <v>0.4863560340771494</v>
       </c>
       <c r="L69">
         <v>10000</v>
       </c>
       <c r="M69">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N69">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3559,25 +3559,25 @@
         <v>20</v>
       </c>
       <c r="H70">
-        <v>9424.120164127329</v>
+        <v>9870.686797317103</v>
       </c>
       <c r="I70">
-        <v>9366.209850745396</v>
+        <v>9825.355811170522</v>
       </c>
       <c r="J70">
-        <v>3764.64053460894</v>
+        <v>3892.463370502946</v>
       </c>
       <c r="K70">
-        <v>14999.68840535328</v>
+        <v>16650.25992034305</v>
       </c>
       <c r="L70">
         <v>10000</v>
       </c>
       <c r="M70">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N70">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -3603,25 +3603,25 @@
         <v>21</v>
       </c>
       <c r="H71">
-        <v>0.4079080343867046</v>
+        <v>0.4046855203188514</v>
       </c>
       <c r="I71">
-        <v>0.4349862293636277</v>
+        <v>0.4287924869821494</v>
       </c>
       <c r="J71">
-        <v>0.1731294827926747</v>
+        <v>0.1753003728616698</v>
       </c>
       <c r="K71">
-        <v>0.4980302509163256</v>
+        <v>0.4970667311488372</v>
       </c>
       <c r="L71">
         <v>10000</v>
       </c>
       <c r="M71">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N71">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3647,25 +3647,25 @@
         <v>22</v>
       </c>
       <c r="H72">
-        <v>0.4291481942730555</v>
+        <v>0.4255249424049858</v>
       </c>
       <c r="I72">
-        <v>0.413295656854233</v>
+        <v>0.4045373922011282</v>
       </c>
       <c r="J72">
-        <v>0.2279127288521244</v>
+        <v>0.2255704074861227</v>
       </c>
       <c r="K72">
-        <v>0.6999512291259542</v>
+        <v>0.6925838837320468</v>
       </c>
       <c r="L72">
         <v>10000</v>
       </c>
       <c r="M72">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N72">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3691,25 +3691,25 @@
         <v>23</v>
       </c>
       <c r="H73">
-        <v>0.7072265132419536</v>
+        <v>0.7032040131265282</v>
       </c>
       <c r="I73">
-        <v>0.6773271860275104</v>
+        <v>0.6753848546172344</v>
       </c>
       <c r="J73">
-        <v>0.3803296850512559</v>
+        <v>0.3944312449429507</v>
       </c>
       <c r="K73">
-        <v>1.119063721154705</v>
+        <v>1.139402517923621</v>
       </c>
       <c r="L73">
         <v>10000</v>
       </c>
       <c r="M73">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N73">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -3735,25 +3735,25 @@
         <v>24</v>
       </c>
       <c r="H74">
-        <v>23346.15658412218</v>
+        <v>24681.42799416303</v>
       </c>
       <c r="I74">
-        <v>23081.87092951552</v>
+        <v>23953.00466639022</v>
       </c>
       <c r="J74">
-        <v>16051.65675828712</v>
+        <v>16101.76018272586</v>
       </c>
       <c r="K74">
-        <v>36209.95456438614</v>
+        <v>40455.83107864425</v>
       </c>
       <c r="L74">
         <v>10000</v>
       </c>
       <c r="M74">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N74">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -3779,25 +3779,25 @@
         <v>25</v>
       </c>
       <c r="H75">
-        <v>0.6073382846980566</v>
+        <v>0.6060332889434535</v>
       </c>
       <c r="I75">
-        <v>0.6067320108867457</v>
+        <v>0.603666656523413</v>
       </c>
       <c r="J75">
-        <v>0.4984386754911733</v>
+        <v>0.4983036453027478</v>
       </c>
       <c r="K75">
-        <v>0.7206693961151469</v>
+        <v>0.7316023758636849</v>
       </c>
       <c r="L75">
         <v>10000</v>
       </c>
       <c r="M75">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N75">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -3823,25 +3823,25 @@
         <v>26</v>
       </c>
       <c r="H76">
-        <v>1703.546648235164</v>
+        <v>1762.659950967558</v>
       </c>
       <c r="I76">
-        <v>1703.69217956934</v>
+        <v>1765.924500991997</v>
       </c>
       <c r="J76">
-        <v>1372.491761234453</v>
+        <v>1490.435222539403</v>
       </c>
       <c r="K76">
-        <v>1897.51437192714</v>
+        <v>1987.696909501695</v>
       </c>
       <c r="L76">
         <v>10000</v>
       </c>
       <c r="M76">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N76">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -3867,25 +3867,25 @@
         <v>27</v>
       </c>
       <c r="H77">
-        <v>2806.783151694705</v>
+        <v>2893.565913683369</v>
       </c>
       <c r="I77">
-        <v>2820.058558751758</v>
+        <v>2902.255968471391</v>
       </c>
       <c r="J77">
-        <v>1061.620412507794</v>
+        <v>1175.071895285549</v>
       </c>
       <c r="K77">
-        <v>4530.514466678316</v>
+        <v>4710.738181766049</v>
       </c>
       <c r="L77">
         <v>10000</v>
       </c>
       <c r="M77">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N77">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -3911,25 +3911,25 @@
         <v>28</v>
       </c>
       <c r="H78">
-        <v>0.2633761018160301</v>
+        <v>0.2615628918722404</v>
       </c>
       <c r="I78">
-        <v>0.2589462884398372</v>
+        <v>0.2559404724794944</v>
       </c>
       <c r="J78">
-        <v>0.155463113349164</v>
+        <v>0.1559310408416311</v>
       </c>
       <c r="K78">
-        <v>0.3850179457043311</v>
+        <v>0.3838676716591814</v>
       </c>
       <c r="L78">
         <v>10000</v>
       </c>
       <c r="M78">
-        <v>983</v>
+        <v>925</v>
       </c>
       <c r="N78">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -3955,25 +3955,25 @@
         <v>18</v>
       </c>
       <c r="H79">
-        <v>6847.365862761894</v>
+        <v>6959.692288384013</v>
       </c>
       <c r="I79">
-        <v>6561.555892633397</v>
+        <v>6745.236025754256</v>
       </c>
       <c r="J79">
-        <v>4444.174856221061</v>
+        <v>4571.583154732904</v>
       </c>
       <c r="K79">
-        <v>10386.03065899823</v>
+        <v>10574.84567296955</v>
       </c>
       <c r="L79">
         <v>10000</v>
       </c>
       <c r="M79">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N79">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -3999,25 +3999,25 @@
         <v>19</v>
       </c>
       <c r="H80">
-        <v>0.3019475154948902</v>
+        <v>0.3053897620051177</v>
       </c>
       <c r="I80">
-        <v>0.2944775250894013</v>
+        <v>0.3002102218427549</v>
       </c>
       <c r="J80">
-        <v>0.1668434898405195</v>
+        <v>0.1614020515612489</v>
       </c>
       <c r="K80">
-        <v>0.5114294336376854</v>
+        <v>0.4902616686210535</v>
       </c>
       <c r="L80">
         <v>10000</v>
       </c>
       <c r="M80">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N80">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4043,25 +4043,25 @@
         <v>20</v>
       </c>
       <c r="H81">
-        <v>9503.749492214793</v>
+        <v>9655.031573022854</v>
       </c>
       <c r="I81">
-        <v>9345.148364978415</v>
+        <v>9588.739736083997</v>
       </c>
       <c r="J81">
-        <v>3587.167608464534</v>
+        <v>3943.321774804654</v>
       </c>
       <c r="K81">
-        <v>15853.75739282912</v>
+        <v>15379.35397565647</v>
       </c>
       <c r="L81">
         <v>10000</v>
       </c>
       <c r="M81">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N81">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4087,25 +4087,25 @@
         <v>21</v>
       </c>
       <c r="H82">
-        <v>0.4046420724478278</v>
+        <v>0.4118324557381227</v>
       </c>
       <c r="I82">
-        <v>0.429408594886071</v>
+        <v>0.4382288055381718</v>
       </c>
       <c r="J82">
-        <v>0.1827028946790849</v>
+        <v>0.2111297024622276</v>
       </c>
       <c r="K82">
-        <v>0.4974522160759803</v>
+        <v>0.4981196830817252</v>
       </c>
       <c r="L82">
         <v>10000</v>
       </c>
       <c r="M82">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N82">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4131,25 +4131,25 @@
         <v>22</v>
       </c>
       <c r="H83">
-        <v>0.4307803998584295</v>
+        <v>0.4485209163697604</v>
       </c>
       <c r="I83">
-        <v>0.4038011461683063</v>
+        <v>0.4255729810041181</v>
       </c>
       <c r="J83">
-        <v>0.2274867233029389</v>
+        <v>0.2307040500332256</v>
       </c>
       <c r="K83">
-        <v>0.7615272827181386</v>
+        <v>0.7756884106103504</v>
       </c>
       <c r="L83">
         <v>10000</v>
       </c>
       <c r="M83">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N83">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4175,25 +4175,25 @@
         <v>23</v>
       </c>
       <c r="H84">
-        <v>0.6900544511333037</v>
+        <v>0.71034980878701</v>
       </c>
       <c r="I84">
-        <v>0.6540668525571338</v>
+        <v>0.6785973336703229</v>
       </c>
       <c r="J84">
-        <v>0.3628599142824936</v>
+        <v>0.3777201676597492</v>
       </c>
       <c r="K84">
-        <v>1.173261808912768</v>
+        <v>1.174028827803994</v>
       </c>
       <c r="L84">
         <v>10000</v>
       </c>
       <c r="M84">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N84">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4219,25 +4219,25 @@
         <v>24</v>
       </c>
       <c r="H85">
-        <v>23606.59172204424</v>
+        <v>23726.31070200475</v>
       </c>
       <c r="I85">
-        <v>23489.98197550223</v>
+        <v>23282.23293023906</v>
       </c>
       <c r="J85">
-        <v>15956.7325530036</v>
+        <v>13285.30507310936</v>
       </c>
       <c r="K85">
-        <v>37536.35915463175</v>
+        <v>37899.49022726239</v>
       </c>
       <c r="L85">
         <v>10000</v>
       </c>
       <c r="M85">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N85">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4263,25 +4263,25 @@
         <v>25</v>
       </c>
       <c r="H86">
-        <v>0.6246231059657705</v>
+        <v>0.6313917580217497</v>
       </c>
       <c r="I86">
-        <v>0.6229046909729917</v>
+        <v>0.6286019690076095</v>
       </c>
       <c r="J86">
-        <v>0.5202119775070408</v>
+        <v>0.5174773413456093</v>
       </c>
       <c r="K86">
-        <v>0.7438123191555193</v>
+        <v>0.7617073641794185</v>
       </c>
       <c r="L86">
         <v>10000</v>
       </c>
       <c r="M86">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N86">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4307,25 +4307,25 @@
         <v>26</v>
       </c>
       <c r="H87">
-        <v>1702.553219208993</v>
+        <v>1778.326837165803</v>
       </c>
       <c r="I87">
-        <v>1689.691650199756</v>
+        <v>1779.892877000475</v>
       </c>
       <c r="J87">
-        <v>1420.416330073579</v>
+        <v>1515.356564447556</v>
       </c>
       <c r="K87">
-        <v>1901.667082821808</v>
+        <v>2018.118535630843</v>
       </c>
       <c r="L87">
         <v>10000</v>
       </c>
       <c r="M87">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N87">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -4351,25 +4351,25 @@
         <v>27</v>
       </c>
       <c r="H88">
-        <v>2789.771183386524</v>
+        <v>2911.41473387027</v>
       </c>
       <c r="I88">
-        <v>2782.15528771223</v>
+        <v>2896.956090033514</v>
       </c>
       <c r="J88">
-        <v>1087.340672336203</v>
+        <v>1421.691069906315</v>
       </c>
       <c r="K88">
-        <v>4592.482352121326</v>
+        <v>4481.689791314777</v>
       </c>
       <c r="L88">
         <v>10000</v>
       </c>
       <c r="M88">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N88">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -4395,25 +4395,25 @@
         <v>28</v>
       </c>
       <c r="H89">
-        <v>0.2617721506285441</v>
+        <v>0.2696011650079878</v>
       </c>
       <c r="I89">
-        <v>0.2522673962638359</v>
+        <v>0.2627973705783089</v>
       </c>
       <c r="J89">
-        <v>0.1523018712391045</v>
+        <v>0.1573736575601379</v>
       </c>
       <c r="K89">
-        <v>0.4056182216698112</v>
+        <v>0.4103193753233522</v>
       </c>
       <c r="L89">
         <v>10000</v>
       </c>
       <c r="M89">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="N89">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -4439,25 +4439,25 @@
         <v>18</v>
       </c>
       <c r="H90">
-        <v>5790.257456297879</v>
+        <v>5962.348037050615</v>
       </c>
       <c r="I90">
-        <v>5618.966662518065</v>
+        <v>5703.247623759566</v>
       </c>
       <c r="J90">
-        <v>4123.318657656348</v>
+        <v>4065.846493004456</v>
       </c>
       <c r="K90">
-        <v>8412.961665266292</v>
+        <v>8967.583522203573</v>
       </c>
       <c r="L90">
         <v>10000</v>
       </c>
       <c r="M90">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N90">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -4483,25 +4483,25 @@
         <v>19</v>
       </c>
       <c r="H91">
-        <v>0.2910599242124465</v>
+        <v>0.2856473467658514</v>
       </c>
       <c r="I91">
-        <v>0.2808003466246271</v>
+        <v>0.2815640977803122</v>
       </c>
       <c r="J91">
-        <v>0.1715113949552468</v>
+        <v>0.1516377397971884</v>
       </c>
       <c r="K91">
-        <v>0.4916102161630939</v>
+        <v>0.4776711103827893</v>
       </c>
       <c r="L91">
         <v>10000</v>
       </c>
       <c r="M91">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N91">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4527,25 +4527,25 @@
         <v>20</v>
       </c>
       <c r="H92">
-        <v>8588.285187367752</v>
+        <v>8914.4986680374</v>
       </c>
       <c r="I92">
-        <v>8753.749967998911</v>
+        <v>9037.262515664428</v>
       </c>
       <c r="J92">
-        <v>3253.031351315968</v>
+        <v>2710.333803647172</v>
       </c>
       <c r="K92">
-        <v>12974.1675378935</v>
+        <v>13819.39082122189</v>
       </c>
       <c r="L92">
         <v>10000</v>
       </c>
       <c r="M92">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N92">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -4571,25 +4571,25 @@
         <v>21</v>
       </c>
       <c r="H93">
-        <v>0.4153690372479473</v>
+        <v>0.4104881444825619</v>
       </c>
       <c r="I93">
-        <v>0.4418078655798539</v>
+        <v>0.4422553769962673</v>
       </c>
       <c r="J93">
-        <v>0.1822191127312429</v>
+        <v>0.1687101842289484</v>
       </c>
       <c r="K93">
-        <v>0.4973522156362331</v>
+        <v>0.4976507202364388</v>
       </c>
       <c r="L93">
         <v>10000</v>
       </c>
       <c r="M93">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N93">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -4615,25 +4615,25 @@
         <v>22</v>
       </c>
       <c r="H94">
-        <v>0.6387636289382056</v>
+        <v>0.6385236077343648</v>
       </c>
       <c r="I94">
-        <v>0.6232002816955886</v>
+        <v>0.6246429473971874</v>
       </c>
       <c r="J94">
-        <v>0.3351103631029397</v>
+        <v>0.3279200865340658</v>
       </c>
       <c r="K94">
-        <v>1.074048760623468</v>
+        <v>1.076588286979793</v>
       </c>
       <c r="L94">
         <v>10000</v>
       </c>
       <c r="M94">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N94">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -4659,25 +4659,25 @@
         <v>23</v>
       </c>
       <c r="H95">
-        <v>0.6958052768721146</v>
+        <v>0.7003438054521957</v>
       </c>
       <c r="I95">
-        <v>0.6818145546979815</v>
+        <v>0.6852960745601874</v>
       </c>
       <c r="J95">
-        <v>0.3750894915691633</v>
+        <v>0.3725661365841554</v>
       </c>
       <c r="K95">
-        <v>1.118718769416768</v>
+        <v>1.14343706174062</v>
       </c>
       <c r="L95">
         <v>10000</v>
       </c>
       <c r="M95">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N95">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -4703,25 +4703,25 @@
         <v>24</v>
       </c>
       <c r="H96">
-        <v>20817.34505741964</v>
+        <v>21876.33507610602</v>
       </c>
       <c r="I96">
-        <v>20697.61026447082</v>
+        <v>22059.54882141604</v>
       </c>
       <c r="J96">
-        <v>11327.70904397855</v>
+        <v>11317.8456973839</v>
       </c>
       <c r="K96">
-        <v>32374.22244807966</v>
+        <v>35097.37198846892</v>
       </c>
       <c r="L96">
         <v>10000</v>
       </c>
       <c r="M96">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N96">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -4747,25 +4747,25 @@
         <v>25</v>
       </c>
       <c r="H97">
-        <v>0.91759004638219</v>
+        <v>0.911660105081246</v>
       </c>
       <c r="I97">
-        <v>0.9128779511555655</v>
+        <v>0.9103834900264469</v>
       </c>
       <c r="J97">
-        <v>0.7636358750824277</v>
+        <v>0.7348790420993268</v>
       </c>
       <c r="K97">
-        <v>1.120263972412907</v>
+        <v>1.111342308033534</v>
       </c>
       <c r="L97">
         <v>10000</v>
       </c>
       <c r="M97">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N97">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -4791,25 +4791,25 @@
         <v>26</v>
       </c>
       <c r="H98">
-        <v>1774.107040278283</v>
+        <v>1812.729668500996</v>
       </c>
       <c r="I98">
-        <v>1779.714733372287</v>
+        <v>1809.239947653631</v>
       </c>
       <c r="J98">
-        <v>1513.226857017925</v>
+        <v>1592.16028491316</v>
       </c>
       <c r="K98">
-        <v>2015.80014922281</v>
+        <v>2018.639912913117</v>
       </c>
       <c r="L98">
         <v>10000</v>
       </c>
       <c r="M98">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N98">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -4835,25 +4835,25 @@
         <v>27</v>
       </c>
       <c r="H99">
-        <v>3139.800828491763</v>
+        <v>3257.509799674157</v>
       </c>
       <c r="I99">
-        <v>3176.731407918291</v>
+        <v>3286.994930722095</v>
       </c>
       <c r="J99">
-        <v>1244.404175276711</v>
+        <v>955.0710459031516</v>
       </c>
       <c r="K99">
-        <v>4738.207463839792</v>
+        <v>5199.633491413317</v>
       </c>
       <c r="L99">
         <v>10000</v>
       </c>
       <c r="M99">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N99">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -4879,25 +4879,25 @@
         <v>28</v>
       </c>
       <c r="H100">
-        <v>0.3181454978978378</v>
+        <v>0.3182169187042447</v>
       </c>
       <c r="I100">
-        <v>0.3181388547589564</v>
+        <v>0.3201619335904252</v>
       </c>
       <c r="J100">
-        <v>0.1950117771885382</v>
+        <v>0.1905716839015798</v>
       </c>
       <c r="K100">
-        <v>0.4538147050650125</v>
+        <v>0.4583550047301129</v>
       </c>
       <c r="L100">
         <v>10000</v>
       </c>
       <c r="M100">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="N100">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -4923,25 +4923,25 @@
         <v>18</v>
       </c>
       <c r="H101">
-        <v>7916.27830871792</v>
+        <v>8015.497639537463</v>
       </c>
       <c r="I101">
-        <v>7177.206061744403</v>
+        <v>7355.62344187386</v>
       </c>
       <c r="J101">
-        <v>4570.98300436285</v>
+        <v>4821.322831302681</v>
       </c>
       <c r="K101">
-        <v>16835.96701840239</v>
+        <v>16410.17931295161</v>
       </c>
       <c r="L101">
         <v>10000</v>
       </c>
       <c r="M101">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N101">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -4967,25 +4967,25 @@
         <v>19</v>
       </c>
       <c r="H102">
-        <v>0.3256335880830005</v>
+        <v>0.3312340166176628</v>
       </c>
       <c r="I102">
-        <v>0.324777855820651</v>
+        <v>0.3309002580108071</v>
       </c>
       <c r="J102">
-        <v>0.1935750835295134</v>
+        <v>0.2002409180546243</v>
       </c>
       <c r="K102">
-        <v>0.4726727576113772</v>
+        <v>0.4770240903591298</v>
       </c>
       <c r="L102">
         <v>10000</v>
       </c>
       <c r="M102">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N102">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -5011,25 +5011,25 @@
         <v>20</v>
       </c>
       <c r="H103">
-        <v>17585.02682308605</v>
+        <v>17335.2299429892</v>
       </c>
       <c r="I103">
-        <v>14441.35164163577</v>
+        <v>14433.49327898721</v>
       </c>
       <c r="J103">
-        <v>7165.780669183731</v>
+        <v>7277.646078304422</v>
       </c>
       <c r="K103">
-        <v>51647.29425687611</v>
+        <v>49576.19490982538</v>
       </c>
       <c r="L103">
         <v>10000</v>
       </c>
       <c r="M103">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N103">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5055,25 +5055,25 @@
         <v>21</v>
       </c>
       <c r="H104">
-        <v>0.683201780960413</v>
+        <v>0.6798898689573918</v>
       </c>
       <c r="I104">
-        <v>0.690027862460305</v>
+        <v>0.6825560171591705</v>
       </c>
       <c r="J104">
-        <v>0.3315769174923187</v>
+        <v>0.3162799124236851</v>
       </c>
       <c r="K104">
-        <v>0.9772457317908091</v>
+        <v>0.9755583466794659</v>
       </c>
       <c r="L104">
         <v>10000</v>
       </c>
       <c r="M104">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N104">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -5099,25 +5099,25 @@
         <v>22</v>
       </c>
       <c r="H105">
-        <v>0.4572107846166508</v>
+        <v>0.4540348627051097</v>
       </c>
       <c r="I105">
-        <v>0.437161486852375</v>
+        <v>0.4345489600059526</v>
       </c>
       <c r="J105">
-        <v>0.2400949828844208</v>
+        <v>0.2329910121368805</v>
       </c>
       <c r="K105">
-        <v>0.7840894481659354</v>
+        <v>0.7674687741503705</v>
       </c>
       <c r="L105">
         <v>10000</v>
       </c>
       <c r="M105">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N105">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5143,25 +5143,25 @@
         <v>23</v>
       </c>
       <c r="H106">
-        <v>0.7457937918147646</v>
+        <v>0.741842943668731</v>
       </c>
       <c r="I106">
-        <v>0.7187859755811506</v>
+        <v>0.7165043331869128</v>
       </c>
       <c r="J106">
-        <v>0.4058883696640245</v>
+        <v>0.3949662550498259</v>
       </c>
       <c r="K106">
-        <v>1.238029547773714</v>
+        <v>1.232357927615672</v>
       </c>
       <c r="L106">
         <v>10000</v>
       </c>
       <c r="M106">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N106">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -5187,25 +5187,25 @@
         <v>24</v>
       </c>
       <c r="H107">
-        <v>24996.1823298301</v>
+        <v>24906.88083530241</v>
       </c>
       <c r="I107">
-        <v>22028.20903469654</v>
+        <v>22207.78975687345</v>
       </c>
       <c r="J107">
-        <v>15660.23671072012</v>
+        <v>15555.94290162477</v>
       </c>
       <c r="K107">
-        <v>57352.54573956707</v>
+        <v>55792.88863152181</v>
       </c>
       <c r="L107">
         <v>10000</v>
       </c>
       <c r="M107">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N107">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -5231,25 +5231,25 @@
         <v>25</v>
       </c>
       <c r="H108">
-        <v>0.6127613700158908</v>
+        <v>0.6123301961253376</v>
       </c>
       <c r="I108">
-        <v>0.6102852484264505</v>
+        <v>0.6091837374855409</v>
       </c>
       <c r="J108">
-        <v>0.5022376209929812</v>
+        <v>0.5062477246922491</v>
       </c>
       <c r="K108">
-        <v>0.7391019269038981</v>
+        <v>0.7342771912411247</v>
       </c>
       <c r="L108">
         <v>10000</v>
       </c>
       <c r="M108">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N108">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -5275,25 +5275,25 @@
         <v>26</v>
       </c>
       <c r="H109">
-        <v>2082.793261539955</v>
+        <v>2105.373891029178</v>
       </c>
       <c r="I109">
-        <v>1885.944024244911</v>
+        <v>1918.338164500087</v>
       </c>
       <c r="J109">
-        <v>1591.185143711475</v>
+        <v>1660.966386973631</v>
       </c>
       <c r="K109">
-        <v>4371.008299309227</v>
+        <v>4267.149540232636</v>
       </c>
       <c r="L109">
         <v>10000</v>
       </c>
       <c r="M109">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N109">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -5319,25 +5319,25 @@
         <v>27</v>
       </c>
       <c r="H110">
-        <v>5078.05835602465</v>
+        <v>5025.644556691486</v>
       </c>
       <c r="I110">
-        <v>4327.529767267876</v>
+        <v>4347.930836764022</v>
       </c>
       <c r="J110">
-        <v>1995.237488144188</v>
+        <v>2008.668530117733</v>
       </c>
       <c r="K110">
-        <v>13500.5384606472</v>
+        <v>13686.29587318977</v>
       </c>
       <c r="L110">
         <v>10000</v>
       </c>
       <c r="M110">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N110">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -5363,25 +5363,25 @@
         <v>28</v>
       </c>
       <c r="H111">
-        <v>0.2761518196158718</v>
+        <v>0.274891672037986</v>
       </c>
       <c r="I111">
-        <v>0.2712362749577821</v>
+        <v>0.2690928574674308</v>
       </c>
       <c r="J111">
-        <v>0.1638273753688913</v>
+        <v>0.159564768287226</v>
       </c>
       <c r="K111">
-        <v>0.4157976769647329</v>
+        <v>0.4142232691010326</v>
       </c>
       <c r="L111">
         <v>10000</v>
       </c>
       <c r="M111">
-        <v>2601</v>
+        <v>2650</v>
       </c>
       <c r="N111">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -5407,25 +5407,25 @@
         <v>18</v>
       </c>
       <c r="H112">
-        <v>7707.4646304921</v>
+        <v>7842.496230585691</v>
       </c>
       <c r="I112">
-        <v>7010.13893036634</v>
+        <v>7164.228170236271</v>
       </c>
       <c r="J112">
-        <v>4634.548848217924</v>
+        <v>4637.607911417929</v>
       </c>
       <c r="K112">
-        <v>15735.43980250948</v>
+        <v>15567.12700026825</v>
       </c>
       <c r="L112">
         <v>10000</v>
       </c>
       <c r="M112">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N112">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -5451,25 +5451,25 @@
         <v>19</v>
       </c>
       <c r="H113">
-        <v>0.3253776203596022</v>
+        <v>0.3251591799296323</v>
       </c>
       <c r="I113">
-        <v>0.3258284038622234</v>
+        <v>0.3266133224467632</v>
       </c>
       <c r="J113">
-        <v>0.1946181793525004</v>
+        <v>0.1947815026148465</v>
       </c>
       <c r="K113">
-        <v>0.4679594895924745</v>
+        <v>0.4666464905543853</v>
       </c>
       <c r="L113">
         <v>10000</v>
       </c>
       <c r="M113">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N113">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5495,25 +5495,25 @@
         <v>20</v>
       </c>
       <c r="H114">
-        <v>17059.9705385993</v>
+        <v>17432.71352463407</v>
       </c>
       <c r="I114">
-        <v>14054.20630192981</v>
+        <v>14270.14542143759</v>
       </c>
       <c r="J114">
-        <v>7174.811228422399</v>
+        <v>7084.11878165702</v>
       </c>
       <c r="K114">
-        <v>47515.54756931293</v>
+        <v>48571.81913981635</v>
       </c>
       <c r="L114">
         <v>10000</v>
       </c>
       <c r="M114">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N114">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -5539,25 +5539,25 @@
         <v>21</v>
       </c>
       <c r="H115">
-        <v>0.6806946023630345</v>
+        <v>0.6832114217746528</v>
       </c>
       <c r="I115">
-        <v>0.6848531588456728</v>
+        <v>0.6878473835443744</v>
       </c>
       <c r="J115">
-        <v>0.3169836918979087</v>
+        <v>0.330256536790952</v>
       </c>
       <c r="K115">
-        <v>0.9770986460179599</v>
+        <v>0.9740181624884201</v>
       </c>
       <c r="L115">
         <v>10000</v>
       </c>
       <c r="M115">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N115">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -5583,25 +5583,25 @@
         <v>22</v>
       </c>
       <c r="H116">
-        <v>0.4703712188802757</v>
+        <v>0.4729544383268965</v>
       </c>
       <c r="I116">
-        <v>0.4520655285363719</v>
+        <v>0.4558971962680298</v>
       </c>
       <c r="J116">
-        <v>0.2541284618742878</v>
+        <v>0.2503992932281701</v>
       </c>
       <c r="K116">
-        <v>0.7851631047242988</v>
+        <v>0.7979297626295356</v>
       </c>
       <c r="L116">
         <v>10000</v>
       </c>
       <c r="M116">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N116">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -5627,25 +5627,25 @@
         <v>23</v>
       </c>
       <c r="H117">
-        <v>0.7491063133589801</v>
+        <v>0.7535986502148458</v>
       </c>
       <c r="I117">
-        <v>0.7233791519649322</v>
+        <v>0.7259861694691486</v>
       </c>
       <c r="J117">
-        <v>0.4185470086432214</v>
+        <v>0.4187191683211219</v>
       </c>
       <c r="K117">
-        <v>1.243277726407205</v>
+        <v>1.244366378770463</v>
       </c>
       <c r="L117">
         <v>10000</v>
       </c>
       <c r="M117">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N117">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -5671,25 +5671,25 @@
         <v>24</v>
       </c>
       <c r="H118">
-        <v>24374.90011729125</v>
+        <v>24853.21473581164</v>
       </c>
       <c r="I118">
-        <v>21636.30457727422</v>
+        <v>22015.53966692206</v>
       </c>
       <c r="J118">
-        <v>15603.80064924322</v>
+        <v>15685.57251884446</v>
       </c>
       <c r="K118">
-        <v>53733.58542557591</v>
+        <v>56372.22247539125</v>
       </c>
       <c r="L118">
         <v>10000</v>
       </c>
       <c r="M118">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N118">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -5715,25 +5715,25 @@
         <v>25</v>
       </c>
       <c r="H119">
-        <v>0.6282838986168311</v>
+        <v>0.6279137223153911</v>
       </c>
       <c r="I119">
-        <v>0.6238525678283064</v>
+        <v>0.6268813581977085</v>
       </c>
       <c r="J119">
-        <v>0.5148318912431213</v>
+        <v>0.5122326767672449</v>
       </c>
       <c r="K119">
-        <v>0.7611831741380765</v>
+        <v>0.7538576495259629</v>
       </c>
       <c r="L119">
         <v>10000</v>
       </c>
       <c r="M119">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N119">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -5759,25 +5759,25 @@
         <v>26</v>
       </c>
       <c r="H120">
-        <v>2071.901064368466</v>
+        <v>2111.999485425955</v>
       </c>
       <c r="I120">
-        <v>1885.59195028412</v>
+        <v>1920.761358638109</v>
       </c>
       <c r="J120">
-        <v>1598.615987764362</v>
+        <v>1679.038645894988</v>
       </c>
       <c r="K120">
-        <v>4064.065480070441</v>
+        <v>4209.683934400912</v>
       </c>
       <c r="L120">
         <v>10000</v>
       </c>
       <c r="M120">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N120">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -5803,25 +5803,25 @@
         <v>27</v>
       </c>
       <c r="H121">
-        <v>5046.181104495868</v>
+        <v>5167.526825099596</v>
       </c>
       <c r="I121">
-        <v>4344.915350850498</v>
+        <v>4435.413685884891</v>
       </c>
       <c r="J121">
-        <v>1939.287662133169</v>
+        <v>2163.045368250185</v>
       </c>
       <c r="K121">
-        <v>13895.96267650609</v>
+        <v>14021.33909671678</v>
       </c>
       <c r="L121">
         <v>10000</v>
       </c>
       <c r="M121">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N121">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -5847,25 +5847,25 @@
         <v>28</v>
       </c>
       <c r="H122">
-        <v>0.2809311849662279</v>
+        <v>0.2822364406750788</v>
       </c>
       <c r="I122">
-        <v>0.2760220731431445</v>
+        <v>0.277711622178094</v>
       </c>
       <c r="J122">
-        <v>0.1699112959845668</v>
+        <v>0.1701489437135044</v>
       </c>
       <c r="K122">
-        <v>0.4192084437424697</v>
+        <v>0.4208470590159274</v>
       </c>
       <c r="L122">
         <v>10000</v>
       </c>
       <c r="M122">
-        <v>2644</v>
+        <v>2633</v>
       </c>
       <c r="N122">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -5891,25 +5891,25 @@
         <v>18</v>
       </c>
       <c r="H123">
-        <v>6754.654247055953</v>
+        <v>6970.221121922668</v>
       </c>
       <c r="I123">
-        <v>5991.178135555809</v>
+        <v>6152.936946955181</v>
       </c>
       <c r="J123">
-        <v>4149.273103418855</v>
+        <v>4221.554350326298</v>
       </c>
       <c r="K123">
-        <v>16026.03853325012</v>
+        <v>16113.80581546458</v>
       </c>
       <c r="L123">
         <v>10000</v>
       </c>
       <c r="M123">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N123">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -5935,25 +5935,25 @@
         <v>19</v>
       </c>
       <c r="H124">
-        <v>0.3054736752821584</v>
+        <v>0.3070326542068031</v>
       </c>
       <c r="I124">
-        <v>0.3062029635508176</v>
+        <v>0.3065085168952886</v>
       </c>
       <c r="J124">
-        <v>0.1819710890571374</v>
+        <v>0.1828521640105685</v>
       </c>
       <c r="K124">
-        <v>0.4237972887743628</v>
+        <v>0.4512671340234631</v>
       </c>
       <c r="L124">
         <v>10000</v>
       </c>
       <c r="M124">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N124">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -5979,25 +5979,25 @@
         <v>20</v>
       </c>
       <c r="H125">
-        <v>16241.16509047429</v>
+        <v>16860.20410364146</v>
       </c>
       <c r="I125">
-        <v>13189.56697507538</v>
+        <v>13743.88580909391</v>
       </c>
       <c r="J125">
-        <v>6426.078411049864</v>
+        <v>7085.855670927393</v>
       </c>
       <c r="K125">
-        <v>53872.16555110524</v>
+        <v>53033.8706740932</v>
       </c>
       <c r="L125">
         <v>10000</v>
       </c>
       <c r="M125">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N125">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6023,25 +6023,25 @@
         <v>21</v>
       </c>
       <c r="H126">
-        <v>0.6880026966595206</v>
+        <v>0.696282152082021</v>
       </c>
       <c r="I126">
-        <v>0.6909544865108406</v>
+        <v>0.6962605096183686</v>
       </c>
       <c r="J126">
-        <v>0.3291478617148254</v>
+        <v>0.3659887544087626</v>
       </c>
       <c r="K126">
-        <v>0.9766430806003654</v>
+        <v>0.9821389474358646</v>
       </c>
       <c r="L126">
         <v>10000</v>
       </c>
       <c r="M126">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N126">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6067,25 +6067,25 @@
         <v>22</v>
       </c>
       <c r="H127">
-        <v>0.6687148767482751</v>
+        <v>0.6609082282041185</v>
       </c>
       <c r="I127">
-        <v>0.6414108565643502</v>
+        <v>0.6406528788352918</v>
       </c>
       <c r="J127">
-        <v>0.3577606834732284</v>
+        <v>0.3612975601440467</v>
       </c>
       <c r="K127">
-        <v>1.111629822469121</v>
+        <v>1.109392061872319</v>
       </c>
       <c r="L127">
         <v>10000</v>
       </c>
       <c r="M127">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N127">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6111,25 +6111,25 @@
         <v>23</v>
       </c>
       <c r="H128">
-        <v>0.7301469080240576</v>
+        <v>0.7246270918141515</v>
       </c>
       <c r="I128">
-        <v>0.7070154995053128</v>
+        <v>0.7043378789587131</v>
       </c>
       <c r="J128">
-        <v>0.4051375344995057</v>
+        <v>0.4034275092855921</v>
       </c>
       <c r="K128">
-        <v>1.192965653848615</v>
+        <v>1.198301792964578</v>
       </c>
       <c r="L128">
         <v>10000</v>
       </c>
       <c r="M128">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N128">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6155,25 +6155,25 @@
         <v>24</v>
       </c>
       <c r="H129">
-        <v>22730.64310743393</v>
+        <v>23377.84207814925</v>
       </c>
       <c r="I129">
-        <v>19492.86309143458</v>
+        <v>20231.302959056</v>
       </c>
       <c r="J129">
-        <v>14881.07370537047</v>
+        <v>14909.76204364769</v>
       </c>
       <c r="K129">
-        <v>58718.31630508169</v>
+        <v>57903.77619178206</v>
       </c>
       <c r="L129">
         <v>10000</v>
       </c>
       <c r="M129">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N129">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6199,25 +6199,25 @@
         <v>25</v>
       </c>
       <c r="H130">
-        <v>0.9159778559824597</v>
+        <v>0.9135751845583476</v>
       </c>
       <c r="I130">
-        <v>0.9104772068179458</v>
+        <v>0.9077448205394676</v>
       </c>
       <c r="J130">
-        <v>0.7506372251264619</v>
+        <v>0.7478800028653962</v>
       </c>
       <c r="K130">
-        <v>1.108465468098505</v>
+        <v>1.105236802511282</v>
       </c>
       <c r="L130">
         <v>10000</v>
       </c>
       <c r="M130">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N130">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6243,25 +6243,25 @@
         <v>26</v>
       </c>
       <c r="H131">
-        <v>2140.497043516758</v>
+        <v>2204.14775223677</v>
       </c>
       <c r="I131">
-        <v>1907.843899139607</v>
+        <v>1932.920679434467</v>
       </c>
       <c r="J131">
-        <v>1658.326533659113</v>
+        <v>1721.930093807285</v>
       </c>
       <c r="K131">
-        <v>5037.183619841665</v>
+        <v>5310.358291766477</v>
       </c>
       <c r="L131">
         <v>10000</v>
       </c>
       <c r="M131">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N131">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6287,25 +6287,25 @@
         <v>27</v>
       </c>
       <c r="H132">
-        <v>5657.11109314147</v>
+        <v>5857.911184278087</v>
       </c>
       <c r="I132">
-        <v>4734.133743749477</v>
+        <v>4827.734695850267</v>
       </c>
       <c r="J132">
-        <v>2286.551771255532</v>
+        <v>2573.927409675144</v>
       </c>
       <c r="K132">
-        <v>17899.99475987996</v>
+        <v>17766.50760161853</v>
       </c>
       <c r="L132">
         <v>10000</v>
       </c>
       <c r="M132">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N132">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -6331,25 +6331,25 @@
         <v>28</v>
       </c>
       <c r="H133">
-        <v>0.3293637528482228</v>
+        <v>0.3271197172476626</v>
       </c>
       <c r="I133">
-        <v>0.3267415796110679</v>
+        <v>0.3263057201396984</v>
       </c>
       <c r="J133">
-        <v>0.2052320899187248</v>
+        <v>0.2072041060977947</v>
       </c>
       <c r="K133">
-        <v>0.4713956396189692</v>
+        <v>0.4721091497850981</v>
       </c>
       <c r="L133">
         <v>10000</v>
       </c>
       <c r="M133">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="N133">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tabela_resumo_dbsra_macarellus.xlsx
+++ b/Catch models/tabela_resumo_dbsra_macarellus.xlsx
@@ -567,25 +567,25 @@
         <v>18</v>
       </c>
       <c r="H2">
-        <v>7273.666107631355</v>
+        <v>7420.143536184993</v>
       </c>
       <c r="I2">
-        <v>7026.3594748932</v>
+        <v>7278.663674722621</v>
       </c>
       <c r="J2">
-        <v>5080.472090872069</v>
+        <v>4599.398135822809</v>
       </c>
       <c r="K2">
-        <v>10464.86748319846</v>
+        <v>10598.16697965652</v>
       </c>
       <c r="L2">
         <v>10000</v>
       </c>
       <c r="M2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N2">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -611,25 +611,25 @@
         <v>19</v>
       </c>
       <c r="H3">
-        <v>0.3119947282247122</v>
+        <v>0.285213524528813</v>
       </c>
       <c r="I3">
-        <v>0.3146381294127724</v>
+        <v>0.2795760013265762</v>
       </c>
       <c r="J3">
-        <v>0.1318318586621171</v>
+        <v>0.1316210012676073</v>
       </c>
       <c r="K3">
-        <v>0.5377221337316416</v>
+        <v>0.444578033645669</v>
       </c>
       <c r="L3">
         <v>10000</v>
       </c>
       <c r="M3">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N3">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -655,25 +655,25 @@
         <v>20</v>
       </c>
       <c r="H4">
-        <v>4749.580687244952</v>
+        <v>5217.290110324049</v>
       </c>
       <c r="I4">
-        <v>4480.713838774964</v>
+        <v>5037.695055299327</v>
       </c>
       <c r="J4">
-        <v>1466.189519168164</v>
+        <v>1604.757798861368</v>
       </c>
       <c r="K4">
-        <v>9325.670353131514</v>
+        <v>9568.93702817576</v>
       </c>
       <c r="L4">
         <v>10000</v>
       </c>
       <c r="M4">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N4">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -699,25 +699,25 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>0.1845226397745648</v>
+        <v>0.1873061908996868</v>
       </c>
       <c r="I5">
-        <v>0.1979537604596424</v>
+        <v>0.2013298753408282</v>
       </c>
       <c r="J5">
-        <v>0.0695236541062873</v>
+        <v>0.06595283592496763</v>
       </c>
       <c r="K5">
-        <v>0.2479766039371336</v>
+        <v>0.2479965850024693</v>
       </c>
       <c r="L5">
         <v>10000</v>
       </c>
       <c r="M5">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N5">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -743,25 +743,25 @@
         <v>22</v>
       </c>
       <c r="H6">
-        <v>0.3892729372683353</v>
+        <v>0.3843562693418132</v>
       </c>
       <c r="I6">
-        <v>0.3686333754642635</v>
+        <v>0.3495423219532524</v>
       </c>
       <c r="J6">
-        <v>0.2219792566046727</v>
+        <v>0.2204690607240764</v>
       </c>
       <c r="K6">
-        <v>0.6712396651401078</v>
+        <v>0.743901744762269</v>
       </c>
       <c r="L6">
         <v>10000</v>
       </c>
       <c r="M6">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N6">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -787,25 +787,25 @@
         <v>23</v>
       </c>
       <c r="H7">
-        <v>0.6546665219535609</v>
+        <v>0.6375829901437179</v>
       </c>
       <c r="I7">
-        <v>0.6194483485435378</v>
+        <v>0.5868128055966139</v>
       </c>
       <c r="J7">
-        <v>0.3692640040481108</v>
+        <v>0.3612777955266537</v>
       </c>
       <c r="K7">
-        <v>1.105798808863663</v>
+        <v>1.125419389573034</v>
       </c>
       <c r="L7">
         <v>10000</v>
       </c>
       <c r="M7">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N7">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -831,25 +831,25 @@
         <v>24</v>
       </c>
       <c r="H8">
-        <v>25681.86796034881</v>
+        <v>27838.062175413</v>
       </c>
       <c r="I8">
-        <v>24701.46922917609</v>
+        <v>24767.69393812165</v>
       </c>
       <c r="J8">
-        <v>11318.77453298669</v>
+        <v>16431.30139911224</v>
       </c>
       <c r="K8">
-        <v>45531.12794537794</v>
+        <v>46797.62727440743</v>
       </c>
       <c r="L8">
         <v>10000</v>
       </c>
       <c r="M8">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N8">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -875,25 +875,25 @@
         <v>25</v>
       </c>
       <c r="H9">
-        <v>0.598300305133563</v>
+        <v>0.6008499856375369</v>
       </c>
       <c r="I9">
-        <v>0.5972509516880646</v>
+        <v>0.5942086983970615</v>
       </c>
       <c r="J9">
-        <v>0.5034576536017115</v>
+        <v>0.507684142971784</v>
       </c>
       <c r="K9">
-        <v>0.7251042421365946</v>
+        <v>0.7358925787066823</v>
       </c>
       <c r="L9">
         <v>10000</v>
       </c>
       <c r="M9">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N9">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -919,25 +919,25 @@
         <v>26</v>
       </c>
       <c r="H10">
-        <v>1701.705992989962</v>
+        <v>1678.238293846935</v>
       </c>
       <c r="I10">
-        <v>1708.684063534089</v>
+        <v>1696.850683904675</v>
       </c>
       <c r="J10">
-        <v>1300.884271090898</v>
+        <v>1354.873080015484</v>
       </c>
       <c r="K10">
-        <v>2028.391810603788</v>
+        <v>1950.388645628003</v>
       </c>
       <c r="L10">
         <v>10000</v>
       </c>
       <c r="M10">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N10">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -963,25 +963,25 @@
         <v>27</v>
       </c>
       <c r="H11">
-        <v>1333.560690292407</v>
+        <v>1451.191258520573</v>
       </c>
       <c r="I11">
-        <v>1330.049233688347</v>
+        <v>1480.25632676221</v>
       </c>
       <c r="J11">
-        <v>458.6331121427226</v>
+        <v>533.0518815817867</v>
       </c>
       <c r="K11">
-        <v>2476.763984489078</v>
+        <v>2696.006344558565</v>
       </c>
       <c r="L11">
         <v>10000</v>
       </c>
       <c r="M11">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N11">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1007,25 +1007,25 @@
         <v>28</v>
       </c>
       <c r="H12">
-        <v>0.24418398771015</v>
+        <v>0.2392801300386966</v>
       </c>
       <c r="I12">
-        <v>0.2365248299874899</v>
+        <v>0.226318019656455</v>
       </c>
       <c r="J12">
-        <v>0.1514465089995924</v>
+        <v>0.1477134686961622</v>
       </c>
       <c r="K12">
-        <v>0.3834690123350735</v>
+        <v>0.4124915969050763</v>
       </c>
       <c r="L12">
         <v>10000</v>
       </c>
       <c r="M12">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N12">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1051,25 +1051,25 @@
         <v>18</v>
       </c>
       <c r="H13">
-        <v>7117.575373257861</v>
+        <v>7115.836611951539</v>
       </c>
       <c r="I13">
-        <v>6980.198127257525</v>
+        <v>6930.273996380904</v>
       </c>
       <c r="J13">
-        <v>4919.553410659139</v>
+        <v>4805.204495227322</v>
       </c>
       <c r="K13">
-        <v>10065.64295354961</v>
+        <v>9912.427344647367</v>
       </c>
       <c r="L13">
         <v>10000</v>
       </c>
       <c r="M13">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N13">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1095,25 +1095,25 @@
         <v>19</v>
       </c>
       <c r="H14">
-        <v>0.3044968517622373</v>
+        <v>0.2757589167447997</v>
       </c>
       <c r="I14">
-        <v>0.3029400063669293</v>
+        <v>0.2723600485056674</v>
       </c>
       <c r="J14">
-        <v>0.140769982663112</v>
+        <v>0.1296566946342195</v>
       </c>
       <c r="K14">
-        <v>0.5003905389844165</v>
+        <v>0.4202544079697499</v>
       </c>
       <c r="L14">
         <v>10000</v>
       </c>
       <c r="M14">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N14">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1139,25 +1139,25 @@
         <v>20</v>
       </c>
       <c r="H15">
-        <v>4834.663620079497</v>
+        <v>5334.081258655536</v>
       </c>
       <c r="I15">
-        <v>4803.283029003742</v>
+        <v>5510.263986301667</v>
       </c>
       <c r="J15">
-        <v>1016.063355464687</v>
+        <v>1549.760781321321</v>
       </c>
       <c r="K15">
-        <v>9270.451368640779</v>
+        <v>9463.869057801297</v>
       </c>
       <c r="L15">
         <v>10000</v>
       </c>
       <c r="M15">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N15">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1183,25 +1183,25 @@
         <v>21</v>
       </c>
       <c r="H16">
-        <v>0.1803898799072416</v>
+        <v>0.1883627333265687</v>
       </c>
       <c r="I16">
-        <v>0.1949983102897295</v>
+        <v>0.2054236156419181</v>
       </c>
       <c r="J16">
-        <v>0.05932911460379973</v>
+        <v>0.06380994895577183</v>
       </c>
       <c r="K16">
-        <v>0.2460156120247551</v>
+        <v>0.246839072375099</v>
       </c>
       <c r="L16">
         <v>10000</v>
       </c>
       <c r="M16">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N16">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1227,25 +1227,25 @@
         <v>22</v>
       </c>
       <c r="H17">
-        <v>0.4053111289118926</v>
+        <v>0.3965898806649449</v>
       </c>
       <c r="I17">
-        <v>0.3781808908070914</v>
+        <v>0.3757656907302915</v>
       </c>
       <c r="J17">
-        <v>0.2394490845309989</v>
+        <v>0.2387335109043745</v>
       </c>
       <c r="K17">
-        <v>0.7357373641540543</v>
+        <v>0.6649302877386957</v>
       </c>
       <c r="L17">
         <v>10000</v>
       </c>
       <c r="M17">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N17">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1271,25 +1271,25 @@
         <v>23</v>
       </c>
       <c r="H18">
-        <v>0.6475482630354171</v>
+        <v>0.637235759450905</v>
       </c>
       <c r="I18">
-        <v>0.6156410432614883</v>
+        <v>0.6000187790628821</v>
       </c>
       <c r="J18">
-        <v>0.3819666946753269</v>
+        <v>0.3730426147532756</v>
       </c>
       <c r="K18">
-        <v>1.052142800875873</v>
+        <v>1.034362206600617</v>
       </c>
       <c r="L18">
         <v>10000</v>
       </c>
       <c r="M18">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N18">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1315,25 +1315,25 @@
         <v>24</v>
       </c>
       <c r="H19">
-        <v>26015.95084798232</v>
+        <v>27894.85568433709</v>
       </c>
       <c r="I19">
-        <v>24729.53172084751</v>
+        <v>24750.50479490741</v>
       </c>
       <c r="J19">
-        <v>11320.63482707048</v>
+        <v>16444.93023251616</v>
       </c>
       <c r="K19">
-        <v>42657.94260705442</v>
+        <v>46738.1348926636</v>
       </c>
       <c r="L19">
         <v>10000</v>
       </c>
       <c r="M19">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N19">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1359,25 +1359,25 @@
         <v>25</v>
       </c>
       <c r="H20">
-        <v>0.6265424125618171</v>
+        <v>0.6240329295002387</v>
       </c>
       <c r="I20">
-        <v>0.6210356083734586</v>
+        <v>0.6209862781292131</v>
       </c>
       <c r="J20">
-        <v>0.5177185333806167</v>
+        <v>0.5167797885940837</v>
       </c>
       <c r="K20">
-        <v>0.7421767292018822</v>
+        <v>0.7287640517831989</v>
       </c>
       <c r="L20">
         <v>10000</v>
       </c>
       <c r="M20">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N20">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1403,25 +1403,25 @@
         <v>26</v>
       </c>
       <c r="H21">
-        <v>1702.932892203744</v>
+        <v>1672.942049788029</v>
       </c>
       <c r="I21">
-        <v>1709.559722288294</v>
+        <v>1700.956682330074</v>
       </c>
       <c r="J21">
-        <v>1266.247664410434</v>
+        <v>1291.853675833786</v>
       </c>
       <c r="K21">
-        <v>2035.531151567974</v>
+        <v>1940.223201231468</v>
       </c>
       <c r="L21">
         <v>10000</v>
       </c>
       <c r="M21">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N21">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1447,25 +1447,25 @@
         <v>27</v>
       </c>
       <c r="H22">
-        <v>1367.469680623748</v>
+        <v>1507.446573240515</v>
       </c>
       <c r="I22">
-        <v>1374.244076104651</v>
+        <v>1519.91068367223</v>
       </c>
       <c r="J22">
-        <v>270.7906287505036</v>
+        <v>421.9317932671632</v>
       </c>
       <c r="K22">
-        <v>2646.395942719191</v>
+        <v>2801.972908843749</v>
       </c>
       <c r="L22">
         <v>10000</v>
       </c>
       <c r="M22">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N22">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1491,25 +1491,25 @@
         <v>28</v>
       </c>
       <c r="H23">
-        <v>0.2491603283435361</v>
+        <v>0.2453315901900185</v>
       </c>
       <c r="I23">
-        <v>0.2402257393814853</v>
+        <v>0.2376739600784294</v>
       </c>
       <c r="J23">
-        <v>0.1609117668623209</v>
+        <v>0.1605527801007567</v>
       </c>
       <c r="K23">
-        <v>0.3896740337999982</v>
+        <v>0.3650425761587303</v>
       </c>
       <c r="L23">
         <v>10000</v>
       </c>
       <c r="M23">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N23">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1535,25 +1535,25 @@
         <v>18</v>
       </c>
       <c r="H24">
-        <v>6512.086158442134</v>
+        <v>6181.018846626639</v>
       </c>
       <c r="I24">
-        <v>6164.039669702978</v>
+        <v>5992.028083036432</v>
       </c>
       <c r="J24">
-        <v>4746.408140420475</v>
+        <v>3614.930432249469</v>
       </c>
       <c r="K24">
-        <v>8898.256786303355</v>
+        <v>8928.20201342741</v>
       </c>
       <c r="L24">
         <v>10000</v>
       </c>
       <c r="M24">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N24">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1579,25 +1579,25 @@
         <v>19</v>
       </c>
       <c r="H25">
-        <v>0.2975337447033494</v>
+        <v>0.2683125040670968</v>
       </c>
       <c r="I25">
-        <v>0.2971029176561058</v>
+        <v>0.2919358451378414</v>
       </c>
       <c r="J25">
-        <v>0.1469359495067342</v>
+        <v>0.1101072443865889</v>
       </c>
       <c r="K25">
-        <v>0.5182878026564417</v>
+        <v>0.3790005025781449</v>
       </c>
       <c r="L25">
         <v>10000</v>
       </c>
       <c r="M25">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N25">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1623,25 +1623,25 @@
         <v>20</v>
       </c>
       <c r="H26">
-        <v>4668.26422737368</v>
+        <v>4772.015350978391</v>
       </c>
       <c r="I26">
-        <v>4112.234751968669</v>
+        <v>3875.765337859823</v>
       </c>
       <c r="J26">
-        <v>1278.602955110076</v>
+        <v>2100.743205146362</v>
       </c>
       <c r="K26">
-        <v>9677.52543389353</v>
+        <v>9805.624843104853</v>
       </c>
       <c r="L26">
         <v>10000</v>
       </c>
       <c r="M26">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N26">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1667,25 +1667,25 @@
         <v>21</v>
       </c>
       <c r="H27">
-        <v>0.1897402161023204</v>
+        <v>0.1883443345437498</v>
       </c>
       <c r="I27">
-        <v>0.2112865384033881</v>
+        <v>0.1942716534292568</v>
       </c>
       <c r="J27">
-        <v>0.07547108679404158</v>
+        <v>0.1043279129785267</v>
       </c>
       <c r="K27">
-        <v>0.2483035144459296</v>
+        <v>0.2471625456085451</v>
       </c>
       <c r="L27">
         <v>10000</v>
       </c>
       <c r="M27">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N27">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1711,25 +1711,25 @@
         <v>22</v>
       </c>
       <c r="H28">
-        <v>0.5285842347904181</v>
+        <v>0.5885139997681964</v>
       </c>
       <c r="I28">
-        <v>0.5221024049511337</v>
+        <v>0.5839541679056551</v>
       </c>
       <c r="J28">
-        <v>0.2953486159981975</v>
+        <v>0.2872041203146866</v>
       </c>
       <c r="K28">
-        <v>0.7940221012144453</v>
+        <v>1.07454523891042</v>
       </c>
       <c r="L28">
         <v>10000</v>
       </c>
       <c r="M28">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N28">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1755,25 +1755,25 @@
         <v>23</v>
       </c>
       <c r="H29">
-        <v>0.5816016237222997</v>
+        <v>0.6379012688544899</v>
       </c>
       <c r="I29">
-        <v>0.5851277809610397</v>
+        <v>0.627594839399552</v>
       </c>
       <c r="J29">
-        <v>0.3566726315803416</v>
+        <v>0.3414407477671657</v>
       </c>
       <c r="K29">
-        <v>0.895343787464733</v>
+        <v>1.209370544711438</v>
       </c>
       <c r="L29">
         <v>10000</v>
       </c>
       <c r="M29">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N29">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1799,25 +1799,25 @@
         <v>24</v>
       </c>
       <c r="H30">
-        <v>24018.75680803393</v>
+        <v>25072.08101003564</v>
       </c>
       <c r="I30">
-        <v>24650.43125338086</v>
+        <v>24729.85913906333</v>
       </c>
       <c r="J30">
-        <v>11324.28453921776</v>
+        <v>16417.0127777126</v>
       </c>
       <c r="K30">
-        <v>40576.98310429195</v>
+        <v>41383.57862206308</v>
       </c>
       <c r="L30">
         <v>10000</v>
       </c>
       <c r="M30">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N30">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1843,25 +1843,25 @@
         <v>25</v>
       </c>
       <c r="H31">
-        <v>0.9107387617162999</v>
+        <v>0.9187351721219049</v>
       </c>
       <c r="I31">
-        <v>0.9254387949400841</v>
+        <v>0.9134943808387522</v>
       </c>
       <c r="J31">
-        <v>0.7427471998798394</v>
+        <v>0.7415590226050284</v>
       </c>
       <c r="K31">
-        <v>1.084090546942615</v>
+        <v>1.164643373544759</v>
       </c>
       <c r="L31">
         <v>10000</v>
       </c>
       <c r="M31">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N31">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1887,25 +1887,25 @@
         <v>26</v>
       </c>
       <c r="H32">
-        <v>1735.00592365522</v>
+        <v>1734.091464296199</v>
       </c>
       <c r="I32">
-        <v>1723.751843001479</v>
+        <v>1767.11944911371</v>
       </c>
       <c r="J32">
-        <v>1359.403179748416</v>
+        <v>1360.82486375688</v>
       </c>
       <c r="K32">
-        <v>2049.381898989173</v>
+        <v>1949.692715692759</v>
       </c>
       <c r="L32">
         <v>10000</v>
       </c>
       <c r="M32">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N32">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -1931,25 +1931,25 @@
         <v>27</v>
       </c>
       <c r="H33">
-        <v>1497.543592308713</v>
+        <v>1674.300453624232</v>
       </c>
       <c r="I33">
-        <v>1386.293094530655</v>
+        <v>1508.984467097493</v>
       </c>
       <c r="J33">
-        <v>453.4566569774877</v>
+        <v>762.2479781402757</v>
       </c>
       <c r="K33">
-        <v>2812.153045380852</v>
+        <v>3821.326493212483</v>
       </c>
       <c r="L33">
         <v>10000</v>
       </c>
       <c r="M33">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N33">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -1975,25 +1975,25 @@
         <v>28</v>
       </c>
       <c r="H34">
-        <v>0.2761781552469334</v>
+        <v>0.2959949433248829</v>
       </c>
       <c r="I34">
-        <v>0.2805996522321547</v>
+        <v>0.3008826500249799</v>
       </c>
       <c r="J34">
-        <v>0.1826426090972972</v>
+        <v>0.1765006189376746</v>
       </c>
       <c r="K34">
-        <v>0.3849720448397478</v>
+        <v>0.4756771299138778</v>
       </c>
       <c r="L34">
         <v>10000</v>
       </c>
       <c r="M34">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N34">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2013,31 +2013,31 @@
         <v>0.01</v>
       </c>
       <c r="F35">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G35" t="s">
         <v>18</v>
       </c>
       <c r="H35">
-        <v>7081.212131263737</v>
+        <v>7213.828227736045</v>
       </c>
       <c r="I35">
-        <v>6881.92847806708</v>
+        <v>7033.65860349374</v>
       </c>
       <c r="J35">
-        <v>4613.816550061457</v>
+        <v>4716.982266430776</v>
       </c>
       <c r="K35">
-        <v>10575.43273916402</v>
+        <v>10805.61712571353</v>
       </c>
       <c r="L35">
         <v>10000</v>
       </c>
       <c r="M35">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N35">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2057,31 +2057,31 @@
         <v>0.01</v>
       </c>
       <c r="F36">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
       </c>
       <c r="H36">
-        <v>0.2918722316690675</v>
+        <v>0.2809055174330626</v>
       </c>
       <c r="I36">
-        <v>0.2855832900832965</v>
+        <v>0.2806749201070768</v>
       </c>
       <c r="J36">
-        <v>0.1565662697548788</v>
+        <v>0.1544818612250496</v>
       </c>
       <c r="K36">
-        <v>0.5020585813992111</v>
+        <v>0.4201304030446216</v>
       </c>
       <c r="L36">
         <v>10000</v>
       </c>
       <c r="M36">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N36">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2101,31 +2101,31 @@
         <v>0.01</v>
       </c>
       <c r="F37">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G37" t="s">
         <v>20</v>
       </c>
       <c r="H37">
-        <v>9129.602839068481</v>
+        <v>9330.686804035286</v>
       </c>
       <c r="I37">
-        <v>9247.544026027543</v>
+        <v>9253.943416538292</v>
       </c>
       <c r="J37">
-        <v>2947.941168275791</v>
+        <v>3433.966106320833</v>
       </c>
       <c r="K37">
-        <v>15591.58716289435</v>
+        <v>15593.31971301264</v>
       </c>
       <c r="L37">
         <v>10000</v>
       </c>
       <c r="M37">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N37">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2145,31 +2145,31 @@
         <v>0.01</v>
       </c>
       <c r="F38">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G38" t="s">
         <v>21</v>
       </c>
       <c r="H38">
-        <v>0.3590967539825784</v>
+        <v>0.3528688981215443</v>
       </c>
       <c r="I38">
-        <v>0.3841574800444664</v>
+        <v>0.3756539009525467</v>
       </c>
       <c r="J38">
-        <v>0.1541277779640113</v>
+        <v>0.1417454094197707</v>
       </c>
       <c r="K38">
-        <v>0.4472047744608935</v>
+        <v>0.4372813008180845</v>
       </c>
       <c r="L38">
         <v>10000</v>
       </c>
       <c r="M38">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N38">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2189,31 +2189,31 @@
         <v>0.01</v>
       </c>
       <c r="F39">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G39" t="s">
         <v>22</v>
       </c>
       <c r="H39">
-        <v>0.4205687786056165</v>
+        <v>0.4094526758589883</v>
       </c>
       <c r="I39">
-        <v>0.3965881871939427</v>
+        <v>0.3922333246447317</v>
       </c>
       <c r="J39">
-        <v>0.2247478580509854</v>
+        <v>0.2198826202210068</v>
       </c>
       <c r="K39">
-        <v>0.7448312624976202</v>
+        <v>0.7112216239855527</v>
       </c>
       <c r="L39">
         <v>10000</v>
       </c>
       <c r="M39">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N39">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2233,31 +2233,31 @@
         <v>0.01</v>
       </c>
       <c r="F40">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G40" t="s">
         <v>23</v>
       </c>
       <c r="H40">
-        <v>0.6944016620833188</v>
+        <v>0.678227004537186</v>
       </c>
       <c r="I40">
-        <v>0.6540911543831536</v>
+        <v>0.6496846828050458</v>
       </c>
       <c r="J40">
-        <v>0.377208510237649</v>
+        <v>0.3673127280179366</v>
       </c>
       <c r="K40">
-        <v>1.179903098335789</v>
+        <v>1.127662002834713</v>
       </c>
       <c r="L40">
         <v>10000</v>
       </c>
       <c r="M40">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N40">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2277,31 +2277,31 @@
         <v>0.01</v>
       </c>
       <c r="F41">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
       </c>
       <c r="H41">
-        <v>25483.04455053248</v>
+        <v>26630.28474394206</v>
       </c>
       <c r="I41">
-        <v>24405.34008941127</v>
+        <v>24561.51319145276</v>
       </c>
       <c r="J41">
-        <v>12430.1013906666</v>
+        <v>16367.23631766664</v>
       </c>
       <c r="K41">
-        <v>41457.12781724922</v>
+        <v>42312.22034698525</v>
       </c>
       <c r="L41">
         <v>10000</v>
       </c>
       <c r="M41">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N41">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2321,31 +2321,31 @@
         <v>0.01</v>
       </c>
       <c r="F42">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
       </c>
       <c r="H42">
-        <v>0.6051555347426545</v>
+        <v>0.6033891391587594</v>
       </c>
       <c r="I42">
-        <v>0.603725457239373</v>
+        <v>0.6011925678965105</v>
       </c>
       <c r="J42">
-        <v>0.4969413246436898</v>
+        <v>0.4926090806945367</v>
       </c>
       <c r="K42">
-        <v>0.7316611604999959</v>
+        <v>0.7329443049431901</v>
       </c>
       <c r="L42">
         <v>10000</v>
       </c>
       <c r="M42">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N42">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2365,31 +2365,31 @@
         <v>0.01</v>
       </c>
       <c r="F43">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G43" t="s">
         <v>26</v>
       </c>
       <c r="H43">
-        <v>1735.617112732825</v>
+        <v>1736.976757328381</v>
       </c>
       <c r="I43">
-        <v>1733.742440530326</v>
+        <v>1747.040288031871</v>
       </c>
       <c r="J43">
-        <v>1480.171469687042</v>
+        <v>1486.154822809619</v>
       </c>
       <c r="K43">
-        <v>2018.431540066693</v>
+        <v>1921.975948387453</v>
       </c>
       <c r="L43">
         <v>10000</v>
       </c>
       <c r="M43">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N43">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2409,31 +2409,31 @@
         <v>0.01</v>
       </c>
       <c r="F44">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G44" t="s">
         <v>27</v>
       </c>
       <c r="H44">
-        <v>2656.791149464195</v>
+        <v>2681.410028524843</v>
       </c>
       <c r="I44">
-        <v>2651.937738454573</v>
+        <v>2633.525931048902</v>
       </c>
       <c r="J44">
-        <v>903.8182139176101</v>
+        <v>1133.642142063275</v>
       </c>
       <c r="K44">
-        <v>4505.263207491404</v>
+        <v>4524.95749816064</v>
       </c>
       <c r="L44">
         <v>10000</v>
       </c>
       <c r="M44">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N44">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -2453,31 +2453,31 @@
         <v>0.01</v>
       </c>
       <c r="F45">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G45" t="s">
         <v>28</v>
       </c>
       <c r="H45">
-        <v>0.2586264569203736</v>
+        <v>0.2535578212281284</v>
       </c>
       <c r="I45">
-        <v>0.2484892464278234</v>
+        <v>0.246901892484016</v>
       </c>
       <c r="J45">
-        <v>0.1568244249127044</v>
+        <v>0.150785416254066</v>
       </c>
       <c r="K45">
-        <v>0.4037852476702263</v>
+        <v>0.3914381020811927</v>
       </c>
       <c r="L45">
         <v>10000</v>
       </c>
       <c r="M45">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="N45">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -2497,31 +2497,31 @@
         <v>0.01</v>
       </c>
       <c r="F46">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G46" t="s">
         <v>18</v>
       </c>
       <c r="H46">
-        <v>6926.666132871042</v>
+        <v>7061.423702450727</v>
       </c>
       <c r="I46">
-        <v>6560.756856819847</v>
+        <v>6749.475560463276</v>
       </c>
       <c r="J46">
-        <v>4564.326589332573</v>
+        <v>4515.133693759002</v>
       </c>
       <c r="K46">
-        <v>10328.60039198555</v>
+        <v>10635.70194777432</v>
       </c>
       <c r="L46">
         <v>10000</v>
       </c>
       <c r="M46">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N46">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2541,31 +2541,31 @@
         <v>0.01</v>
       </c>
       <c r="F47">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G47" t="s">
         <v>19</v>
       </c>
       <c r="H47">
-        <v>0.2927458896963153</v>
+        <v>0.2813837613826723</v>
       </c>
       <c r="I47">
-        <v>0.2762184423268856</v>
+        <v>0.2750284168212704</v>
       </c>
       <c r="J47">
-        <v>0.1560728761225079</v>
+        <v>0.1567092008285599</v>
       </c>
       <c r="K47">
-        <v>0.5028952061565849</v>
+        <v>0.4190543460953496</v>
       </c>
       <c r="L47">
         <v>10000</v>
       </c>
       <c r="M47">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N47">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2585,31 +2585,31 @@
         <v>0.01</v>
       </c>
       <c r="F48">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>
       </c>
       <c r="H48">
-        <v>8920.498522694472</v>
+        <v>9117.815634741748</v>
       </c>
       <c r="I48">
-        <v>9154.17950053701</v>
+        <v>9140.974400613773</v>
       </c>
       <c r="J48">
-        <v>2998.346453373553</v>
+        <v>2990.82940866928</v>
       </c>
       <c r="K48">
-        <v>15414.70941483396</v>
+        <v>15394.51784203279</v>
       </c>
       <c r="L48">
         <v>10000</v>
       </c>
       <c r="M48">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N48">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2629,31 +2629,31 @@
         <v>0.01</v>
       </c>
       <c r="F49">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G49" t="s">
         <v>21</v>
       </c>
       <c r="H49">
-        <v>0.3579523924087352</v>
+        <v>0.3531219223591757</v>
       </c>
       <c r="I49">
-        <v>0.3878196927501113</v>
+        <v>0.3811733476594222</v>
       </c>
       <c r="J49">
-        <v>0.1558440648376862</v>
+        <v>0.1600842839874167</v>
       </c>
       <c r="K49">
-        <v>0.4479430587203607</v>
+        <v>0.4379448551667225</v>
       </c>
       <c r="L49">
         <v>10000</v>
       </c>
       <c r="M49">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N49">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2673,31 +2673,31 @@
         <v>0.01</v>
       </c>
       <c r="F50">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G50" t="s">
         <v>22</v>
       </c>
       <c r="H50">
-        <v>0.4390098956706909</v>
+        <v>0.4333309267763069</v>
       </c>
       <c r="I50">
-        <v>0.4234682019059178</v>
+        <v>0.4112743932034079</v>
       </c>
       <c r="J50">
-        <v>0.2196095322104563</v>
+        <v>0.2171479800450852</v>
       </c>
       <c r="K50">
-        <v>0.7504235416618262</v>
+        <v>0.7562287557395657</v>
       </c>
       <c r="L50">
         <v>10000</v>
       </c>
       <c r="M50">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N50">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2717,31 +2717,31 @@
         <v>0.01</v>
       </c>
       <c r="F51">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G51" t="s">
         <v>23</v>
       </c>
       <c r="H51">
-        <v>0.701527005434837</v>
+        <v>0.6926909252095294</v>
       </c>
       <c r="I51">
-        <v>0.6850281176506614</v>
+        <v>0.6684816152502491</v>
       </c>
       <c r="J51">
-        <v>0.3516158307778227</v>
+        <v>0.3513357190816393</v>
       </c>
       <c r="K51">
-        <v>1.178035138613266</v>
+        <v>1.228678051442317</v>
       </c>
       <c r="L51">
         <v>10000</v>
       </c>
       <c r="M51">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N51">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -2761,31 +2761,31 @@
         <v>0.01</v>
       </c>
       <c r="F52">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G52" t="s">
         <v>24</v>
       </c>
       <c r="H52">
-        <v>24977.52711514215</v>
+        <v>25970.62439484076</v>
       </c>
       <c r="I52">
-        <v>24168.16931097538</v>
+        <v>24425.63779907037</v>
       </c>
       <c r="J52">
-        <v>11337.02672825862</v>
+        <v>16268.73333211352</v>
       </c>
       <c r="K52">
-        <v>41937.09367720256</v>
+        <v>42894.88253626691</v>
       </c>
       <c r="L52">
         <v>10000</v>
       </c>
       <c r="M52">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N52">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -2805,31 +2805,31 @@
         <v>0.01</v>
       </c>
       <c r="F53">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
       </c>
       <c r="H53">
-        <v>0.6275646159781559</v>
+        <v>0.6274184889632043</v>
       </c>
       <c r="I53">
         <v>0.6260601043054146</v>
       </c>
       <c r="J53">
-        <v>0.5077415087583571</v>
+        <v>0.5034532607453749</v>
       </c>
       <c r="K53">
-        <v>0.7621362892738363</v>
+        <v>0.7664672332894895</v>
       </c>
       <c r="L53">
         <v>10000</v>
       </c>
       <c r="M53">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N53">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -2849,31 +2849,31 @@
         <v>0.01</v>
       </c>
       <c r="F54">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G54" t="s">
         <v>26</v>
       </c>
       <c r="H54">
-        <v>1744.390643236002</v>
+        <v>1747.070408672123</v>
       </c>
       <c r="I54">
-        <v>1744.910032740764</v>
+        <v>1759.620244365128</v>
       </c>
       <c r="J54">
-        <v>1431.961778236544</v>
+        <v>1443.090415175505</v>
       </c>
       <c r="K54">
-        <v>2034.32331802209</v>
+        <v>1937.590956103033</v>
       </c>
       <c r="L54">
         <v>10000</v>
       </c>
       <c r="M54">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N54">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -2893,31 +2893,31 @@
         <v>0.01</v>
       </c>
       <c r="F55">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G55" t="s">
         <v>27</v>
       </c>
       <c r="H55">
-        <v>2667.061816488561</v>
+        <v>2707.349482518787</v>
       </c>
       <c r="I55">
-        <v>2681.890846630906</v>
+        <v>2710.857613734113</v>
       </c>
       <c r="J55">
-        <v>887.9716235477307</v>
+        <v>1024.60735551823</v>
       </c>
       <c r="K55">
-        <v>4585.157675749039</v>
+        <v>4579.981106559477</v>
       </c>
       <c r="L55">
         <v>10000</v>
       </c>
       <c r="M55">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N55">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -2937,31 +2937,31 @@
         <v>0.01</v>
       </c>
       <c r="F56">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G56" t="s">
         <v>28</v>
       </c>
       <c r="H56">
-        <v>0.2656034755715275</v>
+        <v>0.2623566961129473</v>
       </c>
       <c r="I56">
-        <v>0.2639603591146208</v>
+        <v>0.2583042680786021</v>
       </c>
       <c r="J56">
-        <v>0.1496525566079671</v>
+        <v>0.1476262429576584</v>
       </c>
       <c r="K56">
-        <v>0.4060961492472046</v>
+        <v>0.4096191912105465</v>
       </c>
       <c r="L56">
         <v>10000</v>
       </c>
       <c r="M56">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="N56">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -2981,31 +2981,31 @@
         <v>0.01</v>
       </c>
       <c r="F57">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G57" t="s">
         <v>18</v>
       </c>
       <c r="H57">
-        <v>5979.769062079871</v>
+        <v>5890.956398882704</v>
       </c>
       <c r="I57">
-        <v>5810.070586125463</v>
+        <v>5702.580174436389</v>
       </c>
       <c r="J57">
-        <v>4176.807925909237</v>
+        <v>4046.075291248972</v>
       </c>
       <c r="K57">
-        <v>9286.01903884224</v>
+        <v>9209.644309610227</v>
       </c>
       <c r="L57">
         <v>10000</v>
       </c>
       <c r="M57">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N57">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3025,31 +3025,31 @@
         <v>0.01</v>
       </c>
       <c r="F58">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G58" t="s">
         <v>19</v>
       </c>
       <c r="H58">
-        <v>0.279552869014069</v>
+        <v>0.2619798534068712</v>
       </c>
       <c r="I58">
-        <v>0.2630976379135611</v>
+        <v>0.2551746152533376</v>
       </c>
       <c r="J58">
-        <v>0.1413682585969316</v>
+        <v>0.1407013510813587</v>
       </c>
       <c r="K58">
-        <v>0.4885716138660823</v>
+        <v>0.3777454249237053</v>
       </c>
       <c r="L58">
         <v>10000</v>
       </c>
       <c r="M58">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N58">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3069,31 +3069,31 @@
         <v>0.01</v>
       </c>
       <c r="F59">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G59" t="s">
         <v>20</v>
       </c>
       <c r="H59">
-        <v>8354.179259331933</v>
+        <v>8495.38891158098</v>
       </c>
       <c r="I59">
-        <v>8779.334141336654</v>
+        <v>8771.731690553468</v>
       </c>
       <c r="J59">
-        <v>3014.489872736845</v>
+        <v>3170.930610429822</v>
       </c>
       <c r="K59">
-        <v>13807.31145936405</v>
+        <v>13741.31516249647</v>
       </c>
       <c r="L59">
         <v>10000</v>
       </c>
       <c r="M59">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N59">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3113,31 +3113,31 @@
         <v>0.01</v>
       </c>
       <c r="F60">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G60" t="s">
         <v>21</v>
       </c>
       <c r="H60">
-        <v>0.3654423104046092</v>
+        <v>0.3608630824069095</v>
       </c>
       <c r="I60">
-        <v>0.3930600305638478</v>
+        <v>0.3902296783432302</v>
       </c>
       <c r="J60">
-        <v>0.1404507906790275</v>
+        <v>0.1597962114544613</v>
       </c>
       <c r="K60">
-        <v>0.448250841621816</v>
+        <v>0.438700396110579</v>
       </c>
       <c r="L60">
         <v>10000</v>
       </c>
       <c r="M60">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N60">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3157,31 +3157,31 @@
         <v>0.01</v>
       </c>
       <c r="F61">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G61" t="s">
         <v>22</v>
       </c>
       <c r="H61">
-        <v>0.624489087555375</v>
+        <v>0.640966655629726</v>
       </c>
       <c r="I61">
-        <v>0.6079699928886959</v>
+        <v>0.6273022196763938</v>
       </c>
       <c r="J61">
-        <v>0.3172517854593201</v>
+        <v>0.324561408951455</v>
       </c>
       <c r="K61">
-        <v>1.032679081407829</v>
+        <v>1.089209651401806</v>
       </c>
       <c r="L61">
         <v>10000</v>
       </c>
       <c r="M61">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N61">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3201,31 +3201,31 @@
         <v>0.01</v>
       </c>
       <c r="F62">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G62" t="s">
         <v>23</v>
       </c>
       <c r="H62">
-        <v>0.6815761238161373</v>
+        <v>0.6979665218481824</v>
       </c>
       <c r="I62">
-        <v>0.6624579525148232</v>
+        <v>0.6912562727881226</v>
       </c>
       <c r="J62">
-        <v>0.3653038072697088</v>
+        <v>0.3819167885584632</v>
       </c>
       <c r="K62">
-        <v>1.098827894049669</v>
+        <v>1.133918073122151</v>
       </c>
       <c r="L62">
         <v>10000</v>
       </c>
       <c r="M62">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N62">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3245,31 +3245,31 @@
         <v>0.01</v>
       </c>
       <c r="F63">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
       </c>
       <c r="H63">
-        <v>22869.67501442028</v>
+        <v>23511.60369619085</v>
       </c>
       <c r="I63">
-        <v>23330.08264553548</v>
+        <v>23571.62167466023</v>
       </c>
       <c r="J63">
-        <v>11307.85839164636</v>
+        <v>16083.77357436489</v>
       </c>
       <c r="K63">
-        <v>35482.36741946277</v>
+        <v>35930.39700530716</v>
       </c>
       <c r="L63">
         <v>10000</v>
       </c>
       <c r="M63">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N63">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3289,31 +3289,31 @@
         <v>0.01</v>
       </c>
       <c r="F64">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
       </c>
       <c r="H64">
-        <v>0.915705671526913</v>
+        <v>0.9177794143075152</v>
       </c>
       <c r="I64">
-        <v>0.9093964438089891</v>
+        <v>0.9148453785423682</v>
       </c>
       <c r="J64">
-        <v>0.756059191718535</v>
+        <v>0.7560020317429994</v>
       </c>
       <c r="K64">
-        <v>1.124820281978111</v>
+        <v>1.121367898162474</v>
       </c>
       <c r="L64">
         <v>10000</v>
       </c>
       <c r="M64">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N64">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3333,31 +3333,31 @@
         <v>0.01</v>
       </c>
       <c r="F65">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G65" t="s">
         <v>26</v>
       </c>
       <c r="H65">
-        <v>1789.828020843936</v>
+        <v>1797.423959433026</v>
       </c>
       <c r="I65">
-        <v>1776.07142858124</v>
+        <v>1791.016931092923</v>
       </c>
       <c r="J65">
-        <v>1560.882264480264</v>
+        <v>1577.997008427687</v>
       </c>
       <c r="K65">
-        <v>2036.431411445723</v>
+        <v>1951.85301680473</v>
       </c>
       <c r="L65">
         <v>10000</v>
       </c>
       <c r="M65">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N65">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3377,31 +3377,31 @@
         <v>0.01</v>
       </c>
       <c r="F66">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
       </c>
       <c r="H66">
-        <v>2990.697749110368</v>
+        <v>3086.183713638615</v>
       </c>
       <c r="I66">
-        <v>2977.546748999448</v>
+        <v>3043.978363052135</v>
       </c>
       <c r="J66">
-        <v>1074.808615500149</v>
+        <v>1478.387924017004</v>
       </c>
       <c r="K66">
-        <v>4786.554537504044</v>
+        <v>4905.562300291056</v>
       </c>
       <c r="L66">
         <v>10000</v>
       </c>
       <c r="M66">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N66">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3421,31 +3421,31 @@
         <v>0.01</v>
       </c>
       <c r="F67">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G67" t="s">
         <v>28</v>
       </c>
       <c r="H67">
-        <v>0.3126184405210486</v>
+        <v>0.3185157972829226</v>
       </c>
       <c r="I67">
-        <v>0.3132141090443412</v>
+        <v>0.3187345429937479</v>
       </c>
       <c r="J67">
-        <v>0.1864835577424698</v>
+        <v>0.1883147563034057</v>
       </c>
       <c r="K67">
-        <v>0.4470068613906618</v>
+        <v>0.4654897795653924</v>
       </c>
       <c r="L67">
         <v>10000</v>
       </c>
       <c r="M67">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3471,25 +3471,25 @@
         <v>18</v>
       </c>
       <c r="H68">
-        <v>7076.604302601146</v>
+        <v>7228.301828151285</v>
       </c>
       <c r="I68">
-        <v>6828.313280389134</v>
+        <v>6985.635889308945</v>
       </c>
       <c r="J68">
-        <v>4841.490846866111</v>
+        <v>4900.991661799811</v>
       </c>
       <c r="K68">
-        <v>10608.89470740364</v>
+        <v>10845.67410023743</v>
       </c>
       <c r="L68">
         <v>10000</v>
       </c>
       <c r="M68">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N68">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3515,25 +3515,25 @@
         <v>19</v>
       </c>
       <c r="H69">
-        <v>0.2994290747573696</v>
+        <v>0.2942488646684371</v>
       </c>
       <c r="I69">
-        <v>0.2939212185213084</v>
+        <v>0.2917911357804145</v>
       </c>
       <c r="J69">
-        <v>0.1625732707919263</v>
+        <v>0.1670704867082733</v>
       </c>
       <c r="K69">
-        <v>0.4863560340771494</v>
+        <v>0.4377493355097463</v>
       </c>
       <c r="L69">
         <v>10000</v>
       </c>
       <c r="M69">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N69">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3559,25 +3559,25 @@
         <v>20</v>
       </c>
       <c r="H70">
-        <v>9870.686797317103</v>
+        <v>10107.39196932055</v>
       </c>
       <c r="I70">
-        <v>9825.355811170522</v>
+        <v>9902.839577133769</v>
       </c>
       <c r="J70">
-        <v>3892.463370502946</v>
+        <v>4603.379789574868</v>
       </c>
       <c r="K70">
-        <v>16650.25992034305</v>
+        <v>16999.03511969426</v>
       </c>
       <c r="L70">
         <v>10000</v>
       </c>
       <c r="M70">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N70">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -3603,25 +3603,25 @@
         <v>21</v>
       </c>
       <c r="H71">
-        <v>0.4046855203188514</v>
+        <v>0.4036001636573127</v>
       </c>
       <c r="I71">
-        <v>0.4287924869821494</v>
+        <v>0.4261617899620097</v>
       </c>
       <c r="J71">
-        <v>0.1753003728616698</v>
+        <v>0.1861038708935039</v>
       </c>
       <c r="K71">
-        <v>0.4970667311488372</v>
+        <v>0.4973915646661645</v>
       </c>
       <c r="L71">
         <v>10000</v>
       </c>
       <c r="M71">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N71">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3647,25 +3647,25 @@
         <v>22</v>
       </c>
       <c r="H72">
-        <v>0.4255249424049858</v>
+        <v>0.4186572733361379</v>
       </c>
       <c r="I72">
-        <v>0.4045373922011282</v>
+        <v>0.3950723747495367</v>
       </c>
       <c r="J72">
-        <v>0.2255704074861227</v>
+        <v>0.2252620967459882</v>
       </c>
       <c r="K72">
-        <v>0.6925838837320468</v>
+        <v>0.6897022128627138</v>
       </c>
       <c r="L72">
         <v>10000</v>
       </c>
       <c r="M72">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N72">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3691,25 +3691,25 @@
         <v>23</v>
       </c>
       <c r="H73">
-        <v>0.7032040131265282</v>
+        <v>0.6930037839442545</v>
       </c>
       <c r="I73">
-        <v>0.6753848546172344</v>
+        <v>0.6608968049901074</v>
       </c>
       <c r="J73">
-        <v>0.3944312449429507</v>
+        <v>0.3925765752785361</v>
       </c>
       <c r="K73">
-        <v>1.139402517923621</v>
+        <v>1.128067130899296</v>
       </c>
       <c r="L73">
         <v>10000</v>
       </c>
       <c r="M73">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N73">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -3735,25 +3735,25 @@
         <v>24</v>
       </c>
       <c r="H74">
-        <v>24681.42799416303</v>
+        <v>25387.60273153029</v>
       </c>
       <c r="I74">
-        <v>23953.00466639022</v>
+        <v>24181.79596042938</v>
       </c>
       <c r="J74">
-        <v>16101.76018272586</v>
+        <v>16283.49032224925</v>
       </c>
       <c r="K74">
-        <v>40455.83107864425</v>
+        <v>41746.04820469258</v>
       </c>
       <c r="L74">
         <v>10000</v>
       </c>
       <c r="M74">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N74">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -3779,25 +3779,25 @@
         <v>25</v>
       </c>
       <c r="H75">
-        <v>0.6060332889434535</v>
+        <v>0.6051886748115241</v>
       </c>
       <c r="I75">
-        <v>0.603666656523413</v>
+        <v>0.602271466330522</v>
       </c>
       <c r="J75">
-        <v>0.4983036453027478</v>
+        <v>0.4978757922592603</v>
       </c>
       <c r="K75">
-        <v>0.7316023758636849</v>
+        <v>0.7283792138608973</v>
       </c>
       <c r="L75">
         <v>10000</v>
       </c>
       <c r="M75">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N75">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -3823,25 +3823,25 @@
         <v>26</v>
       </c>
       <c r="H76">
-        <v>1762.659950967558</v>
+        <v>1774.916737057017</v>
       </c>
       <c r="I76">
-        <v>1765.924500991997</v>
+        <v>1784.283712225263</v>
       </c>
       <c r="J76">
-        <v>1490.435222539403</v>
+        <v>1518.496886906868</v>
       </c>
       <c r="K76">
-        <v>1987.696909501695</v>
+        <v>1940.173157832319</v>
       </c>
       <c r="L76">
         <v>10000</v>
       </c>
       <c r="M76">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N76">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -3867,25 +3867,25 @@
         <v>27</v>
       </c>
       <c r="H77">
-        <v>2893.565913683369</v>
+        <v>2937.725104180584</v>
       </c>
       <c r="I77">
-        <v>2902.255968471391</v>
+        <v>2948.578693307132</v>
       </c>
       <c r="J77">
-        <v>1175.071895285549</v>
+        <v>1147.062672160754</v>
       </c>
       <c r="K77">
-        <v>4710.738181766049</v>
+        <v>4759.271695409166</v>
       </c>
       <c r="L77">
         <v>10000</v>
       </c>
       <c r="M77">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N77">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -3911,25 +3911,25 @@
         <v>28</v>
       </c>
       <c r="H78">
-        <v>0.2615628918722404</v>
+        <v>0.258210897985744</v>
       </c>
       <c r="I78">
-        <v>0.2559404724794944</v>
+        <v>0.2512005891057879</v>
       </c>
       <c r="J78">
-        <v>0.1559310408416311</v>
+        <v>0.1555485553524608</v>
       </c>
       <c r="K78">
-        <v>0.3838676716591814</v>
+        <v>0.38072802873739</v>
       </c>
       <c r="L78">
         <v>10000</v>
       </c>
       <c r="M78">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="N78">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -3955,22 +3955,22 @@
         <v>18</v>
       </c>
       <c r="H79">
-        <v>6959.692288384013</v>
+        <v>7104.679733497839</v>
       </c>
       <c r="I79">
-        <v>6745.236025754256</v>
+        <v>6909.16021221402</v>
       </c>
       <c r="J79">
-        <v>4571.583154732904</v>
+        <v>4534.714641140341</v>
       </c>
       <c r="K79">
-        <v>10574.84567296955</v>
+        <v>10789.04920754235</v>
       </c>
       <c r="L79">
         <v>10000</v>
       </c>
       <c r="M79">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N79">
         <v>9.199999999999999</v>
@@ -3999,22 +3999,22 @@
         <v>19</v>
       </c>
       <c r="H80">
-        <v>0.3053897620051177</v>
+        <v>0.2964809588201907</v>
       </c>
       <c r="I80">
-        <v>0.3002102218427549</v>
+        <v>0.2946035285858469</v>
       </c>
       <c r="J80">
-        <v>0.1614020515612489</v>
+        <v>0.1616090234188522</v>
       </c>
       <c r="K80">
-        <v>0.4902616686210535</v>
+        <v>0.4325128531910694</v>
       </c>
       <c r="L80">
         <v>10000</v>
       </c>
       <c r="M80">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N80">
         <v>9.199999999999999</v>
@@ -4043,22 +4043,22 @@
         <v>20</v>
       </c>
       <c r="H81">
-        <v>9655.031573022854</v>
+        <v>9887.05818513096</v>
       </c>
       <c r="I81">
-        <v>9588.739736083997</v>
+        <v>9700.109290632703</v>
       </c>
       <c r="J81">
-        <v>3943.321774804654</v>
+        <v>4165.362612465369</v>
       </c>
       <c r="K81">
-        <v>15379.35397565647</v>
+        <v>15745.44919962826</v>
       </c>
       <c r="L81">
         <v>10000</v>
       </c>
       <c r="M81">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N81">
         <v>9.199999999999999</v>
@@ -4087,22 +4087,22 @@
         <v>21</v>
       </c>
       <c r="H82">
-        <v>0.4118324557381227</v>
+        <v>0.4069375167909677</v>
       </c>
       <c r="I82">
-        <v>0.4382288055381718</v>
+        <v>0.4331344528081748</v>
       </c>
       <c r="J82">
-        <v>0.2111297024622276</v>
+        <v>0.1712605555011415</v>
       </c>
       <c r="K82">
-        <v>0.4981196830817252</v>
+        <v>0.4981950358249172</v>
       </c>
       <c r="L82">
         <v>10000</v>
       </c>
       <c r="M82">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N82">
         <v>9.199999999999999</v>
@@ -4131,22 +4131,22 @@
         <v>22</v>
       </c>
       <c r="H83">
-        <v>0.4485209163697604</v>
+        <v>0.4410058768210747</v>
       </c>
       <c r="I83">
-        <v>0.4255729810041181</v>
+        <v>0.4171197199292808</v>
       </c>
       <c r="J83">
-        <v>0.2307040500332256</v>
+        <v>0.2295095627741115</v>
       </c>
       <c r="K83">
-        <v>0.7756884106103504</v>
+        <v>0.7748337617953769</v>
       </c>
       <c r="L83">
         <v>10000</v>
       </c>
       <c r="M83">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N83">
         <v>9.199999999999999</v>
@@ -4175,22 +4175,22 @@
         <v>23</v>
       </c>
       <c r="H84">
-        <v>0.71034980878701</v>
+        <v>0.6975752397737116</v>
       </c>
       <c r="I84">
-        <v>0.6785973336703229</v>
+        <v>0.6643898640276635</v>
       </c>
       <c r="J84">
-        <v>0.3777201676597492</v>
+        <v>0.3760419393466448</v>
       </c>
       <c r="K84">
-        <v>1.174028827803994</v>
+        <v>1.165022169776089</v>
       </c>
       <c r="L84">
         <v>10000</v>
       </c>
       <c r="M84">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N84">
         <v>9.199999999999999</v>
@@ -4219,22 +4219,22 @@
         <v>24</v>
       </c>
       <c r="H85">
-        <v>23726.31070200475</v>
+        <v>24640.66355741043</v>
       </c>
       <c r="I85">
-        <v>23282.23293023906</v>
+        <v>23689.47242382409</v>
       </c>
       <c r="J85">
-        <v>13285.30507310936</v>
+        <v>16322.72377279126</v>
       </c>
       <c r="K85">
-        <v>37899.49022726239</v>
+        <v>38759.09320509435</v>
       </c>
       <c r="L85">
         <v>10000</v>
       </c>
       <c r="M85">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N85">
         <v>9.199999999999999</v>
@@ -4263,22 +4263,22 @@
         <v>25</v>
       </c>
       <c r="H86">
-        <v>0.6313917580217497</v>
+        <v>0.631784856713851</v>
       </c>
       <c r="I86">
-        <v>0.6286019690076095</v>
+        <v>0.6306923238822338</v>
       </c>
       <c r="J86">
-        <v>0.5174773413456093</v>
+        <v>0.5169246670088024</v>
       </c>
       <c r="K86">
-        <v>0.7617073641794185</v>
+        <v>0.7606875582002121</v>
       </c>
       <c r="L86">
         <v>10000</v>
       </c>
       <c r="M86">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N86">
         <v>9.199999999999999</v>
@@ -4307,22 +4307,22 @@
         <v>26</v>
       </c>
       <c r="H87">
-        <v>1778.326837165803</v>
+        <v>1784.389475454859</v>
       </c>
       <c r="I87">
-        <v>1779.892877000475</v>
+        <v>1794.76870347512</v>
       </c>
       <c r="J87">
-        <v>1515.356564447556</v>
+        <v>1525.423854101622</v>
       </c>
       <c r="K87">
-        <v>2018.118535630843</v>
+        <v>1945.524657936332</v>
       </c>
       <c r="L87">
         <v>10000</v>
       </c>
       <c r="M87">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N87">
         <v>9.199999999999999</v>
@@ -4351,22 +4351,22 @@
         <v>27</v>
       </c>
       <c r="H88">
-        <v>2911.41473387027</v>
+        <v>2951.27550700334</v>
       </c>
       <c r="I88">
-        <v>2896.956090033514</v>
+        <v>2949.503305608136</v>
       </c>
       <c r="J88">
-        <v>1421.691069906315</v>
+        <v>1240.425284376159</v>
       </c>
       <c r="K88">
-        <v>4481.689791314777</v>
+        <v>4551.54645824736</v>
       </c>
       <c r="L88">
         <v>10000</v>
       </c>
       <c r="M88">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N88">
         <v>9.199999999999999</v>
@@ -4395,22 +4395,22 @@
         <v>28</v>
       </c>
       <c r="H89">
-        <v>0.2696011650079878</v>
+        <v>0.2656205873273115</v>
       </c>
       <c r="I89">
-        <v>0.2627973705783089</v>
+        <v>0.2590479066942992</v>
       </c>
       <c r="J89">
-        <v>0.1573736575601379</v>
+        <v>0.1557495488304625</v>
       </c>
       <c r="K89">
-        <v>0.4103193753233522</v>
+        <v>0.4109173974148805</v>
       </c>
       <c r="L89">
         <v>10000</v>
       </c>
       <c r="M89">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="N89">
         <v>9.199999999999999</v>
@@ -4439,22 +4439,22 @@
         <v>18</v>
       </c>
       <c r="H90">
-        <v>5962.348037050615</v>
+        <v>5989.026818883715</v>
       </c>
       <c r="I90">
-        <v>5703.247623759566</v>
+        <v>5732.411610767316</v>
       </c>
       <c r="J90">
-        <v>4065.846493004456</v>
+        <v>3976.621915805695</v>
       </c>
       <c r="K90">
-        <v>8967.583522203573</v>
+        <v>9097.521095850983</v>
       </c>
       <c r="L90">
         <v>10000</v>
       </c>
       <c r="M90">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N90">
         <v>5.9</v>
@@ -4483,22 +4483,22 @@
         <v>19</v>
       </c>
       <c r="H91">
-        <v>0.2856473467658514</v>
+        <v>0.2730087013020184</v>
       </c>
       <c r="I91">
-        <v>0.2815640977803122</v>
+        <v>0.275885911747011</v>
       </c>
       <c r="J91">
-        <v>0.1516377397971884</v>
+        <v>0.1508172101064331</v>
       </c>
       <c r="K91">
-        <v>0.4776711103827893</v>
+        <v>0.3800985680894826</v>
       </c>
       <c r="L91">
         <v>10000</v>
       </c>
       <c r="M91">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N91">
         <v>5.9</v>
@@ -4527,22 +4527,22 @@
         <v>20</v>
       </c>
       <c r="H92">
-        <v>8914.4986680374</v>
+        <v>9203.103408091472</v>
       </c>
       <c r="I92">
-        <v>9037.262515664428</v>
+        <v>9140.753769515979</v>
       </c>
       <c r="J92">
-        <v>2710.333803647172</v>
+        <v>3756.470868498046</v>
       </c>
       <c r="K92">
-        <v>13819.39082122189</v>
+        <v>14106.83144234554</v>
       </c>
       <c r="L92">
         <v>10000</v>
       </c>
       <c r="M92">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N92">
         <v>5.9</v>
@@ -4571,22 +4571,22 @@
         <v>21</v>
       </c>
       <c r="H93">
-        <v>0.4104881444825619</v>
+        <v>0.4122737871350761</v>
       </c>
       <c r="I93">
-        <v>0.4422553769962673</v>
+        <v>0.4400713447527587</v>
       </c>
       <c r="J93">
-        <v>0.1687101842289484</v>
+        <v>0.1784805682810741</v>
       </c>
       <c r="K93">
-        <v>0.4976507202364388</v>
+        <v>0.4978682367365326</v>
       </c>
       <c r="L93">
         <v>10000</v>
       </c>
       <c r="M93">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N93">
         <v>5.9</v>
@@ -4615,22 +4615,22 @@
         <v>22</v>
       </c>
       <c r="H94">
-        <v>0.6385236077343648</v>
+        <v>0.6440526453636363</v>
       </c>
       <c r="I94">
-        <v>0.6246429473971874</v>
+        <v>0.6205398344120141</v>
       </c>
       <c r="J94">
-        <v>0.3279200865340658</v>
+        <v>0.3272140560583266</v>
       </c>
       <c r="K94">
-        <v>1.076588286979793</v>
+        <v>1.144965439366791</v>
       </c>
       <c r="L94">
         <v>10000</v>
       </c>
       <c r="M94">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N94">
         <v>5.9</v>
@@ -4659,22 +4659,22 @@
         <v>23</v>
       </c>
       <c r="H95">
-        <v>0.7003438054521957</v>
+        <v>0.7056909029784273</v>
       </c>
       <c r="I95">
-        <v>0.6852960745601874</v>
+        <v>0.6799606587902443</v>
       </c>
       <c r="J95">
-        <v>0.3725661365841554</v>
+        <v>0.3672791353625943</v>
       </c>
       <c r="K95">
-        <v>1.14343706174062</v>
+        <v>1.194776100540162</v>
       </c>
       <c r="L95">
         <v>10000</v>
       </c>
       <c r="M95">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N95">
         <v>5.9</v>
@@ -4703,22 +4703,22 @@
         <v>24</v>
       </c>
       <c r="H96">
-        <v>21876.33507610602</v>
+        <v>22620.73831866449</v>
       </c>
       <c r="I96">
-        <v>22059.54882141604</v>
+        <v>22580.90052802123</v>
       </c>
       <c r="J96">
-        <v>11317.8456973839</v>
+        <v>15501.46963614614</v>
       </c>
       <c r="K96">
-        <v>35097.37198846892</v>
+        <v>35736.16908711569</v>
       </c>
       <c r="L96">
         <v>10000</v>
       </c>
       <c r="M96">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N96">
         <v>5.9</v>
@@ -4747,22 +4747,22 @@
         <v>25</v>
       </c>
       <c r="H97">
-        <v>0.911660105081246</v>
+        <v>0.9115435019529975</v>
       </c>
       <c r="I97">
-        <v>0.9103834900264469</v>
+        <v>0.9107676286877378</v>
       </c>
       <c r="J97">
-        <v>0.7348790420993268</v>
+        <v>0.7351167663812121</v>
       </c>
       <c r="K97">
-        <v>1.111342308033534</v>
+        <v>1.098955265558163</v>
       </c>
       <c r="L97">
         <v>10000</v>
       </c>
       <c r="M97">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N97">
         <v>5.9</v>
@@ -4791,22 +4791,22 @@
         <v>26</v>
       </c>
       <c r="H98">
-        <v>1812.729668500996</v>
+        <v>1819.552900339769</v>
       </c>
       <c r="I98">
-        <v>1809.239947653631</v>
+        <v>1823.742474777411</v>
       </c>
       <c r="J98">
-        <v>1592.16028491316</v>
+        <v>1601.349058998593</v>
       </c>
       <c r="K98">
-        <v>2018.639912913117</v>
+        <v>1958.959221091168</v>
       </c>
       <c r="L98">
         <v>10000</v>
       </c>
       <c r="M98">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N98">
         <v>5.9</v>
@@ -4835,22 +4835,22 @@
         <v>27</v>
       </c>
       <c r="H99">
-        <v>3257.509799674157</v>
+        <v>3378.329263270105</v>
       </c>
       <c r="I99">
-        <v>3286.994930722095</v>
+        <v>3385.349745391607</v>
       </c>
       <c r="J99">
-        <v>955.0710459031516</v>
+        <v>1249.554245786393</v>
       </c>
       <c r="K99">
-        <v>5199.633491413317</v>
+        <v>5320.88448002758</v>
       </c>
       <c r="L99">
         <v>10000</v>
       </c>
       <c r="M99">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N99">
         <v>5.9</v>
@@ -4879,22 +4879,22 @@
         <v>28</v>
       </c>
       <c r="H100">
-        <v>0.3182169187042447</v>
+        <v>0.3194859379023526</v>
       </c>
       <c r="I100">
-        <v>0.3201619335904252</v>
+        <v>0.319118129195926</v>
       </c>
       <c r="J100">
-        <v>0.1905716839015798</v>
+        <v>0.1901291586532246</v>
       </c>
       <c r="K100">
-        <v>0.4583550047301129</v>
+        <v>0.4779196239162807</v>
       </c>
       <c r="L100">
         <v>10000</v>
       </c>
       <c r="M100">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N100">
         <v>5.9</v>
@@ -4923,25 +4923,25 @@
         <v>18</v>
       </c>
       <c r="H101">
-        <v>8015.497639537463</v>
+        <v>8119.762841902184</v>
       </c>
       <c r="I101">
-        <v>7355.62344187386</v>
+        <v>7491.856635161394</v>
       </c>
       <c r="J101">
-        <v>4821.322831302681</v>
+        <v>4837.790487355238</v>
       </c>
       <c r="K101">
-        <v>16410.17931295161</v>
+        <v>16071.30737939708</v>
       </c>
       <c r="L101">
         <v>10000</v>
       </c>
       <c r="M101">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N101">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -4967,25 +4967,25 @@
         <v>19</v>
       </c>
       <c r="H102">
-        <v>0.3312340166176628</v>
+        <v>0.3285186726466539</v>
       </c>
       <c r="I102">
-        <v>0.3309002580108071</v>
+        <v>0.3295434107003332</v>
       </c>
       <c r="J102">
-        <v>0.2002409180546243</v>
+        <v>0.2008678751646964</v>
       </c>
       <c r="K102">
-        <v>0.4770240903591298</v>
+        <v>0.4538472856946284</v>
       </c>
       <c r="L102">
         <v>10000</v>
       </c>
       <c r="M102">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N102">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -5011,25 +5011,25 @@
         <v>20</v>
       </c>
       <c r="H103">
-        <v>17335.2299429892</v>
+        <v>17483.24359799903</v>
       </c>
       <c r="I103">
-        <v>14433.49327898721</v>
+        <v>14720.74258740152</v>
       </c>
       <c r="J103">
-        <v>7277.646078304422</v>
+        <v>7481.763968298376</v>
       </c>
       <c r="K103">
-        <v>49576.19490982538</v>
+        <v>46494.23662131499</v>
       </c>
       <c r="L103">
         <v>10000</v>
       </c>
       <c r="M103">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N103">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5055,25 +5055,25 @@
         <v>21</v>
       </c>
       <c r="H104">
-        <v>0.6798898689573918</v>
+        <v>0.6769498313585793</v>
       </c>
       <c r="I104">
-        <v>0.6825560171591705</v>
+        <v>0.6817027437964387</v>
       </c>
       <c r="J104">
-        <v>0.3162799124236851</v>
+        <v>0.3048876079395699</v>
       </c>
       <c r="K104">
-        <v>0.9755583466794659</v>
+        <v>0.9728207211250463</v>
       </c>
       <c r="L104">
         <v>10000</v>
       </c>
       <c r="M104">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N104">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -5099,25 +5099,25 @@
         <v>22</v>
       </c>
       <c r="H105">
-        <v>0.4540348627051097</v>
+        <v>0.4512809585864296</v>
       </c>
       <c r="I105">
-        <v>0.4345489600059526</v>
+        <v>0.4304797508166252</v>
       </c>
       <c r="J105">
-        <v>0.2329910121368805</v>
+        <v>0.2321294045725282</v>
       </c>
       <c r="K105">
-        <v>0.7674687741503705</v>
+        <v>0.7746825793486029</v>
       </c>
       <c r="L105">
         <v>10000</v>
       </c>
       <c r="M105">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N105">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5143,25 +5143,25 @@
         <v>23</v>
       </c>
       <c r="H106">
-        <v>0.741842943668731</v>
+        <v>0.7376046320011784</v>
       </c>
       <c r="I106">
-        <v>0.7165043331869128</v>
+        <v>0.7117391891210572</v>
       </c>
       <c r="J106">
-        <v>0.3949662550498259</v>
+        <v>0.3927063045084127</v>
       </c>
       <c r="K106">
-        <v>1.232357927615672</v>
+        <v>1.233456578843351</v>
       </c>
       <c r="L106">
         <v>10000</v>
       </c>
       <c r="M106">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N106">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -5187,25 +5187,25 @@
         <v>24</v>
       </c>
       <c r="H107">
-        <v>24906.88083530241</v>
+        <v>25335.23933779319</v>
       </c>
       <c r="I107">
-        <v>22207.78975687345</v>
+        <v>22566.75420796861</v>
       </c>
       <c r="J107">
-        <v>15555.94290162477</v>
+        <v>15784.52907038987</v>
       </c>
       <c r="K107">
-        <v>55792.88863152181</v>
+        <v>54630.27935036673</v>
       </c>
       <c r="L107">
         <v>10000</v>
       </c>
       <c r="M107">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N107">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -5231,25 +5231,25 @@
         <v>25</v>
       </c>
       <c r="H108">
-        <v>0.6123301961253376</v>
+        <v>0.612023292488673</v>
       </c>
       <c r="I108">
-        <v>0.6091837374855409</v>
+        <v>0.6091056217120796</v>
       </c>
       <c r="J108">
-        <v>0.5062477246922491</v>
+        <v>0.5069234021019091</v>
       </c>
       <c r="K108">
-        <v>0.7342771912411247</v>
+        <v>0.7349245378220548</v>
       </c>
       <c r="L108">
         <v>10000</v>
       </c>
       <c r="M108">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N108">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -5275,25 +5275,25 @@
         <v>26</v>
       </c>
       <c r="H109">
-        <v>2105.373891029178</v>
+        <v>2115.926113187684</v>
       </c>
       <c r="I109">
-        <v>1918.338164500087</v>
+        <v>1937.033007604601</v>
       </c>
       <c r="J109">
-        <v>1660.966386973631</v>
+        <v>1686.761622314374</v>
       </c>
       <c r="K109">
-        <v>4267.149540232636</v>
+        <v>4145.43755607229</v>
       </c>
       <c r="L109">
         <v>10000</v>
       </c>
       <c r="M109">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N109">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -5319,25 +5319,25 @@
         <v>27</v>
       </c>
       <c r="H110">
-        <v>5025.644556691486</v>
+        <v>5046.766336659575</v>
       </c>
       <c r="I110">
-        <v>4347.930836764022</v>
+        <v>4419.617823580329</v>
       </c>
       <c r="J110">
-        <v>2008.668530117733</v>
+        <v>2013.441631260376</v>
       </c>
       <c r="K110">
-        <v>13686.29587318977</v>
+        <v>13147.59383981601</v>
       </c>
       <c r="L110">
         <v>10000</v>
       </c>
       <c r="M110">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N110">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -5363,25 +5363,25 @@
         <v>28</v>
       </c>
       <c r="H111">
-        <v>0.274891672037986</v>
+        <v>0.2734665117281446</v>
       </c>
       <c r="I111">
-        <v>0.2690928574674308</v>
+        <v>0.2680347872869123</v>
       </c>
       <c r="J111">
-        <v>0.159564768287226</v>
+        <v>0.1583253834319198</v>
       </c>
       <c r="K111">
-        <v>0.4142232691010326</v>
+        <v>0.4164942356607738</v>
       </c>
       <c r="L111">
         <v>10000</v>
       </c>
       <c r="M111">
-        <v>2650</v>
+        <v>2642</v>
       </c>
       <c r="N111">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -5407,25 +5407,25 @@
         <v>18</v>
       </c>
       <c r="H112">
-        <v>7842.496230585691</v>
+        <v>7962.074701339703</v>
       </c>
       <c r="I112">
-        <v>7164.228170236271</v>
+        <v>7227.798838610486</v>
       </c>
       <c r="J112">
-        <v>4637.607911417929</v>
+        <v>4675.948760256611</v>
       </c>
       <c r="K112">
-        <v>15567.12700026825</v>
+        <v>15859.9738757268</v>
       </c>
       <c r="L112">
         <v>10000</v>
       </c>
       <c r="M112">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N112">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -5451,25 +5451,25 @@
         <v>19</v>
       </c>
       <c r="H113">
-        <v>0.3251591799296323</v>
+        <v>0.3222754536702834</v>
       </c>
       <c r="I113">
-        <v>0.3266133224467632</v>
+        <v>0.3250377523756274</v>
       </c>
       <c r="J113">
-        <v>0.1947815026148465</v>
+        <v>0.1950422845806733</v>
       </c>
       <c r="K113">
-        <v>0.4666464905543853</v>
+        <v>0.4438709172393835</v>
       </c>
       <c r="L113">
         <v>10000</v>
       </c>
       <c r="M113">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N113">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5495,25 +5495,25 @@
         <v>20</v>
       </c>
       <c r="H114">
-        <v>17432.71352463407</v>
+        <v>17753.87505452802</v>
       </c>
       <c r="I114">
-        <v>14270.14542143759</v>
+        <v>14548.61395874533</v>
       </c>
       <c r="J114">
-        <v>7084.11878165702</v>
+        <v>7655.495757518576</v>
       </c>
       <c r="K114">
-        <v>48571.81913981635</v>
+        <v>49667.99342309686</v>
       </c>
       <c r="L114">
         <v>10000</v>
       </c>
       <c r="M114">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N114">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -5539,25 +5539,25 @@
         <v>21</v>
       </c>
       <c r="H115">
-        <v>0.6832114217746528</v>
+        <v>0.6838717875782767</v>
       </c>
       <c r="I115">
-        <v>0.6878473835443744</v>
+        <v>0.6880992826189964</v>
       </c>
       <c r="J115">
-        <v>0.330256536790952</v>
+        <v>0.3347820979287328</v>
       </c>
       <c r="K115">
-        <v>0.9740181624884201</v>
+        <v>0.972648977628557</v>
       </c>
       <c r="L115">
         <v>10000</v>
       </c>
       <c r="M115">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N115">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -5583,25 +5583,25 @@
         <v>22</v>
       </c>
       <c r="H116">
-        <v>0.4729544383268965</v>
+        <v>0.4738073043176297</v>
       </c>
       <c r="I116">
-        <v>0.4558971962680298</v>
+        <v>0.4556675816672673</v>
       </c>
       <c r="J116">
-        <v>0.2503992932281701</v>
+        <v>0.2506590239641213</v>
       </c>
       <c r="K116">
-        <v>0.7979297626295356</v>
+        <v>0.8020222246645029</v>
       </c>
       <c r="L116">
         <v>10000</v>
       </c>
       <c r="M116">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N116">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -5627,25 +5627,25 @@
         <v>23</v>
       </c>
       <c r="H117">
-        <v>0.7535986502148458</v>
+        <v>0.7551226172868476</v>
       </c>
       <c r="I117">
-        <v>0.7259861694691486</v>
+        <v>0.7244353533579355</v>
       </c>
       <c r="J117">
-        <v>0.4187191683211219</v>
+        <v>0.4183652110417431</v>
       </c>
       <c r="K117">
-        <v>1.244366378770463</v>
+        <v>1.258518315552414</v>
       </c>
       <c r="L117">
         <v>10000</v>
       </c>
       <c r="M117">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N117">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -5671,25 +5671,25 @@
         <v>24</v>
       </c>
       <c r="H118">
-        <v>24853.21473581164</v>
+        <v>25343.1085855419</v>
       </c>
       <c r="I118">
-        <v>22015.53966692206</v>
+        <v>22453.11609092495</v>
       </c>
       <c r="J118">
-        <v>15685.57251884446</v>
+        <v>15714.81497434122</v>
       </c>
       <c r="K118">
-        <v>56372.22247539125</v>
+        <v>56084.63006425366</v>
       </c>
       <c r="L118">
         <v>10000</v>
       </c>
       <c r="M118">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N118">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -5715,25 +5715,25 @@
         <v>25</v>
       </c>
       <c r="H119">
-        <v>0.6279137223153911</v>
+        <v>0.6279656358244009</v>
       </c>
       <c r="I119">
-        <v>0.6268813581977085</v>
+        <v>0.6264755513662901</v>
       </c>
       <c r="J119">
-        <v>0.5122326767672449</v>
+        <v>0.5137499217299981</v>
       </c>
       <c r="K119">
-        <v>0.7538576495259629</v>
+        <v>0.7556799723673778</v>
       </c>
       <c r="L119">
         <v>10000</v>
       </c>
       <c r="M119">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N119">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -5759,25 +5759,25 @@
         <v>26</v>
       </c>
       <c r="H120">
-        <v>2111.999485425955</v>
+        <v>2143.029204902569</v>
       </c>
       <c r="I120">
-        <v>1920.761358638109</v>
+        <v>1942.500674549699</v>
       </c>
       <c r="J120">
-        <v>1679.038645894988</v>
+        <v>1699.756208731219</v>
       </c>
       <c r="K120">
-        <v>4209.683934400912</v>
+        <v>4469.785983526052</v>
       </c>
       <c r="L120">
         <v>10000</v>
       </c>
       <c r="M120">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N120">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -5803,25 +5803,25 @@
         <v>27</v>
       </c>
       <c r="H121">
-        <v>5167.526825099596</v>
+        <v>5263.527102558</v>
       </c>
       <c r="I121">
-        <v>4435.413685884891</v>
+        <v>4515.016209176123</v>
       </c>
       <c r="J121">
-        <v>2163.045368250185</v>
+        <v>2287.06100499488</v>
       </c>
       <c r="K121">
-        <v>14021.33909671678</v>
+        <v>13873.90553710796</v>
       </c>
       <c r="L121">
         <v>10000</v>
       </c>
       <c r="M121">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N121">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -5847,25 +5847,25 @@
         <v>28</v>
       </c>
       <c r="H122">
-        <v>0.2822364406750788</v>
+        <v>0.2826062678500544</v>
       </c>
       <c r="I122">
-        <v>0.277711622178094</v>
+        <v>0.2776634573259283</v>
       </c>
       <c r="J122">
-        <v>0.1701489437135044</v>
+        <v>0.1702457201257425</v>
       </c>
       <c r="K122">
-        <v>0.4208470590159274</v>
+        <v>0.4223041827111378</v>
       </c>
       <c r="L122">
         <v>10000</v>
       </c>
       <c r="M122">
-        <v>2633</v>
+        <v>2608</v>
       </c>
       <c r="N122">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -5891,25 +5891,25 @@
         <v>18</v>
       </c>
       <c r="H123">
-        <v>6970.221121922668</v>
+        <v>6944.485726321076</v>
       </c>
       <c r="I123">
-        <v>6152.936946955181</v>
+        <v>6242.133988493962</v>
       </c>
       <c r="J123">
-        <v>4221.554350326298</v>
+        <v>4169.094319223973</v>
       </c>
       <c r="K123">
-        <v>16113.80581546458</v>
+        <v>14975.59727746418</v>
       </c>
       <c r="L123">
         <v>10000</v>
       </c>
       <c r="M123">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N123">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -5935,25 +5935,25 @@
         <v>19</v>
       </c>
       <c r="H124">
-        <v>0.3070326542068031</v>
+        <v>0.3026592601360286</v>
       </c>
       <c r="I124">
-        <v>0.3065085168952886</v>
+        <v>0.3046607381058272</v>
       </c>
       <c r="J124">
-        <v>0.1828521640105685</v>
+        <v>0.1835899442941865</v>
       </c>
       <c r="K124">
-        <v>0.4512671340234631</v>
+        <v>0.4104155831507375</v>
       </c>
       <c r="L124">
         <v>10000</v>
       </c>
       <c r="M124">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N124">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -5979,25 +5979,25 @@
         <v>20</v>
       </c>
       <c r="H125">
-        <v>16860.20410364146</v>
+        <v>16846.15088093045</v>
       </c>
       <c r="I125">
-        <v>13743.88580909391</v>
+        <v>13956.86179869062</v>
       </c>
       <c r="J125">
-        <v>7085.855670927393</v>
+        <v>7609.881581274316</v>
       </c>
       <c r="K125">
-        <v>53033.8706740932</v>
+        <v>48581.11668245043</v>
       </c>
       <c r="L125">
         <v>10000</v>
       </c>
       <c r="M125">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N125">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6023,25 +6023,25 @@
         <v>21</v>
       </c>
       <c r="H126">
-        <v>0.696282152082021</v>
+        <v>0.6959613073841994</v>
       </c>
       <c r="I126">
-        <v>0.6962605096183686</v>
+        <v>0.6965712893653727</v>
       </c>
       <c r="J126">
-        <v>0.3659887544087626</v>
+        <v>0.3642853639807682</v>
       </c>
       <c r="K126">
-        <v>0.9821389474358646</v>
+        <v>0.9840470870780513</v>
       </c>
       <c r="L126">
         <v>10000</v>
       </c>
       <c r="M126">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N126">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6067,25 +6067,25 @@
         <v>22</v>
       </c>
       <c r="H127">
-        <v>0.6609082282041185</v>
+        <v>0.6667421837760942</v>
       </c>
       <c r="I127">
-        <v>0.6406528788352918</v>
+        <v>0.6422657986635796</v>
       </c>
       <c r="J127">
-        <v>0.3612975601440467</v>
+        <v>0.361252215225785</v>
       </c>
       <c r="K127">
-        <v>1.109392061872319</v>
+        <v>1.135328420989136</v>
       </c>
       <c r="L127">
         <v>10000</v>
       </c>
       <c r="M127">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N127">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6111,25 +6111,25 @@
         <v>23</v>
       </c>
       <c r="H128">
-        <v>0.7246270918141515</v>
+        <v>0.7295897480987833</v>
       </c>
       <c r="I128">
-        <v>0.7043378789587131</v>
+        <v>0.7051972237919142</v>
       </c>
       <c r="J128">
-        <v>0.4034275092855921</v>
+        <v>0.4031572416088204</v>
       </c>
       <c r="K128">
-        <v>1.198301792964578</v>
+        <v>1.214278808799202</v>
       </c>
       <c r="L128">
         <v>10000</v>
       </c>
       <c r="M128">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N128">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6155,25 +6155,25 @@
         <v>24</v>
       </c>
       <c r="H129">
-        <v>23377.84207814925</v>
+        <v>23529.16125747104</v>
       </c>
       <c r="I129">
-        <v>20231.302959056</v>
+        <v>20622.12006181981</v>
       </c>
       <c r="J129">
-        <v>14909.76204364769</v>
+        <v>15035.76046299748</v>
       </c>
       <c r="K129">
-        <v>57903.77619178206</v>
+        <v>54989.29504853386</v>
       </c>
       <c r="L129">
         <v>10000</v>
       </c>
       <c r="M129">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N129">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6199,25 +6199,25 @@
         <v>25</v>
       </c>
       <c r="H130">
-        <v>0.9135751845583476</v>
+        <v>0.9148173485005032</v>
       </c>
       <c r="I130">
-        <v>0.9077448205394676</v>
+        <v>0.9097819547049919</v>
       </c>
       <c r="J130">
-        <v>0.7478800028653962</v>
+        <v>0.7478435299279644</v>
       </c>
       <c r="K130">
-        <v>1.105236802511282</v>
+        <v>1.106415035687719</v>
       </c>
       <c r="L130">
         <v>10000</v>
       </c>
       <c r="M130">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N130">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6243,25 +6243,25 @@
         <v>26</v>
       </c>
       <c r="H131">
-        <v>2204.14775223677</v>
+        <v>2195.038915162423</v>
       </c>
       <c r="I131">
-        <v>1932.920679434467</v>
+        <v>1953.552927866017</v>
       </c>
       <c r="J131">
-        <v>1721.930093807285</v>
+        <v>1748.428582592553</v>
       </c>
       <c r="K131">
-        <v>5310.358291766477</v>
+        <v>4827.306308731374</v>
       </c>
       <c r="L131">
         <v>10000</v>
       </c>
       <c r="M131">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N131">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6287,25 +6287,25 @@
         <v>27</v>
       </c>
       <c r="H132">
-        <v>5857.911184278087</v>
+        <v>5862.029024452128</v>
       </c>
       <c r="I132">
-        <v>4827.734695850267</v>
+        <v>4922.783370182885</v>
       </c>
       <c r="J132">
-        <v>2573.927409675144</v>
+        <v>2696.295479689487</v>
       </c>
       <c r="K132">
-        <v>17766.50760161853</v>
+        <v>16038.55376526878</v>
       </c>
       <c r="L132">
         <v>10000</v>
       </c>
       <c r="M132">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N132">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -6331,25 +6331,25 @@
         <v>28</v>
       </c>
       <c r="H133">
-        <v>0.3271197172476626</v>
+        <v>0.3287274970640047</v>
       </c>
       <c r="I133">
-        <v>0.3263057201396984</v>
+        <v>0.3267229819474264</v>
       </c>
       <c r="J133">
-        <v>0.2072041060977947</v>
+        <v>0.2069483464907446</v>
       </c>
       <c r="K133">
-        <v>0.4721091497850981</v>
+        <v>0.4787161815153684</v>
       </c>
       <c r="L133">
         <v>10000</v>
       </c>
       <c r="M133">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="N133">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
     </row>
   </sheetData>
